--- a/data/多流量段批量计算_导入Excel（模板）.xlsx
+++ b/data/多流量段批量计算_导入Excel（模板）.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="导入模板" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入模板" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1119,7 +1119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T46"/>
+  <dimension ref="A1:T48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" min="1" max="1"/>
@@ -4302,6 +4302,122 @@
         <v>100</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="7" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D47" s="8" t="inlineStr">
+        <is>
+          <t>明渠-U形</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>647350.0</t>
+        </is>
+      </c>
+      <c r="F47" s="8" t="inlineStr">
+        <is>
+          <t>3376350.0</t>
+        </is>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" s="8" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I47" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J47" s="8" t="n"/>
+      <c r="K47" s="8" t="n"/>
+      <c r="L47" s="8" t="n"/>
+      <c r="M47" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="8" t="n"/>
+      <c r="P47" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q47" s="8" t="n"/>
+      <c r="R47" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="S47" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D48" s="8" t="inlineStr">
+        <is>
+          <t>明渠-U形</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>647280.0</t>
+        </is>
+      </c>
+      <c r="F48" s="8" t="inlineStr">
+        <is>
+          <t>3376280.0</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H48" s="8" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="I48" s="8" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J48" s="8" t="n"/>
+      <c r="K48" s="8" t="n"/>
+      <c r="L48" s="8" t="n"/>
+      <c r="M48" s="8" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N48" s="8" t="n"/>
+      <c r="O48" s="8" t="n"/>
+      <c r="P48" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q48" s="8" t="n"/>
+      <c r="R48" s="8" t="n">
+        <v>152</v>
+      </c>
+      <c r="S48" s="8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/多流量段批量计算_导入Excel（模板）.xlsx
+++ b/data/多流量段批量计算_导入Excel（模板）.xlsx
@@ -18,7 +18,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0\+000.000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -203,6 +203,11 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="36">
@@ -686,7 +691,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -707,6 +712,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1119,7 +1130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="9.375" customWidth="1" min="1" max="1"/>
@@ -1140,6 +1151,7 @@
     <col width="10.625" customWidth="1" min="17" max="17"/>
     <col width="9.625" customWidth="1" min="18" max="18"/>
     <col width="7.625" customWidth="1" min="19" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1279,6 +1291,11 @@
       <c r="T2" s="4" t="inlineStr">
         <is>
           <t>不冲流速</t>
+        </is>
+      </c>
+      <c r="U2" s="10" t="inlineStr">
+        <is>
+          <t>转弯半径(m)</t>
         </is>
       </c>
     </row>
@@ -1355,6 +1372,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U3" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -1429,6 +1449,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U4" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1503,6 +1526,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U5" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -1573,6 +1599,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U6" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1642,6 +1671,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U7" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1717,6 +1749,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U8" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1790,6 +1825,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U9" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1853,6 +1891,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U10" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1926,6 +1967,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U11" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1989,6 +2033,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U12" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -2051,6 +2098,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U13" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -2113,6 +2163,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U14" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -2175,6 +2228,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U15" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -2237,6 +2293,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U16" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2311,6 +2370,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U17" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -2384,6 +2446,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U18" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2447,6 +2512,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U19" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -2509,6 +2577,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U20" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2571,6 +2642,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U21" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -2633,6 +2707,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U22" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -2707,6 +2784,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U23" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -2781,6 +2861,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U24" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -2855,6 +2938,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U25" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -2937,6 +3023,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U26" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3018,6 +3107,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U27" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -3081,6 +3173,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U28" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3143,6 +3238,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U29" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -3205,6 +3303,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U30" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3267,6 +3368,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U31" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -3329,6 +3433,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U32" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -3391,6 +3498,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U33" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -3453,6 +3563,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U34" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -3527,6 +3640,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U35" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -3601,6 +3717,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U36" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -3670,6 +3789,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U37" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -3733,6 +3855,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U38" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -3803,6 +3928,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U39" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -3872,6 +4000,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U40" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -3943,6 +4074,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U41" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -4012,6 +4146,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U42" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4087,6 +4224,9 @@
           <t>100</t>
         </is>
       </c>
+      <c r="U43" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -4160,6 +4300,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U44" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4234,6 +4377,9 @@
         <is>
           <t>100</t>
         </is>
+      </c>
+      <c r="U45" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -4301,6 +4447,9 @@
       <c r="T46" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="U46" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -4359,6 +4508,9 @@
       <c r="T47" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="U47" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -4417,6 +4569,9 @@
       <c r="T48" s="8" t="n">
         <v>100</v>
       </c>
+      <c r="U48" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/多流量段批量计算_导入Excel（模板）.xlsx
+++ b/data/多流量段批量计算_导入Excel（模板）.xlsx
@@ -1768,6 +1768,7 @@
     <col min="18" max="18" width="9.62727272727273" customWidth="1"/>
     <col min="19" max="20" width="7.62727272727273" customWidth="1"/>
     <col min="21" max="21" width="12" customWidth="1"/>
+    <col min="22" max="22" width="11.8181818181818" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1" spans="1:22">

--- a/data/多流量段批量计算_导入Excel（模板）.xlsx
+++ b/data/多流量段批量计算_导入Excel（模板）.xlsx
@@ -17,9 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7-字段速查" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'导入模板'!$A$2:$AF$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'导入模板'!$A$2:$AP$500</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'0-先看这里'!$A$6:$F$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'7-字段速查'!$A$6:$G$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'7-字段速查'!$A$6:$G$48</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -1279,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF500"/>
+  <dimension ref="A1:AP500"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="9.09090909090909" customWidth="1" min="1" max="1"/>
@@ -1309,6 +1309,16 @@
     <col width="13" customWidth="1" min="30" max="30"/>
     <col width="10" customWidth="1" min="31" max="31"/>
     <col width="14" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
+    <col width="18" customWidth="1" min="37" max="37"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="40" max="40"/>
+    <col width="18" customWidth="1" min="41" max="41"/>
+    <col width="18" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -1538,6 +1548,56 @@
           <t>平台高差h1(m)</t>
         </is>
       </c>
+      <c r="AG2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠入口宽度(m)</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠堰上总水头(m)</t>
+        </is>
+      </c>
+      <c r="AI2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠入口连接形式</t>
+        </is>
+      </c>
+      <c r="AJ2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠手动流量系数</t>
+        </is>
+      </c>
+      <c r="AK2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠侧收缩系数</t>
+        </is>
+      </c>
+      <c r="AL2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠动能修正系数</t>
+        </is>
+      </c>
+      <c r="AM2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠掺气系数</t>
+        </is>
+      </c>
+      <c r="AN2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠侧墙安全超高(m)</t>
+        </is>
+      </c>
+      <c r="AO2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠池深系数</t>
+        </is>
+      </c>
+      <c r="AP2" s="3" t="inlineStr">
+        <is>
+          <t>泄水渠整流长度系数</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
@@ -1626,6 +1686,16 @@
       <c r="AD3" s="10" t="n"/>
       <c r="AE3" s="10" t="n"/>
       <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="10" t="n"/>
+      <c r="AI3" s="10" t="n"/>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="10" t="n"/>
+      <c r="AO3" s="10" t="n"/>
+      <c r="AP3" s="10" t="n"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -1714,6 +1784,16 @@
       <c r="AD4" s="12" t="n"/>
       <c r="AE4" s="12" t="n"/>
       <c r="AF4" s="12" t="n"/>
+      <c r="AG4" s="12" t="n"/>
+      <c r="AH4" s="12" t="n"/>
+      <c r="AI4" s="12" t="n"/>
+      <c r="AJ4" s="12" t="n"/>
+      <c r="AK4" s="12" t="n"/>
+      <c r="AL4" s="12" t="n"/>
+      <c r="AM4" s="12" t="n"/>
+      <c r="AN4" s="12" t="n"/>
+      <c r="AO4" s="12" t="n"/>
+      <c r="AP4" s="12" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
@@ -1802,6 +1882,16 @@
       <c r="AD5" s="10" t="n"/>
       <c r="AE5" s="10" t="n"/>
       <c r="AF5" s="10" t="n"/>
+      <c r="AG5" s="10" t="n"/>
+      <c r="AH5" s="10" t="n"/>
+      <c r="AI5" s="10" t="n"/>
+      <c r="AJ5" s="10" t="n"/>
+      <c r="AK5" s="10" t="n"/>
+      <c r="AL5" s="10" t="n"/>
+      <c r="AM5" s="10" t="n"/>
+      <c r="AN5" s="10" t="n"/>
+      <c r="AO5" s="10" t="n"/>
+      <c r="AP5" s="10" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -1886,6 +1976,16 @@
       <c r="AD6" s="12" t="n"/>
       <c r="AE6" s="12" t="n"/>
       <c r="AF6" s="12" t="n"/>
+      <c r="AG6" s="12" t="n"/>
+      <c r="AH6" s="12" t="n"/>
+      <c r="AI6" s="12" t="n"/>
+      <c r="AJ6" s="12" t="n"/>
+      <c r="AK6" s="12" t="n"/>
+      <c r="AL6" s="12" t="n"/>
+      <c r="AM6" s="12" t="n"/>
+      <c r="AN6" s="12" t="n"/>
+      <c r="AO6" s="12" t="n"/>
+      <c r="AP6" s="12" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
@@ -1970,6 +2070,16 @@
       <c r="AD7" s="10" t="n"/>
       <c r="AE7" s="10" t="n"/>
       <c r="AF7" s="10" t="n"/>
+      <c r="AG7" s="10" t="n"/>
+      <c r="AH7" s="10" t="n"/>
+      <c r="AI7" s="10" t="n"/>
+      <c r="AJ7" s="10" t="n"/>
+      <c r="AK7" s="10" t="n"/>
+      <c r="AL7" s="10" t="n"/>
+      <c r="AM7" s="10" t="n"/>
+      <c r="AN7" s="10" t="n"/>
+      <c r="AO7" s="10" t="n"/>
+      <c r="AP7" s="10" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -2058,6 +2168,16 @@
       <c r="AD8" s="12" t="n"/>
       <c r="AE8" s="12" t="n"/>
       <c r="AF8" s="12" t="n"/>
+      <c r="AG8" s="12" t="n"/>
+      <c r="AH8" s="12" t="n"/>
+      <c r="AI8" s="12" t="n"/>
+      <c r="AJ8" s="12" t="n"/>
+      <c r="AK8" s="12" t="n"/>
+      <c r="AL8" s="12" t="n"/>
+      <c r="AM8" s="12" t="n"/>
+      <c r="AN8" s="12" t="n"/>
+      <c r="AO8" s="12" t="n"/>
+      <c r="AP8" s="12" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
@@ -2146,6 +2266,16 @@
       <c r="AD9" s="10" t="n"/>
       <c r="AE9" s="10" t="n"/>
       <c r="AF9" s="10" t="n"/>
+      <c r="AG9" s="10" t="n"/>
+      <c r="AH9" s="10" t="n"/>
+      <c r="AI9" s="10" t="n"/>
+      <c r="AJ9" s="10" t="n"/>
+      <c r="AK9" s="10" t="n"/>
+      <c r="AL9" s="10" t="n"/>
+      <c r="AM9" s="10" t="n"/>
+      <c r="AN9" s="10" t="n"/>
+      <c r="AO9" s="10" t="n"/>
+      <c r="AP9" s="10" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -2222,6 +2352,16 @@
       <c r="AD10" s="12" t="n"/>
       <c r="AE10" s="12" t="n"/>
       <c r="AF10" s="12" t="n"/>
+      <c r="AG10" s="12" t="n"/>
+      <c r="AH10" s="12" t="n"/>
+      <c r="AI10" s="12" t="n"/>
+      <c r="AJ10" s="12" t="n"/>
+      <c r="AK10" s="12" t="n"/>
+      <c r="AL10" s="12" t="n"/>
+      <c r="AM10" s="12" t="n"/>
+      <c r="AN10" s="12" t="n"/>
+      <c r="AO10" s="12" t="n"/>
+      <c r="AP10" s="12" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
@@ -2310,6 +2450,16 @@
       <c r="AD11" s="10" t="n"/>
       <c r="AE11" s="10" t="n"/>
       <c r="AF11" s="10" t="n"/>
+      <c r="AG11" s="10" t="n"/>
+      <c r="AH11" s="10" t="n"/>
+      <c r="AI11" s="10" t="n"/>
+      <c r="AJ11" s="10" t="n"/>
+      <c r="AK11" s="10" t="n"/>
+      <c r="AL11" s="10" t="n"/>
+      <c r="AM11" s="10" t="n"/>
+      <c r="AN11" s="10" t="n"/>
+      <c r="AO11" s="10" t="n"/>
+      <c r="AP11" s="10" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -2386,6 +2536,16 @@
       <c r="AD12" s="12" t="n"/>
       <c r="AE12" s="12" t="n"/>
       <c r="AF12" s="12" t="n"/>
+      <c r="AG12" s="12" t="n"/>
+      <c r="AH12" s="12" t="n"/>
+      <c r="AI12" s="12" t="n"/>
+      <c r="AJ12" s="12" t="n"/>
+      <c r="AK12" s="12" t="n"/>
+      <c r="AL12" s="12" t="n"/>
+      <c r="AM12" s="12" t="n"/>
+      <c r="AN12" s="12" t="n"/>
+      <c r="AO12" s="12" t="n"/>
+      <c r="AP12" s="12" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
@@ -2462,6 +2622,16 @@
       <c r="AD13" s="10" t="n"/>
       <c r="AE13" s="10" t="n"/>
       <c r="AF13" s="10" t="n"/>
+      <c r="AG13" s="10" t="n"/>
+      <c r="AH13" s="10" t="n"/>
+      <c r="AI13" s="10" t="n"/>
+      <c r="AJ13" s="10" t="n"/>
+      <c r="AK13" s="10" t="n"/>
+      <c r="AL13" s="10" t="n"/>
+      <c r="AM13" s="10" t="n"/>
+      <c r="AN13" s="10" t="n"/>
+      <c r="AO13" s="10" t="n"/>
+      <c r="AP13" s="10" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="11" t="inlineStr">
@@ -2538,6 +2708,16 @@
       <c r="AD14" s="12" t="n"/>
       <c r="AE14" s="12" t="n"/>
       <c r="AF14" s="12" t="n"/>
+      <c r="AG14" s="12" t="n"/>
+      <c r="AH14" s="12" t="n"/>
+      <c r="AI14" s="12" t="n"/>
+      <c r="AJ14" s="12" t="n"/>
+      <c r="AK14" s="12" t="n"/>
+      <c r="AL14" s="12" t="n"/>
+      <c r="AM14" s="12" t="n"/>
+      <c r="AN14" s="12" t="n"/>
+      <c r="AO14" s="12" t="n"/>
+      <c r="AP14" s="12" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
@@ -2614,6 +2794,16 @@
       <c r="AD15" s="10" t="n"/>
       <c r="AE15" s="10" t="n"/>
       <c r="AF15" s="10" t="n"/>
+      <c r="AG15" s="10" t="n"/>
+      <c r="AH15" s="10" t="n"/>
+      <c r="AI15" s="10" t="n"/>
+      <c r="AJ15" s="10" t="n"/>
+      <c r="AK15" s="10" t="n"/>
+      <c r="AL15" s="10" t="n"/>
+      <c r="AM15" s="10" t="n"/>
+      <c r="AN15" s="10" t="n"/>
+      <c r="AO15" s="10" t="n"/>
+      <c r="AP15" s="10" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="11" t="inlineStr">
@@ -2690,6 +2880,16 @@
       <c r="AD16" s="12" t="n"/>
       <c r="AE16" s="12" t="n"/>
       <c r="AF16" s="12" t="n"/>
+      <c r="AG16" s="12" t="n"/>
+      <c r="AH16" s="12" t="n"/>
+      <c r="AI16" s="12" t="n"/>
+      <c r="AJ16" s="12" t="n"/>
+      <c r="AK16" s="12" t="n"/>
+      <c r="AL16" s="12" t="n"/>
+      <c r="AM16" s="12" t="n"/>
+      <c r="AN16" s="12" t="n"/>
+      <c r="AO16" s="12" t="n"/>
+      <c r="AP16" s="12" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
@@ -2778,6 +2978,16 @@
       <c r="AD17" s="10" t="n"/>
       <c r="AE17" s="10" t="n"/>
       <c r="AF17" s="10" t="n"/>
+      <c r="AG17" s="10" t="n"/>
+      <c r="AH17" s="10" t="n"/>
+      <c r="AI17" s="10" t="n"/>
+      <c r="AJ17" s="10" t="n"/>
+      <c r="AK17" s="10" t="n"/>
+      <c r="AL17" s="10" t="n"/>
+      <c r="AM17" s="10" t="n"/>
+      <c r="AN17" s="10" t="n"/>
+      <c r="AO17" s="10" t="n"/>
+      <c r="AP17" s="10" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="11" t="inlineStr">
@@ -2866,6 +3076,16 @@
       <c r="AD18" s="12" t="n"/>
       <c r="AE18" s="12" t="n"/>
       <c r="AF18" s="12" t="n"/>
+      <c r="AG18" s="12" t="n"/>
+      <c r="AH18" s="12" t="n"/>
+      <c r="AI18" s="12" t="n"/>
+      <c r="AJ18" s="12" t="n"/>
+      <c r="AK18" s="12" t="n"/>
+      <c r="AL18" s="12" t="n"/>
+      <c r="AM18" s="12" t="n"/>
+      <c r="AN18" s="12" t="n"/>
+      <c r="AO18" s="12" t="n"/>
+      <c r="AP18" s="12" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="9" t="inlineStr">
@@ -2942,6 +3162,16 @@
       <c r="AD19" s="10" t="n"/>
       <c r="AE19" s="10" t="n"/>
       <c r="AF19" s="10" t="n"/>
+      <c r="AG19" s="10" t="n"/>
+      <c r="AH19" s="10" t="n"/>
+      <c r="AI19" s="10" t="n"/>
+      <c r="AJ19" s="10" t="n"/>
+      <c r="AK19" s="10" t="n"/>
+      <c r="AL19" s="10" t="n"/>
+      <c r="AM19" s="10" t="n"/>
+      <c r="AN19" s="10" t="n"/>
+      <c r="AO19" s="10" t="n"/>
+      <c r="AP19" s="10" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
@@ -3018,6 +3248,16 @@
       <c r="AD20" s="12" t="n"/>
       <c r="AE20" s="12" t="n"/>
       <c r="AF20" s="12" t="n"/>
+      <c r="AG20" s="12" t="n"/>
+      <c r="AH20" s="12" t="n"/>
+      <c r="AI20" s="12" t="n"/>
+      <c r="AJ20" s="12" t="n"/>
+      <c r="AK20" s="12" t="n"/>
+      <c r="AL20" s="12" t="n"/>
+      <c r="AM20" s="12" t="n"/>
+      <c r="AN20" s="12" t="n"/>
+      <c r="AO20" s="12" t="n"/>
+      <c r="AP20" s="12" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="9" t="inlineStr">
@@ -3094,6 +3334,16 @@
       <c r="AD21" s="10" t="n"/>
       <c r="AE21" s="10" t="n"/>
       <c r="AF21" s="10" t="n"/>
+      <c r="AG21" s="10" t="n"/>
+      <c r="AH21" s="10" t="n"/>
+      <c r="AI21" s="10" t="n"/>
+      <c r="AJ21" s="10" t="n"/>
+      <c r="AK21" s="10" t="n"/>
+      <c r="AL21" s="10" t="n"/>
+      <c r="AM21" s="10" t="n"/>
+      <c r="AN21" s="10" t="n"/>
+      <c r="AO21" s="10" t="n"/>
+      <c r="AP21" s="10" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="11" t="inlineStr">
@@ -3170,6 +3420,16 @@
       <c r="AD22" s="12" t="n"/>
       <c r="AE22" s="12" t="n"/>
       <c r="AF22" s="12" t="n"/>
+      <c r="AG22" s="12" t="n"/>
+      <c r="AH22" s="12" t="n"/>
+      <c r="AI22" s="12" t="n"/>
+      <c r="AJ22" s="12" t="n"/>
+      <c r="AK22" s="12" t="n"/>
+      <c r="AL22" s="12" t="n"/>
+      <c r="AM22" s="12" t="n"/>
+      <c r="AN22" s="12" t="n"/>
+      <c r="AO22" s="12" t="n"/>
+      <c r="AP22" s="12" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
@@ -3258,6 +3518,16 @@
       <c r="AD23" s="10" t="n"/>
       <c r="AE23" s="10" t="n"/>
       <c r="AF23" s="10" t="n"/>
+      <c r="AG23" s="10" t="n"/>
+      <c r="AH23" s="10" t="n"/>
+      <c r="AI23" s="10" t="n"/>
+      <c r="AJ23" s="10" t="n"/>
+      <c r="AK23" s="10" t="n"/>
+      <c r="AL23" s="10" t="n"/>
+      <c r="AM23" s="10" t="n"/>
+      <c r="AN23" s="10" t="n"/>
+      <c r="AO23" s="10" t="n"/>
+      <c r="AP23" s="10" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="11" t="inlineStr">
@@ -3346,6 +3616,16 @@
       <c r="AD24" s="12" t="n"/>
       <c r="AE24" s="12" t="n"/>
       <c r="AF24" s="12" t="n"/>
+      <c r="AG24" s="12" t="n"/>
+      <c r="AH24" s="12" t="n"/>
+      <c r="AI24" s="12" t="n"/>
+      <c r="AJ24" s="12" t="n"/>
+      <c r="AK24" s="12" t="n"/>
+      <c r="AL24" s="12" t="n"/>
+      <c r="AM24" s="12" t="n"/>
+      <c r="AN24" s="12" t="n"/>
+      <c r="AO24" s="12" t="n"/>
+      <c r="AP24" s="12" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
@@ -3434,6 +3714,16 @@
       <c r="AD25" s="10" t="n"/>
       <c r="AE25" s="10" t="n"/>
       <c r="AF25" s="10" t="n"/>
+      <c r="AG25" s="10" t="n"/>
+      <c r="AH25" s="10" t="n"/>
+      <c r="AI25" s="10" t="n"/>
+      <c r="AJ25" s="10" t="n"/>
+      <c r="AK25" s="10" t="n"/>
+      <c r="AL25" s="10" t="n"/>
+      <c r="AM25" s="10" t="n"/>
+      <c r="AN25" s="10" t="n"/>
+      <c r="AO25" s="10" t="n"/>
+      <c r="AP25" s="10" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="11" t="inlineStr">
@@ -3530,6 +3820,16 @@
       <c r="AD26" s="12" t="n"/>
       <c r="AE26" s="12" t="n"/>
       <c r="AF26" s="12" t="n"/>
+      <c r="AG26" s="12" t="n"/>
+      <c r="AH26" s="12" t="n"/>
+      <c r="AI26" s="12" t="n"/>
+      <c r="AJ26" s="12" t="n"/>
+      <c r="AK26" s="12" t="n"/>
+      <c r="AL26" s="12" t="n"/>
+      <c r="AM26" s="12" t="n"/>
+      <c r="AN26" s="12" t="n"/>
+      <c r="AO26" s="12" t="n"/>
+      <c r="AP26" s="12" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="9" t="inlineStr">
@@ -3626,6 +3926,16 @@
       <c r="AD27" s="10" t="n"/>
       <c r="AE27" s="10" t="n"/>
       <c r="AF27" s="10" t="n"/>
+      <c r="AG27" s="10" t="n"/>
+      <c r="AH27" s="10" t="n"/>
+      <c r="AI27" s="10" t="n"/>
+      <c r="AJ27" s="10" t="n"/>
+      <c r="AK27" s="10" t="n"/>
+      <c r="AL27" s="10" t="n"/>
+      <c r="AM27" s="10" t="n"/>
+      <c r="AN27" s="10" t="n"/>
+      <c r="AO27" s="10" t="n"/>
+      <c r="AP27" s="10" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="11" t="inlineStr">
@@ -3702,6 +4012,16 @@
       <c r="AD28" s="12" t="n"/>
       <c r="AE28" s="12" t="n"/>
       <c r="AF28" s="12" t="n"/>
+      <c r="AG28" s="12" t="n"/>
+      <c r="AH28" s="12" t="n"/>
+      <c r="AI28" s="12" t="n"/>
+      <c r="AJ28" s="12" t="n"/>
+      <c r="AK28" s="12" t="n"/>
+      <c r="AL28" s="12" t="n"/>
+      <c r="AM28" s="12" t="n"/>
+      <c r="AN28" s="12" t="n"/>
+      <c r="AO28" s="12" t="n"/>
+      <c r="AP28" s="12" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="9" t="inlineStr">
@@ -3778,6 +4098,16 @@
       <c r="AD29" s="10" t="n"/>
       <c r="AE29" s="10" t="n"/>
       <c r="AF29" s="10" t="n"/>
+      <c r="AG29" s="10" t="n"/>
+      <c r="AH29" s="10" t="n"/>
+      <c r="AI29" s="10" t="n"/>
+      <c r="AJ29" s="10" t="n"/>
+      <c r="AK29" s="10" t="n"/>
+      <c r="AL29" s="10" t="n"/>
+      <c r="AM29" s="10" t="n"/>
+      <c r="AN29" s="10" t="n"/>
+      <c r="AO29" s="10" t="n"/>
+      <c r="AP29" s="10" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="11" t="inlineStr">
@@ -3854,6 +4184,16 @@
       <c r="AD30" s="12" t="n"/>
       <c r="AE30" s="12" t="n"/>
       <c r="AF30" s="12" t="n"/>
+      <c r="AG30" s="12" t="n"/>
+      <c r="AH30" s="12" t="n"/>
+      <c r="AI30" s="12" t="n"/>
+      <c r="AJ30" s="12" t="n"/>
+      <c r="AK30" s="12" t="n"/>
+      <c r="AL30" s="12" t="n"/>
+      <c r="AM30" s="12" t="n"/>
+      <c r="AN30" s="12" t="n"/>
+      <c r="AO30" s="12" t="n"/>
+      <c r="AP30" s="12" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="A31" s="9" t="inlineStr">
@@ -3930,6 +4270,16 @@
       <c r="AD31" s="10" t="n"/>
       <c r="AE31" s="10" t="n"/>
       <c r="AF31" s="10" t="n"/>
+      <c r="AG31" s="10" t="n"/>
+      <c r="AH31" s="10" t="n"/>
+      <c r="AI31" s="10" t="n"/>
+      <c r="AJ31" s="10" t="n"/>
+      <c r="AK31" s="10" t="n"/>
+      <c r="AL31" s="10" t="n"/>
+      <c r="AM31" s="10" t="n"/>
+      <c r="AN31" s="10" t="n"/>
+      <c r="AO31" s="10" t="n"/>
+      <c r="AP31" s="10" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="11" t="inlineStr">
@@ -4006,6 +4356,16 @@
       <c r="AD32" s="12" t="n"/>
       <c r="AE32" s="12" t="n"/>
       <c r="AF32" s="12" t="n"/>
+      <c r="AG32" s="12" t="n"/>
+      <c r="AH32" s="12" t="n"/>
+      <c r="AI32" s="12" t="n"/>
+      <c r="AJ32" s="12" t="n"/>
+      <c r="AK32" s="12" t="n"/>
+      <c r="AL32" s="12" t="n"/>
+      <c r="AM32" s="12" t="n"/>
+      <c r="AN32" s="12" t="n"/>
+      <c r="AO32" s="12" t="n"/>
+      <c r="AP32" s="12" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
       <c r="A33" s="9" t="inlineStr">
@@ -4082,6 +4442,16 @@
       <c r="AD33" s="10" t="n"/>
       <c r="AE33" s="10" t="n"/>
       <c r="AF33" s="10" t="n"/>
+      <c r="AG33" s="10" t="n"/>
+      <c r="AH33" s="10" t="n"/>
+      <c r="AI33" s="10" t="n"/>
+      <c r="AJ33" s="10" t="n"/>
+      <c r="AK33" s="10" t="n"/>
+      <c r="AL33" s="10" t="n"/>
+      <c r="AM33" s="10" t="n"/>
+      <c r="AN33" s="10" t="n"/>
+      <c r="AO33" s="10" t="n"/>
+      <c r="AP33" s="10" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="11" t="inlineStr">
@@ -4158,6 +4528,16 @@
       <c r="AD34" s="12" t="n"/>
       <c r="AE34" s="12" t="n"/>
       <c r="AF34" s="12" t="n"/>
+      <c r="AG34" s="12" t="n"/>
+      <c r="AH34" s="12" t="n"/>
+      <c r="AI34" s="12" t="n"/>
+      <c r="AJ34" s="12" t="n"/>
+      <c r="AK34" s="12" t="n"/>
+      <c r="AL34" s="12" t="n"/>
+      <c r="AM34" s="12" t="n"/>
+      <c r="AN34" s="12" t="n"/>
+      <c r="AO34" s="12" t="n"/>
+      <c r="AP34" s="12" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
@@ -4246,6 +4626,16 @@
       <c r="AD35" s="10" t="n"/>
       <c r="AE35" s="10" t="n"/>
       <c r="AF35" s="10" t="n"/>
+      <c r="AG35" s="10" t="n"/>
+      <c r="AH35" s="10" t="n"/>
+      <c r="AI35" s="10" t="n"/>
+      <c r="AJ35" s="10" t="n"/>
+      <c r="AK35" s="10" t="n"/>
+      <c r="AL35" s="10" t="n"/>
+      <c r="AM35" s="10" t="n"/>
+      <c r="AN35" s="10" t="n"/>
+      <c r="AO35" s="10" t="n"/>
+      <c r="AP35" s="10" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="11" t="inlineStr">
@@ -4334,6 +4724,16 @@
       <c r="AD36" s="12" t="n"/>
       <c r="AE36" s="12" t="n"/>
       <c r="AF36" s="12" t="n"/>
+      <c r="AG36" s="12" t="n"/>
+      <c r="AH36" s="12" t="n"/>
+      <c r="AI36" s="12" t="n"/>
+      <c r="AJ36" s="12" t="n"/>
+      <c r="AK36" s="12" t="n"/>
+      <c r="AL36" s="12" t="n"/>
+      <c r="AM36" s="12" t="n"/>
+      <c r="AN36" s="12" t="n"/>
+      <c r="AO36" s="12" t="n"/>
+      <c r="AP36" s="12" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
@@ -4418,6 +4818,16 @@
       <c r="AD37" s="10" t="n"/>
       <c r="AE37" s="10" t="n"/>
       <c r="AF37" s="10" t="n"/>
+      <c r="AG37" s="10" t="n"/>
+      <c r="AH37" s="10" t="n"/>
+      <c r="AI37" s="10" t="n"/>
+      <c r="AJ37" s="10" t="n"/>
+      <c r="AK37" s="10" t="n"/>
+      <c r="AL37" s="10" t="n"/>
+      <c r="AM37" s="10" t="n"/>
+      <c r="AN37" s="10" t="n"/>
+      <c r="AO37" s="10" t="n"/>
+      <c r="AP37" s="10" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
@@ -4494,6 +4904,16 @@
       <c r="AD38" s="12" t="n"/>
       <c r="AE38" s="12" t="n"/>
       <c r="AF38" s="12" t="n"/>
+      <c r="AG38" s="12" t="n"/>
+      <c r="AH38" s="12" t="n"/>
+      <c r="AI38" s="12" t="n"/>
+      <c r="AJ38" s="12" t="n"/>
+      <c r="AK38" s="12" t="n"/>
+      <c r="AL38" s="12" t="n"/>
+      <c r="AM38" s="12" t="n"/>
+      <c r="AN38" s="12" t="n"/>
+      <c r="AO38" s="12" t="n"/>
+      <c r="AP38" s="12" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
@@ -4578,6 +4998,16 @@
       <c r="AD39" s="10" t="n"/>
       <c r="AE39" s="10" t="n"/>
       <c r="AF39" s="10" t="n"/>
+      <c r="AG39" s="10" t="n"/>
+      <c r="AH39" s="10" t="n"/>
+      <c r="AI39" s="10" t="n"/>
+      <c r="AJ39" s="10" t="n"/>
+      <c r="AK39" s="10" t="n"/>
+      <c r="AL39" s="10" t="n"/>
+      <c r="AM39" s="10" t="n"/>
+      <c r="AN39" s="10" t="n"/>
+      <c r="AO39" s="10" t="n"/>
+      <c r="AP39" s="10" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
       <c r="A40" s="11" t="inlineStr">
@@ -4662,6 +5092,16 @@
       <c r="AD40" s="12" t="n"/>
       <c r="AE40" s="12" t="n"/>
       <c r="AF40" s="12" t="n"/>
+      <c r="AG40" s="12" t="n"/>
+      <c r="AH40" s="12" t="n"/>
+      <c r="AI40" s="12" t="n"/>
+      <c r="AJ40" s="12" t="n"/>
+      <c r="AK40" s="12" t="n"/>
+      <c r="AL40" s="12" t="n"/>
+      <c r="AM40" s="12" t="n"/>
+      <c r="AN40" s="12" t="n"/>
+      <c r="AO40" s="12" t="n"/>
+      <c r="AP40" s="12" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
@@ -4746,6 +5186,16 @@
       <c r="AD41" s="10" t="n"/>
       <c r="AE41" s="10" t="n"/>
       <c r="AF41" s="10" t="n"/>
+      <c r="AG41" s="10" t="n"/>
+      <c r="AH41" s="10" t="n"/>
+      <c r="AI41" s="10" t="n"/>
+      <c r="AJ41" s="10" t="n"/>
+      <c r="AK41" s="10" t="n"/>
+      <c r="AL41" s="10" t="n"/>
+      <c r="AM41" s="10" t="n"/>
+      <c r="AN41" s="10" t="n"/>
+      <c r="AO41" s="10" t="n"/>
+      <c r="AP41" s="10" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
       <c r="A42" s="11" t="inlineStr">
@@ -4830,6 +5280,16 @@
       <c r="AD42" s="12" t="n"/>
       <c r="AE42" s="12" t="n"/>
       <c r="AF42" s="12" t="n"/>
+      <c r="AG42" s="12" t="n"/>
+      <c r="AH42" s="12" t="n"/>
+      <c r="AI42" s="12" t="n"/>
+      <c r="AJ42" s="12" t="n"/>
+      <c r="AK42" s="12" t="n"/>
+      <c r="AL42" s="12" t="n"/>
+      <c r="AM42" s="12" t="n"/>
+      <c r="AN42" s="12" t="n"/>
+      <c r="AO42" s="12" t="n"/>
+      <c r="AP42" s="12" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="9" t="inlineStr">
@@ -4918,6 +5378,16 @@
       <c r="AD43" s="10" t="n"/>
       <c r="AE43" s="10" t="n"/>
       <c r="AF43" s="10" t="n"/>
+      <c r="AG43" s="10" t="n"/>
+      <c r="AH43" s="10" t="n"/>
+      <c r="AI43" s="10" t="n"/>
+      <c r="AJ43" s="10" t="n"/>
+      <c r="AK43" s="10" t="n"/>
+      <c r="AL43" s="10" t="n"/>
+      <c r="AM43" s="10" t="n"/>
+      <c r="AN43" s="10" t="n"/>
+      <c r="AO43" s="10" t="n"/>
+      <c r="AP43" s="10" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="11" t="inlineStr">
@@ -5006,6 +5476,16 @@
       <c r="AD44" s="12" t="n"/>
       <c r="AE44" s="12" t="n"/>
       <c r="AF44" s="12" t="n"/>
+      <c r="AG44" s="12" t="n"/>
+      <c r="AH44" s="12" t="n"/>
+      <c r="AI44" s="12" t="n"/>
+      <c r="AJ44" s="12" t="n"/>
+      <c r="AK44" s="12" t="n"/>
+      <c r="AL44" s="12" t="n"/>
+      <c r="AM44" s="12" t="n"/>
+      <c r="AN44" s="12" t="n"/>
+      <c r="AO44" s="12" t="n"/>
+      <c r="AP44" s="12" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
@@ -5094,6 +5574,16 @@
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="10" t="n"/>
       <c r="AF45" s="10" t="n"/>
+      <c r="AG45" s="10" t="n"/>
+      <c r="AH45" s="10" t="n"/>
+      <c r="AI45" s="10" t="n"/>
+      <c r="AJ45" s="10" t="n"/>
+      <c r="AK45" s="10" t="n"/>
+      <c r="AL45" s="10" t="n"/>
+      <c r="AM45" s="10" t="n"/>
+      <c r="AN45" s="10" t="n"/>
+      <c r="AO45" s="10" t="n"/>
+      <c r="AP45" s="10" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="11" t="inlineStr">
@@ -5174,6 +5664,16 @@
       <c r="AD46" s="12" t="n"/>
       <c r="AE46" s="12" t="n"/>
       <c r="AF46" s="12" t="n"/>
+      <c r="AG46" s="12" t="n"/>
+      <c r="AH46" s="12" t="n"/>
+      <c r="AI46" s="12" t="n"/>
+      <c r="AJ46" s="12" t="n"/>
+      <c r="AK46" s="12" t="n"/>
+      <c r="AL46" s="12" t="n"/>
+      <c r="AM46" s="12" t="n"/>
+      <c r="AN46" s="12" t="n"/>
+      <c r="AO46" s="12" t="n"/>
+      <c r="AP46" s="12" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="9" t="n">
@@ -5246,6 +5746,16 @@
       <c r="AD47" s="10" t="n"/>
       <c r="AE47" s="10" t="n"/>
       <c r="AF47" s="10" t="n"/>
+      <c r="AG47" s="10" t="n"/>
+      <c r="AH47" s="10" t="n"/>
+      <c r="AI47" s="10" t="n"/>
+      <c r="AJ47" s="10" t="n"/>
+      <c r="AK47" s="10" t="n"/>
+      <c r="AL47" s="10" t="n"/>
+      <c r="AM47" s="10" t="n"/>
+      <c r="AN47" s="10" t="n"/>
+      <c r="AO47" s="10" t="n"/>
+      <c r="AP47" s="10" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="11" t="n">
@@ -5318,6 +5828,16 @@
       <c r="AD48" s="12" t="n"/>
       <c r="AE48" s="12" t="n"/>
       <c r="AF48" s="12" t="n"/>
+      <c r="AG48" s="12" t="n"/>
+      <c r="AH48" s="12" t="n"/>
+      <c r="AI48" s="12" t="n"/>
+      <c r="AJ48" s="12" t="n"/>
+      <c r="AK48" s="12" t="n"/>
+      <c r="AL48" s="12" t="n"/>
+      <c r="AM48" s="12" t="n"/>
+      <c r="AN48" s="12" t="n"/>
+      <c r="AO48" s="12" t="n"/>
+      <c r="AP48" s="12" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
@@ -5398,6 +5918,16 @@
       <c r="AD49" s="10" t="n"/>
       <c r="AE49" s="10" t="n"/>
       <c r="AF49" s="10" t="n"/>
+      <c r="AG49" s="10" t="n"/>
+      <c r="AH49" s="10" t="n"/>
+      <c r="AI49" s="10" t="n"/>
+      <c r="AJ49" s="10" t="n"/>
+      <c r="AK49" s="10" t="n"/>
+      <c r="AL49" s="10" t="n"/>
+      <c r="AM49" s="10" t="n"/>
+      <c r="AN49" s="10" t="n"/>
+      <c r="AO49" s="10" t="n"/>
+      <c r="AP49" s="10" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="11" t="inlineStr">
@@ -5476,6 +6006,16 @@
       <c r="AD50" s="12" t="n"/>
       <c r="AE50" s="12" t="n"/>
       <c r="AF50" s="12" t="n"/>
+      <c r="AG50" s="12" t="n"/>
+      <c r="AH50" s="12" t="n"/>
+      <c r="AI50" s="12" t="n"/>
+      <c r="AJ50" s="12" t="n"/>
+      <c r="AK50" s="12" t="n"/>
+      <c r="AL50" s="12" t="n"/>
+      <c r="AM50" s="12" t="n"/>
+      <c r="AN50" s="12" t="n"/>
+      <c r="AO50" s="12" t="n"/>
+      <c r="AP50" s="12" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
@@ -5554,6 +6094,16 @@
       <c r="AD51" s="10" t="n"/>
       <c r="AE51" s="10" t="n"/>
       <c r="AF51" s="10" t="n"/>
+      <c r="AG51" s="10" t="n"/>
+      <c r="AH51" s="10" t="n"/>
+      <c r="AI51" s="10" t="n"/>
+      <c r="AJ51" s="10" t="n"/>
+      <c r="AK51" s="10" t="n"/>
+      <c r="AL51" s="10" t="n"/>
+      <c r="AM51" s="10" t="n"/>
+      <c r="AN51" s="10" t="n"/>
+      <c r="AO51" s="10" t="n"/>
+      <c r="AP51" s="10" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="11" t="inlineStr">
@@ -5634,6 +6184,16 @@
       <c r="AD52" s="12" t="n"/>
       <c r="AE52" s="12" t="n"/>
       <c r="AF52" s="12" t="n"/>
+      <c r="AG52" s="12" t="n"/>
+      <c r="AH52" s="12" t="n"/>
+      <c r="AI52" s="12" t="n"/>
+      <c r="AJ52" s="12" t="n"/>
+      <c r="AK52" s="12" t="n"/>
+      <c r="AL52" s="12" t="n"/>
+      <c r="AM52" s="12" t="n"/>
+      <c r="AN52" s="12" t="n"/>
+      <c r="AO52" s="12" t="n"/>
+      <c r="AP52" s="12" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="9" t="n">
@@ -5708,6 +6268,16 @@
       <c r="AF53" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="AG53" s="10" t="n"/>
+      <c r="AH53" s="10" t="n"/>
+      <c r="AI53" s="10" t="n"/>
+      <c r="AJ53" s="10" t="n"/>
+      <c r="AK53" s="10" t="n"/>
+      <c r="AL53" s="10" t="n"/>
+      <c r="AM53" s="10" t="n"/>
+      <c r="AN53" s="10" t="n"/>
+      <c r="AO53" s="10" t="n"/>
+      <c r="AP53" s="10" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
       <c r="A54" s="11" t="n">
@@ -5782,6 +6352,16 @@
       <c r="AF54" s="12" t="n">
         <v>1</v>
       </c>
+      <c r="AG54" s="12" t="n"/>
+      <c r="AH54" s="12" t="n"/>
+      <c r="AI54" s="12" t="n"/>
+      <c r="AJ54" s="12" t="n"/>
+      <c r="AK54" s="12" t="n"/>
+      <c r="AL54" s="12" t="n"/>
+      <c r="AM54" s="12" t="n"/>
+      <c r="AN54" s="12" t="n"/>
+      <c r="AO54" s="12" t="n"/>
+      <c r="AP54" s="12" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="9" t="n">
@@ -5856,6 +6436,16 @@
       <c r="AF55" s="10" t="n">
         <v>1</v>
       </c>
+      <c r="AG55" s="10" t="n"/>
+      <c r="AH55" s="10" t="n"/>
+      <c r="AI55" s="10" t="n"/>
+      <c r="AJ55" s="10" t="n"/>
+      <c r="AK55" s="10" t="n"/>
+      <c r="AL55" s="10" t="n"/>
+      <c r="AM55" s="10" t="n"/>
+      <c r="AN55" s="10" t="n"/>
+      <c r="AO55" s="10" t="n"/>
+      <c r="AP55" s="10" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="11" t="n">
@@ -5922,6 +6512,16 @@
       <c r="AD56" s="12" t="n"/>
       <c r="AE56" s="12" t="n"/>
       <c r="AF56" s="12" t="n"/>
+      <c r="AG56" s="12" t="n"/>
+      <c r="AH56" s="12" t="n"/>
+      <c r="AI56" s="12" t="n"/>
+      <c r="AJ56" s="12" t="n"/>
+      <c r="AK56" s="12" t="n"/>
+      <c r="AL56" s="12" t="n"/>
+      <c r="AM56" s="12" t="n"/>
+      <c r="AN56" s="12" t="n"/>
+      <c r="AO56" s="12" t="n"/>
+      <c r="AP56" s="12" t="n"/>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="9" t="n">
@@ -5988,6 +6588,16 @@
       <c r="AD57" s="10" t="n"/>
       <c r="AE57" s="10" t="n"/>
       <c r="AF57" s="10" t="n"/>
+      <c r="AG57" s="10" t="n"/>
+      <c r="AH57" s="10" t="n"/>
+      <c r="AI57" s="10" t="n"/>
+      <c r="AJ57" s="10" t="n"/>
+      <c r="AK57" s="10" t="n"/>
+      <c r="AL57" s="10" t="n"/>
+      <c r="AM57" s="10" t="n"/>
+      <c r="AN57" s="10" t="n"/>
+      <c r="AO57" s="10" t="n"/>
+      <c r="AP57" s="10" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="11" t="n">
@@ -6054,6 +6664,16 @@
       <c r="AD58" s="12" t="n"/>
       <c r="AE58" s="12" t="n"/>
       <c r="AF58" s="12" t="n"/>
+      <c r="AG58" s="12" t="n"/>
+      <c r="AH58" s="12" t="n"/>
+      <c r="AI58" s="12" t="n"/>
+      <c r="AJ58" s="12" t="n"/>
+      <c r="AK58" s="12" t="n"/>
+      <c r="AL58" s="12" t="n"/>
+      <c r="AM58" s="12" t="n"/>
+      <c r="AN58" s="12" t="n"/>
+      <c r="AO58" s="12" t="n"/>
+      <c r="AP58" s="12" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="9" t="n">
@@ -6120,6 +6740,16 @@
       <c r="AD59" s="10" t="n"/>
       <c r="AE59" s="10" t="n"/>
       <c r="AF59" s="10" t="n"/>
+      <c r="AG59" s="10" t="n"/>
+      <c r="AH59" s="10" t="n"/>
+      <c r="AI59" s="10" t="n"/>
+      <c r="AJ59" s="10" t="n"/>
+      <c r="AK59" s="10" t="n"/>
+      <c r="AL59" s="10" t="n"/>
+      <c r="AM59" s="10" t="n"/>
+      <c r="AN59" s="10" t="n"/>
+      <c r="AO59" s="10" t="n"/>
+      <c r="AP59" s="10" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
       <c r="A60" s="11" t="n">
@@ -6186,6 +6816,16 @@
       <c r="AD60" s="12" t="n"/>
       <c r="AE60" s="12" t="n"/>
       <c r="AF60" s="12" t="n"/>
+      <c r="AG60" s="12" t="n"/>
+      <c r="AH60" s="12" t="n"/>
+      <c r="AI60" s="12" t="n"/>
+      <c r="AJ60" s="12" t="n"/>
+      <c r="AK60" s="12" t="n"/>
+      <c r="AL60" s="12" t="n"/>
+      <c r="AM60" s="12" t="n"/>
+      <c r="AN60" s="12" t="n"/>
+      <c r="AO60" s="12" t="n"/>
+      <c r="AP60" s="12" t="n"/>
     </row>
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="9" t="n">
@@ -6252,6 +6892,16 @@
       <c r="AD61" s="10" t="n"/>
       <c r="AE61" s="10" t="n"/>
       <c r="AF61" s="10" t="n"/>
+      <c r="AG61" s="10" t="n"/>
+      <c r="AH61" s="10" t="n"/>
+      <c r="AI61" s="10" t="n"/>
+      <c r="AJ61" s="10" t="n"/>
+      <c r="AK61" s="10" t="n"/>
+      <c r="AL61" s="10" t="n"/>
+      <c r="AM61" s="10" t="n"/>
+      <c r="AN61" s="10" t="n"/>
+      <c r="AO61" s="10" t="n"/>
+      <c r="AP61" s="10" t="n"/>
     </row>
     <row r="62" ht="22" customHeight="1">
       <c r="A62" s="11" t="n"/>
@@ -6286,6 +6936,16 @@
       <c r="AD62" s="12" t="n"/>
       <c r="AE62" s="12" t="n"/>
       <c r="AF62" s="12" t="n"/>
+      <c r="AG62" s="12" t="n"/>
+      <c r="AH62" s="12" t="n"/>
+      <c r="AI62" s="12" t="n"/>
+      <c r="AJ62" s="12" t="n"/>
+      <c r="AK62" s="12" t="n"/>
+      <c r="AL62" s="12" t="n"/>
+      <c r="AM62" s="12" t="n"/>
+      <c r="AN62" s="12" t="n"/>
+      <c r="AO62" s="12" t="n"/>
+      <c r="AP62" s="12" t="n"/>
     </row>
     <row r="63" ht="22" customHeight="1">
       <c r="A63" s="9" t="n"/>
@@ -6320,6 +6980,16 @@
       <c r="AD63" s="10" t="n"/>
       <c r="AE63" s="10" t="n"/>
       <c r="AF63" s="10" t="n"/>
+      <c r="AG63" s="10" t="n"/>
+      <c r="AH63" s="10" t="n"/>
+      <c r="AI63" s="10" t="n"/>
+      <c r="AJ63" s="10" t="n"/>
+      <c r="AK63" s="10" t="n"/>
+      <c r="AL63" s="10" t="n"/>
+      <c r="AM63" s="10" t="n"/>
+      <c r="AN63" s="10" t="n"/>
+      <c r="AO63" s="10" t="n"/>
+      <c r="AP63" s="10" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="11" t="n"/>
@@ -6354,6 +7024,16 @@
       <c r="AD64" s="12" t="n"/>
       <c r="AE64" s="12" t="n"/>
       <c r="AF64" s="12" t="n"/>
+      <c r="AG64" s="12" t="n"/>
+      <c r="AH64" s="12" t="n"/>
+      <c r="AI64" s="12" t="n"/>
+      <c r="AJ64" s="12" t="n"/>
+      <c r="AK64" s="12" t="n"/>
+      <c r="AL64" s="12" t="n"/>
+      <c r="AM64" s="12" t="n"/>
+      <c r="AN64" s="12" t="n"/>
+      <c r="AO64" s="12" t="n"/>
+      <c r="AP64" s="12" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
       <c r="A65" s="9" t="n"/>
@@ -6388,6 +7068,16 @@
       <c r="AD65" s="10" t="n"/>
       <c r="AE65" s="10" t="n"/>
       <c r="AF65" s="10" t="n"/>
+      <c r="AG65" s="10" t="n"/>
+      <c r="AH65" s="10" t="n"/>
+      <c r="AI65" s="10" t="n"/>
+      <c r="AJ65" s="10" t="n"/>
+      <c r="AK65" s="10" t="n"/>
+      <c r="AL65" s="10" t="n"/>
+      <c r="AM65" s="10" t="n"/>
+      <c r="AN65" s="10" t="n"/>
+      <c r="AO65" s="10" t="n"/>
+      <c r="AP65" s="10" t="n"/>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="11" t="n"/>
@@ -6422,6 +7112,16 @@
       <c r="AD66" s="12" t="n"/>
       <c r="AE66" s="12" t="n"/>
       <c r="AF66" s="12" t="n"/>
+      <c r="AG66" s="12" t="n"/>
+      <c r="AH66" s="12" t="n"/>
+      <c r="AI66" s="12" t="n"/>
+      <c r="AJ66" s="12" t="n"/>
+      <c r="AK66" s="12" t="n"/>
+      <c r="AL66" s="12" t="n"/>
+      <c r="AM66" s="12" t="n"/>
+      <c r="AN66" s="12" t="n"/>
+      <c r="AO66" s="12" t="n"/>
+      <c r="AP66" s="12" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
       <c r="A67" s="9" t="n"/>
@@ -6456,6 +7156,16 @@
       <c r="AD67" s="10" t="n"/>
       <c r="AE67" s="10" t="n"/>
       <c r="AF67" s="10" t="n"/>
+      <c r="AG67" s="10" t="n"/>
+      <c r="AH67" s="10" t="n"/>
+      <c r="AI67" s="10" t="n"/>
+      <c r="AJ67" s="10" t="n"/>
+      <c r="AK67" s="10" t="n"/>
+      <c r="AL67" s="10" t="n"/>
+      <c r="AM67" s="10" t="n"/>
+      <c r="AN67" s="10" t="n"/>
+      <c r="AO67" s="10" t="n"/>
+      <c r="AP67" s="10" t="n"/>
     </row>
     <row r="68" ht="22" customHeight="1">
       <c r="A68" s="11" t="n"/>
@@ -6490,6 +7200,16 @@
       <c r="AD68" s="12" t="n"/>
       <c r="AE68" s="12" t="n"/>
       <c r="AF68" s="12" t="n"/>
+      <c r="AG68" s="12" t="n"/>
+      <c r="AH68" s="12" t="n"/>
+      <c r="AI68" s="12" t="n"/>
+      <c r="AJ68" s="12" t="n"/>
+      <c r="AK68" s="12" t="n"/>
+      <c r="AL68" s="12" t="n"/>
+      <c r="AM68" s="12" t="n"/>
+      <c r="AN68" s="12" t="n"/>
+      <c r="AO68" s="12" t="n"/>
+      <c r="AP68" s="12" t="n"/>
     </row>
     <row r="69" ht="22" customHeight="1">
       <c r="A69" s="9" t="n"/>
@@ -6524,6 +7244,16 @@
       <c r="AD69" s="10" t="n"/>
       <c r="AE69" s="10" t="n"/>
       <c r="AF69" s="10" t="n"/>
+      <c r="AG69" s="10" t="n"/>
+      <c r="AH69" s="10" t="n"/>
+      <c r="AI69" s="10" t="n"/>
+      <c r="AJ69" s="10" t="n"/>
+      <c r="AK69" s="10" t="n"/>
+      <c r="AL69" s="10" t="n"/>
+      <c r="AM69" s="10" t="n"/>
+      <c r="AN69" s="10" t="n"/>
+      <c r="AO69" s="10" t="n"/>
+      <c r="AP69" s="10" t="n"/>
     </row>
     <row r="70" ht="22" customHeight="1">
       <c r="A70" s="11" t="n"/>
@@ -6558,6 +7288,16 @@
       <c r="AD70" s="12" t="n"/>
       <c r="AE70" s="12" t="n"/>
       <c r="AF70" s="12" t="n"/>
+      <c r="AG70" s="12" t="n"/>
+      <c r="AH70" s="12" t="n"/>
+      <c r="AI70" s="12" t="n"/>
+      <c r="AJ70" s="12" t="n"/>
+      <c r="AK70" s="12" t="n"/>
+      <c r="AL70" s="12" t="n"/>
+      <c r="AM70" s="12" t="n"/>
+      <c r="AN70" s="12" t="n"/>
+      <c r="AO70" s="12" t="n"/>
+      <c r="AP70" s="12" t="n"/>
     </row>
     <row r="71" ht="22" customHeight="1">
       <c r="A71" s="9" t="n"/>
@@ -6592,6 +7332,16 @@
       <c r="AD71" s="10" t="n"/>
       <c r="AE71" s="10" t="n"/>
       <c r="AF71" s="10" t="n"/>
+      <c r="AG71" s="10" t="n"/>
+      <c r="AH71" s="10" t="n"/>
+      <c r="AI71" s="10" t="n"/>
+      <c r="AJ71" s="10" t="n"/>
+      <c r="AK71" s="10" t="n"/>
+      <c r="AL71" s="10" t="n"/>
+      <c r="AM71" s="10" t="n"/>
+      <c r="AN71" s="10" t="n"/>
+      <c r="AO71" s="10" t="n"/>
+      <c r="AP71" s="10" t="n"/>
     </row>
     <row r="72" ht="22" customHeight="1">
       <c r="A72" s="11" t="n"/>
@@ -6626,6 +7376,16 @@
       <c r="AD72" s="12" t="n"/>
       <c r="AE72" s="12" t="n"/>
       <c r="AF72" s="12" t="n"/>
+      <c r="AG72" s="12" t="n"/>
+      <c r="AH72" s="12" t="n"/>
+      <c r="AI72" s="12" t="n"/>
+      <c r="AJ72" s="12" t="n"/>
+      <c r="AK72" s="12" t="n"/>
+      <c r="AL72" s="12" t="n"/>
+      <c r="AM72" s="12" t="n"/>
+      <c r="AN72" s="12" t="n"/>
+      <c r="AO72" s="12" t="n"/>
+      <c r="AP72" s="12" t="n"/>
     </row>
     <row r="73" ht="22" customHeight="1">
       <c r="A73" s="9" t="n"/>
@@ -6660,6 +7420,16 @@
       <c r="AD73" s="10" t="n"/>
       <c r="AE73" s="10" t="n"/>
       <c r="AF73" s="10" t="n"/>
+      <c r="AG73" s="10" t="n"/>
+      <c r="AH73" s="10" t="n"/>
+      <c r="AI73" s="10" t="n"/>
+      <c r="AJ73" s="10" t="n"/>
+      <c r="AK73" s="10" t="n"/>
+      <c r="AL73" s="10" t="n"/>
+      <c r="AM73" s="10" t="n"/>
+      <c r="AN73" s="10" t="n"/>
+      <c r="AO73" s="10" t="n"/>
+      <c r="AP73" s="10" t="n"/>
     </row>
     <row r="74" ht="22" customHeight="1">
       <c r="A74" s="11" t="n"/>
@@ -6694,6 +7464,16 @@
       <c r="AD74" s="12" t="n"/>
       <c r="AE74" s="12" t="n"/>
       <c r="AF74" s="12" t="n"/>
+      <c r="AG74" s="12" t="n"/>
+      <c r="AH74" s="12" t="n"/>
+      <c r="AI74" s="12" t="n"/>
+      <c r="AJ74" s="12" t="n"/>
+      <c r="AK74" s="12" t="n"/>
+      <c r="AL74" s="12" t="n"/>
+      <c r="AM74" s="12" t="n"/>
+      <c r="AN74" s="12" t="n"/>
+      <c r="AO74" s="12" t="n"/>
+      <c r="AP74" s="12" t="n"/>
     </row>
     <row r="75" ht="22" customHeight="1">
       <c r="A75" s="9" t="n"/>
@@ -6728,6 +7508,16 @@
       <c r="AD75" s="10" t="n"/>
       <c r="AE75" s="10" t="n"/>
       <c r="AF75" s="10" t="n"/>
+      <c r="AG75" s="10" t="n"/>
+      <c r="AH75" s="10" t="n"/>
+      <c r="AI75" s="10" t="n"/>
+      <c r="AJ75" s="10" t="n"/>
+      <c r="AK75" s="10" t="n"/>
+      <c r="AL75" s="10" t="n"/>
+      <c r="AM75" s="10" t="n"/>
+      <c r="AN75" s="10" t="n"/>
+      <c r="AO75" s="10" t="n"/>
+      <c r="AP75" s="10" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
       <c r="A76" s="11" t="n"/>
@@ -6762,6 +7552,16 @@
       <c r="AD76" s="12" t="n"/>
       <c r="AE76" s="12" t="n"/>
       <c r="AF76" s="12" t="n"/>
+      <c r="AG76" s="12" t="n"/>
+      <c r="AH76" s="12" t="n"/>
+      <c r="AI76" s="12" t="n"/>
+      <c r="AJ76" s="12" t="n"/>
+      <c r="AK76" s="12" t="n"/>
+      <c r="AL76" s="12" t="n"/>
+      <c r="AM76" s="12" t="n"/>
+      <c r="AN76" s="12" t="n"/>
+      <c r="AO76" s="12" t="n"/>
+      <c r="AP76" s="12" t="n"/>
     </row>
     <row r="77" ht="22" customHeight="1">
       <c r="A77" s="9" t="n"/>
@@ -6796,6 +7596,16 @@
       <c r="AD77" s="10" t="n"/>
       <c r="AE77" s="10" t="n"/>
       <c r="AF77" s="10" t="n"/>
+      <c r="AG77" s="10" t="n"/>
+      <c r="AH77" s="10" t="n"/>
+      <c r="AI77" s="10" t="n"/>
+      <c r="AJ77" s="10" t="n"/>
+      <c r="AK77" s="10" t="n"/>
+      <c r="AL77" s="10" t="n"/>
+      <c r="AM77" s="10" t="n"/>
+      <c r="AN77" s="10" t="n"/>
+      <c r="AO77" s="10" t="n"/>
+      <c r="AP77" s="10" t="n"/>
     </row>
     <row r="78" ht="22" customHeight="1">
       <c r="A78" s="11" t="n"/>
@@ -6830,6 +7640,16 @@
       <c r="AD78" s="12" t="n"/>
       <c r="AE78" s="12" t="n"/>
       <c r="AF78" s="12" t="n"/>
+      <c r="AG78" s="12" t="n"/>
+      <c r="AH78" s="12" t="n"/>
+      <c r="AI78" s="12" t="n"/>
+      <c r="AJ78" s="12" t="n"/>
+      <c r="AK78" s="12" t="n"/>
+      <c r="AL78" s="12" t="n"/>
+      <c r="AM78" s="12" t="n"/>
+      <c r="AN78" s="12" t="n"/>
+      <c r="AO78" s="12" t="n"/>
+      <c r="AP78" s="12" t="n"/>
     </row>
     <row r="79" ht="22" customHeight="1">
       <c r="A79" s="9" t="n"/>
@@ -6864,6 +7684,16 @@
       <c r="AD79" s="10" t="n"/>
       <c r="AE79" s="10" t="n"/>
       <c r="AF79" s="10" t="n"/>
+      <c r="AG79" s="10" t="n"/>
+      <c r="AH79" s="10" t="n"/>
+      <c r="AI79" s="10" t="n"/>
+      <c r="AJ79" s="10" t="n"/>
+      <c r="AK79" s="10" t="n"/>
+      <c r="AL79" s="10" t="n"/>
+      <c r="AM79" s="10" t="n"/>
+      <c r="AN79" s="10" t="n"/>
+      <c r="AO79" s="10" t="n"/>
+      <c r="AP79" s="10" t="n"/>
     </row>
     <row r="80" ht="22" customHeight="1">
       <c r="A80" s="11" t="n"/>
@@ -6898,6 +7728,16 @@
       <c r="AD80" s="12" t="n"/>
       <c r="AE80" s="12" t="n"/>
       <c r="AF80" s="12" t="n"/>
+      <c r="AG80" s="12" t="n"/>
+      <c r="AH80" s="12" t="n"/>
+      <c r="AI80" s="12" t="n"/>
+      <c r="AJ80" s="12" t="n"/>
+      <c r="AK80" s="12" t="n"/>
+      <c r="AL80" s="12" t="n"/>
+      <c r="AM80" s="12" t="n"/>
+      <c r="AN80" s="12" t="n"/>
+      <c r="AO80" s="12" t="n"/>
+      <c r="AP80" s="12" t="n"/>
     </row>
     <row r="81" ht="22" customHeight="1">
       <c r="A81" s="9" t="n"/>
@@ -6932,6 +7772,16 @@
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="10" t="n"/>
       <c r="AF81" s="10" t="n"/>
+      <c r="AG81" s="10" t="n"/>
+      <c r="AH81" s="10" t="n"/>
+      <c r="AI81" s="10" t="n"/>
+      <c r="AJ81" s="10" t="n"/>
+      <c r="AK81" s="10" t="n"/>
+      <c r="AL81" s="10" t="n"/>
+      <c r="AM81" s="10" t="n"/>
+      <c r="AN81" s="10" t="n"/>
+      <c r="AO81" s="10" t="n"/>
+      <c r="AP81" s="10" t="n"/>
     </row>
     <row r="82" ht="22" customHeight="1">
       <c r="A82" s="11" t="n"/>
@@ -6966,6 +7816,16 @@
       <c r="AD82" s="12" t="n"/>
       <c r="AE82" s="12" t="n"/>
       <c r="AF82" s="12" t="n"/>
+      <c r="AG82" s="12" t="n"/>
+      <c r="AH82" s="12" t="n"/>
+      <c r="AI82" s="12" t="n"/>
+      <c r="AJ82" s="12" t="n"/>
+      <c r="AK82" s="12" t="n"/>
+      <c r="AL82" s="12" t="n"/>
+      <c r="AM82" s="12" t="n"/>
+      <c r="AN82" s="12" t="n"/>
+      <c r="AO82" s="12" t="n"/>
+      <c r="AP82" s="12" t="n"/>
     </row>
     <row r="83" ht="22" customHeight="1">
       <c r="A83" s="9" t="n"/>
@@ -7000,6 +7860,16 @@
       <c r="AD83" s="10" t="n"/>
       <c r="AE83" s="10" t="n"/>
       <c r="AF83" s="10" t="n"/>
+      <c r="AG83" s="10" t="n"/>
+      <c r="AH83" s="10" t="n"/>
+      <c r="AI83" s="10" t="n"/>
+      <c r="AJ83" s="10" t="n"/>
+      <c r="AK83" s="10" t="n"/>
+      <c r="AL83" s="10" t="n"/>
+      <c r="AM83" s="10" t="n"/>
+      <c r="AN83" s="10" t="n"/>
+      <c r="AO83" s="10" t="n"/>
+      <c r="AP83" s="10" t="n"/>
     </row>
     <row r="84" ht="22" customHeight="1">
       <c r="A84" s="11" t="n"/>
@@ -7034,6 +7904,16 @@
       <c r="AD84" s="12" t="n"/>
       <c r="AE84" s="12" t="n"/>
       <c r="AF84" s="12" t="n"/>
+      <c r="AG84" s="12" t="n"/>
+      <c r="AH84" s="12" t="n"/>
+      <c r="AI84" s="12" t="n"/>
+      <c r="AJ84" s="12" t="n"/>
+      <c r="AK84" s="12" t="n"/>
+      <c r="AL84" s="12" t="n"/>
+      <c r="AM84" s="12" t="n"/>
+      <c r="AN84" s="12" t="n"/>
+      <c r="AO84" s="12" t="n"/>
+      <c r="AP84" s="12" t="n"/>
     </row>
     <row r="85" ht="22" customHeight="1">
       <c r="A85" s="9" t="n"/>
@@ -7068,6 +7948,16 @@
       <c r="AD85" s="10" t="n"/>
       <c r="AE85" s="10" t="n"/>
       <c r="AF85" s="10" t="n"/>
+      <c r="AG85" s="10" t="n"/>
+      <c r="AH85" s="10" t="n"/>
+      <c r="AI85" s="10" t="n"/>
+      <c r="AJ85" s="10" t="n"/>
+      <c r="AK85" s="10" t="n"/>
+      <c r="AL85" s="10" t="n"/>
+      <c r="AM85" s="10" t="n"/>
+      <c r="AN85" s="10" t="n"/>
+      <c r="AO85" s="10" t="n"/>
+      <c r="AP85" s="10" t="n"/>
     </row>
     <row r="86" ht="22" customHeight="1">
       <c r="A86" s="11" t="n"/>
@@ -7102,6 +7992,16 @@
       <c r="AD86" s="12" t="n"/>
       <c r="AE86" s="12" t="n"/>
       <c r="AF86" s="12" t="n"/>
+      <c r="AG86" s="12" t="n"/>
+      <c r="AH86" s="12" t="n"/>
+      <c r="AI86" s="12" t="n"/>
+      <c r="AJ86" s="12" t="n"/>
+      <c r="AK86" s="12" t="n"/>
+      <c r="AL86" s="12" t="n"/>
+      <c r="AM86" s="12" t="n"/>
+      <c r="AN86" s="12" t="n"/>
+      <c r="AO86" s="12" t="n"/>
+      <c r="AP86" s="12" t="n"/>
     </row>
     <row r="87" ht="22" customHeight="1">
       <c r="A87" s="9" t="n"/>
@@ -7136,6 +8036,16 @@
       <c r="AD87" s="10" t="n"/>
       <c r="AE87" s="10" t="n"/>
       <c r="AF87" s="10" t="n"/>
+      <c r="AG87" s="10" t="n"/>
+      <c r="AH87" s="10" t="n"/>
+      <c r="AI87" s="10" t="n"/>
+      <c r="AJ87" s="10" t="n"/>
+      <c r="AK87" s="10" t="n"/>
+      <c r="AL87" s="10" t="n"/>
+      <c r="AM87" s="10" t="n"/>
+      <c r="AN87" s="10" t="n"/>
+      <c r="AO87" s="10" t="n"/>
+      <c r="AP87" s="10" t="n"/>
     </row>
     <row r="88" ht="22" customHeight="1">
       <c r="A88" s="11" t="n"/>
@@ -7170,6 +8080,16 @@
       <c r="AD88" s="12" t="n"/>
       <c r="AE88" s="12" t="n"/>
       <c r="AF88" s="12" t="n"/>
+      <c r="AG88" s="12" t="n"/>
+      <c r="AH88" s="12" t="n"/>
+      <c r="AI88" s="12" t="n"/>
+      <c r="AJ88" s="12" t="n"/>
+      <c r="AK88" s="12" t="n"/>
+      <c r="AL88" s="12" t="n"/>
+      <c r="AM88" s="12" t="n"/>
+      <c r="AN88" s="12" t="n"/>
+      <c r="AO88" s="12" t="n"/>
+      <c r="AP88" s="12" t="n"/>
     </row>
     <row r="89" ht="22" customHeight="1">
       <c r="A89" s="9" t="n"/>
@@ -7204,6 +8124,16 @@
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="10" t="n"/>
       <c r="AF89" s="10" t="n"/>
+      <c r="AG89" s="10" t="n"/>
+      <c r="AH89" s="10" t="n"/>
+      <c r="AI89" s="10" t="n"/>
+      <c r="AJ89" s="10" t="n"/>
+      <c r="AK89" s="10" t="n"/>
+      <c r="AL89" s="10" t="n"/>
+      <c r="AM89" s="10" t="n"/>
+      <c r="AN89" s="10" t="n"/>
+      <c r="AO89" s="10" t="n"/>
+      <c r="AP89" s="10" t="n"/>
     </row>
     <row r="90" ht="22" customHeight="1">
       <c r="A90" s="11" t="n"/>
@@ -7238,6 +8168,16 @@
       <c r="AD90" s="12" t="n"/>
       <c r="AE90" s="12" t="n"/>
       <c r="AF90" s="12" t="n"/>
+      <c r="AG90" s="12" t="n"/>
+      <c r="AH90" s="12" t="n"/>
+      <c r="AI90" s="12" t="n"/>
+      <c r="AJ90" s="12" t="n"/>
+      <c r="AK90" s="12" t="n"/>
+      <c r="AL90" s="12" t="n"/>
+      <c r="AM90" s="12" t="n"/>
+      <c r="AN90" s="12" t="n"/>
+      <c r="AO90" s="12" t="n"/>
+      <c r="AP90" s="12" t="n"/>
     </row>
     <row r="91" ht="22" customHeight="1">
       <c r="A91" s="9" t="n"/>
@@ -7272,6 +8212,16 @@
       <c r="AD91" s="10" t="n"/>
       <c r="AE91" s="10" t="n"/>
       <c r="AF91" s="10" t="n"/>
+      <c r="AG91" s="10" t="n"/>
+      <c r="AH91" s="10" t="n"/>
+      <c r="AI91" s="10" t="n"/>
+      <c r="AJ91" s="10" t="n"/>
+      <c r="AK91" s="10" t="n"/>
+      <c r="AL91" s="10" t="n"/>
+      <c r="AM91" s="10" t="n"/>
+      <c r="AN91" s="10" t="n"/>
+      <c r="AO91" s="10" t="n"/>
+      <c r="AP91" s="10" t="n"/>
     </row>
     <row r="92" ht="22" customHeight="1">
       <c r="A92" s="11" t="n"/>
@@ -7306,6 +8256,16 @@
       <c r="AD92" s="12" t="n"/>
       <c r="AE92" s="12" t="n"/>
       <c r="AF92" s="12" t="n"/>
+      <c r="AG92" s="12" t="n"/>
+      <c r="AH92" s="12" t="n"/>
+      <c r="AI92" s="12" t="n"/>
+      <c r="AJ92" s="12" t="n"/>
+      <c r="AK92" s="12" t="n"/>
+      <c r="AL92" s="12" t="n"/>
+      <c r="AM92" s="12" t="n"/>
+      <c r="AN92" s="12" t="n"/>
+      <c r="AO92" s="12" t="n"/>
+      <c r="AP92" s="12" t="n"/>
     </row>
     <row r="93" ht="22" customHeight="1">
       <c r="A93" s="9" t="n"/>
@@ -7340,6 +8300,16 @@
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="10" t="n"/>
       <c r="AF93" s="10" t="n"/>
+      <c r="AG93" s="10" t="n"/>
+      <c r="AH93" s="10" t="n"/>
+      <c r="AI93" s="10" t="n"/>
+      <c r="AJ93" s="10" t="n"/>
+      <c r="AK93" s="10" t="n"/>
+      <c r="AL93" s="10" t="n"/>
+      <c r="AM93" s="10" t="n"/>
+      <c r="AN93" s="10" t="n"/>
+      <c r="AO93" s="10" t="n"/>
+      <c r="AP93" s="10" t="n"/>
     </row>
     <row r="94" ht="22" customHeight="1">
       <c r="A94" s="11" t="n"/>
@@ -7374,6 +8344,16 @@
       <c r="AD94" s="12" t="n"/>
       <c r="AE94" s="12" t="n"/>
       <c r="AF94" s="12" t="n"/>
+      <c r="AG94" s="12" t="n"/>
+      <c r="AH94" s="12" t="n"/>
+      <c r="AI94" s="12" t="n"/>
+      <c r="AJ94" s="12" t="n"/>
+      <c r="AK94" s="12" t="n"/>
+      <c r="AL94" s="12" t="n"/>
+      <c r="AM94" s="12" t="n"/>
+      <c r="AN94" s="12" t="n"/>
+      <c r="AO94" s="12" t="n"/>
+      <c r="AP94" s="12" t="n"/>
     </row>
     <row r="95" ht="22" customHeight="1">
       <c r="A95" s="9" t="n"/>
@@ -7408,6 +8388,16 @@
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="10" t="n"/>
       <c r="AF95" s="10" t="n"/>
+      <c r="AG95" s="10" t="n"/>
+      <c r="AH95" s="10" t="n"/>
+      <c r="AI95" s="10" t="n"/>
+      <c r="AJ95" s="10" t="n"/>
+      <c r="AK95" s="10" t="n"/>
+      <c r="AL95" s="10" t="n"/>
+      <c r="AM95" s="10" t="n"/>
+      <c r="AN95" s="10" t="n"/>
+      <c r="AO95" s="10" t="n"/>
+      <c r="AP95" s="10" t="n"/>
     </row>
     <row r="96" ht="22" customHeight="1">
       <c r="A96" s="11" t="n"/>
@@ -7442,6 +8432,16 @@
       <c r="AD96" s="12" t="n"/>
       <c r="AE96" s="12" t="n"/>
       <c r="AF96" s="12" t="n"/>
+      <c r="AG96" s="12" t="n"/>
+      <c r="AH96" s="12" t="n"/>
+      <c r="AI96" s="12" t="n"/>
+      <c r="AJ96" s="12" t="n"/>
+      <c r="AK96" s="12" t="n"/>
+      <c r="AL96" s="12" t="n"/>
+      <c r="AM96" s="12" t="n"/>
+      <c r="AN96" s="12" t="n"/>
+      <c r="AO96" s="12" t="n"/>
+      <c r="AP96" s="12" t="n"/>
     </row>
     <row r="97" ht="22" customHeight="1">
       <c r="A97" s="9" t="n"/>
@@ -7476,6 +8476,16 @@
       <c r="AD97" s="10" t="n"/>
       <c r="AE97" s="10" t="n"/>
       <c r="AF97" s="10" t="n"/>
+      <c r="AG97" s="10" t="n"/>
+      <c r="AH97" s="10" t="n"/>
+      <c r="AI97" s="10" t="n"/>
+      <c r="AJ97" s="10" t="n"/>
+      <c r="AK97" s="10" t="n"/>
+      <c r="AL97" s="10" t="n"/>
+      <c r="AM97" s="10" t="n"/>
+      <c r="AN97" s="10" t="n"/>
+      <c r="AO97" s="10" t="n"/>
+      <c r="AP97" s="10" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
       <c r="A98" s="11" t="n"/>
@@ -7510,6 +8520,16 @@
       <c r="AD98" s="12" t="n"/>
       <c r="AE98" s="12" t="n"/>
       <c r="AF98" s="12" t="n"/>
+      <c r="AG98" s="12" t="n"/>
+      <c r="AH98" s="12" t="n"/>
+      <c r="AI98" s="12" t="n"/>
+      <c r="AJ98" s="12" t="n"/>
+      <c r="AK98" s="12" t="n"/>
+      <c r="AL98" s="12" t="n"/>
+      <c r="AM98" s="12" t="n"/>
+      <c r="AN98" s="12" t="n"/>
+      <c r="AO98" s="12" t="n"/>
+      <c r="AP98" s="12" t="n"/>
     </row>
     <row r="99" ht="22" customHeight="1">
       <c r="A99" s="9" t="n"/>
@@ -7544,6 +8564,16 @@
       <c r="AD99" s="10" t="n"/>
       <c r="AE99" s="10" t="n"/>
       <c r="AF99" s="10" t="n"/>
+      <c r="AG99" s="10" t="n"/>
+      <c r="AH99" s="10" t="n"/>
+      <c r="AI99" s="10" t="n"/>
+      <c r="AJ99" s="10" t="n"/>
+      <c r="AK99" s="10" t="n"/>
+      <c r="AL99" s="10" t="n"/>
+      <c r="AM99" s="10" t="n"/>
+      <c r="AN99" s="10" t="n"/>
+      <c r="AO99" s="10" t="n"/>
+      <c r="AP99" s="10" t="n"/>
     </row>
     <row r="100" ht="22" customHeight="1">
       <c r="A100" s="11" t="n"/>
@@ -7578,6 +8608,16 @@
       <c r="AD100" s="12" t="n"/>
       <c r="AE100" s="12" t="n"/>
       <c r="AF100" s="12" t="n"/>
+      <c r="AG100" s="12" t="n"/>
+      <c r="AH100" s="12" t="n"/>
+      <c r="AI100" s="12" t="n"/>
+      <c r="AJ100" s="12" t="n"/>
+      <c r="AK100" s="12" t="n"/>
+      <c r="AL100" s="12" t="n"/>
+      <c r="AM100" s="12" t="n"/>
+      <c r="AN100" s="12" t="n"/>
+      <c r="AO100" s="12" t="n"/>
+      <c r="AP100" s="12" t="n"/>
     </row>
     <row r="101" ht="22" customHeight="1">
       <c r="A101" s="9" t="n"/>
@@ -7612,6 +8652,16 @@
       <c r="AD101" s="10" t="n"/>
       <c r="AE101" s="10" t="n"/>
       <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="10" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="10" t="n"/>
+      <c r="AP101" s="10" t="n"/>
     </row>
     <row r="102" ht="22" customHeight="1">
       <c r="A102" s="11" t="n"/>
@@ -7646,6 +8696,16 @@
       <c r="AD102" s="12" t="n"/>
       <c r="AE102" s="12" t="n"/>
       <c r="AF102" s="12" t="n"/>
+      <c r="AG102" s="12" t="n"/>
+      <c r="AH102" s="12" t="n"/>
+      <c r="AI102" s="12" t="n"/>
+      <c r="AJ102" s="12" t="n"/>
+      <c r="AK102" s="12" t="n"/>
+      <c r="AL102" s="12" t="n"/>
+      <c r="AM102" s="12" t="n"/>
+      <c r="AN102" s="12" t="n"/>
+      <c r="AO102" s="12" t="n"/>
+      <c r="AP102" s="12" t="n"/>
     </row>
     <row r="103" ht="22" customHeight="1">
       <c r="A103" s="9" t="n"/>
@@ -7680,6 +8740,16 @@
       <c r="AD103" s="10" t="n"/>
       <c r="AE103" s="10" t="n"/>
       <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="10" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="10" t="n"/>
+      <c r="AP103" s="10" t="n"/>
     </row>
     <row r="104" ht="22" customHeight="1">
       <c r="A104" s="11" t="n"/>
@@ -7714,6 +8784,16 @@
       <c r="AD104" s="12" t="n"/>
       <c r="AE104" s="12" t="n"/>
       <c r="AF104" s="12" t="n"/>
+      <c r="AG104" s="12" t="n"/>
+      <c r="AH104" s="12" t="n"/>
+      <c r="AI104" s="12" t="n"/>
+      <c r="AJ104" s="12" t="n"/>
+      <c r="AK104" s="12" t="n"/>
+      <c r="AL104" s="12" t="n"/>
+      <c r="AM104" s="12" t="n"/>
+      <c r="AN104" s="12" t="n"/>
+      <c r="AO104" s="12" t="n"/>
+      <c r="AP104" s="12" t="n"/>
     </row>
     <row r="105" ht="22" customHeight="1">
       <c r="A105" s="9" t="n"/>
@@ -7748,6 +8828,16 @@
       <c r="AD105" s="10" t="n"/>
       <c r="AE105" s="10" t="n"/>
       <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="10" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="10" t="n"/>
+      <c r="AP105" s="10" t="n"/>
     </row>
     <row r="106" ht="22" customHeight="1">
       <c r="A106" s="11" t="n"/>
@@ -7782,6 +8872,16 @@
       <c r="AD106" s="12" t="n"/>
       <c r="AE106" s="12" t="n"/>
       <c r="AF106" s="12" t="n"/>
+      <c r="AG106" s="12" t="n"/>
+      <c r="AH106" s="12" t="n"/>
+      <c r="AI106" s="12" t="n"/>
+      <c r="AJ106" s="12" t="n"/>
+      <c r="AK106" s="12" t="n"/>
+      <c r="AL106" s="12" t="n"/>
+      <c r="AM106" s="12" t="n"/>
+      <c r="AN106" s="12" t="n"/>
+      <c r="AO106" s="12" t="n"/>
+      <c r="AP106" s="12" t="n"/>
     </row>
     <row r="107" ht="22" customHeight="1">
       <c r="A107" s="9" t="n"/>
@@ -7816,6 +8916,16 @@
       <c r="AD107" s="10" t="n"/>
       <c r="AE107" s="10" t="n"/>
       <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="10" t="n"/>
+      <c r="AK107" s="10" t="n"/>
+      <c r="AL107" s="10" t="n"/>
+      <c r="AM107" s="10" t="n"/>
+      <c r="AN107" s="10" t="n"/>
+      <c r="AO107" s="10" t="n"/>
+      <c r="AP107" s="10" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="11" t="n"/>
@@ -7850,6 +8960,16 @@
       <c r="AD108" s="12" t="n"/>
       <c r="AE108" s="12" t="n"/>
       <c r="AF108" s="12" t="n"/>
+      <c r="AG108" s="12" t="n"/>
+      <c r="AH108" s="12" t="n"/>
+      <c r="AI108" s="12" t="n"/>
+      <c r="AJ108" s="12" t="n"/>
+      <c r="AK108" s="12" t="n"/>
+      <c r="AL108" s="12" t="n"/>
+      <c r="AM108" s="12" t="n"/>
+      <c r="AN108" s="12" t="n"/>
+      <c r="AO108" s="12" t="n"/>
+      <c r="AP108" s="12" t="n"/>
     </row>
     <row r="109" ht="22" customHeight="1">
       <c r="A109" s="9" t="n"/>
@@ -7884,6 +9004,16 @@
       <c r="AD109" s="10" t="n"/>
       <c r="AE109" s="10" t="n"/>
       <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="10" t="n"/>
+      <c r="AK109" s="10" t="n"/>
+      <c r="AL109" s="10" t="n"/>
+      <c r="AM109" s="10" t="n"/>
+      <c r="AN109" s="10" t="n"/>
+      <c r="AO109" s="10" t="n"/>
+      <c r="AP109" s="10" t="n"/>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="11" t="n"/>
@@ -7918,6 +9048,16 @@
       <c r="AD110" s="12" t="n"/>
       <c r="AE110" s="12" t="n"/>
       <c r="AF110" s="12" t="n"/>
+      <c r="AG110" s="12" t="n"/>
+      <c r="AH110" s="12" t="n"/>
+      <c r="AI110" s="12" t="n"/>
+      <c r="AJ110" s="12" t="n"/>
+      <c r="AK110" s="12" t="n"/>
+      <c r="AL110" s="12" t="n"/>
+      <c r="AM110" s="12" t="n"/>
+      <c r="AN110" s="12" t="n"/>
+      <c r="AO110" s="12" t="n"/>
+      <c r="AP110" s="12" t="n"/>
     </row>
     <row r="111" ht="22" customHeight="1">
       <c r="A111" s="9" t="n"/>
@@ -7952,6 +9092,16 @@
       <c r="AD111" s="10" t="n"/>
       <c r="AE111" s="10" t="n"/>
       <c r="AF111" s="10" t="n"/>
+      <c r="AG111" s="10" t="n"/>
+      <c r="AH111" s="10" t="n"/>
+      <c r="AI111" s="10" t="n"/>
+      <c r="AJ111" s="10" t="n"/>
+      <c r="AK111" s="10" t="n"/>
+      <c r="AL111" s="10" t="n"/>
+      <c r="AM111" s="10" t="n"/>
+      <c r="AN111" s="10" t="n"/>
+      <c r="AO111" s="10" t="n"/>
+      <c r="AP111" s="10" t="n"/>
     </row>
     <row r="112" ht="22" customHeight="1">
       <c r="A112" s="11" t="n"/>
@@ -7986,6 +9136,16 @@
       <c r="AD112" s="12" t="n"/>
       <c r="AE112" s="12" t="n"/>
       <c r="AF112" s="12" t="n"/>
+      <c r="AG112" s="12" t="n"/>
+      <c r="AH112" s="12" t="n"/>
+      <c r="AI112" s="12" t="n"/>
+      <c r="AJ112" s="12" t="n"/>
+      <c r="AK112" s="12" t="n"/>
+      <c r="AL112" s="12" t="n"/>
+      <c r="AM112" s="12" t="n"/>
+      <c r="AN112" s="12" t="n"/>
+      <c r="AO112" s="12" t="n"/>
+      <c r="AP112" s="12" t="n"/>
     </row>
     <row r="113" ht="22" customHeight="1">
       <c r="A113" s="9" t="n"/>
@@ -8020,6 +9180,16 @@
       <c r="AD113" s="10" t="n"/>
       <c r="AE113" s="10" t="n"/>
       <c r="AF113" s="10" t="n"/>
+      <c r="AG113" s="10" t="n"/>
+      <c r="AH113" s="10" t="n"/>
+      <c r="AI113" s="10" t="n"/>
+      <c r="AJ113" s="10" t="n"/>
+      <c r="AK113" s="10" t="n"/>
+      <c r="AL113" s="10" t="n"/>
+      <c r="AM113" s="10" t="n"/>
+      <c r="AN113" s="10" t="n"/>
+      <c r="AO113" s="10" t="n"/>
+      <c r="AP113" s="10" t="n"/>
     </row>
     <row r="114" ht="22" customHeight="1">
       <c r="A114" s="11" t="n"/>
@@ -8054,6 +9224,16 @@
       <c r="AD114" s="12" t="n"/>
       <c r="AE114" s="12" t="n"/>
       <c r="AF114" s="12" t="n"/>
+      <c r="AG114" s="12" t="n"/>
+      <c r="AH114" s="12" t="n"/>
+      <c r="AI114" s="12" t="n"/>
+      <c r="AJ114" s="12" t="n"/>
+      <c r="AK114" s="12" t="n"/>
+      <c r="AL114" s="12" t="n"/>
+      <c r="AM114" s="12" t="n"/>
+      <c r="AN114" s="12" t="n"/>
+      <c r="AO114" s="12" t="n"/>
+      <c r="AP114" s="12" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="9" t="n"/>
@@ -8088,6 +9268,16 @@
       <c r="AD115" s="10" t="n"/>
       <c r="AE115" s="10" t="n"/>
       <c r="AF115" s="10" t="n"/>
+      <c r="AG115" s="10" t="n"/>
+      <c r="AH115" s="10" t="n"/>
+      <c r="AI115" s="10" t="n"/>
+      <c r="AJ115" s="10" t="n"/>
+      <c r="AK115" s="10" t="n"/>
+      <c r="AL115" s="10" t="n"/>
+      <c r="AM115" s="10" t="n"/>
+      <c r="AN115" s="10" t="n"/>
+      <c r="AO115" s="10" t="n"/>
+      <c r="AP115" s="10" t="n"/>
     </row>
     <row r="116" ht="22" customHeight="1">
       <c r="A116" s="11" t="n"/>
@@ -8122,6 +9312,16 @@
       <c r="AD116" s="12" t="n"/>
       <c r="AE116" s="12" t="n"/>
       <c r="AF116" s="12" t="n"/>
+      <c r="AG116" s="12" t="n"/>
+      <c r="AH116" s="12" t="n"/>
+      <c r="AI116" s="12" t="n"/>
+      <c r="AJ116" s="12" t="n"/>
+      <c r="AK116" s="12" t="n"/>
+      <c r="AL116" s="12" t="n"/>
+      <c r="AM116" s="12" t="n"/>
+      <c r="AN116" s="12" t="n"/>
+      <c r="AO116" s="12" t="n"/>
+      <c r="AP116" s="12" t="n"/>
     </row>
     <row r="117" ht="22" customHeight="1">
       <c r="A117" s="9" t="n"/>
@@ -8156,6 +9356,16 @@
       <c r="AD117" s="10" t="n"/>
       <c r="AE117" s="10" t="n"/>
       <c r="AF117" s="10" t="n"/>
+      <c r="AG117" s="10" t="n"/>
+      <c r="AH117" s="10" t="n"/>
+      <c r="AI117" s="10" t="n"/>
+      <c r="AJ117" s="10" t="n"/>
+      <c r="AK117" s="10" t="n"/>
+      <c r="AL117" s="10" t="n"/>
+      <c r="AM117" s="10" t="n"/>
+      <c r="AN117" s="10" t="n"/>
+      <c r="AO117" s="10" t="n"/>
+      <c r="AP117" s="10" t="n"/>
     </row>
     <row r="118" ht="22" customHeight="1">
       <c r="A118" s="11" t="n"/>
@@ -8190,6 +9400,16 @@
       <c r="AD118" s="12" t="n"/>
       <c r="AE118" s="12" t="n"/>
       <c r="AF118" s="12" t="n"/>
+      <c r="AG118" s="12" t="n"/>
+      <c r="AH118" s="12" t="n"/>
+      <c r="AI118" s="12" t="n"/>
+      <c r="AJ118" s="12" t="n"/>
+      <c r="AK118" s="12" t="n"/>
+      <c r="AL118" s="12" t="n"/>
+      <c r="AM118" s="12" t="n"/>
+      <c r="AN118" s="12" t="n"/>
+      <c r="AO118" s="12" t="n"/>
+      <c r="AP118" s="12" t="n"/>
     </row>
     <row r="119" ht="22" customHeight="1">
       <c r="A119" s="9" t="n"/>
@@ -8224,6 +9444,16 @@
       <c r="AD119" s="10" t="n"/>
       <c r="AE119" s="10" t="n"/>
       <c r="AF119" s="10" t="n"/>
+      <c r="AG119" s="10" t="n"/>
+      <c r="AH119" s="10" t="n"/>
+      <c r="AI119" s="10" t="n"/>
+      <c r="AJ119" s="10" t="n"/>
+      <c r="AK119" s="10" t="n"/>
+      <c r="AL119" s="10" t="n"/>
+      <c r="AM119" s="10" t="n"/>
+      <c r="AN119" s="10" t="n"/>
+      <c r="AO119" s="10" t="n"/>
+      <c r="AP119" s="10" t="n"/>
     </row>
     <row r="120" ht="22" customHeight="1">
       <c r="A120" s="11" t="n"/>
@@ -8258,6 +9488,16 @@
       <c r="AD120" s="12" t="n"/>
       <c r="AE120" s="12" t="n"/>
       <c r="AF120" s="12" t="n"/>
+      <c r="AG120" s="12" t="n"/>
+      <c r="AH120" s="12" t="n"/>
+      <c r="AI120" s="12" t="n"/>
+      <c r="AJ120" s="12" t="n"/>
+      <c r="AK120" s="12" t="n"/>
+      <c r="AL120" s="12" t="n"/>
+      <c r="AM120" s="12" t="n"/>
+      <c r="AN120" s="12" t="n"/>
+      <c r="AO120" s="12" t="n"/>
+      <c r="AP120" s="12" t="n"/>
     </row>
     <row r="121" ht="22" customHeight="1">
       <c r="A121" s="9" t="n"/>
@@ -8292,6 +9532,16 @@
       <c r="AD121" s="10" t="n"/>
       <c r="AE121" s="10" t="n"/>
       <c r="AF121" s="10" t="n"/>
+      <c r="AG121" s="10" t="n"/>
+      <c r="AH121" s="10" t="n"/>
+      <c r="AI121" s="10" t="n"/>
+      <c r="AJ121" s="10" t="n"/>
+      <c r="AK121" s="10" t="n"/>
+      <c r="AL121" s="10" t="n"/>
+      <c r="AM121" s="10" t="n"/>
+      <c r="AN121" s="10" t="n"/>
+      <c r="AO121" s="10" t="n"/>
+      <c r="AP121" s="10" t="n"/>
     </row>
     <row r="122" ht="22" customHeight="1">
       <c r="A122" s="11" t="n"/>
@@ -8326,6 +9576,16 @@
       <c r="AD122" s="12" t="n"/>
       <c r="AE122" s="12" t="n"/>
       <c r="AF122" s="12" t="n"/>
+      <c r="AG122" s="12" t="n"/>
+      <c r="AH122" s="12" t="n"/>
+      <c r="AI122" s="12" t="n"/>
+      <c r="AJ122" s="12" t="n"/>
+      <c r="AK122" s="12" t="n"/>
+      <c r="AL122" s="12" t="n"/>
+      <c r="AM122" s="12" t="n"/>
+      <c r="AN122" s="12" t="n"/>
+      <c r="AO122" s="12" t="n"/>
+      <c r="AP122" s="12" t="n"/>
     </row>
     <row r="123" ht="22" customHeight="1">
       <c r="A123" s="9" t="n"/>
@@ -8360,6 +9620,16 @@
       <c r="AD123" s="10" t="n"/>
       <c r="AE123" s="10" t="n"/>
       <c r="AF123" s="10" t="n"/>
+      <c r="AG123" s="10" t="n"/>
+      <c r="AH123" s="10" t="n"/>
+      <c r="AI123" s="10" t="n"/>
+      <c r="AJ123" s="10" t="n"/>
+      <c r="AK123" s="10" t="n"/>
+      <c r="AL123" s="10" t="n"/>
+      <c r="AM123" s="10" t="n"/>
+      <c r="AN123" s="10" t="n"/>
+      <c r="AO123" s="10" t="n"/>
+      <c r="AP123" s="10" t="n"/>
     </row>
     <row r="124" ht="22" customHeight="1">
       <c r="A124" s="11" t="n"/>
@@ -8394,6 +9664,16 @@
       <c r="AD124" s="12" t="n"/>
       <c r="AE124" s="12" t="n"/>
       <c r="AF124" s="12" t="n"/>
+      <c r="AG124" s="12" t="n"/>
+      <c r="AH124" s="12" t="n"/>
+      <c r="AI124" s="12" t="n"/>
+      <c r="AJ124" s="12" t="n"/>
+      <c r="AK124" s="12" t="n"/>
+      <c r="AL124" s="12" t="n"/>
+      <c r="AM124" s="12" t="n"/>
+      <c r="AN124" s="12" t="n"/>
+      <c r="AO124" s="12" t="n"/>
+      <c r="AP124" s="12" t="n"/>
     </row>
     <row r="125" ht="22" customHeight="1">
       <c r="A125" s="9" t="n"/>
@@ -8428,6 +9708,16 @@
       <c r="AD125" s="10" t="n"/>
       <c r="AE125" s="10" t="n"/>
       <c r="AF125" s="10" t="n"/>
+      <c r="AG125" s="10" t="n"/>
+      <c r="AH125" s="10" t="n"/>
+      <c r="AI125" s="10" t="n"/>
+      <c r="AJ125" s="10" t="n"/>
+      <c r="AK125" s="10" t="n"/>
+      <c r="AL125" s="10" t="n"/>
+      <c r="AM125" s="10" t="n"/>
+      <c r="AN125" s="10" t="n"/>
+      <c r="AO125" s="10" t="n"/>
+      <c r="AP125" s="10" t="n"/>
     </row>
     <row r="126" ht="22" customHeight="1">
       <c r="A126" s="11" t="n"/>
@@ -8462,6 +9752,16 @@
       <c r="AD126" s="12" t="n"/>
       <c r="AE126" s="12" t="n"/>
       <c r="AF126" s="12" t="n"/>
+      <c r="AG126" s="12" t="n"/>
+      <c r="AH126" s="12" t="n"/>
+      <c r="AI126" s="12" t="n"/>
+      <c r="AJ126" s="12" t="n"/>
+      <c r="AK126" s="12" t="n"/>
+      <c r="AL126" s="12" t="n"/>
+      <c r="AM126" s="12" t="n"/>
+      <c r="AN126" s="12" t="n"/>
+      <c r="AO126" s="12" t="n"/>
+      <c r="AP126" s="12" t="n"/>
     </row>
     <row r="127" ht="22" customHeight="1">
       <c r="A127" s="9" t="n"/>
@@ -8496,6 +9796,16 @@
       <c r="AD127" s="10" t="n"/>
       <c r="AE127" s="10" t="n"/>
       <c r="AF127" s="10" t="n"/>
+      <c r="AG127" s="10" t="n"/>
+      <c r="AH127" s="10" t="n"/>
+      <c r="AI127" s="10" t="n"/>
+      <c r="AJ127" s="10" t="n"/>
+      <c r="AK127" s="10" t="n"/>
+      <c r="AL127" s="10" t="n"/>
+      <c r="AM127" s="10" t="n"/>
+      <c r="AN127" s="10" t="n"/>
+      <c r="AO127" s="10" t="n"/>
+      <c r="AP127" s="10" t="n"/>
     </row>
     <row r="128" ht="22" customHeight="1">
       <c r="A128" s="11" t="n"/>
@@ -8530,6 +9840,16 @@
       <c r="AD128" s="12" t="n"/>
       <c r="AE128" s="12" t="n"/>
       <c r="AF128" s="12" t="n"/>
+      <c r="AG128" s="12" t="n"/>
+      <c r="AH128" s="12" t="n"/>
+      <c r="AI128" s="12" t="n"/>
+      <c r="AJ128" s="12" t="n"/>
+      <c r="AK128" s="12" t="n"/>
+      <c r="AL128" s="12" t="n"/>
+      <c r="AM128" s="12" t="n"/>
+      <c r="AN128" s="12" t="n"/>
+      <c r="AO128" s="12" t="n"/>
+      <c r="AP128" s="12" t="n"/>
     </row>
     <row r="129" ht="22" customHeight="1">
       <c r="A129" s="9" t="n"/>
@@ -8564,6 +9884,16 @@
       <c r="AD129" s="10" t="n"/>
       <c r="AE129" s="10" t="n"/>
       <c r="AF129" s="10" t="n"/>
+      <c r="AG129" s="10" t="n"/>
+      <c r="AH129" s="10" t="n"/>
+      <c r="AI129" s="10" t="n"/>
+      <c r="AJ129" s="10" t="n"/>
+      <c r="AK129" s="10" t="n"/>
+      <c r="AL129" s="10" t="n"/>
+      <c r="AM129" s="10" t="n"/>
+      <c r="AN129" s="10" t="n"/>
+      <c r="AO129" s="10" t="n"/>
+      <c r="AP129" s="10" t="n"/>
     </row>
     <row r="130" ht="22" customHeight="1">
       <c r="A130" s="11" t="n"/>
@@ -8598,6 +9928,16 @@
       <c r="AD130" s="12" t="n"/>
       <c r="AE130" s="12" t="n"/>
       <c r="AF130" s="12" t="n"/>
+      <c r="AG130" s="12" t="n"/>
+      <c r="AH130" s="12" t="n"/>
+      <c r="AI130" s="12" t="n"/>
+      <c r="AJ130" s="12" t="n"/>
+      <c r="AK130" s="12" t="n"/>
+      <c r="AL130" s="12" t="n"/>
+      <c r="AM130" s="12" t="n"/>
+      <c r="AN130" s="12" t="n"/>
+      <c r="AO130" s="12" t="n"/>
+      <c r="AP130" s="12" t="n"/>
     </row>
     <row r="131" ht="22" customHeight="1">
       <c r="A131" s="9" t="n"/>
@@ -8632,6 +9972,16 @@
       <c r="AD131" s="10" t="n"/>
       <c r="AE131" s="10" t="n"/>
       <c r="AF131" s="10" t="n"/>
+      <c r="AG131" s="10" t="n"/>
+      <c r="AH131" s="10" t="n"/>
+      <c r="AI131" s="10" t="n"/>
+      <c r="AJ131" s="10" t="n"/>
+      <c r="AK131" s="10" t="n"/>
+      <c r="AL131" s="10" t="n"/>
+      <c r="AM131" s="10" t="n"/>
+      <c r="AN131" s="10" t="n"/>
+      <c r="AO131" s="10" t="n"/>
+      <c r="AP131" s="10" t="n"/>
     </row>
     <row r="132" ht="22" customHeight="1">
       <c r="A132" s="11" t="n"/>
@@ -8666,6 +10016,16 @@
       <c r="AD132" s="12" t="n"/>
       <c r="AE132" s="12" t="n"/>
       <c r="AF132" s="12" t="n"/>
+      <c r="AG132" s="12" t="n"/>
+      <c r="AH132" s="12" t="n"/>
+      <c r="AI132" s="12" t="n"/>
+      <c r="AJ132" s="12" t="n"/>
+      <c r="AK132" s="12" t="n"/>
+      <c r="AL132" s="12" t="n"/>
+      <c r="AM132" s="12" t="n"/>
+      <c r="AN132" s="12" t="n"/>
+      <c r="AO132" s="12" t="n"/>
+      <c r="AP132" s="12" t="n"/>
     </row>
     <row r="133" ht="22" customHeight="1">
       <c r="A133" s="9" t="n"/>
@@ -8700,6 +10060,16 @@
       <c r="AD133" s="10" t="n"/>
       <c r="AE133" s="10" t="n"/>
       <c r="AF133" s="10" t="n"/>
+      <c r="AG133" s="10" t="n"/>
+      <c r="AH133" s="10" t="n"/>
+      <c r="AI133" s="10" t="n"/>
+      <c r="AJ133" s="10" t="n"/>
+      <c r="AK133" s="10" t="n"/>
+      <c r="AL133" s="10" t="n"/>
+      <c r="AM133" s="10" t="n"/>
+      <c r="AN133" s="10" t="n"/>
+      <c r="AO133" s="10" t="n"/>
+      <c r="AP133" s="10" t="n"/>
     </row>
     <row r="134" ht="22" customHeight="1">
       <c r="A134" s="11" t="n"/>
@@ -8734,6 +10104,16 @@
       <c r="AD134" s="12" t="n"/>
       <c r="AE134" s="12" t="n"/>
       <c r="AF134" s="12" t="n"/>
+      <c r="AG134" s="12" t="n"/>
+      <c r="AH134" s="12" t="n"/>
+      <c r="AI134" s="12" t="n"/>
+      <c r="AJ134" s="12" t="n"/>
+      <c r="AK134" s="12" t="n"/>
+      <c r="AL134" s="12" t="n"/>
+      <c r="AM134" s="12" t="n"/>
+      <c r="AN134" s="12" t="n"/>
+      <c r="AO134" s="12" t="n"/>
+      <c r="AP134" s="12" t="n"/>
     </row>
     <row r="135" ht="22" customHeight="1">
       <c r="A135" s="9" t="n"/>
@@ -8768,6 +10148,16 @@
       <c r="AD135" s="10" t="n"/>
       <c r="AE135" s="10" t="n"/>
       <c r="AF135" s="10" t="n"/>
+      <c r="AG135" s="10" t="n"/>
+      <c r="AH135" s="10" t="n"/>
+      <c r="AI135" s="10" t="n"/>
+      <c r="AJ135" s="10" t="n"/>
+      <c r="AK135" s="10" t="n"/>
+      <c r="AL135" s="10" t="n"/>
+      <c r="AM135" s="10" t="n"/>
+      <c r="AN135" s="10" t="n"/>
+      <c r="AO135" s="10" t="n"/>
+      <c r="AP135" s="10" t="n"/>
     </row>
     <row r="136" ht="22" customHeight="1">
       <c r="A136" s="11" t="n"/>
@@ -8802,6 +10192,16 @@
       <c r="AD136" s="12" t="n"/>
       <c r="AE136" s="12" t="n"/>
       <c r="AF136" s="12" t="n"/>
+      <c r="AG136" s="12" t="n"/>
+      <c r="AH136" s="12" t="n"/>
+      <c r="AI136" s="12" t="n"/>
+      <c r="AJ136" s="12" t="n"/>
+      <c r="AK136" s="12" t="n"/>
+      <c r="AL136" s="12" t="n"/>
+      <c r="AM136" s="12" t="n"/>
+      <c r="AN136" s="12" t="n"/>
+      <c r="AO136" s="12" t="n"/>
+      <c r="AP136" s="12" t="n"/>
     </row>
     <row r="137" ht="22" customHeight="1">
       <c r="A137" s="9" t="n"/>
@@ -8836,6 +10236,16 @@
       <c r="AD137" s="10" t="n"/>
       <c r="AE137" s="10" t="n"/>
       <c r="AF137" s="10" t="n"/>
+      <c r="AG137" s="10" t="n"/>
+      <c r="AH137" s="10" t="n"/>
+      <c r="AI137" s="10" t="n"/>
+      <c r="AJ137" s="10" t="n"/>
+      <c r="AK137" s="10" t="n"/>
+      <c r="AL137" s="10" t="n"/>
+      <c r="AM137" s="10" t="n"/>
+      <c r="AN137" s="10" t="n"/>
+      <c r="AO137" s="10" t="n"/>
+      <c r="AP137" s="10" t="n"/>
     </row>
     <row r="138" ht="22" customHeight="1">
       <c r="A138" s="11" t="n"/>
@@ -8870,6 +10280,16 @@
       <c r="AD138" s="12" t="n"/>
       <c r="AE138" s="12" t="n"/>
       <c r="AF138" s="12" t="n"/>
+      <c r="AG138" s="12" t="n"/>
+      <c r="AH138" s="12" t="n"/>
+      <c r="AI138" s="12" t="n"/>
+      <c r="AJ138" s="12" t="n"/>
+      <c r="AK138" s="12" t="n"/>
+      <c r="AL138" s="12" t="n"/>
+      <c r="AM138" s="12" t="n"/>
+      <c r="AN138" s="12" t="n"/>
+      <c r="AO138" s="12" t="n"/>
+      <c r="AP138" s="12" t="n"/>
     </row>
     <row r="139" ht="22" customHeight="1">
       <c r="A139" s="9" t="n"/>
@@ -8904,6 +10324,16 @@
       <c r="AD139" s="10" t="n"/>
       <c r="AE139" s="10" t="n"/>
       <c r="AF139" s="10" t="n"/>
+      <c r="AG139" s="10" t="n"/>
+      <c r="AH139" s="10" t="n"/>
+      <c r="AI139" s="10" t="n"/>
+      <c r="AJ139" s="10" t="n"/>
+      <c r="AK139" s="10" t="n"/>
+      <c r="AL139" s="10" t="n"/>
+      <c r="AM139" s="10" t="n"/>
+      <c r="AN139" s="10" t="n"/>
+      <c r="AO139" s="10" t="n"/>
+      <c r="AP139" s="10" t="n"/>
     </row>
     <row r="140" ht="22" customHeight="1">
       <c r="A140" s="11" t="n"/>
@@ -8938,6 +10368,16 @@
       <c r="AD140" s="12" t="n"/>
       <c r="AE140" s="12" t="n"/>
       <c r="AF140" s="12" t="n"/>
+      <c r="AG140" s="12" t="n"/>
+      <c r="AH140" s="12" t="n"/>
+      <c r="AI140" s="12" t="n"/>
+      <c r="AJ140" s="12" t="n"/>
+      <c r="AK140" s="12" t="n"/>
+      <c r="AL140" s="12" t="n"/>
+      <c r="AM140" s="12" t="n"/>
+      <c r="AN140" s="12" t="n"/>
+      <c r="AO140" s="12" t="n"/>
+      <c r="AP140" s="12" t="n"/>
     </row>
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="9" t="n"/>
@@ -8972,6 +10412,16 @@
       <c r="AD141" s="10" t="n"/>
       <c r="AE141" s="10" t="n"/>
       <c r="AF141" s="10" t="n"/>
+      <c r="AG141" s="10" t="n"/>
+      <c r="AH141" s="10" t="n"/>
+      <c r="AI141" s="10" t="n"/>
+      <c r="AJ141" s="10" t="n"/>
+      <c r="AK141" s="10" t="n"/>
+      <c r="AL141" s="10" t="n"/>
+      <c r="AM141" s="10" t="n"/>
+      <c r="AN141" s="10" t="n"/>
+      <c r="AO141" s="10" t="n"/>
+      <c r="AP141" s="10" t="n"/>
     </row>
     <row r="142" ht="22" customHeight="1">
       <c r="A142" s="11" t="n"/>
@@ -9006,6 +10456,16 @@
       <c r="AD142" s="12" t="n"/>
       <c r="AE142" s="12" t="n"/>
       <c r="AF142" s="12" t="n"/>
+      <c r="AG142" s="12" t="n"/>
+      <c r="AH142" s="12" t="n"/>
+      <c r="AI142" s="12" t="n"/>
+      <c r="AJ142" s="12" t="n"/>
+      <c r="AK142" s="12" t="n"/>
+      <c r="AL142" s="12" t="n"/>
+      <c r="AM142" s="12" t="n"/>
+      <c r="AN142" s="12" t="n"/>
+      <c r="AO142" s="12" t="n"/>
+      <c r="AP142" s="12" t="n"/>
     </row>
     <row r="143" ht="22" customHeight="1">
       <c r="A143" s="9" t="n"/>
@@ -9040,6 +10500,16 @@
       <c r="AD143" s="10" t="n"/>
       <c r="AE143" s="10" t="n"/>
       <c r="AF143" s="10" t="n"/>
+      <c r="AG143" s="10" t="n"/>
+      <c r="AH143" s="10" t="n"/>
+      <c r="AI143" s="10" t="n"/>
+      <c r="AJ143" s="10" t="n"/>
+      <c r="AK143" s="10" t="n"/>
+      <c r="AL143" s="10" t="n"/>
+      <c r="AM143" s="10" t="n"/>
+      <c r="AN143" s="10" t="n"/>
+      <c r="AO143" s="10" t="n"/>
+      <c r="AP143" s="10" t="n"/>
     </row>
     <row r="144" ht="22" customHeight="1">
       <c r="A144" s="11" t="n"/>
@@ -9074,6 +10544,16 @@
       <c r="AD144" s="12" t="n"/>
       <c r="AE144" s="12" t="n"/>
       <c r="AF144" s="12" t="n"/>
+      <c r="AG144" s="12" t="n"/>
+      <c r="AH144" s="12" t="n"/>
+      <c r="AI144" s="12" t="n"/>
+      <c r="AJ144" s="12" t="n"/>
+      <c r="AK144" s="12" t="n"/>
+      <c r="AL144" s="12" t="n"/>
+      <c r="AM144" s="12" t="n"/>
+      <c r="AN144" s="12" t="n"/>
+      <c r="AO144" s="12" t="n"/>
+      <c r="AP144" s="12" t="n"/>
     </row>
     <row r="145" ht="22" customHeight="1">
       <c r="A145" s="9" t="n"/>
@@ -9108,6 +10588,16 @@
       <c r="AD145" s="10" t="n"/>
       <c r="AE145" s="10" t="n"/>
       <c r="AF145" s="10" t="n"/>
+      <c r="AG145" s="10" t="n"/>
+      <c r="AH145" s="10" t="n"/>
+      <c r="AI145" s="10" t="n"/>
+      <c r="AJ145" s="10" t="n"/>
+      <c r="AK145" s="10" t="n"/>
+      <c r="AL145" s="10" t="n"/>
+      <c r="AM145" s="10" t="n"/>
+      <c r="AN145" s="10" t="n"/>
+      <c r="AO145" s="10" t="n"/>
+      <c r="AP145" s="10" t="n"/>
     </row>
     <row r="146" ht="22" customHeight="1">
       <c r="A146" s="11" t="n"/>
@@ -9142,6 +10632,16 @@
       <c r="AD146" s="12" t="n"/>
       <c r="AE146" s="12" t="n"/>
       <c r="AF146" s="12" t="n"/>
+      <c r="AG146" s="12" t="n"/>
+      <c r="AH146" s="12" t="n"/>
+      <c r="AI146" s="12" t="n"/>
+      <c r="AJ146" s="12" t="n"/>
+      <c r="AK146" s="12" t="n"/>
+      <c r="AL146" s="12" t="n"/>
+      <c r="AM146" s="12" t="n"/>
+      <c r="AN146" s="12" t="n"/>
+      <c r="AO146" s="12" t="n"/>
+      <c r="AP146" s="12" t="n"/>
     </row>
     <row r="147" ht="22" customHeight="1">
       <c r="A147" s="9" t="n"/>
@@ -9176,6 +10676,16 @@
       <c r="AD147" s="10" t="n"/>
       <c r="AE147" s="10" t="n"/>
       <c r="AF147" s="10" t="n"/>
+      <c r="AG147" s="10" t="n"/>
+      <c r="AH147" s="10" t="n"/>
+      <c r="AI147" s="10" t="n"/>
+      <c r="AJ147" s="10" t="n"/>
+      <c r="AK147" s="10" t="n"/>
+      <c r="AL147" s="10" t="n"/>
+      <c r="AM147" s="10" t="n"/>
+      <c r="AN147" s="10" t="n"/>
+      <c r="AO147" s="10" t="n"/>
+      <c r="AP147" s="10" t="n"/>
     </row>
     <row r="148" ht="22" customHeight="1">
       <c r="A148" s="11" t="n"/>
@@ -9210,6 +10720,16 @@
       <c r="AD148" s="12" t="n"/>
       <c r="AE148" s="12" t="n"/>
       <c r="AF148" s="12" t="n"/>
+      <c r="AG148" s="12" t="n"/>
+      <c r="AH148" s="12" t="n"/>
+      <c r="AI148" s="12" t="n"/>
+      <c r="AJ148" s="12" t="n"/>
+      <c r="AK148" s="12" t="n"/>
+      <c r="AL148" s="12" t="n"/>
+      <c r="AM148" s="12" t="n"/>
+      <c r="AN148" s="12" t="n"/>
+      <c r="AO148" s="12" t="n"/>
+      <c r="AP148" s="12" t="n"/>
     </row>
     <row r="149" ht="22" customHeight="1">
       <c r="A149" s="9" t="n"/>
@@ -9244,6 +10764,16 @@
       <c r="AD149" s="10" t="n"/>
       <c r="AE149" s="10" t="n"/>
       <c r="AF149" s="10" t="n"/>
+      <c r="AG149" s="10" t="n"/>
+      <c r="AH149" s="10" t="n"/>
+      <c r="AI149" s="10" t="n"/>
+      <c r="AJ149" s="10" t="n"/>
+      <c r="AK149" s="10" t="n"/>
+      <c r="AL149" s="10" t="n"/>
+      <c r="AM149" s="10" t="n"/>
+      <c r="AN149" s="10" t="n"/>
+      <c r="AO149" s="10" t="n"/>
+      <c r="AP149" s="10" t="n"/>
     </row>
     <row r="150" ht="22" customHeight="1">
       <c r="A150" s="11" t="n"/>
@@ -9278,6 +10808,16 @@
       <c r="AD150" s="12" t="n"/>
       <c r="AE150" s="12" t="n"/>
       <c r="AF150" s="12" t="n"/>
+      <c r="AG150" s="12" t="n"/>
+      <c r="AH150" s="12" t="n"/>
+      <c r="AI150" s="12" t="n"/>
+      <c r="AJ150" s="12" t="n"/>
+      <c r="AK150" s="12" t="n"/>
+      <c r="AL150" s="12" t="n"/>
+      <c r="AM150" s="12" t="n"/>
+      <c r="AN150" s="12" t="n"/>
+      <c r="AO150" s="12" t="n"/>
+      <c r="AP150" s="12" t="n"/>
     </row>
     <row r="151" ht="22" customHeight="1">
       <c r="A151" s="9" t="n"/>
@@ -9312,6 +10852,16 @@
       <c r="AD151" s="10" t="n"/>
       <c r="AE151" s="10" t="n"/>
       <c r="AF151" s="10" t="n"/>
+      <c r="AG151" s="10" t="n"/>
+      <c r="AH151" s="10" t="n"/>
+      <c r="AI151" s="10" t="n"/>
+      <c r="AJ151" s="10" t="n"/>
+      <c r="AK151" s="10" t="n"/>
+      <c r="AL151" s="10" t="n"/>
+      <c r="AM151" s="10" t="n"/>
+      <c r="AN151" s="10" t="n"/>
+      <c r="AO151" s="10" t="n"/>
+      <c r="AP151" s="10" t="n"/>
     </row>
     <row r="152" ht="22" customHeight="1">
       <c r="A152" s="11" t="n"/>
@@ -9346,6 +10896,16 @@
       <c r="AD152" s="12" t="n"/>
       <c r="AE152" s="12" t="n"/>
       <c r="AF152" s="12" t="n"/>
+      <c r="AG152" s="12" t="n"/>
+      <c r="AH152" s="12" t="n"/>
+      <c r="AI152" s="12" t="n"/>
+      <c r="AJ152" s="12" t="n"/>
+      <c r="AK152" s="12" t="n"/>
+      <c r="AL152" s="12" t="n"/>
+      <c r="AM152" s="12" t="n"/>
+      <c r="AN152" s="12" t="n"/>
+      <c r="AO152" s="12" t="n"/>
+      <c r="AP152" s="12" t="n"/>
     </row>
     <row r="153" ht="22" customHeight="1">
       <c r="A153" s="9" t="n"/>
@@ -9380,6 +10940,16 @@
       <c r="AD153" s="10" t="n"/>
       <c r="AE153" s="10" t="n"/>
       <c r="AF153" s="10" t="n"/>
+      <c r="AG153" s="10" t="n"/>
+      <c r="AH153" s="10" t="n"/>
+      <c r="AI153" s="10" t="n"/>
+      <c r="AJ153" s="10" t="n"/>
+      <c r="AK153" s="10" t="n"/>
+      <c r="AL153" s="10" t="n"/>
+      <c r="AM153" s="10" t="n"/>
+      <c r="AN153" s="10" t="n"/>
+      <c r="AO153" s="10" t="n"/>
+      <c r="AP153" s="10" t="n"/>
     </row>
     <row r="154" ht="22" customHeight="1">
       <c r="A154" s="11" t="n"/>
@@ -9414,6 +10984,16 @@
       <c r="AD154" s="12" t="n"/>
       <c r="AE154" s="12" t="n"/>
       <c r="AF154" s="12" t="n"/>
+      <c r="AG154" s="12" t="n"/>
+      <c r="AH154" s="12" t="n"/>
+      <c r="AI154" s="12" t="n"/>
+      <c r="AJ154" s="12" t="n"/>
+      <c r="AK154" s="12" t="n"/>
+      <c r="AL154" s="12" t="n"/>
+      <c r="AM154" s="12" t="n"/>
+      <c r="AN154" s="12" t="n"/>
+      <c r="AO154" s="12" t="n"/>
+      <c r="AP154" s="12" t="n"/>
     </row>
     <row r="155" ht="22" customHeight="1">
       <c r="A155" s="9" t="n"/>
@@ -9448,6 +11028,16 @@
       <c r="AD155" s="10" t="n"/>
       <c r="AE155" s="10" t="n"/>
       <c r="AF155" s="10" t="n"/>
+      <c r="AG155" s="10" t="n"/>
+      <c r="AH155" s="10" t="n"/>
+      <c r="AI155" s="10" t="n"/>
+      <c r="AJ155" s="10" t="n"/>
+      <c r="AK155" s="10" t="n"/>
+      <c r="AL155" s="10" t="n"/>
+      <c r="AM155" s="10" t="n"/>
+      <c r="AN155" s="10" t="n"/>
+      <c r="AO155" s="10" t="n"/>
+      <c r="AP155" s="10" t="n"/>
     </row>
     <row r="156" ht="22" customHeight="1">
       <c r="A156" s="11" t="n"/>
@@ -9482,6 +11072,16 @@
       <c r="AD156" s="12" t="n"/>
       <c r="AE156" s="12" t="n"/>
       <c r="AF156" s="12" t="n"/>
+      <c r="AG156" s="12" t="n"/>
+      <c r="AH156" s="12" t="n"/>
+      <c r="AI156" s="12" t="n"/>
+      <c r="AJ156" s="12" t="n"/>
+      <c r="AK156" s="12" t="n"/>
+      <c r="AL156" s="12" t="n"/>
+      <c r="AM156" s="12" t="n"/>
+      <c r="AN156" s="12" t="n"/>
+      <c r="AO156" s="12" t="n"/>
+      <c r="AP156" s="12" t="n"/>
     </row>
     <row r="157" ht="22" customHeight="1">
       <c r="A157" s="9" t="n"/>
@@ -9516,6 +11116,16 @@
       <c r="AD157" s="10" t="n"/>
       <c r="AE157" s="10" t="n"/>
       <c r="AF157" s="10" t="n"/>
+      <c r="AG157" s="10" t="n"/>
+      <c r="AH157" s="10" t="n"/>
+      <c r="AI157" s="10" t="n"/>
+      <c r="AJ157" s="10" t="n"/>
+      <c r="AK157" s="10" t="n"/>
+      <c r="AL157" s="10" t="n"/>
+      <c r="AM157" s="10" t="n"/>
+      <c r="AN157" s="10" t="n"/>
+      <c r="AO157" s="10" t="n"/>
+      <c r="AP157" s="10" t="n"/>
     </row>
     <row r="158" ht="22" customHeight="1">
       <c r="A158" s="11" t="n"/>
@@ -9550,6 +11160,16 @@
       <c r="AD158" s="12" t="n"/>
       <c r="AE158" s="12" t="n"/>
       <c r="AF158" s="12" t="n"/>
+      <c r="AG158" s="12" t="n"/>
+      <c r="AH158" s="12" t="n"/>
+      <c r="AI158" s="12" t="n"/>
+      <c r="AJ158" s="12" t="n"/>
+      <c r="AK158" s="12" t="n"/>
+      <c r="AL158" s="12" t="n"/>
+      <c r="AM158" s="12" t="n"/>
+      <c r="AN158" s="12" t="n"/>
+      <c r="AO158" s="12" t="n"/>
+      <c r="AP158" s="12" t="n"/>
     </row>
     <row r="159" ht="22" customHeight="1">
       <c r="A159" s="9" t="n"/>
@@ -9584,6 +11204,16 @@
       <c r="AD159" s="10" t="n"/>
       <c r="AE159" s="10" t="n"/>
       <c r="AF159" s="10" t="n"/>
+      <c r="AG159" s="10" t="n"/>
+      <c r="AH159" s="10" t="n"/>
+      <c r="AI159" s="10" t="n"/>
+      <c r="AJ159" s="10" t="n"/>
+      <c r="AK159" s="10" t="n"/>
+      <c r="AL159" s="10" t="n"/>
+      <c r="AM159" s="10" t="n"/>
+      <c r="AN159" s="10" t="n"/>
+      <c r="AO159" s="10" t="n"/>
+      <c r="AP159" s="10" t="n"/>
     </row>
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="11" t="n"/>
@@ -9618,6 +11248,16 @@
       <c r="AD160" s="12" t="n"/>
       <c r="AE160" s="12" t="n"/>
       <c r="AF160" s="12" t="n"/>
+      <c r="AG160" s="12" t="n"/>
+      <c r="AH160" s="12" t="n"/>
+      <c r="AI160" s="12" t="n"/>
+      <c r="AJ160" s="12" t="n"/>
+      <c r="AK160" s="12" t="n"/>
+      <c r="AL160" s="12" t="n"/>
+      <c r="AM160" s="12" t="n"/>
+      <c r="AN160" s="12" t="n"/>
+      <c r="AO160" s="12" t="n"/>
+      <c r="AP160" s="12" t="n"/>
     </row>
     <row r="161" ht="22" customHeight="1">
       <c r="A161" s="9" t="n"/>
@@ -9652,6 +11292,16 @@
       <c r="AD161" s="10" t="n"/>
       <c r="AE161" s="10" t="n"/>
       <c r="AF161" s="10" t="n"/>
+      <c r="AG161" s="10" t="n"/>
+      <c r="AH161" s="10" t="n"/>
+      <c r="AI161" s="10" t="n"/>
+      <c r="AJ161" s="10" t="n"/>
+      <c r="AK161" s="10" t="n"/>
+      <c r="AL161" s="10" t="n"/>
+      <c r="AM161" s="10" t="n"/>
+      <c r="AN161" s="10" t="n"/>
+      <c r="AO161" s="10" t="n"/>
+      <c r="AP161" s="10" t="n"/>
     </row>
     <row r="162" ht="22" customHeight="1">
       <c r="A162" s="11" t="n"/>
@@ -9686,6 +11336,16 @@
       <c r="AD162" s="12" t="n"/>
       <c r="AE162" s="12" t="n"/>
       <c r="AF162" s="12" t="n"/>
+      <c r="AG162" s="12" t="n"/>
+      <c r="AH162" s="12" t="n"/>
+      <c r="AI162" s="12" t="n"/>
+      <c r="AJ162" s="12" t="n"/>
+      <c r="AK162" s="12" t="n"/>
+      <c r="AL162" s="12" t="n"/>
+      <c r="AM162" s="12" t="n"/>
+      <c r="AN162" s="12" t="n"/>
+      <c r="AO162" s="12" t="n"/>
+      <c r="AP162" s="12" t="n"/>
     </row>
     <row r="163" ht="22" customHeight="1">
       <c r="A163" s="9" t="n"/>
@@ -9720,6 +11380,16 @@
       <c r="AD163" s="10" t="n"/>
       <c r="AE163" s="10" t="n"/>
       <c r="AF163" s="10" t="n"/>
+      <c r="AG163" s="10" t="n"/>
+      <c r="AH163" s="10" t="n"/>
+      <c r="AI163" s="10" t="n"/>
+      <c r="AJ163" s="10" t="n"/>
+      <c r="AK163" s="10" t="n"/>
+      <c r="AL163" s="10" t="n"/>
+      <c r="AM163" s="10" t="n"/>
+      <c r="AN163" s="10" t="n"/>
+      <c r="AO163" s="10" t="n"/>
+      <c r="AP163" s="10" t="n"/>
     </row>
     <row r="164" ht="22" customHeight="1">
       <c r="A164" s="11" t="n"/>
@@ -9754,6 +11424,16 @@
       <c r="AD164" s="12" t="n"/>
       <c r="AE164" s="12" t="n"/>
       <c r="AF164" s="12" t="n"/>
+      <c r="AG164" s="12" t="n"/>
+      <c r="AH164" s="12" t="n"/>
+      <c r="AI164" s="12" t="n"/>
+      <c r="AJ164" s="12" t="n"/>
+      <c r="AK164" s="12" t="n"/>
+      <c r="AL164" s="12" t="n"/>
+      <c r="AM164" s="12" t="n"/>
+      <c r="AN164" s="12" t="n"/>
+      <c r="AO164" s="12" t="n"/>
+      <c r="AP164" s="12" t="n"/>
     </row>
     <row r="165" ht="22" customHeight="1">
       <c r="A165" s="9" t="n"/>
@@ -9788,6 +11468,16 @@
       <c r="AD165" s="10" t="n"/>
       <c r="AE165" s="10" t="n"/>
       <c r="AF165" s="10" t="n"/>
+      <c r="AG165" s="10" t="n"/>
+      <c r="AH165" s="10" t="n"/>
+      <c r="AI165" s="10" t="n"/>
+      <c r="AJ165" s="10" t="n"/>
+      <c r="AK165" s="10" t="n"/>
+      <c r="AL165" s="10" t="n"/>
+      <c r="AM165" s="10" t="n"/>
+      <c r="AN165" s="10" t="n"/>
+      <c r="AO165" s="10" t="n"/>
+      <c r="AP165" s="10" t="n"/>
     </row>
     <row r="166" ht="22" customHeight="1">
       <c r="A166" s="11" t="n"/>
@@ -9822,6 +11512,16 @@
       <c r="AD166" s="12" t="n"/>
       <c r="AE166" s="12" t="n"/>
       <c r="AF166" s="12" t="n"/>
+      <c r="AG166" s="12" t="n"/>
+      <c r="AH166" s="12" t="n"/>
+      <c r="AI166" s="12" t="n"/>
+      <c r="AJ166" s="12" t="n"/>
+      <c r="AK166" s="12" t="n"/>
+      <c r="AL166" s="12" t="n"/>
+      <c r="AM166" s="12" t="n"/>
+      <c r="AN166" s="12" t="n"/>
+      <c r="AO166" s="12" t="n"/>
+      <c r="AP166" s="12" t="n"/>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="9" t="n"/>
@@ -9856,6 +11556,16 @@
       <c r="AD167" s="10" t="n"/>
       <c r="AE167" s="10" t="n"/>
       <c r="AF167" s="10" t="n"/>
+      <c r="AG167" s="10" t="n"/>
+      <c r="AH167" s="10" t="n"/>
+      <c r="AI167" s="10" t="n"/>
+      <c r="AJ167" s="10" t="n"/>
+      <c r="AK167" s="10" t="n"/>
+      <c r="AL167" s="10" t="n"/>
+      <c r="AM167" s="10" t="n"/>
+      <c r="AN167" s="10" t="n"/>
+      <c r="AO167" s="10" t="n"/>
+      <c r="AP167" s="10" t="n"/>
     </row>
     <row r="168" ht="22" customHeight="1">
       <c r="A168" s="11" t="n"/>
@@ -9890,6 +11600,16 @@
       <c r="AD168" s="12" t="n"/>
       <c r="AE168" s="12" t="n"/>
       <c r="AF168" s="12" t="n"/>
+      <c r="AG168" s="12" t="n"/>
+      <c r="AH168" s="12" t="n"/>
+      <c r="AI168" s="12" t="n"/>
+      <c r="AJ168" s="12" t="n"/>
+      <c r="AK168" s="12" t="n"/>
+      <c r="AL168" s="12" t="n"/>
+      <c r="AM168" s="12" t="n"/>
+      <c r="AN168" s="12" t="n"/>
+      <c r="AO168" s="12" t="n"/>
+      <c r="AP168" s="12" t="n"/>
     </row>
     <row r="169" ht="22" customHeight="1">
       <c r="A169" s="9" t="n"/>
@@ -9924,6 +11644,16 @@
       <c r="AD169" s="10" t="n"/>
       <c r="AE169" s="10" t="n"/>
       <c r="AF169" s="10" t="n"/>
+      <c r="AG169" s="10" t="n"/>
+      <c r="AH169" s="10" t="n"/>
+      <c r="AI169" s="10" t="n"/>
+      <c r="AJ169" s="10" t="n"/>
+      <c r="AK169" s="10" t="n"/>
+      <c r="AL169" s="10" t="n"/>
+      <c r="AM169" s="10" t="n"/>
+      <c r="AN169" s="10" t="n"/>
+      <c r="AO169" s="10" t="n"/>
+      <c r="AP169" s="10" t="n"/>
     </row>
     <row r="170" ht="22" customHeight="1">
       <c r="A170" s="11" t="n"/>
@@ -9958,6 +11688,16 @@
       <c r="AD170" s="12" t="n"/>
       <c r="AE170" s="12" t="n"/>
       <c r="AF170" s="12" t="n"/>
+      <c r="AG170" s="12" t="n"/>
+      <c r="AH170" s="12" t="n"/>
+      <c r="AI170" s="12" t="n"/>
+      <c r="AJ170" s="12" t="n"/>
+      <c r="AK170" s="12" t="n"/>
+      <c r="AL170" s="12" t="n"/>
+      <c r="AM170" s="12" t="n"/>
+      <c r="AN170" s="12" t="n"/>
+      <c r="AO170" s="12" t="n"/>
+      <c r="AP170" s="12" t="n"/>
     </row>
     <row r="171" ht="22" customHeight="1">
       <c r="A171" s="9" t="n"/>
@@ -9992,6 +11732,16 @@
       <c r="AD171" s="10" t="n"/>
       <c r="AE171" s="10" t="n"/>
       <c r="AF171" s="10" t="n"/>
+      <c r="AG171" s="10" t="n"/>
+      <c r="AH171" s="10" t="n"/>
+      <c r="AI171" s="10" t="n"/>
+      <c r="AJ171" s="10" t="n"/>
+      <c r="AK171" s="10" t="n"/>
+      <c r="AL171" s="10" t="n"/>
+      <c r="AM171" s="10" t="n"/>
+      <c r="AN171" s="10" t="n"/>
+      <c r="AO171" s="10" t="n"/>
+      <c r="AP171" s="10" t="n"/>
     </row>
     <row r="172" ht="22" customHeight="1">
       <c r="A172" s="11" t="n"/>
@@ -10026,6 +11776,16 @@
       <c r="AD172" s="12" t="n"/>
       <c r="AE172" s="12" t="n"/>
       <c r="AF172" s="12" t="n"/>
+      <c r="AG172" s="12" t="n"/>
+      <c r="AH172" s="12" t="n"/>
+      <c r="AI172" s="12" t="n"/>
+      <c r="AJ172" s="12" t="n"/>
+      <c r="AK172" s="12" t="n"/>
+      <c r="AL172" s="12" t="n"/>
+      <c r="AM172" s="12" t="n"/>
+      <c r="AN172" s="12" t="n"/>
+      <c r="AO172" s="12" t="n"/>
+      <c r="AP172" s="12" t="n"/>
     </row>
     <row r="173" ht="22" customHeight="1">
       <c r="A173" s="9" t="n"/>
@@ -10060,6 +11820,16 @@
       <c r="AD173" s="10" t="n"/>
       <c r="AE173" s="10" t="n"/>
       <c r="AF173" s="10" t="n"/>
+      <c r="AG173" s="10" t="n"/>
+      <c r="AH173" s="10" t="n"/>
+      <c r="AI173" s="10" t="n"/>
+      <c r="AJ173" s="10" t="n"/>
+      <c r="AK173" s="10" t="n"/>
+      <c r="AL173" s="10" t="n"/>
+      <c r="AM173" s="10" t="n"/>
+      <c r="AN173" s="10" t="n"/>
+      <c r="AO173" s="10" t="n"/>
+      <c r="AP173" s="10" t="n"/>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="11" t="n"/>
@@ -10094,6 +11864,16 @@
       <c r="AD174" s="12" t="n"/>
       <c r="AE174" s="12" t="n"/>
       <c r="AF174" s="12" t="n"/>
+      <c r="AG174" s="12" t="n"/>
+      <c r="AH174" s="12" t="n"/>
+      <c r="AI174" s="12" t="n"/>
+      <c r="AJ174" s="12" t="n"/>
+      <c r="AK174" s="12" t="n"/>
+      <c r="AL174" s="12" t="n"/>
+      <c r="AM174" s="12" t="n"/>
+      <c r="AN174" s="12" t="n"/>
+      <c r="AO174" s="12" t="n"/>
+      <c r="AP174" s="12" t="n"/>
     </row>
     <row r="175" ht="22" customHeight="1">
       <c r="A175" s="9" t="n"/>
@@ -10128,6 +11908,16 @@
       <c r="AD175" s="10" t="n"/>
       <c r="AE175" s="10" t="n"/>
       <c r="AF175" s="10" t="n"/>
+      <c r="AG175" s="10" t="n"/>
+      <c r="AH175" s="10" t="n"/>
+      <c r="AI175" s="10" t="n"/>
+      <c r="AJ175" s="10" t="n"/>
+      <c r="AK175" s="10" t="n"/>
+      <c r="AL175" s="10" t="n"/>
+      <c r="AM175" s="10" t="n"/>
+      <c r="AN175" s="10" t="n"/>
+      <c r="AO175" s="10" t="n"/>
+      <c r="AP175" s="10" t="n"/>
     </row>
     <row r="176" ht="22" customHeight="1">
       <c r="A176" s="11" t="n"/>
@@ -10162,6 +11952,16 @@
       <c r="AD176" s="12" t="n"/>
       <c r="AE176" s="12" t="n"/>
       <c r="AF176" s="12" t="n"/>
+      <c r="AG176" s="12" t="n"/>
+      <c r="AH176" s="12" t="n"/>
+      <c r="AI176" s="12" t="n"/>
+      <c r="AJ176" s="12" t="n"/>
+      <c r="AK176" s="12" t="n"/>
+      <c r="AL176" s="12" t="n"/>
+      <c r="AM176" s="12" t="n"/>
+      <c r="AN176" s="12" t="n"/>
+      <c r="AO176" s="12" t="n"/>
+      <c r="AP176" s="12" t="n"/>
     </row>
     <row r="177" ht="22" customHeight="1">
       <c r="A177" s="9" t="n"/>
@@ -10196,6 +11996,16 @@
       <c r="AD177" s="10" t="n"/>
       <c r="AE177" s="10" t="n"/>
       <c r="AF177" s="10" t="n"/>
+      <c r="AG177" s="10" t="n"/>
+      <c r="AH177" s="10" t="n"/>
+      <c r="AI177" s="10" t="n"/>
+      <c r="AJ177" s="10" t="n"/>
+      <c r="AK177" s="10" t="n"/>
+      <c r="AL177" s="10" t="n"/>
+      <c r="AM177" s="10" t="n"/>
+      <c r="AN177" s="10" t="n"/>
+      <c r="AO177" s="10" t="n"/>
+      <c r="AP177" s="10" t="n"/>
     </row>
     <row r="178" ht="22" customHeight="1">
       <c r="A178" s="11" t="n"/>
@@ -10230,6 +12040,16 @@
       <c r="AD178" s="12" t="n"/>
       <c r="AE178" s="12" t="n"/>
       <c r="AF178" s="12" t="n"/>
+      <c r="AG178" s="12" t="n"/>
+      <c r="AH178" s="12" t="n"/>
+      <c r="AI178" s="12" t="n"/>
+      <c r="AJ178" s="12" t="n"/>
+      <c r="AK178" s="12" t="n"/>
+      <c r="AL178" s="12" t="n"/>
+      <c r="AM178" s="12" t="n"/>
+      <c r="AN178" s="12" t="n"/>
+      <c r="AO178" s="12" t="n"/>
+      <c r="AP178" s="12" t="n"/>
     </row>
     <row r="179" ht="22" customHeight="1">
       <c r="A179" s="9" t="n"/>
@@ -10264,6 +12084,16 @@
       <c r="AD179" s="10" t="n"/>
       <c r="AE179" s="10" t="n"/>
       <c r="AF179" s="10" t="n"/>
+      <c r="AG179" s="10" t="n"/>
+      <c r="AH179" s="10" t="n"/>
+      <c r="AI179" s="10" t="n"/>
+      <c r="AJ179" s="10" t="n"/>
+      <c r="AK179" s="10" t="n"/>
+      <c r="AL179" s="10" t="n"/>
+      <c r="AM179" s="10" t="n"/>
+      <c r="AN179" s="10" t="n"/>
+      <c r="AO179" s="10" t="n"/>
+      <c r="AP179" s="10" t="n"/>
     </row>
     <row r="180" ht="22" customHeight="1">
       <c r="A180" s="11" t="n"/>
@@ -10298,6 +12128,16 @@
       <c r="AD180" s="12" t="n"/>
       <c r="AE180" s="12" t="n"/>
       <c r="AF180" s="12" t="n"/>
+      <c r="AG180" s="12" t="n"/>
+      <c r="AH180" s="12" t="n"/>
+      <c r="AI180" s="12" t="n"/>
+      <c r="AJ180" s="12" t="n"/>
+      <c r="AK180" s="12" t="n"/>
+      <c r="AL180" s="12" t="n"/>
+      <c r="AM180" s="12" t="n"/>
+      <c r="AN180" s="12" t="n"/>
+      <c r="AO180" s="12" t="n"/>
+      <c r="AP180" s="12" t="n"/>
     </row>
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="9" t="n"/>
@@ -10332,6 +12172,16 @@
       <c r="AD181" s="10" t="n"/>
       <c r="AE181" s="10" t="n"/>
       <c r="AF181" s="10" t="n"/>
+      <c r="AG181" s="10" t="n"/>
+      <c r="AH181" s="10" t="n"/>
+      <c r="AI181" s="10" t="n"/>
+      <c r="AJ181" s="10" t="n"/>
+      <c r="AK181" s="10" t="n"/>
+      <c r="AL181" s="10" t="n"/>
+      <c r="AM181" s="10" t="n"/>
+      <c r="AN181" s="10" t="n"/>
+      <c r="AO181" s="10" t="n"/>
+      <c r="AP181" s="10" t="n"/>
     </row>
     <row r="182" ht="22" customHeight="1">
       <c r="A182" s="11" t="n"/>
@@ -10366,6 +12216,16 @@
       <c r="AD182" s="12" t="n"/>
       <c r="AE182" s="12" t="n"/>
       <c r="AF182" s="12" t="n"/>
+      <c r="AG182" s="12" t="n"/>
+      <c r="AH182" s="12" t="n"/>
+      <c r="AI182" s="12" t="n"/>
+      <c r="AJ182" s="12" t="n"/>
+      <c r="AK182" s="12" t="n"/>
+      <c r="AL182" s="12" t="n"/>
+      <c r="AM182" s="12" t="n"/>
+      <c r="AN182" s="12" t="n"/>
+      <c r="AO182" s="12" t="n"/>
+      <c r="AP182" s="12" t="n"/>
     </row>
     <row r="183" ht="22" customHeight="1">
       <c r="A183" s="9" t="n"/>
@@ -10400,6 +12260,16 @@
       <c r="AD183" s="10" t="n"/>
       <c r="AE183" s="10" t="n"/>
       <c r="AF183" s="10" t="n"/>
+      <c r="AG183" s="10" t="n"/>
+      <c r="AH183" s="10" t="n"/>
+      <c r="AI183" s="10" t="n"/>
+      <c r="AJ183" s="10" t="n"/>
+      <c r="AK183" s="10" t="n"/>
+      <c r="AL183" s="10" t="n"/>
+      <c r="AM183" s="10" t="n"/>
+      <c r="AN183" s="10" t="n"/>
+      <c r="AO183" s="10" t="n"/>
+      <c r="AP183" s="10" t="n"/>
     </row>
     <row r="184" ht="22" customHeight="1">
       <c r="A184" s="11" t="n"/>
@@ -10434,6 +12304,16 @@
       <c r="AD184" s="12" t="n"/>
       <c r="AE184" s="12" t="n"/>
       <c r="AF184" s="12" t="n"/>
+      <c r="AG184" s="12" t="n"/>
+      <c r="AH184" s="12" t="n"/>
+      <c r="AI184" s="12" t="n"/>
+      <c r="AJ184" s="12" t="n"/>
+      <c r="AK184" s="12" t="n"/>
+      <c r="AL184" s="12" t="n"/>
+      <c r="AM184" s="12" t="n"/>
+      <c r="AN184" s="12" t="n"/>
+      <c r="AO184" s="12" t="n"/>
+      <c r="AP184" s="12" t="n"/>
     </row>
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="9" t="n"/>
@@ -10468,6 +12348,16 @@
       <c r="AD185" s="10" t="n"/>
       <c r="AE185" s="10" t="n"/>
       <c r="AF185" s="10" t="n"/>
+      <c r="AG185" s="10" t="n"/>
+      <c r="AH185" s="10" t="n"/>
+      <c r="AI185" s="10" t="n"/>
+      <c r="AJ185" s="10" t="n"/>
+      <c r="AK185" s="10" t="n"/>
+      <c r="AL185" s="10" t="n"/>
+      <c r="AM185" s="10" t="n"/>
+      <c r="AN185" s="10" t="n"/>
+      <c r="AO185" s="10" t="n"/>
+      <c r="AP185" s="10" t="n"/>
     </row>
     <row r="186" ht="22" customHeight="1">
       <c r="A186" s="11" t="n"/>
@@ -10502,6 +12392,16 @@
       <c r="AD186" s="12" t="n"/>
       <c r="AE186" s="12" t="n"/>
       <c r="AF186" s="12" t="n"/>
+      <c r="AG186" s="12" t="n"/>
+      <c r="AH186" s="12" t="n"/>
+      <c r="AI186" s="12" t="n"/>
+      <c r="AJ186" s="12" t="n"/>
+      <c r="AK186" s="12" t="n"/>
+      <c r="AL186" s="12" t="n"/>
+      <c r="AM186" s="12" t="n"/>
+      <c r="AN186" s="12" t="n"/>
+      <c r="AO186" s="12" t="n"/>
+      <c r="AP186" s="12" t="n"/>
     </row>
     <row r="187" ht="22" customHeight="1">
       <c r="A187" s="9" t="n"/>
@@ -10536,6 +12436,16 @@
       <c r="AD187" s="10" t="n"/>
       <c r="AE187" s="10" t="n"/>
       <c r="AF187" s="10" t="n"/>
+      <c r="AG187" s="10" t="n"/>
+      <c r="AH187" s="10" t="n"/>
+      <c r="AI187" s="10" t="n"/>
+      <c r="AJ187" s="10" t="n"/>
+      <c r="AK187" s="10" t="n"/>
+      <c r="AL187" s="10" t="n"/>
+      <c r="AM187" s="10" t="n"/>
+      <c r="AN187" s="10" t="n"/>
+      <c r="AO187" s="10" t="n"/>
+      <c r="AP187" s="10" t="n"/>
     </row>
     <row r="188" ht="22" customHeight="1">
       <c r="A188" s="11" t="n"/>
@@ -10570,6 +12480,16 @@
       <c r="AD188" s="12" t="n"/>
       <c r="AE188" s="12" t="n"/>
       <c r="AF188" s="12" t="n"/>
+      <c r="AG188" s="12" t="n"/>
+      <c r="AH188" s="12" t="n"/>
+      <c r="AI188" s="12" t="n"/>
+      <c r="AJ188" s="12" t="n"/>
+      <c r="AK188" s="12" t="n"/>
+      <c r="AL188" s="12" t="n"/>
+      <c r="AM188" s="12" t="n"/>
+      <c r="AN188" s="12" t="n"/>
+      <c r="AO188" s="12" t="n"/>
+      <c r="AP188" s="12" t="n"/>
     </row>
     <row r="189" ht="22" customHeight="1">
       <c r="A189" s="9" t="n"/>
@@ -10604,6 +12524,16 @@
       <c r="AD189" s="10" t="n"/>
       <c r="AE189" s="10" t="n"/>
       <c r="AF189" s="10" t="n"/>
+      <c r="AG189" s="10" t="n"/>
+      <c r="AH189" s="10" t="n"/>
+      <c r="AI189" s="10" t="n"/>
+      <c r="AJ189" s="10" t="n"/>
+      <c r="AK189" s="10" t="n"/>
+      <c r="AL189" s="10" t="n"/>
+      <c r="AM189" s="10" t="n"/>
+      <c r="AN189" s="10" t="n"/>
+      <c r="AO189" s="10" t="n"/>
+      <c r="AP189" s="10" t="n"/>
     </row>
     <row r="190" ht="22" customHeight="1">
       <c r="A190" s="11" t="n"/>
@@ -10638,6 +12568,16 @@
       <c r="AD190" s="12" t="n"/>
       <c r="AE190" s="12" t="n"/>
       <c r="AF190" s="12" t="n"/>
+      <c r="AG190" s="12" t="n"/>
+      <c r="AH190" s="12" t="n"/>
+      <c r="AI190" s="12" t="n"/>
+      <c r="AJ190" s="12" t="n"/>
+      <c r="AK190" s="12" t="n"/>
+      <c r="AL190" s="12" t="n"/>
+      <c r="AM190" s="12" t="n"/>
+      <c r="AN190" s="12" t="n"/>
+      <c r="AO190" s="12" t="n"/>
+      <c r="AP190" s="12" t="n"/>
     </row>
     <row r="191" ht="22" customHeight="1">
       <c r="A191" s="9" t="n"/>
@@ -10672,6 +12612,16 @@
       <c r="AD191" s="10" t="n"/>
       <c r="AE191" s="10" t="n"/>
       <c r="AF191" s="10" t="n"/>
+      <c r="AG191" s="10" t="n"/>
+      <c r="AH191" s="10" t="n"/>
+      <c r="AI191" s="10" t="n"/>
+      <c r="AJ191" s="10" t="n"/>
+      <c r="AK191" s="10" t="n"/>
+      <c r="AL191" s="10" t="n"/>
+      <c r="AM191" s="10" t="n"/>
+      <c r="AN191" s="10" t="n"/>
+      <c r="AO191" s="10" t="n"/>
+      <c r="AP191" s="10" t="n"/>
     </row>
     <row r="192" ht="22" customHeight="1">
       <c r="A192" s="11" t="n"/>
@@ -10706,6 +12656,16 @@
       <c r="AD192" s="12" t="n"/>
       <c r="AE192" s="12" t="n"/>
       <c r="AF192" s="12" t="n"/>
+      <c r="AG192" s="12" t="n"/>
+      <c r="AH192" s="12" t="n"/>
+      <c r="AI192" s="12" t="n"/>
+      <c r="AJ192" s="12" t="n"/>
+      <c r="AK192" s="12" t="n"/>
+      <c r="AL192" s="12" t="n"/>
+      <c r="AM192" s="12" t="n"/>
+      <c r="AN192" s="12" t="n"/>
+      <c r="AO192" s="12" t="n"/>
+      <c r="AP192" s="12" t="n"/>
     </row>
     <row r="193" ht="22" customHeight="1">
       <c r="A193" s="9" t="n"/>
@@ -10740,6 +12700,16 @@
       <c r="AD193" s="10" t="n"/>
       <c r="AE193" s="10" t="n"/>
       <c r="AF193" s="10" t="n"/>
+      <c r="AG193" s="10" t="n"/>
+      <c r="AH193" s="10" t="n"/>
+      <c r="AI193" s="10" t="n"/>
+      <c r="AJ193" s="10" t="n"/>
+      <c r="AK193" s="10" t="n"/>
+      <c r="AL193" s="10" t="n"/>
+      <c r="AM193" s="10" t="n"/>
+      <c r="AN193" s="10" t="n"/>
+      <c r="AO193" s="10" t="n"/>
+      <c r="AP193" s="10" t="n"/>
     </row>
     <row r="194" ht="22" customHeight="1">
       <c r="A194" s="11" t="n"/>
@@ -10774,6 +12744,16 @@
       <c r="AD194" s="12" t="n"/>
       <c r="AE194" s="12" t="n"/>
       <c r="AF194" s="12" t="n"/>
+      <c r="AG194" s="12" t="n"/>
+      <c r="AH194" s="12" t="n"/>
+      <c r="AI194" s="12" t="n"/>
+      <c r="AJ194" s="12" t="n"/>
+      <c r="AK194" s="12" t="n"/>
+      <c r="AL194" s="12" t="n"/>
+      <c r="AM194" s="12" t="n"/>
+      <c r="AN194" s="12" t="n"/>
+      <c r="AO194" s="12" t="n"/>
+      <c r="AP194" s="12" t="n"/>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="9" t="n"/>
@@ -10808,6 +12788,16 @@
       <c r="AD195" s="10" t="n"/>
       <c r="AE195" s="10" t="n"/>
       <c r="AF195" s="10" t="n"/>
+      <c r="AG195" s="10" t="n"/>
+      <c r="AH195" s="10" t="n"/>
+      <c r="AI195" s="10" t="n"/>
+      <c r="AJ195" s="10" t="n"/>
+      <c r="AK195" s="10" t="n"/>
+      <c r="AL195" s="10" t="n"/>
+      <c r="AM195" s="10" t="n"/>
+      <c r="AN195" s="10" t="n"/>
+      <c r="AO195" s="10" t="n"/>
+      <c r="AP195" s="10" t="n"/>
     </row>
     <row r="196" ht="22" customHeight="1">
       <c r="A196" s="11" t="n"/>
@@ -10842,6 +12832,16 @@
       <c r="AD196" s="12" t="n"/>
       <c r="AE196" s="12" t="n"/>
       <c r="AF196" s="12" t="n"/>
+      <c r="AG196" s="12" t="n"/>
+      <c r="AH196" s="12" t="n"/>
+      <c r="AI196" s="12" t="n"/>
+      <c r="AJ196" s="12" t="n"/>
+      <c r="AK196" s="12" t="n"/>
+      <c r="AL196" s="12" t="n"/>
+      <c r="AM196" s="12" t="n"/>
+      <c r="AN196" s="12" t="n"/>
+      <c r="AO196" s="12" t="n"/>
+      <c r="AP196" s="12" t="n"/>
     </row>
     <row r="197" ht="22" customHeight="1">
       <c r="A197" s="9" t="n"/>
@@ -10876,6 +12876,16 @@
       <c r="AD197" s="10" t="n"/>
       <c r="AE197" s="10" t="n"/>
       <c r="AF197" s="10" t="n"/>
+      <c r="AG197" s="10" t="n"/>
+      <c r="AH197" s="10" t="n"/>
+      <c r="AI197" s="10" t="n"/>
+      <c r="AJ197" s="10" t="n"/>
+      <c r="AK197" s="10" t="n"/>
+      <c r="AL197" s="10" t="n"/>
+      <c r="AM197" s="10" t="n"/>
+      <c r="AN197" s="10" t="n"/>
+      <c r="AO197" s="10" t="n"/>
+      <c r="AP197" s="10" t="n"/>
     </row>
     <row r="198" ht="22" customHeight="1">
       <c r="A198" s="11" t="n"/>
@@ -10910,6 +12920,16 @@
       <c r="AD198" s="12" t="n"/>
       <c r="AE198" s="12" t="n"/>
       <c r="AF198" s="12" t="n"/>
+      <c r="AG198" s="12" t="n"/>
+      <c r="AH198" s="12" t="n"/>
+      <c r="AI198" s="12" t="n"/>
+      <c r="AJ198" s="12" t="n"/>
+      <c r="AK198" s="12" t="n"/>
+      <c r="AL198" s="12" t="n"/>
+      <c r="AM198" s="12" t="n"/>
+      <c r="AN198" s="12" t="n"/>
+      <c r="AO198" s="12" t="n"/>
+      <c r="AP198" s="12" t="n"/>
     </row>
     <row r="199" ht="22" customHeight="1">
       <c r="A199" s="9" t="n"/>
@@ -10944,6 +12964,16 @@
       <c r="AD199" s="10" t="n"/>
       <c r="AE199" s="10" t="n"/>
       <c r="AF199" s="10" t="n"/>
+      <c r="AG199" s="10" t="n"/>
+      <c r="AH199" s="10" t="n"/>
+      <c r="AI199" s="10" t="n"/>
+      <c r="AJ199" s="10" t="n"/>
+      <c r="AK199" s="10" t="n"/>
+      <c r="AL199" s="10" t="n"/>
+      <c r="AM199" s="10" t="n"/>
+      <c r="AN199" s="10" t="n"/>
+      <c r="AO199" s="10" t="n"/>
+      <c r="AP199" s="10" t="n"/>
     </row>
     <row r="200" ht="22" customHeight="1">
       <c r="A200" s="11" t="n"/>
@@ -10978,6 +13008,16 @@
       <c r="AD200" s="12" t="n"/>
       <c r="AE200" s="12" t="n"/>
       <c r="AF200" s="12" t="n"/>
+      <c r="AG200" s="12" t="n"/>
+      <c r="AH200" s="12" t="n"/>
+      <c r="AI200" s="12" t="n"/>
+      <c r="AJ200" s="12" t="n"/>
+      <c r="AK200" s="12" t="n"/>
+      <c r="AL200" s="12" t="n"/>
+      <c r="AM200" s="12" t="n"/>
+      <c r="AN200" s="12" t="n"/>
+      <c r="AO200" s="12" t="n"/>
+      <c r="AP200" s="12" t="n"/>
     </row>
     <row r="201" ht="22" customHeight="1">
       <c r="A201" s="9" t="n"/>
@@ -11012,6 +13052,16 @@
       <c r="AD201" s="10" t="n"/>
       <c r="AE201" s="10" t="n"/>
       <c r="AF201" s="10" t="n"/>
+      <c r="AG201" s="10" t="n"/>
+      <c r="AH201" s="10" t="n"/>
+      <c r="AI201" s="10" t="n"/>
+      <c r="AJ201" s="10" t="n"/>
+      <c r="AK201" s="10" t="n"/>
+      <c r="AL201" s="10" t="n"/>
+      <c r="AM201" s="10" t="n"/>
+      <c r="AN201" s="10" t="n"/>
+      <c r="AO201" s="10" t="n"/>
+      <c r="AP201" s="10" t="n"/>
     </row>
     <row r="202" ht="22" customHeight="1">
       <c r="A202" s="11" t="n"/>
@@ -11046,6 +13096,16 @@
       <c r="AD202" s="12" t="n"/>
       <c r="AE202" s="12" t="n"/>
       <c r="AF202" s="12" t="n"/>
+      <c r="AG202" s="12" t="n"/>
+      <c r="AH202" s="12" t="n"/>
+      <c r="AI202" s="12" t="n"/>
+      <c r="AJ202" s="12" t="n"/>
+      <c r="AK202" s="12" t="n"/>
+      <c r="AL202" s="12" t="n"/>
+      <c r="AM202" s="12" t="n"/>
+      <c r="AN202" s="12" t="n"/>
+      <c r="AO202" s="12" t="n"/>
+      <c r="AP202" s="12" t="n"/>
     </row>
     <row r="203" ht="22" customHeight="1">
       <c r="A203" s="9" t="n"/>
@@ -11080,6 +13140,16 @@
       <c r="AD203" s="10" t="n"/>
       <c r="AE203" s="10" t="n"/>
       <c r="AF203" s="10" t="n"/>
+      <c r="AG203" s="10" t="n"/>
+      <c r="AH203" s="10" t="n"/>
+      <c r="AI203" s="10" t="n"/>
+      <c r="AJ203" s="10" t="n"/>
+      <c r="AK203" s="10" t="n"/>
+      <c r="AL203" s="10" t="n"/>
+      <c r="AM203" s="10" t="n"/>
+      <c r="AN203" s="10" t="n"/>
+      <c r="AO203" s="10" t="n"/>
+      <c r="AP203" s="10" t="n"/>
     </row>
     <row r="204" ht="22" customHeight="1">
       <c r="A204" s="11" t="n"/>
@@ -11114,6 +13184,16 @@
       <c r="AD204" s="12" t="n"/>
       <c r="AE204" s="12" t="n"/>
       <c r="AF204" s="12" t="n"/>
+      <c r="AG204" s="12" t="n"/>
+      <c r="AH204" s="12" t="n"/>
+      <c r="AI204" s="12" t="n"/>
+      <c r="AJ204" s="12" t="n"/>
+      <c r="AK204" s="12" t="n"/>
+      <c r="AL204" s="12" t="n"/>
+      <c r="AM204" s="12" t="n"/>
+      <c r="AN204" s="12" t="n"/>
+      <c r="AO204" s="12" t="n"/>
+      <c r="AP204" s="12" t="n"/>
     </row>
     <row r="205" ht="22" customHeight="1">
       <c r="A205" s="9" t="n"/>
@@ -11148,6 +13228,16 @@
       <c r="AD205" s="10" t="n"/>
       <c r="AE205" s="10" t="n"/>
       <c r="AF205" s="10" t="n"/>
+      <c r="AG205" s="10" t="n"/>
+      <c r="AH205" s="10" t="n"/>
+      <c r="AI205" s="10" t="n"/>
+      <c r="AJ205" s="10" t="n"/>
+      <c r="AK205" s="10" t="n"/>
+      <c r="AL205" s="10" t="n"/>
+      <c r="AM205" s="10" t="n"/>
+      <c r="AN205" s="10" t="n"/>
+      <c r="AO205" s="10" t="n"/>
+      <c r="AP205" s="10" t="n"/>
     </row>
     <row r="206" ht="22" customHeight="1">
       <c r="A206" s="11" t="n"/>
@@ -11182,6 +13272,16 @@
       <c r="AD206" s="12" t="n"/>
       <c r="AE206" s="12" t="n"/>
       <c r="AF206" s="12" t="n"/>
+      <c r="AG206" s="12" t="n"/>
+      <c r="AH206" s="12" t="n"/>
+      <c r="AI206" s="12" t="n"/>
+      <c r="AJ206" s="12" t="n"/>
+      <c r="AK206" s="12" t="n"/>
+      <c r="AL206" s="12" t="n"/>
+      <c r="AM206" s="12" t="n"/>
+      <c r="AN206" s="12" t="n"/>
+      <c r="AO206" s="12" t="n"/>
+      <c r="AP206" s="12" t="n"/>
     </row>
     <row r="207" ht="22" customHeight="1">
       <c r="A207" s="9" t="n"/>
@@ -11216,6 +13316,16 @@
       <c r="AD207" s="10" t="n"/>
       <c r="AE207" s="10" t="n"/>
       <c r="AF207" s="10" t="n"/>
+      <c r="AG207" s="10" t="n"/>
+      <c r="AH207" s="10" t="n"/>
+      <c r="AI207" s="10" t="n"/>
+      <c r="AJ207" s="10" t="n"/>
+      <c r="AK207" s="10" t="n"/>
+      <c r="AL207" s="10" t="n"/>
+      <c r="AM207" s="10" t="n"/>
+      <c r="AN207" s="10" t="n"/>
+      <c r="AO207" s="10" t="n"/>
+      <c r="AP207" s="10" t="n"/>
     </row>
     <row r="208" ht="22" customHeight="1">
       <c r="A208" s="11" t="n"/>
@@ -11250,6 +13360,16 @@
       <c r="AD208" s="12" t="n"/>
       <c r="AE208" s="12" t="n"/>
       <c r="AF208" s="12" t="n"/>
+      <c r="AG208" s="12" t="n"/>
+      <c r="AH208" s="12" t="n"/>
+      <c r="AI208" s="12" t="n"/>
+      <c r="AJ208" s="12" t="n"/>
+      <c r="AK208" s="12" t="n"/>
+      <c r="AL208" s="12" t="n"/>
+      <c r="AM208" s="12" t="n"/>
+      <c r="AN208" s="12" t="n"/>
+      <c r="AO208" s="12" t="n"/>
+      <c r="AP208" s="12" t="n"/>
     </row>
     <row r="209" ht="22" customHeight="1">
       <c r="A209" s="9" t="n"/>
@@ -11284,6 +13404,16 @@
       <c r="AD209" s="10" t="n"/>
       <c r="AE209" s="10" t="n"/>
       <c r="AF209" s="10" t="n"/>
+      <c r="AG209" s="10" t="n"/>
+      <c r="AH209" s="10" t="n"/>
+      <c r="AI209" s="10" t="n"/>
+      <c r="AJ209" s="10" t="n"/>
+      <c r="AK209" s="10" t="n"/>
+      <c r="AL209" s="10" t="n"/>
+      <c r="AM209" s="10" t="n"/>
+      <c r="AN209" s="10" t="n"/>
+      <c r="AO209" s="10" t="n"/>
+      <c r="AP209" s="10" t="n"/>
     </row>
     <row r="210" ht="22" customHeight="1">
       <c r="A210" s="11" t="n"/>
@@ -11318,6 +13448,16 @@
       <c r="AD210" s="12" t="n"/>
       <c r="AE210" s="12" t="n"/>
       <c r="AF210" s="12" t="n"/>
+      <c r="AG210" s="12" t="n"/>
+      <c r="AH210" s="12" t="n"/>
+      <c r="AI210" s="12" t="n"/>
+      <c r="AJ210" s="12" t="n"/>
+      <c r="AK210" s="12" t="n"/>
+      <c r="AL210" s="12" t="n"/>
+      <c r="AM210" s="12" t="n"/>
+      <c r="AN210" s="12" t="n"/>
+      <c r="AO210" s="12" t="n"/>
+      <c r="AP210" s="12" t="n"/>
     </row>
     <row r="211" ht="22" customHeight="1">
       <c r="A211" s="9" t="n"/>
@@ -11352,6 +13492,16 @@
       <c r="AD211" s="10" t="n"/>
       <c r="AE211" s="10" t="n"/>
       <c r="AF211" s="10" t="n"/>
+      <c r="AG211" s="10" t="n"/>
+      <c r="AH211" s="10" t="n"/>
+      <c r="AI211" s="10" t="n"/>
+      <c r="AJ211" s="10" t="n"/>
+      <c r="AK211" s="10" t="n"/>
+      <c r="AL211" s="10" t="n"/>
+      <c r="AM211" s="10" t="n"/>
+      <c r="AN211" s="10" t="n"/>
+      <c r="AO211" s="10" t="n"/>
+      <c r="AP211" s="10" t="n"/>
     </row>
     <row r="212" ht="22" customHeight="1">
       <c r="A212" s="11" t="n"/>
@@ -11386,6 +13536,16 @@
       <c r="AD212" s="12" t="n"/>
       <c r="AE212" s="12" t="n"/>
       <c r="AF212" s="12" t="n"/>
+      <c r="AG212" s="12" t="n"/>
+      <c r="AH212" s="12" t="n"/>
+      <c r="AI212" s="12" t="n"/>
+      <c r="AJ212" s="12" t="n"/>
+      <c r="AK212" s="12" t="n"/>
+      <c r="AL212" s="12" t="n"/>
+      <c r="AM212" s="12" t="n"/>
+      <c r="AN212" s="12" t="n"/>
+      <c r="AO212" s="12" t="n"/>
+      <c r="AP212" s="12" t="n"/>
     </row>
     <row r="213" ht="22" customHeight="1">
       <c r="A213" s="9" t="n"/>
@@ -11420,6 +13580,16 @@
       <c r="AD213" s="10" t="n"/>
       <c r="AE213" s="10" t="n"/>
       <c r="AF213" s="10" t="n"/>
+      <c r="AG213" s="10" t="n"/>
+      <c r="AH213" s="10" t="n"/>
+      <c r="AI213" s="10" t="n"/>
+      <c r="AJ213" s="10" t="n"/>
+      <c r="AK213" s="10" t="n"/>
+      <c r="AL213" s="10" t="n"/>
+      <c r="AM213" s="10" t="n"/>
+      <c r="AN213" s="10" t="n"/>
+      <c r="AO213" s="10" t="n"/>
+      <c r="AP213" s="10" t="n"/>
     </row>
     <row r="214" ht="22" customHeight="1">
       <c r="A214" s="11" t="n"/>
@@ -11454,6 +13624,16 @@
       <c r="AD214" s="12" t="n"/>
       <c r="AE214" s="12" t="n"/>
       <c r="AF214" s="12" t="n"/>
+      <c r="AG214" s="12" t="n"/>
+      <c r="AH214" s="12" t="n"/>
+      <c r="AI214" s="12" t="n"/>
+      <c r="AJ214" s="12" t="n"/>
+      <c r="AK214" s="12" t="n"/>
+      <c r="AL214" s="12" t="n"/>
+      <c r="AM214" s="12" t="n"/>
+      <c r="AN214" s="12" t="n"/>
+      <c r="AO214" s="12" t="n"/>
+      <c r="AP214" s="12" t="n"/>
     </row>
     <row r="215" ht="22" customHeight="1">
       <c r="A215" s="9" t="n"/>
@@ -11488,6 +13668,16 @@
       <c r="AD215" s="10" t="n"/>
       <c r="AE215" s="10" t="n"/>
       <c r="AF215" s="10" t="n"/>
+      <c r="AG215" s="10" t="n"/>
+      <c r="AH215" s="10" t="n"/>
+      <c r="AI215" s="10" t="n"/>
+      <c r="AJ215" s="10" t="n"/>
+      <c r="AK215" s="10" t="n"/>
+      <c r="AL215" s="10" t="n"/>
+      <c r="AM215" s="10" t="n"/>
+      <c r="AN215" s="10" t="n"/>
+      <c r="AO215" s="10" t="n"/>
+      <c r="AP215" s="10" t="n"/>
     </row>
     <row r="216" ht="22" customHeight="1">
       <c r="A216" s="11" t="n"/>
@@ -11522,6 +13712,16 @@
       <c r="AD216" s="12" t="n"/>
       <c r="AE216" s="12" t="n"/>
       <c r="AF216" s="12" t="n"/>
+      <c r="AG216" s="12" t="n"/>
+      <c r="AH216" s="12" t="n"/>
+      <c r="AI216" s="12" t="n"/>
+      <c r="AJ216" s="12" t="n"/>
+      <c r="AK216" s="12" t="n"/>
+      <c r="AL216" s="12" t="n"/>
+      <c r="AM216" s="12" t="n"/>
+      <c r="AN216" s="12" t="n"/>
+      <c r="AO216" s="12" t="n"/>
+      <c r="AP216" s="12" t="n"/>
     </row>
     <row r="217" ht="22" customHeight="1">
       <c r="A217" s="9" t="n"/>
@@ -11556,6 +13756,16 @@
       <c r="AD217" s="10" t="n"/>
       <c r="AE217" s="10" t="n"/>
       <c r="AF217" s="10" t="n"/>
+      <c r="AG217" s="10" t="n"/>
+      <c r="AH217" s="10" t="n"/>
+      <c r="AI217" s="10" t="n"/>
+      <c r="AJ217" s="10" t="n"/>
+      <c r="AK217" s="10" t="n"/>
+      <c r="AL217" s="10" t="n"/>
+      <c r="AM217" s="10" t="n"/>
+      <c r="AN217" s="10" t="n"/>
+      <c r="AO217" s="10" t="n"/>
+      <c r="AP217" s="10" t="n"/>
     </row>
     <row r="218" ht="22" customHeight="1">
       <c r="A218" s="11" t="n"/>
@@ -11590,6 +13800,16 @@
       <c r="AD218" s="12" t="n"/>
       <c r="AE218" s="12" t="n"/>
       <c r="AF218" s="12" t="n"/>
+      <c r="AG218" s="12" t="n"/>
+      <c r="AH218" s="12" t="n"/>
+      <c r="AI218" s="12" t="n"/>
+      <c r="AJ218" s="12" t="n"/>
+      <c r="AK218" s="12" t="n"/>
+      <c r="AL218" s="12" t="n"/>
+      <c r="AM218" s="12" t="n"/>
+      <c r="AN218" s="12" t="n"/>
+      <c r="AO218" s="12" t="n"/>
+      <c r="AP218" s="12" t="n"/>
     </row>
     <row r="219" ht="22" customHeight="1">
       <c r="A219" s="9" t="n"/>
@@ -11624,6 +13844,16 @@
       <c r="AD219" s="10" t="n"/>
       <c r="AE219" s="10" t="n"/>
       <c r="AF219" s="10" t="n"/>
+      <c r="AG219" s="10" t="n"/>
+      <c r="AH219" s="10" t="n"/>
+      <c r="AI219" s="10" t="n"/>
+      <c r="AJ219" s="10" t="n"/>
+      <c r="AK219" s="10" t="n"/>
+      <c r="AL219" s="10" t="n"/>
+      <c r="AM219" s="10" t="n"/>
+      <c r="AN219" s="10" t="n"/>
+      <c r="AO219" s="10" t="n"/>
+      <c r="AP219" s="10" t="n"/>
     </row>
     <row r="220" ht="22" customHeight="1">
       <c r="A220" s="11" t="n"/>
@@ -11658,6 +13888,16 @@
       <c r="AD220" s="12" t="n"/>
       <c r="AE220" s="12" t="n"/>
       <c r="AF220" s="12" t="n"/>
+      <c r="AG220" s="12" t="n"/>
+      <c r="AH220" s="12" t="n"/>
+      <c r="AI220" s="12" t="n"/>
+      <c r="AJ220" s="12" t="n"/>
+      <c r="AK220" s="12" t="n"/>
+      <c r="AL220" s="12" t="n"/>
+      <c r="AM220" s="12" t="n"/>
+      <c r="AN220" s="12" t="n"/>
+      <c r="AO220" s="12" t="n"/>
+      <c r="AP220" s="12" t="n"/>
     </row>
     <row r="221" ht="22" customHeight="1">
       <c r="A221" s="9" t="n"/>
@@ -11692,6 +13932,16 @@
       <c r="AD221" s="10" t="n"/>
       <c r="AE221" s="10" t="n"/>
       <c r="AF221" s="10" t="n"/>
+      <c r="AG221" s="10" t="n"/>
+      <c r="AH221" s="10" t="n"/>
+      <c r="AI221" s="10" t="n"/>
+      <c r="AJ221" s="10" t="n"/>
+      <c r="AK221" s="10" t="n"/>
+      <c r="AL221" s="10" t="n"/>
+      <c r="AM221" s="10" t="n"/>
+      <c r="AN221" s="10" t="n"/>
+      <c r="AO221" s="10" t="n"/>
+      <c r="AP221" s="10" t="n"/>
     </row>
     <row r="222" ht="22" customHeight="1">
       <c r="A222" s="11" t="n"/>
@@ -11726,6 +13976,16 @@
       <c r="AD222" s="12" t="n"/>
       <c r="AE222" s="12" t="n"/>
       <c r="AF222" s="12" t="n"/>
+      <c r="AG222" s="12" t="n"/>
+      <c r="AH222" s="12" t="n"/>
+      <c r="AI222" s="12" t="n"/>
+      <c r="AJ222" s="12" t="n"/>
+      <c r="AK222" s="12" t="n"/>
+      <c r="AL222" s="12" t="n"/>
+      <c r="AM222" s="12" t="n"/>
+      <c r="AN222" s="12" t="n"/>
+      <c r="AO222" s="12" t="n"/>
+      <c r="AP222" s="12" t="n"/>
     </row>
     <row r="223" ht="22" customHeight="1">
       <c r="A223" s="9" t="n"/>
@@ -11760,6 +14020,16 @@
       <c r="AD223" s="10" t="n"/>
       <c r="AE223" s="10" t="n"/>
       <c r="AF223" s="10" t="n"/>
+      <c r="AG223" s="10" t="n"/>
+      <c r="AH223" s="10" t="n"/>
+      <c r="AI223" s="10" t="n"/>
+      <c r="AJ223" s="10" t="n"/>
+      <c r="AK223" s="10" t="n"/>
+      <c r="AL223" s="10" t="n"/>
+      <c r="AM223" s="10" t="n"/>
+      <c r="AN223" s="10" t="n"/>
+      <c r="AO223" s="10" t="n"/>
+      <c r="AP223" s="10" t="n"/>
     </row>
     <row r="224" ht="22" customHeight="1">
       <c r="A224" s="11" t="n"/>
@@ -11794,6 +14064,16 @@
       <c r="AD224" s="12" t="n"/>
       <c r="AE224" s="12" t="n"/>
       <c r="AF224" s="12" t="n"/>
+      <c r="AG224" s="12" t="n"/>
+      <c r="AH224" s="12" t="n"/>
+      <c r="AI224" s="12" t="n"/>
+      <c r="AJ224" s="12" t="n"/>
+      <c r="AK224" s="12" t="n"/>
+      <c r="AL224" s="12" t="n"/>
+      <c r="AM224" s="12" t="n"/>
+      <c r="AN224" s="12" t="n"/>
+      <c r="AO224" s="12" t="n"/>
+      <c r="AP224" s="12" t="n"/>
     </row>
     <row r="225" ht="22" customHeight="1">
       <c r="A225" s="9" t="n"/>
@@ -11828,6 +14108,16 @@
       <c r="AD225" s="10" t="n"/>
       <c r="AE225" s="10" t="n"/>
       <c r="AF225" s="10" t="n"/>
+      <c r="AG225" s="10" t="n"/>
+      <c r="AH225" s="10" t="n"/>
+      <c r="AI225" s="10" t="n"/>
+      <c r="AJ225" s="10" t="n"/>
+      <c r="AK225" s="10" t="n"/>
+      <c r="AL225" s="10" t="n"/>
+      <c r="AM225" s="10" t="n"/>
+      <c r="AN225" s="10" t="n"/>
+      <c r="AO225" s="10" t="n"/>
+      <c r="AP225" s="10" t="n"/>
     </row>
     <row r="226" ht="22" customHeight="1">
       <c r="A226" s="11" t="n"/>
@@ -11862,6 +14152,16 @@
       <c r="AD226" s="12" t="n"/>
       <c r="AE226" s="12" t="n"/>
       <c r="AF226" s="12" t="n"/>
+      <c r="AG226" s="12" t="n"/>
+      <c r="AH226" s="12" t="n"/>
+      <c r="AI226" s="12" t="n"/>
+      <c r="AJ226" s="12" t="n"/>
+      <c r="AK226" s="12" t="n"/>
+      <c r="AL226" s="12" t="n"/>
+      <c r="AM226" s="12" t="n"/>
+      <c r="AN226" s="12" t="n"/>
+      <c r="AO226" s="12" t="n"/>
+      <c r="AP226" s="12" t="n"/>
     </row>
     <row r="227" ht="22" customHeight="1">
       <c r="A227" s="9" t="n"/>
@@ -11896,6 +14196,16 @@
       <c r="AD227" s="10" t="n"/>
       <c r="AE227" s="10" t="n"/>
       <c r="AF227" s="10" t="n"/>
+      <c r="AG227" s="10" t="n"/>
+      <c r="AH227" s="10" t="n"/>
+      <c r="AI227" s="10" t="n"/>
+      <c r="AJ227" s="10" t="n"/>
+      <c r="AK227" s="10" t="n"/>
+      <c r="AL227" s="10" t="n"/>
+      <c r="AM227" s="10" t="n"/>
+      <c r="AN227" s="10" t="n"/>
+      <c r="AO227" s="10" t="n"/>
+      <c r="AP227" s="10" t="n"/>
     </row>
     <row r="228" ht="22" customHeight="1">
       <c r="A228" s="11" t="n"/>
@@ -11930,6 +14240,16 @@
       <c r="AD228" s="12" t="n"/>
       <c r="AE228" s="12" t="n"/>
       <c r="AF228" s="12" t="n"/>
+      <c r="AG228" s="12" t="n"/>
+      <c r="AH228" s="12" t="n"/>
+      <c r="AI228" s="12" t="n"/>
+      <c r="AJ228" s="12" t="n"/>
+      <c r="AK228" s="12" t="n"/>
+      <c r="AL228" s="12" t="n"/>
+      <c r="AM228" s="12" t="n"/>
+      <c r="AN228" s="12" t="n"/>
+      <c r="AO228" s="12" t="n"/>
+      <c r="AP228" s="12" t="n"/>
     </row>
     <row r="229" ht="22" customHeight="1">
       <c r="A229" s="9" t="n"/>
@@ -11964,6 +14284,16 @@
       <c r="AD229" s="10" t="n"/>
       <c r="AE229" s="10" t="n"/>
       <c r="AF229" s="10" t="n"/>
+      <c r="AG229" s="10" t="n"/>
+      <c r="AH229" s="10" t="n"/>
+      <c r="AI229" s="10" t="n"/>
+      <c r="AJ229" s="10" t="n"/>
+      <c r="AK229" s="10" t="n"/>
+      <c r="AL229" s="10" t="n"/>
+      <c r="AM229" s="10" t="n"/>
+      <c r="AN229" s="10" t="n"/>
+      <c r="AO229" s="10" t="n"/>
+      <c r="AP229" s="10" t="n"/>
     </row>
     <row r="230" ht="22" customHeight="1">
       <c r="A230" s="11" t="n"/>
@@ -11998,6 +14328,16 @@
       <c r="AD230" s="12" t="n"/>
       <c r="AE230" s="12" t="n"/>
       <c r="AF230" s="12" t="n"/>
+      <c r="AG230" s="12" t="n"/>
+      <c r="AH230" s="12" t="n"/>
+      <c r="AI230" s="12" t="n"/>
+      <c r="AJ230" s="12" t="n"/>
+      <c r="AK230" s="12" t="n"/>
+      <c r="AL230" s="12" t="n"/>
+      <c r="AM230" s="12" t="n"/>
+      <c r="AN230" s="12" t="n"/>
+      <c r="AO230" s="12" t="n"/>
+      <c r="AP230" s="12" t="n"/>
     </row>
     <row r="231" ht="22" customHeight="1">
       <c r="A231" s="9" t="n"/>
@@ -12032,6 +14372,16 @@
       <c r="AD231" s="10" t="n"/>
       <c r="AE231" s="10" t="n"/>
       <c r="AF231" s="10" t="n"/>
+      <c r="AG231" s="10" t="n"/>
+      <c r="AH231" s="10" t="n"/>
+      <c r="AI231" s="10" t="n"/>
+      <c r="AJ231" s="10" t="n"/>
+      <c r="AK231" s="10" t="n"/>
+      <c r="AL231" s="10" t="n"/>
+      <c r="AM231" s="10" t="n"/>
+      <c r="AN231" s="10" t="n"/>
+      <c r="AO231" s="10" t="n"/>
+      <c r="AP231" s="10" t="n"/>
     </row>
     <row r="232" ht="22" customHeight="1">
       <c r="A232" s="11" t="n"/>
@@ -12066,6 +14416,16 @@
       <c r="AD232" s="12" t="n"/>
       <c r="AE232" s="12" t="n"/>
       <c r="AF232" s="12" t="n"/>
+      <c r="AG232" s="12" t="n"/>
+      <c r="AH232" s="12" t="n"/>
+      <c r="AI232" s="12" t="n"/>
+      <c r="AJ232" s="12" t="n"/>
+      <c r="AK232" s="12" t="n"/>
+      <c r="AL232" s="12" t="n"/>
+      <c r="AM232" s="12" t="n"/>
+      <c r="AN232" s="12" t="n"/>
+      <c r="AO232" s="12" t="n"/>
+      <c r="AP232" s="12" t="n"/>
     </row>
     <row r="233" ht="22" customHeight="1">
       <c r="A233" s="9" t="n"/>
@@ -12100,6 +14460,16 @@
       <c r="AD233" s="10" t="n"/>
       <c r="AE233" s="10" t="n"/>
       <c r="AF233" s="10" t="n"/>
+      <c r="AG233" s="10" t="n"/>
+      <c r="AH233" s="10" t="n"/>
+      <c r="AI233" s="10" t="n"/>
+      <c r="AJ233" s="10" t="n"/>
+      <c r="AK233" s="10" t="n"/>
+      <c r="AL233" s="10" t="n"/>
+      <c r="AM233" s="10" t="n"/>
+      <c r="AN233" s="10" t="n"/>
+      <c r="AO233" s="10" t="n"/>
+      <c r="AP233" s="10" t="n"/>
     </row>
     <row r="234" ht="22" customHeight="1">
       <c r="A234" s="11" t="n"/>
@@ -12134,6 +14504,16 @@
       <c r="AD234" s="12" t="n"/>
       <c r="AE234" s="12" t="n"/>
       <c r="AF234" s="12" t="n"/>
+      <c r="AG234" s="12" t="n"/>
+      <c r="AH234" s="12" t="n"/>
+      <c r="AI234" s="12" t="n"/>
+      <c r="AJ234" s="12" t="n"/>
+      <c r="AK234" s="12" t="n"/>
+      <c r="AL234" s="12" t="n"/>
+      <c r="AM234" s="12" t="n"/>
+      <c r="AN234" s="12" t="n"/>
+      <c r="AO234" s="12" t="n"/>
+      <c r="AP234" s="12" t="n"/>
     </row>
     <row r="235" ht="22" customHeight="1">
       <c r="A235" s="9" t="n"/>
@@ -12168,6 +14548,16 @@
       <c r="AD235" s="10" t="n"/>
       <c r="AE235" s="10" t="n"/>
       <c r="AF235" s="10" t="n"/>
+      <c r="AG235" s="10" t="n"/>
+      <c r="AH235" s="10" t="n"/>
+      <c r="AI235" s="10" t="n"/>
+      <c r="AJ235" s="10" t="n"/>
+      <c r="AK235" s="10" t="n"/>
+      <c r="AL235" s="10" t="n"/>
+      <c r="AM235" s="10" t="n"/>
+      <c r="AN235" s="10" t="n"/>
+      <c r="AO235" s="10" t="n"/>
+      <c r="AP235" s="10" t="n"/>
     </row>
     <row r="236" ht="22" customHeight="1">
       <c r="A236" s="11" t="n"/>
@@ -12202,6 +14592,16 @@
       <c r="AD236" s="12" t="n"/>
       <c r="AE236" s="12" t="n"/>
       <c r="AF236" s="12" t="n"/>
+      <c r="AG236" s="12" t="n"/>
+      <c r="AH236" s="12" t="n"/>
+      <c r="AI236" s="12" t="n"/>
+      <c r="AJ236" s="12" t="n"/>
+      <c r="AK236" s="12" t="n"/>
+      <c r="AL236" s="12" t="n"/>
+      <c r="AM236" s="12" t="n"/>
+      <c r="AN236" s="12" t="n"/>
+      <c r="AO236" s="12" t="n"/>
+      <c r="AP236" s="12" t="n"/>
     </row>
     <row r="237" ht="22" customHeight="1">
       <c r="A237" s="9" t="n"/>
@@ -12236,6 +14636,16 @@
       <c r="AD237" s="10" t="n"/>
       <c r="AE237" s="10" t="n"/>
       <c r="AF237" s="10" t="n"/>
+      <c r="AG237" s="10" t="n"/>
+      <c r="AH237" s="10" t="n"/>
+      <c r="AI237" s="10" t="n"/>
+      <c r="AJ237" s="10" t="n"/>
+      <c r="AK237" s="10" t="n"/>
+      <c r="AL237" s="10" t="n"/>
+      <c r="AM237" s="10" t="n"/>
+      <c r="AN237" s="10" t="n"/>
+      <c r="AO237" s="10" t="n"/>
+      <c r="AP237" s="10" t="n"/>
     </row>
     <row r="238" ht="22" customHeight="1">
       <c r="A238" s="11" t="n"/>
@@ -12270,6 +14680,16 @@
       <c r="AD238" s="12" t="n"/>
       <c r="AE238" s="12" t="n"/>
       <c r="AF238" s="12" t="n"/>
+      <c r="AG238" s="12" t="n"/>
+      <c r="AH238" s="12" t="n"/>
+      <c r="AI238" s="12" t="n"/>
+      <c r="AJ238" s="12" t="n"/>
+      <c r="AK238" s="12" t="n"/>
+      <c r="AL238" s="12" t="n"/>
+      <c r="AM238" s="12" t="n"/>
+      <c r="AN238" s="12" t="n"/>
+      <c r="AO238" s="12" t="n"/>
+      <c r="AP238" s="12" t="n"/>
     </row>
     <row r="239" ht="22" customHeight="1">
       <c r="A239" s="9" t="n"/>
@@ -12304,6 +14724,16 @@
       <c r="AD239" s="10" t="n"/>
       <c r="AE239" s="10" t="n"/>
       <c r="AF239" s="10" t="n"/>
+      <c r="AG239" s="10" t="n"/>
+      <c r="AH239" s="10" t="n"/>
+      <c r="AI239" s="10" t="n"/>
+      <c r="AJ239" s="10" t="n"/>
+      <c r="AK239" s="10" t="n"/>
+      <c r="AL239" s="10" t="n"/>
+      <c r="AM239" s="10" t="n"/>
+      <c r="AN239" s="10" t="n"/>
+      <c r="AO239" s="10" t="n"/>
+      <c r="AP239" s="10" t="n"/>
     </row>
     <row r="240" ht="22" customHeight="1">
       <c r="A240" s="11" t="n"/>
@@ -12338,6 +14768,16 @@
       <c r="AD240" s="12" t="n"/>
       <c r="AE240" s="12" t="n"/>
       <c r="AF240" s="12" t="n"/>
+      <c r="AG240" s="12" t="n"/>
+      <c r="AH240" s="12" t="n"/>
+      <c r="AI240" s="12" t="n"/>
+      <c r="AJ240" s="12" t="n"/>
+      <c r="AK240" s="12" t="n"/>
+      <c r="AL240" s="12" t="n"/>
+      <c r="AM240" s="12" t="n"/>
+      <c r="AN240" s="12" t="n"/>
+      <c r="AO240" s="12" t="n"/>
+      <c r="AP240" s="12" t="n"/>
     </row>
     <row r="241" ht="22" customHeight="1">
       <c r="A241" s="9" t="n"/>
@@ -12372,6 +14812,16 @@
       <c r="AD241" s="10" t="n"/>
       <c r="AE241" s="10" t="n"/>
       <c r="AF241" s="10" t="n"/>
+      <c r="AG241" s="10" t="n"/>
+      <c r="AH241" s="10" t="n"/>
+      <c r="AI241" s="10" t="n"/>
+      <c r="AJ241" s="10" t="n"/>
+      <c r="AK241" s="10" t="n"/>
+      <c r="AL241" s="10" t="n"/>
+      <c r="AM241" s="10" t="n"/>
+      <c r="AN241" s="10" t="n"/>
+      <c r="AO241" s="10" t="n"/>
+      <c r="AP241" s="10" t="n"/>
     </row>
     <row r="242" ht="22" customHeight="1">
       <c r="A242" s="11" t="n"/>
@@ -12406,6 +14856,16 @@
       <c r="AD242" s="12" t="n"/>
       <c r="AE242" s="12" t="n"/>
       <c r="AF242" s="12" t="n"/>
+      <c r="AG242" s="12" t="n"/>
+      <c r="AH242" s="12" t="n"/>
+      <c r="AI242" s="12" t="n"/>
+      <c r="AJ242" s="12" t="n"/>
+      <c r="AK242" s="12" t="n"/>
+      <c r="AL242" s="12" t="n"/>
+      <c r="AM242" s="12" t="n"/>
+      <c r="AN242" s="12" t="n"/>
+      <c r="AO242" s="12" t="n"/>
+      <c r="AP242" s="12" t="n"/>
     </row>
     <row r="243" ht="22" customHeight="1">
       <c r="A243" s="9" t="n"/>
@@ -12440,6 +14900,16 @@
       <c r="AD243" s="10" t="n"/>
       <c r="AE243" s="10" t="n"/>
       <c r="AF243" s="10" t="n"/>
+      <c r="AG243" s="10" t="n"/>
+      <c r="AH243" s="10" t="n"/>
+      <c r="AI243" s="10" t="n"/>
+      <c r="AJ243" s="10" t="n"/>
+      <c r="AK243" s="10" t="n"/>
+      <c r="AL243" s="10" t="n"/>
+      <c r="AM243" s="10" t="n"/>
+      <c r="AN243" s="10" t="n"/>
+      <c r="AO243" s="10" t="n"/>
+      <c r="AP243" s="10" t="n"/>
     </row>
     <row r="244" ht="22" customHeight="1">
       <c r="A244" s="11" t="n"/>
@@ -12474,6 +14944,16 @@
       <c r="AD244" s="12" t="n"/>
       <c r="AE244" s="12" t="n"/>
       <c r="AF244" s="12" t="n"/>
+      <c r="AG244" s="12" t="n"/>
+      <c r="AH244" s="12" t="n"/>
+      <c r="AI244" s="12" t="n"/>
+      <c r="AJ244" s="12" t="n"/>
+      <c r="AK244" s="12" t="n"/>
+      <c r="AL244" s="12" t="n"/>
+      <c r="AM244" s="12" t="n"/>
+      <c r="AN244" s="12" t="n"/>
+      <c r="AO244" s="12" t="n"/>
+      <c r="AP244" s="12" t="n"/>
     </row>
     <row r="245" ht="22" customHeight="1">
       <c r="A245" s="9" t="n"/>
@@ -12508,6 +14988,16 @@
       <c r="AD245" s="10" t="n"/>
       <c r="AE245" s="10" t="n"/>
       <c r="AF245" s="10" t="n"/>
+      <c r="AG245" s="10" t="n"/>
+      <c r="AH245" s="10" t="n"/>
+      <c r="AI245" s="10" t="n"/>
+      <c r="AJ245" s="10" t="n"/>
+      <c r="AK245" s="10" t="n"/>
+      <c r="AL245" s="10" t="n"/>
+      <c r="AM245" s="10" t="n"/>
+      <c r="AN245" s="10" t="n"/>
+      <c r="AO245" s="10" t="n"/>
+      <c r="AP245" s="10" t="n"/>
     </row>
     <row r="246" ht="22" customHeight="1">
       <c r="A246" s="11" t="n"/>
@@ -12542,6 +15032,16 @@
       <c r="AD246" s="12" t="n"/>
       <c r="AE246" s="12" t="n"/>
       <c r="AF246" s="12" t="n"/>
+      <c r="AG246" s="12" t="n"/>
+      <c r="AH246" s="12" t="n"/>
+      <c r="AI246" s="12" t="n"/>
+      <c r="AJ246" s="12" t="n"/>
+      <c r="AK246" s="12" t="n"/>
+      <c r="AL246" s="12" t="n"/>
+      <c r="AM246" s="12" t="n"/>
+      <c r="AN246" s="12" t="n"/>
+      <c r="AO246" s="12" t="n"/>
+      <c r="AP246" s="12" t="n"/>
     </row>
     <row r="247" ht="22" customHeight="1">
       <c r="A247" s="9" t="n"/>
@@ -12576,6 +15076,16 @@
       <c r="AD247" s="10" t="n"/>
       <c r="AE247" s="10" t="n"/>
       <c r="AF247" s="10" t="n"/>
+      <c r="AG247" s="10" t="n"/>
+      <c r="AH247" s="10" t="n"/>
+      <c r="AI247" s="10" t="n"/>
+      <c r="AJ247" s="10" t="n"/>
+      <c r="AK247" s="10" t="n"/>
+      <c r="AL247" s="10" t="n"/>
+      <c r="AM247" s="10" t="n"/>
+      <c r="AN247" s="10" t="n"/>
+      <c r="AO247" s="10" t="n"/>
+      <c r="AP247" s="10" t="n"/>
     </row>
     <row r="248" ht="22" customHeight="1">
       <c r="A248" s="11" t="n"/>
@@ -12610,6 +15120,16 @@
       <c r="AD248" s="12" t="n"/>
       <c r="AE248" s="12" t="n"/>
       <c r="AF248" s="12" t="n"/>
+      <c r="AG248" s="12" t="n"/>
+      <c r="AH248" s="12" t="n"/>
+      <c r="AI248" s="12" t="n"/>
+      <c r="AJ248" s="12" t="n"/>
+      <c r="AK248" s="12" t="n"/>
+      <c r="AL248" s="12" t="n"/>
+      <c r="AM248" s="12" t="n"/>
+      <c r="AN248" s="12" t="n"/>
+      <c r="AO248" s="12" t="n"/>
+      <c r="AP248" s="12" t="n"/>
     </row>
     <row r="249" ht="22" customHeight="1">
       <c r="A249" s="9" t="n"/>
@@ -12644,6 +15164,16 @@
       <c r="AD249" s="10" t="n"/>
       <c r="AE249" s="10" t="n"/>
       <c r="AF249" s="10" t="n"/>
+      <c r="AG249" s="10" t="n"/>
+      <c r="AH249" s="10" t="n"/>
+      <c r="AI249" s="10" t="n"/>
+      <c r="AJ249" s="10" t="n"/>
+      <c r="AK249" s="10" t="n"/>
+      <c r="AL249" s="10" t="n"/>
+      <c r="AM249" s="10" t="n"/>
+      <c r="AN249" s="10" t="n"/>
+      <c r="AO249" s="10" t="n"/>
+      <c r="AP249" s="10" t="n"/>
     </row>
     <row r="250" ht="22" customHeight="1">
       <c r="A250" s="11" t="n"/>
@@ -12678,6 +15208,16 @@
       <c r="AD250" s="12" t="n"/>
       <c r="AE250" s="12" t="n"/>
       <c r="AF250" s="12" t="n"/>
+      <c r="AG250" s="12" t="n"/>
+      <c r="AH250" s="12" t="n"/>
+      <c r="AI250" s="12" t="n"/>
+      <c r="AJ250" s="12" t="n"/>
+      <c r="AK250" s="12" t="n"/>
+      <c r="AL250" s="12" t="n"/>
+      <c r="AM250" s="12" t="n"/>
+      <c r="AN250" s="12" t="n"/>
+      <c r="AO250" s="12" t="n"/>
+      <c r="AP250" s="12" t="n"/>
     </row>
     <row r="251" ht="22" customHeight="1">
       <c r="A251" s="9" t="n"/>
@@ -12712,6 +15252,16 @@
       <c r="AD251" s="10" t="n"/>
       <c r="AE251" s="10" t="n"/>
       <c r="AF251" s="10" t="n"/>
+      <c r="AG251" s="10" t="n"/>
+      <c r="AH251" s="10" t="n"/>
+      <c r="AI251" s="10" t="n"/>
+      <c r="AJ251" s="10" t="n"/>
+      <c r="AK251" s="10" t="n"/>
+      <c r="AL251" s="10" t="n"/>
+      <c r="AM251" s="10" t="n"/>
+      <c r="AN251" s="10" t="n"/>
+      <c r="AO251" s="10" t="n"/>
+      <c r="AP251" s="10" t="n"/>
     </row>
     <row r="252" ht="22" customHeight="1">
       <c r="A252" s="11" t="n"/>
@@ -12746,6 +15296,16 @@
       <c r="AD252" s="12" t="n"/>
       <c r="AE252" s="12" t="n"/>
       <c r="AF252" s="12" t="n"/>
+      <c r="AG252" s="12" t="n"/>
+      <c r="AH252" s="12" t="n"/>
+      <c r="AI252" s="12" t="n"/>
+      <c r="AJ252" s="12" t="n"/>
+      <c r="AK252" s="12" t="n"/>
+      <c r="AL252" s="12" t="n"/>
+      <c r="AM252" s="12" t="n"/>
+      <c r="AN252" s="12" t="n"/>
+      <c r="AO252" s="12" t="n"/>
+      <c r="AP252" s="12" t="n"/>
     </row>
     <row r="253" ht="22" customHeight="1">
       <c r="A253" s="9" t="n"/>
@@ -12780,6 +15340,16 @@
       <c r="AD253" s="10" t="n"/>
       <c r="AE253" s="10" t="n"/>
       <c r="AF253" s="10" t="n"/>
+      <c r="AG253" s="10" t="n"/>
+      <c r="AH253" s="10" t="n"/>
+      <c r="AI253" s="10" t="n"/>
+      <c r="AJ253" s="10" t="n"/>
+      <c r="AK253" s="10" t="n"/>
+      <c r="AL253" s="10" t="n"/>
+      <c r="AM253" s="10" t="n"/>
+      <c r="AN253" s="10" t="n"/>
+      <c r="AO253" s="10" t="n"/>
+      <c r="AP253" s="10" t="n"/>
     </row>
     <row r="254" ht="22" customHeight="1">
       <c r="A254" s="11" t="n"/>
@@ -12814,6 +15384,16 @@
       <c r="AD254" s="12" t="n"/>
       <c r="AE254" s="12" t="n"/>
       <c r="AF254" s="12" t="n"/>
+      <c r="AG254" s="12" t="n"/>
+      <c r="AH254" s="12" t="n"/>
+      <c r="AI254" s="12" t="n"/>
+      <c r="AJ254" s="12" t="n"/>
+      <c r="AK254" s="12" t="n"/>
+      <c r="AL254" s="12" t="n"/>
+      <c r="AM254" s="12" t="n"/>
+      <c r="AN254" s="12" t="n"/>
+      <c r="AO254" s="12" t="n"/>
+      <c r="AP254" s="12" t="n"/>
     </row>
     <row r="255" ht="22" customHeight="1">
       <c r="A255" s="9" t="n"/>
@@ -12848,6 +15428,16 @@
       <c r="AD255" s="10" t="n"/>
       <c r="AE255" s="10" t="n"/>
       <c r="AF255" s="10" t="n"/>
+      <c r="AG255" s="10" t="n"/>
+      <c r="AH255" s="10" t="n"/>
+      <c r="AI255" s="10" t="n"/>
+      <c r="AJ255" s="10" t="n"/>
+      <c r="AK255" s="10" t="n"/>
+      <c r="AL255" s="10" t="n"/>
+      <c r="AM255" s="10" t="n"/>
+      <c r="AN255" s="10" t="n"/>
+      <c r="AO255" s="10" t="n"/>
+      <c r="AP255" s="10" t="n"/>
     </row>
     <row r="256" ht="22" customHeight="1">
       <c r="A256" s="11" t="n"/>
@@ -12882,6 +15472,16 @@
       <c r="AD256" s="12" t="n"/>
       <c r="AE256" s="12" t="n"/>
       <c r="AF256" s="12" t="n"/>
+      <c r="AG256" s="12" t="n"/>
+      <c r="AH256" s="12" t="n"/>
+      <c r="AI256" s="12" t="n"/>
+      <c r="AJ256" s="12" t="n"/>
+      <c r="AK256" s="12" t="n"/>
+      <c r="AL256" s="12" t="n"/>
+      <c r="AM256" s="12" t="n"/>
+      <c r="AN256" s="12" t="n"/>
+      <c r="AO256" s="12" t="n"/>
+      <c r="AP256" s="12" t="n"/>
     </row>
     <row r="257" ht="22" customHeight="1">
       <c r="A257" s="9" t="n"/>
@@ -12916,6 +15516,16 @@
       <c r="AD257" s="10" t="n"/>
       <c r="AE257" s="10" t="n"/>
       <c r="AF257" s="10" t="n"/>
+      <c r="AG257" s="10" t="n"/>
+      <c r="AH257" s="10" t="n"/>
+      <c r="AI257" s="10" t="n"/>
+      <c r="AJ257" s="10" t="n"/>
+      <c r="AK257" s="10" t="n"/>
+      <c r="AL257" s="10" t="n"/>
+      <c r="AM257" s="10" t="n"/>
+      <c r="AN257" s="10" t="n"/>
+      <c r="AO257" s="10" t="n"/>
+      <c r="AP257" s="10" t="n"/>
     </row>
     <row r="258" ht="22" customHeight="1">
       <c r="A258" s="11" t="n"/>
@@ -12950,6 +15560,16 @@
       <c r="AD258" s="12" t="n"/>
       <c r="AE258" s="12" t="n"/>
       <c r="AF258" s="12" t="n"/>
+      <c r="AG258" s="12" t="n"/>
+      <c r="AH258" s="12" t="n"/>
+      <c r="AI258" s="12" t="n"/>
+      <c r="AJ258" s="12" t="n"/>
+      <c r="AK258" s="12" t="n"/>
+      <c r="AL258" s="12" t="n"/>
+      <c r="AM258" s="12" t="n"/>
+      <c r="AN258" s="12" t="n"/>
+      <c r="AO258" s="12" t="n"/>
+      <c r="AP258" s="12" t="n"/>
     </row>
     <row r="259" ht="22" customHeight="1">
       <c r="A259" s="9" t="n"/>
@@ -12984,6 +15604,16 @@
       <c r="AD259" s="10" t="n"/>
       <c r="AE259" s="10" t="n"/>
       <c r="AF259" s="10" t="n"/>
+      <c r="AG259" s="10" t="n"/>
+      <c r="AH259" s="10" t="n"/>
+      <c r="AI259" s="10" t="n"/>
+      <c r="AJ259" s="10" t="n"/>
+      <c r="AK259" s="10" t="n"/>
+      <c r="AL259" s="10" t="n"/>
+      <c r="AM259" s="10" t="n"/>
+      <c r="AN259" s="10" t="n"/>
+      <c r="AO259" s="10" t="n"/>
+      <c r="AP259" s="10" t="n"/>
     </row>
     <row r="260" ht="22" customHeight="1">
       <c r="A260" s="11" t="n"/>
@@ -13018,6 +15648,16 @@
       <c r="AD260" s="12" t="n"/>
       <c r="AE260" s="12" t="n"/>
       <c r="AF260" s="12" t="n"/>
+      <c r="AG260" s="12" t="n"/>
+      <c r="AH260" s="12" t="n"/>
+      <c r="AI260" s="12" t="n"/>
+      <c r="AJ260" s="12" t="n"/>
+      <c r="AK260" s="12" t="n"/>
+      <c r="AL260" s="12" t="n"/>
+      <c r="AM260" s="12" t="n"/>
+      <c r="AN260" s="12" t="n"/>
+      <c r="AO260" s="12" t="n"/>
+      <c r="AP260" s="12" t="n"/>
     </row>
     <row r="261" ht="22" customHeight="1">
       <c r="A261" s="9" t="n"/>
@@ -13052,6 +15692,16 @@
       <c r="AD261" s="10" t="n"/>
       <c r="AE261" s="10" t="n"/>
       <c r="AF261" s="10" t="n"/>
+      <c r="AG261" s="10" t="n"/>
+      <c r="AH261" s="10" t="n"/>
+      <c r="AI261" s="10" t="n"/>
+      <c r="AJ261" s="10" t="n"/>
+      <c r="AK261" s="10" t="n"/>
+      <c r="AL261" s="10" t="n"/>
+      <c r="AM261" s="10" t="n"/>
+      <c r="AN261" s="10" t="n"/>
+      <c r="AO261" s="10" t="n"/>
+      <c r="AP261" s="10" t="n"/>
     </row>
     <row r="262" ht="22" customHeight="1">
       <c r="A262" s="11" t="n"/>
@@ -13086,6 +15736,16 @@
       <c r="AD262" s="12" t="n"/>
       <c r="AE262" s="12" t="n"/>
       <c r="AF262" s="12" t="n"/>
+      <c r="AG262" s="12" t="n"/>
+      <c r="AH262" s="12" t="n"/>
+      <c r="AI262" s="12" t="n"/>
+      <c r="AJ262" s="12" t="n"/>
+      <c r="AK262" s="12" t="n"/>
+      <c r="AL262" s="12" t="n"/>
+      <c r="AM262" s="12" t="n"/>
+      <c r="AN262" s="12" t="n"/>
+      <c r="AO262" s="12" t="n"/>
+      <c r="AP262" s="12" t="n"/>
     </row>
     <row r="263" ht="22" customHeight="1">
       <c r="A263" s="9" t="n"/>
@@ -13120,6 +15780,16 @@
       <c r="AD263" s="10" t="n"/>
       <c r="AE263" s="10" t="n"/>
       <c r="AF263" s="10" t="n"/>
+      <c r="AG263" s="10" t="n"/>
+      <c r="AH263" s="10" t="n"/>
+      <c r="AI263" s="10" t="n"/>
+      <c r="AJ263" s="10" t="n"/>
+      <c r="AK263" s="10" t="n"/>
+      <c r="AL263" s="10" t="n"/>
+      <c r="AM263" s="10" t="n"/>
+      <c r="AN263" s="10" t="n"/>
+      <c r="AO263" s="10" t="n"/>
+      <c r="AP263" s="10" t="n"/>
     </row>
     <row r="264" ht="22" customHeight="1">
       <c r="A264" s="11" t="n"/>
@@ -13154,6 +15824,16 @@
       <c r="AD264" s="12" t="n"/>
       <c r="AE264" s="12" t="n"/>
       <c r="AF264" s="12" t="n"/>
+      <c r="AG264" s="12" t="n"/>
+      <c r="AH264" s="12" t="n"/>
+      <c r="AI264" s="12" t="n"/>
+      <c r="AJ264" s="12" t="n"/>
+      <c r="AK264" s="12" t="n"/>
+      <c r="AL264" s="12" t="n"/>
+      <c r="AM264" s="12" t="n"/>
+      <c r="AN264" s="12" t="n"/>
+      <c r="AO264" s="12" t="n"/>
+      <c r="AP264" s="12" t="n"/>
     </row>
     <row r="265" ht="22" customHeight="1">
       <c r="A265" s="9" t="n"/>
@@ -13188,6 +15868,16 @@
       <c r="AD265" s="10" t="n"/>
       <c r="AE265" s="10" t="n"/>
       <c r="AF265" s="10" t="n"/>
+      <c r="AG265" s="10" t="n"/>
+      <c r="AH265" s="10" t="n"/>
+      <c r="AI265" s="10" t="n"/>
+      <c r="AJ265" s="10" t="n"/>
+      <c r="AK265" s="10" t="n"/>
+      <c r="AL265" s="10" t="n"/>
+      <c r="AM265" s="10" t="n"/>
+      <c r="AN265" s="10" t="n"/>
+      <c r="AO265" s="10" t="n"/>
+      <c r="AP265" s="10" t="n"/>
     </row>
     <row r="266" ht="22" customHeight="1">
       <c r="A266" s="11" t="n"/>
@@ -13222,6 +15912,16 @@
       <c r="AD266" s="12" t="n"/>
       <c r="AE266" s="12" t="n"/>
       <c r="AF266" s="12" t="n"/>
+      <c r="AG266" s="12" t="n"/>
+      <c r="AH266" s="12" t="n"/>
+      <c r="AI266" s="12" t="n"/>
+      <c r="AJ266" s="12" t="n"/>
+      <c r="AK266" s="12" t="n"/>
+      <c r="AL266" s="12" t="n"/>
+      <c r="AM266" s="12" t="n"/>
+      <c r="AN266" s="12" t="n"/>
+      <c r="AO266" s="12" t="n"/>
+      <c r="AP266" s="12" t="n"/>
     </row>
     <row r="267" ht="22" customHeight="1">
       <c r="A267" s="9" t="n"/>
@@ -13256,6 +15956,16 @@
       <c r="AD267" s="10" t="n"/>
       <c r="AE267" s="10" t="n"/>
       <c r="AF267" s="10" t="n"/>
+      <c r="AG267" s="10" t="n"/>
+      <c r="AH267" s="10" t="n"/>
+      <c r="AI267" s="10" t="n"/>
+      <c r="AJ267" s="10" t="n"/>
+      <c r="AK267" s="10" t="n"/>
+      <c r="AL267" s="10" t="n"/>
+      <c r="AM267" s="10" t="n"/>
+      <c r="AN267" s="10" t="n"/>
+      <c r="AO267" s="10" t="n"/>
+      <c r="AP267" s="10" t="n"/>
     </row>
     <row r="268" ht="22" customHeight="1">
       <c r="A268" s="11" t="n"/>
@@ -13290,6 +16000,16 @@
       <c r="AD268" s="12" t="n"/>
       <c r="AE268" s="12" t="n"/>
       <c r="AF268" s="12" t="n"/>
+      <c r="AG268" s="12" t="n"/>
+      <c r="AH268" s="12" t="n"/>
+      <c r="AI268" s="12" t="n"/>
+      <c r="AJ268" s="12" t="n"/>
+      <c r="AK268" s="12" t="n"/>
+      <c r="AL268" s="12" t="n"/>
+      <c r="AM268" s="12" t="n"/>
+      <c r="AN268" s="12" t="n"/>
+      <c r="AO268" s="12" t="n"/>
+      <c r="AP268" s="12" t="n"/>
     </row>
     <row r="269" ht="22" customHeight="1">
       <c r="A269" s="9" t="n"/>
@@ -13324,6 +16044,16 @@
       <c r="AD269" s="10" t="n"/>
       <c r="AE269" s="10" t="n"/>
       <c r="AF269" s="10" t="n"/>
+      <c r="AG269" s="10" t="n"/>
+      <c r="AH269" s="10" t="n"/>
+      <c r="AI269" s="10" t="n"/>
+      <c r="AJ269" s="10" t="n"/>
+      <c r="AK269" s="10" t="n"/>
+      <c r="AL269" s="10" t="n"/>
+      <c r="AM269" s="10" t="n"/>
+      <c r="AN269" s="10" t="n"/>
+      <c r="AO269" s="10" t="n"/>
+      <c r="AP269" s="10" t="n"/>
     </row>
     <row r="270" ht="22" customHeight="1">
       <c r="A270" s="11" t="n"/>
@@ -13358,6 +16088,16 @@
       <c r="AD270" s="12" t="n"/>
       <c r="AE270" s="12" t="n"/>
       <c r="AF270" s="12" t="n"/>
+      <c r="AG270" s="12" t="n"/>
+      <c r="AH270" s="12" t="n"/>
+      <c r="AI270" s="12" t="n"/>
+      <c r="AJ270" s="12" t="n"/>
+      <c r="AK270" s="12" t="n"/>
+      <c r="AL270" s="12" t="n"/>
+      <c r="AM270" s="12" t="n"/>
+      <c r="AN270" s="12" t="n"/>
+      <c r="AO270" s="12" t="n"/>
+      <c r="AP270" s="12" t="n"/>
     </row>
     <row r="271" ht="22" customHeight="1">
       <c r="A271" s="9" t="n"/>
@@ -13392,6 +16132,16 @@
       <c r="AD271" s="10" t="n"/>
       <c r="AE271" s="10" t="n"/>
       <c r="AF271" s="10" t="n"/>
+      <c r="AG271" s="10" t="n"/>
+      <c r="AH271" s="10" t="n"/>
+      <c r="AI271" s="10" t="n"/>
+      <c r="AJ271" s="10" t="n"/>
+      <c r="AK271" s="10" t="n"/>
+      <c r="AL271" s="10" t="n"/>
+      <c r="AM271" s="10" t="n"/>
+      <c r="AN271" s="10" t="n"/>
+      <c r="AO271" s="10" t="n"/>
+      <c r="AP271" s="10" t="n"/>
     </row>
     <row r="272" ht="22" customHeight="1">
       <c r="A272" s="11" t="n"/>
@@ -13426,6 +16176,16 @@
       <c r="AD272" s="12" t="n"/>
       <c r="AE272" s="12" t="n"/>
       <c r="AF272" s="12" t="n"/>
+      <c r="AG272" s="12" t="n"/>
+      <c r="AH272" s="12" t="n"/>
+      <c r="AI272" s="12" t="n"/>
+      <c r="AJ272" s="12" t="n"/>
+      <c r="AK272" s="12" t="n"/>
+      <c r="AL272" s="12" t="n"/>
+      <c r="AM272" s="12" t="n"/>
+      <c r="AN272" s="12" t="n"/>
+      <c r="AO272" s="12" t="n"/>
+      <c r="AP272" s="12" t="n"/>
     </row>
     <row r="273" ht="22" customHeight="1">
       <c r="A273" s="9" t="n"/>
@@ -13460,6 +16220,16 @@
       <c r="AD273" s="10" t="n"/>
       <c r="AE273" s="10" t="n"/>
       <c r="AF273" s="10" t="n"/>
+      <c r="AG273" s="10" t="n"/>
+      <c r="AH273" s="10" t="n"/>
+      <c r="AI273" s="10" t="n"/>
+      <c r="AJ273" s="10" t="n"/>
+      <c r="AK273" s="10" t="n"/>
+      <c r="AL273" s="10" t="n"/>
+      <c r="AM273" s="10" t="n"/>
+      <c r="AN273" s="10" t="n"/>
+      <c r="AO273" s="10" t="n"/>
+      <c r="AP273" s="10" t="n"/>
     </row>
     <row r="274" ht="22" customHeight="1">
       <c r="A274" s="11" t="n"/>
@@ -13494,6 +16264,16 @@
       <c r="AD274" s="12" t="n"/>
       <c r="AE274" s="12" t="n"/>
       <c r="AF274" s="12" t="n"/>
+      <c r="AG274" s="12" t="n"/>
+      <c r="AH274" s="12" t="n"/>
+      <c r="AI274" s="12" t="n"/>
+      <c r="AJ274" s="12" t="n"/>
+      <c r="AK274" s="12" t="n"/>
+      <c r="AL274" s="12" t="n"/>
+      <c r="AM274" s="12" t="n"/>
+      <c r="AN274" s="12" t="n"/>
+      <c r="AO274" s="12" t="n"/>
+      <c r="AP274" s="12" t="n"/>
     </row>
     <row r="275" ht="22" customHeight="1">
       <c r="A275" s="9" t="n"/>
@@ -13528,6 +16308,16 @@
       <c r="AD275" s="10" t="n"/>
       <c r="AE275" s="10" t="n"/>
       <c r="AF275" s="10" t="n"/>
+      <c r="AG275" s="10" t="n"/>
+      <c r="AH275" s="10" t="n"/>
+      <c r="AI275" s="10" t="n"/>
+      <c r="AJ275" s="10" t="n"/>
+      <c r="AK275" s="10" t="n"/>
+      <c r="AL275" s="10" t="n"/>
+      <c r="AM275" s="10" t="n"/>
+      <c r="AN275" s="10" t="n"/>
+      <c r="AO275" s="10" t="n"/>
+      <c r="AP275" s="10" t="n"/>
     </row>
     <row r="276" ht="22" customHeight="1">
       <c r="A276" s="11" t="n"/>
@@ -13562,6 +16352,16 @@
       <c r="AD276" s="12" t="n"/>
       <c r="AE276" s="12" t="n"/>
       <c r="AF276" s="12" t="n"/>
+      <c r="AG276" s="12" t="n"/>
+      <c r="AH276" s="12" t="n"/>
+      <c r="AI276" s="12" t="n"/>
+      <c r="AJ276" s="12" t="n"/>
+      <c r="AK276" s="12" t="n"/>
+      <c r="AL276" s="12" t="n"/>
+      <c r="AM276" s="12" t="n"/>
+      <c r="AN276" s="12" t="n"/>
+      <c r="AO276" s="12" t="n"/>
+      <c r="AP276" s="12" t="n"/>
     </row>
     <row r="277" ht="22" customHeight="1">
       <c r="A277" s="9" t="n"/>
@@ -13596,6 +16396,16 @@
       <c r="AD277" s="10" t="n"/>
       <c r="AE277" s="10" t="n"/>
       <c r="AF277" s="10" t="n"/>
+      <c r="AG277" s="10" t="n"/>
+      <c r="AH277" s="10" t="n"/>
+      <c r="AI277" s="10" t="n"/>
+      <c r="AJ277" s="10" t="n"/>
+      <c r="AK277" s="10" t="n"/>
+      <c r="AL277" s="10" t="n"/>
+      <c r="AM277" s="10" t="n"/>
+      <c r="AN277" s="10" t="n"/>
+      <c r="AO277" s="10" t="n"/>
+      <c r="AP277" s="10" t="n"/>
     </row>
     <row r="278" ht="22" customHeight="1">
       <c r="A278" s="11" t="n"/>
@@ -13630,6 +16440,16 @@
       <c r="AD278" s="12" t="n"/>
       <c r="AE278" s="12" t="n"/>
       <c r="AF278" s="12" t="n"/>
+      <c r="AG278" s="12" t="n"/>
+      <c r="AH278" s="12" t="n"/>
+      <c r="AI278" s="12" t="n"/>
+      <c r="AJ278" s="12" t="n"/>
+      <c r="AK278" s="12" t="n"/>
+      <c r="AL278" s="12" t="n"/>
+      <c r="AM278" s="12" t="n"/>
+      <c r="AN278" s="12" t="n"/>
+      <c r="AO278" s="12" t="n"/>
+      <c r="AP278" s="12" t="n"/>
     </row>
     <row r="279" ht="22" customHeight="1">
       <c r="A279" s="9" t="n"/>
@@ -13664,6 +16484,16 @@
       <c r="AD279" s="10" t="n"/>
       <c r="AE279" s="10" t="n"/>
       <c r="AF279" s="10" t="n"/>
+      <c r="AG279" s="10" t="n"/>
+      <c r="AH279" s="10" t="n"/>
+      <c r="AI279" s="10" t="n"/>
+      <c r="AJ279" s="10" t="n"/>
+      <c r="AK279" s="10" t="n"/>
+      <c r="AL279" s="10" t="n"/>
+      <c r="AM279" s="10" t="n"/>
+      <c r="AN279" s="10" t="n"/>
+      <c r="AO279" s="10" t="n"/>
+      <c r="AP279" s="10" t="n"/>
     </row>
     <row r="280" ht="22" customHeight="1">
       <c r="A280" s="11" t="n"/>
@@ -13698,6 +16528,16 @@
       <c r="AD280" s="12" t="n"/>
       <c r="AE280" s="12" t="n"/>
       <c r="AF280" s="12" t="n"/>
+      <c r="AG280" s="12" t="n"/>
+      <c r="AH280" s="12" t="n"/>
+      <c r="AI280" s="12" t="n"/>
+      <c r="AJ280" s="12" t="n"/>
+      <c r="AK280" s="12" t="n"/>
+      <c r="AL280" s="12" t="n"/>
+      <c r="AM280" s="12" t="n"/>
+      <c r="AN280" s="12" t="n"/>
+      <c r="AO280" s="12" t="n"/>
+      <c r="AP280" s="12" t="n"/>
     </row>
     <row r="281" ht="22" customHeight="1">
       <c r="A281" s="9" t="n"/>
@@ -13732,6 +16572,16 @@
       <c r="AD281" s="10" t="n"/>
       <c r="AE281" s="10" t="n"/>
       <c r="AF281" s="10" t="n"/>
+      <c r="AG281" s="10" t="n"/>
+      <c r="AH281" s="10" t="n"/>
+      <c r="AI281" s="10" t="n"/>
+      <c r="AJ281" s="10" t="n"/>
+      <c r="AK281" s="10" t="n"/>
+      <c r="AL281" s="10" t="n"/>
+      <c r="AM281" s="10" t="n"/>
+      <c r="AN281" s="10" t="n"/>
+      <c r="AO281" s="10" t="n"/>
+      <c r="AP281" s="10" t="n"/>
     </row>
     <row r="282" ht="22" customHeight="1">
       <c r="A282" s="11" t="n"/>
@@ -13766,6 +16616,16 @@
       <c r="AD282" s="12" t="n"/>
       <c r="AE282" s="12" t="n"/>
       <c r="AF282" s="12" t="n"/>
+      <c r="AG282" s="12" t="n"/>
+      <c r="AH282" s="12" t="n"/>
+      <c r="AI282" s="12" t="n"/>
+      <c r="AJ282" s="12" t="n"/>
+      <c r="AK282" s="12" t="n"/>
+      <c r="AL282" s="12" t="n"/>
+      <c r="AM282" s="12" t="n"/>
+      <c r="AN282" s="12" t="n"/>
+      <c r="AO282" s="12" t="n"/>
+      <c r="AP282" s="12" t="n"/>
     </row>
     <row r="283" ht="22" customHeight="1">
       <c r="A283" s="9" t="n"/>
@@ -13800,6 +16660,16 @@
       <c r="AD283" s="10" t="n"/>
       <c r="AE283" s="10" t="n"/>
       <c r="AF283" s="10" t="n"/>
+      <c r="AG283" s="10" t="n"/>
+      <c r="AH283" s="10" t="n"/>
+      <c r="AI283" s="10" t="n"/>
+      <c r="AJ283" s="10" t="n"/>
+      <c r="AK283" s="10" t="n"/>
+      <c r="AL283" s="10" t="n"/>
+      <c r="AM283" s="10" t="n"/>
+      <c r="AN283" s="10" t="n"/>
+      <c r="AO283" s="10" t="n"/>
+      <c r="AP283" s="10" t="n"/>
     </row>
     <row r="284" ht="22" customHeight="1">
       <c r="A284" s="11" t="n"/>
@@ -13834,6 +16704,16 @@
       <c r="AD284" s="12" t="n"/>
       <c r="AE284" s="12" t="n"/>
       <c r="AF284" s="12" t="n"/>
+      <c r="AG284" s="12" t="n"/>
+      <c r="AH284" s="12" t="n"/>
+      <c r="AI284" s="12" t="n"/>
+      <c r="AJ284" s="12" t="n"/>
+      <c r="AK284" s="12" t="n"/>
+      <c r="AL284" s="12" t="n"/>
+      <c r="AM284" s="12" t="n"/>
+      <c r="AN284" s="12" t="n"/>
+      <c r="AO284" s="12" t="n"/>
+      <c r="AP284" s="12" t="n"/>
     </row>
     <row r="285" ht="22" customHeight="1">
       <c r="A285" s="9" t="n"/>
@@ -13868,6 +16748,16 @@
       <c r="AD285" s="10" t="n"/>
       <c r="AE285" s="10" t="n"/>
       <c r="AF285" s="10" t="n"/>
+      <c r="AG285" s="10" t="n"/>
+      <c r="AH285" s="10" t="n"/>
+      <c r="AI285" s="10" t="n"/>
+      <c r="AJ285" s="10" t="n"/>
+      <c r="AK285" s="10" t="n"/>
+      <c r="AL285" s="10" t="n"/>
+      <c r="AM285" s="10" t="n"/>
+      <c r="AN285" s="10" t="n"/>
+      <c r="AO285" s="10" t="n"/>
+      <c r="AP285" s="10" t="n"/>
     </row>
     <row r="286" ht="22" customHeight="1">
       <c r="A286" s="11" t="n"/>
@@ -13902,6 +16792,16 @@
       <c r="AD286" s="12" t="n"/>
       <c r="AE286" s="12" t="n"/>
       <c r="AF286" s="12" t="n"/>
+      <c r="AG286" s="12" t="n"/>
+      <c r="AH286" s="12" t="n"/>
+      <c r="AI286" s="12" t="n"/>
+      <c r="AJ286" s="12" t="n"/>
+      <c r="AK286" s="12" t="n"/>
+      <c r="AL286" s="12" t="n"/>
+      <c r="AM286" s="12" t="n"/>
+      <c r="AN286" s="12" t="n"/>
+      <c r="AO286" s="12" t="n"/>
+      <c r="AP286" s="12" t="n"/>
     </row>
     <row r="287" ht="22" customHeight="1">
       <c r="A287" s="9" t="n"/>
@@ -13936,6 +16836,16 @@
       <c r="AD287" s="10" t="n"/>
       <c r="AE287" s="10" t="n"/>
       <c r="AF287" s="10" t="n"/>
+      <c r="AG287" s="10" t="n"/>
+      <c r="AH287" s="10" t="n"/>
+      <c r="AI287" s="10" t="n"/>
+      <c r="AJ287" s="10" t="n"/>
+      <c r="AK287" s="10" t="n"/>
+      <c r="AL287" s="10" t="n"/>
+      <c r="AM287" s="10" t="n"/>
+      <c r="AN287" s="10" t="n"/>
+      <c r="AO287" s="10" t="n"/>
+      <c r="AP287" s="10" t="n"/>
     </row>
     <row r="288" ht="22" customHeight="1">
       <c r="A288" s="11" t="n"/>
@@ -13970,6 +16880,16 @@
       <c r="AD288" s="12" t="n"/>
       <c r="AE288" s="12" t="n"/>
       <c r="AF288" s="12" t="n"/>
+      <c r="AG288" s="12" t="n"/>
+      <c r="AH288" s="12" t="n"/>
+      <c r="AI288" s="12" t="n"/>
+      <c r="AJ288" s="12" t="n"/>
+      <c r="AK288" s="12" t="n"/>
+      <c r="AL288" s="12" t="n"/>
+      <c r="AM288" s="12" t="n"/>
+      <c r="AN288" s="12" t="n"/>
+      <c r="AO288" s="12" t="n"/>
+      <c r="AP288" s="12" t="n"/>
     </row>
     <row r="289" ht="22" customHeight="1">
       <c r="A289" s="9" t="n"/>
@@ -14004,6 +16924,16 @@
       <c r="AD289" s="10" t="n"/>
       <c r="AE289" s="10" t="n"/>
       <c r="AF289" s="10" t="n"/>
+      <c r="AG289" s="10" t="n"/>
+      <c r="AH289" s="10" t="n"/>
+      <c r="AI289" s="10" t="n"/>
+      <c r="AJ289" s="10" t="n"/>
+      <c r="AK289" s="10" t="n"/>
+      <c r="AL289" s="10" t="n"/>
+      <c r="AM289" s="10" t="n"/>
+      <c r="AN289" s="10" t="n"/>
+      <c r="AO289" s="10" t="n"/>
+      <c r="AP289" s="10" t="n"/>
     </row>
     <row r="290" ht="22" customHeight="1">
       <c r="A290" s="11" t="n"/>
@@ -14038,6 +16968,16 @@
       <c r="AD290" s="12" t="n"/>
       <c r="AE290" s="12" t="n"/>
       <c r="AF290" s="12" t="n"/>
+      <c r="AG290" s="12" t="n"/>
+      <c r="AH290" s="12" t="n"/>
+      <c r="AI290" s="12" t="n"/>
+      <c r="AJ290" s="12" t="n"/>
+      <c r="AK290" s="12" t="n"/>
+      <c r="AL290" s="12" t="n"/>
+      <c r="AM290" s="12" t="n"/>
+      <c r="AN290" s="12" t="n"/>
+      <c r="AO290" s="12" t="n"/>
+      <c r="AP290" s="12" t="n"/>
     </row>
     <row r="291" ht="22" customHeight="1">
       <c r="A291" s="9" t="n"/>
@@ -14072,6 +17012,16 @@
       <c r="AD291" s="10" t="n"/>
       <c r="AE291" s="10" t="n"/>
       <c r="AF291" s="10" t="n"/>
+      <c r="AG291" s="10" t="n"/>
+      <c r="AH291" s="10" t="n"/>
+      <c r="AI291" s="10" t="n"/>
+      <c r="AJ291" s="10" t="n"/>
+      <c r="AK291" s="10" t="n"/>
+      <c r="AL291" s="10" t="n"/>
+      <c r="AM291" s="10" t="n"/>
+      <c r="AN291" s="10" t="n"/>
+      <c r="AO291" s="10" t="n"/>
+      <c r="AP291" s="10" t="n"/>
     </row>
     <row r="292" ht="22" customHeight="1">
       <c r="A292" s="11" t="n"/>
@@ -14106,6 +17056,16 @@
       <c r="AD292" s="12" t="n"/>
       <c r="AE292" s="12" t="n"/>
       <c r="AF292" s="12" t="n"/>
+      <c r="AG292" s="12" t="n"/>
+      <c r="AH292" s="12" t="n"/>
+      <c r="AI292" s="12" t="n"/>
+      <c r="AJ292" s="12" t="n"/>
+      <c r="AK292" s="12" t="n"/>
+      <c r="AL292" s="12" t="n"/>
+      <c r="AM292" s="12" t="n"/>
+      <c r="AN292" s="12" t="n"/>
+      <c r="AO292" s="12" t="n"/>
+      <c r="AP292" s="12" t="n"/>
     </row>
     <row r="293" ht="22" customHeight="1">
       <c r="A293" s="9" t="n"/>
@@ -14140,6 +17100,16 @@
       <c r="AD293" s="10" t="n"/>
       <c r="AE293" s="10" t="n"/>
       <c r="AF293" s="10" t="n"/>
+      <c r="AG293" s="10" t="n"/>
+      <c r="AH293" s="10" t="n"/>
+      <c r="AI293" s="10" t="n"/>
+      <c r="AJ293" s="10" t="n"/>
+      <c r="AK293" s="10" t="n"/>
+      <c r="AL293" s="10" t="n"/>
+      <c r="AM293" s="10" t="n"/>
+      <c r="AN293" s="10" t="n"/>
+      <c r="AO293" s="10" t="n"/>
+      <c r="AP293" s="10" t="n"/>
     </row>
     <row r="294" ht="22" customHeight="1">
       <c r="A294" s="11" t="n"/>
@@ -14174,6 +17144,16 @@
       <c r="AD294" s="12" t="n"/>
       <c r="AE294" s="12" t="n"/>
       <c r="AF294" s="12" t="n"/>
+      <c r="AG294" s="12" t="n"/>
+      <c r="AH294" s="12" t="n"/>
+      <c r="AI294" s="12" t="n"/>
+      <c r="AJ294" s="12" t="n"/>
+      <c r="AK294" s="12" t="n"/>
+      <c r="AL294" s="12" t="n"/>
+      <c r="AM294" s="12" t="n"/>
+      <c r="AN294" s="12" t="n"/>
+      <c r="AO294" s="12" t="n"/>
+      <c r="AP294" s="12" t="n"/>
     </row>
     <row r="295" ht="22" customHeight="1">
       <c r="A295" s="9" t="n"/>
@@ -14208,6 +17188,16 @@
       <c r="AD295" s="10" t="n"/>
       <c r="AE295" s="10" t="n"/>
       <c r="AF295" s="10" t="n"/>
+      <c r="AG295" s="10" t="n"/>
+      <c r="AH295" s="10" t="n"/>
+      <c r="AI295" s="10" t="n"/>
+      <c r="AJ295" s="10" t="n"/>
+      <c r="AK295" s="10" t="n"/>
+      <c r="AL295" s="10" t="n"/>
+      <c r="AM295" s="10" t="n"/>
+      <c r="AN295" s="10" t="n"/>
+      <c r="AO295" s="10" t="n"/>
+      <c r="AP295" s="10" t="n"/>
     </row>
     <row r="296" ht="22" customHeight="1">
       <c r="A296" s="11" t="n"/>
@@ -14242,6 +17232,16 @@
       <c r="AD296" s="12" t="n"/>
       <c r="AE296" s="12" t="n"/>
       <c r="AF296" s="12" t="n"/>
+      <c r="AG296" s="12" t="n"/>
+      <c r="AH296" s="12" t="n"/>
+      <c r="AI296" s="12" t="n"/>
+      <c r="AJ296" s="12" t="n"/>
+      <c r="AK296" s="12" t="n"/>
+      <c r="AL296" s="12" t="n"/>
+      <c r="AM296" s="12" t="n"/>
+      <c r="AN296" s="12" t="n"/>
+      <c r="AO296" s="12" t="n"/>
+      <c r="AP296" s="12" t="n"/>
     </row>
     <row r="297" ht="22" customHeight="1">
       <c r="A297" s="9" t="n"/>
@@ -14276,6 +17276,16 @@
       <c r="AD297" s="10" t="n"/>
       <c r="AE297" s="10" t="n"/>
       <c r="AF297" s="10" t="n"/>
+      <c r="AG297" s="10" t="n"/>
+      <c r="AH297" s="10" t="n"/>
+      <c r="AI297" s="10" t="n"/>
+      <c r="AJ297" s="10" t="n"/>
+      <c r="AK297" s="10" t="n"/>
+      <c r="AL297" s="10" t="n"/>
+      <c r="AM297" s="10" t="n"/>
+      <c r="AN297" s="10" t="n"/>
+      <c r="AO297" s="10" t="n"/>
+      <c r="AP297" s="10" t="n"/>
     </row>
     <row r="298" ht="22" customHeight="1">
       <c r="A298" s="11" t="n"/>
@@ -14310,6 +17320,16 @@
       <c r="AD298" s="12" t="n"/>
       <c r="AE298" s="12" t="n"/>
       <c r="AF298" s="12" t="n"/>
+      <c r="AG298" s="12" t="n"/>
+      <c r="AH298" s="12" t="n"/>
+      <c r="AI298" s="12" t="n"/>
+      <c r="AJ298" s="12" t="n"/>
+      <c r="AK298" s="12" t="n"/>
+      <c r="AL298" s="12" t="n"/>
+      <c r="AM298" s="12" t="n"/>
+      <c r="AN298" s="12" t="n"/>
+      <c r="AO298" s="12" t="n"/>
+      <c r="AP298" s="12" t="n"/>
     </row>
     <row r="299" ht="22" customHeight="1">
       <c r="A299" s="9" t="n"/>
@@ -14344,6 +17364,16 @@
       <c r="AD299" s="10" t="n"/>
       <c r="AE299" s="10" t="n"/>
       <c r="AF299" s="10" t="n"/>
+      <c r="AG299" s="10" t="n"/>
+      <c r="AH299" s="10" t="n"/>
+      <c r="AI299" s="10" t="n"/>
+      <c r="AJ299" s="10" t="n"/>
+      <c r="AK299" s="10" t="n"/>
+      <c r="AL299" s="10" t="n"/>
+      <c r="AM299" s="10" t="n"/>
+      <c r="AN299" s="10" t="n"/>
+      <c r="AO299" s="10" t="n"/>
+      <c r="AP299" s="10" t="n"/>
     </row>
     <row r="300" ht="22" customHeight="1">
       <c r="A300" s="11" t="n"/>
@@ -14378,6 +17408,16 @@
       <c r="AD300" s="12" t="n"/>
       <c r="AE300" s="12" t="n"/>
       <c r="AF300" s="12" t="n"/>
+      <c r="AG300" s="12" t="n"/>
+      <c r="AH300" s="12" t="n"/>
+      <c r="AI300" s="12" t="n"/>
+      <c r="AJ300" s="12" t="n"/>
+      <c r="AK300" s="12" t="n"/>
+      <c r="AL300" s="12" t="n"/>
+      <c r="AM300" s="12" t="n"/>
+      <c r="AN300" s="12" t="n"/>
+      <c r="AO300" s="12" t="n"/>
+      <c r="AP300" s="12" t="n"/>
     </row>
     <row r="301" ht="22" customHeight="1">
       <c r="A301" s="9" t="n"/>
@@ -14412,6 +17452,16 @@
       <c r="AD301" s="10" t="n"/>
       <c r="AE301" s="10" t="n"/>
       <c r="AF301" s="10" t="n"/>
+      <c r="AG301" s="10" t="n"/>
+      <c r="AH301" s="10" t="n"/>
+      <c r="AI301" s="10" t="n"/>
+      <c r="AJ301" s="10" t="n"/>
+      <c r="AK301" s="10" t="n"/>
+      <c r="AL301" s="10" t="n"/>
+      <c r="AM301" s="10" t="n"/>
+      <c r="AN301" s="10" t="n"/>
+      <c r="AO301" s="10" t="n"/>
+      <c r="AP301" s="10" t="n"/>
     </row>
     <row r="302" ht="22" customHeight="1">
       <c r="A302" s="11" t="n"/>
@@ -14446,6 +17496,16 @@
       <c r="AD302" s="12" t="n"/>
       <c r="AE302" s="12" t="n"/>
       <c r="AF302" s="12" t="n"/>
+      <c r="AG302" s="12" t="n"/>
+      <c r="AH302" s="12" t="n"/>
+      <c r="AI302" s="12" t="n"/>
+      <c r="AJ302" s="12" t="n"/>
+      <c r="AK302" s="12" t="n"/>
+      <c r="AL302" s="12" t="n"/>
+      <c r="AM302" s="12" t="n"/>
+      <c r="AN302" s="12" t="n"/>
+      <c r="AO302" s="12" t="n"/>
+      <c r="AP302" s="12" t="n"/>
     </row>
     <row r="303" ht="22" customHeight="1">
       <c r="A303" s="9" t="n"/>
@@ -14480,6 +17540,16 @@
       <c r="AD303" s="10" t="n"/>
       <c r="AE303" s="10" t="n"/>
       <c r="AF303" s="10" t="n"/>
+      <c r="AG303" s="10" t="n"/>
+      <c r="AH303" s="10" t="n"/>
+      <c r="AI303" s="10" t="n"/>
+      <c r="AJ303" s="10" t="n"/>
+      <c r="AK303" s="10" t="n"/>
+      <c r="AL303" s="10" t="n"/>
+      <c r="AM303" s="10" t="n"/>
+      <c r="AN303" s="10" t="n"/>
+      <c r="AO303" s="10" t="n"/>
+      <c r="AP303" s="10" t="n"/>
     </row>
     <row r="304" ht="22" customHeight="1">
       <c r="A304" s="11" t="n"/>
@@ -14514,6 +17584,16 @@
       <c r="AD304" s="12" t="n"/>
       <c r="AE304" s="12" t="n"/>
       <c r="AF304" s="12" t="n"/>
+      <c r="AG304" s="12" t="n"/>
+      <c r="AH304" s="12" t="n"/>
+      <c r="AI304" s="12" t="n"/>
+      <c r="AJ304" s="12" t="n"/>
+      <c r="AK304" s="12" t="n"/>
+      <c r="AL304" s="12" t="n"/>
+      <c r="AM304" s="12" t="n"/>
+      <c r="AN304" s="12" t="n"/>
+      <c r="AO304" s="12" t="n"/>
+      <c r="AP304" s="12" t="n"/>
     </row>
     <row r="305" ht="22" customHeight="1">
       <c r="A305" s="9" t="n"/>
@@ -14548,6 +17628,16 @@
       <c r="AD305" s="10" t="n"/>
       <c r="AE305" s="10" t="n"/>
       <c r="AF305" s="10" t="n"/>
+      <c r="AG305" s="10" t="n"/>
+      <c r="AH305" s="10" t="n"/>
+      <c r="AI305" s="10" t="n"/>
+      <c r="AJ305" s="10" t="n"/>
+      <c r="AK305" s="10" t="n"/>
+      <c r="AL305" s="10" t="n"/>
+      <c r="AM305" s="10" t="n"/>
+      <c r="AN305" s="10" t="n"/>
+      <c r="AO305" s="10" t="n"/>
+      <c r="AP305" s="10" t="n"/>
     </row>
     <row r="306" ht="22" customHeight="1">
       <c r="A306" s="11" t="n"/>
@@ -14582,6 +17672,16 @@
       <c r="AD306" s="12" t="n"/>
       <c r="AE306" s="12" t="n"/>
       <c r="AF306" s="12" t="n"/>
+      <c r="AG306" s="12" t="n"/>
+      <c r="AH306" s="12" t="n"/>
+      <c r="AI306" s="12" t="n"/>
+      <c r="AJ306" s="12" t="n"/>
+      <c r="AK306" s="12" t="n"/>
+      <c r="AL306" s="12" t="n"/>
+      <c r="AM306" s="12" t="n"/>
+      <c r="AN306" s="12" t="n"/>
+      <c r="AO306" s="12" t="n"/>
+      <c r="AP306" s="12" t="n"/>
     </row>
     <row r="307" ht="22" customHeight="1">
       <c r="A307" s="9" t="n"/>
@@ -14616,6 +17716,16 @@
       <c r="AD307" s="10" t="n"/>
       <c r="AE307" s="10" t="n"/>
       <c r="AF307" s="10" t="n"/>
+      <c r="AG307" s="10" t="n"/>
+      <c r="AH307" s="10" t="n"/>
+      <c r="AI307" s="10" t="n"/>
+      <c r="AJ307" s="10" t="n"/>
+      <c r="AK307" s="10" t="n"/>
+      <c r="AL307" s="10" t="n"/>
+      <c r="AM307" s="10" t="n"/>
+      <c r="AN307" s="10" t="n"/>
+      <c r="AO307" s="10" t="n"/>
+      <c r="AP307" s="10" t="n"/>
     </row>
     <row r="308" ht="22" customHeight="1">
       <c r="A308" s="11" t="n"/>
@@ -14650,6 +17760,16 @@
       <c r="AD308" s="12" t="n"/>
       <c r="AE308" s="12" t="n"/>
       <c r="AF308" s="12" t="n"/>
+      <c r="AG308" s="12" t="n"/>
+      <c r="AH308" s="12" t="n"/>
+      <c r="AI308" s="12" t="n"/>
+      <c r="AJ308" s="12" t="n"/>
+      <c r="AK308" s="12" t="n"/>
+      <c r="AL308" s="12" t="n"/>
+      <c r="AM308" s="12" t="n"/>
+      <c r="AN308" s="12" t="n"/>
+      <c r="AO308" s="12" t="n"/>
+      <c r="AP308" s="12" t="n"/>
     </row>
     <row r="309" ht="22" customHeight="1">
       <c r="A309" s="9" t="n"/>
@@ -14684,6 +17804,16 @@
       <c r="AD309" s="10" t="n"/>
       <c r="AE309" s="10" t="n"/>
       <c r="AF309" s="10" t="n"/>
+      <c r="AG309" s="10" t="n"/>
+      <c r="AH309" s="10" t="n"/>
+      <c r="AI309" s="10" t="n"/>
+      <c r="AJ309" s="10" t="n"/>
+      <c r="AK309" s="10" t="n"/>
+      <c r="AL309" s="10" t="n"/>
+      <c r="AM309" s="10" t="n"/>
+      <c r="AN309" s="10" t="n"/>
+      <c r="AO309" s="10" t="n"/>
+      <c r="AP309" s="10" t="n"/>
     </row>
     <row r="310" ht="22" customHeight="1">
       <c r="A310" s="11" t="n"/>
@@ -14718,6 +17848,16 @@
       <c r="AD310" s="12" t="n"/>
       <c r="AE310" s="12" t="n"/>
       <c r="AF310" s="12" t="n"/>
+      <c r="AG310" s="12" t="n"/>
+      <c r="AH310" s="12" t="n"/>
+      <c r="AI310" s="12" t="n"/>
+      <c r="AJ310" s="12" t="n"/>
+      <c r="AK310" s="12" t="n"/>
+      <c r="AL310" s="12" t="n"/>
+      <c r="AM310" s="12" t="n"/>
+      <c r="AN310" s="12" t="n"/>
+      <c r="AO310" s="12" t="n"/>
+      <c r="AP310" s="12" t="n"/>
     </row>
     <row r="311" ht="22" customHeight="1">
       <c r="A311" s="9" t="n"/>
@@ -14752,6 +17892,16 @@
       <c r="AD311" s="10" t="n"/>
       <c r="AE311" s="10" t="n"/>
       <c r="AF311" s="10" t="n"/>
+      <c r="AG311" s="10" t="n"/>
+      <c r="AH311" s="10" t="n"/>
+      <c r="AI311" s="10" t="n"/>
+      <c r="AJ311" s="10" t="n"/>
+      <c r="AK311" s="10" t="n"/>
+      <c r="AL311" s="10" t="n"/>
+      <c r="AM311" s="10" t="n"/>
+      <c r="AN311" s="10" t="n"/>
+      <c r="AO311" s="10" t="n"/>
+      <c r="AP311" s="10" t="n"/>
     </row>
     <row r="312" ht="22" customHeight="1">
       <c r="A312" s="11" t="n"/>
@@ -14786,6 +17936,16 @@
       <c r="AD312" s="12" t="n"/>
       <c r="AE312" s="12" t="n"/>
       <c r="AF312" s="12" t="n"/>
+      <c r="AG312" s="12" t="n"/>
+      <c r="AH312" s="12" t="n"/>
+      <c r="AI312" s="12" t="n"/>
+      <c r="AJ312" s="12" t="n"/>
+      <c r="AK312" s="12" t="n"/>
+      <c r="AL312" s="12" t="n"/>
+      <c r="AM312" s="12" t="n"/>
+      <c r="AN312" s="12" t="n"/>
+      <c r="AO312" s="12" t="n"/>
+      <c r="AP312" s="12" t="n"/>
     </row>
     <row r="313" ht="22" customHeight="1">
       <c r="A313" s="9" t="n"/>
@@ -14820,6 +17980,16 @@
       <c r="AD313" s="10" t="n"/>
       <c r="AE313" s="10" t="n"/>
       <c r="AF313" s="10" t="n"/>
+      <c r="AG313" s="10" t="n"/>
+      <c r="AH313" s="10" t="n"/>
+      <c r="AI313" s="10" t="n"/>
+      <c r="AJ313" s="10" t="n"/>
+      <c r="AK313" s="10" t="n"/>
+      <c r="AL313" s="10" t="n"/>
+      <c r="AM313" s="10" t="n"/>
+      <c r="AN313" s="10" t="n"/>
+      <c r="AO313" s="10" t="n"/>
+      <c r="AP313" s="10" t="n"/>
     </row>
     <row r="314" ht="22" customHeight="1">
       <c r="A314" s="11" t="n"/>
@@ -14854,6 +18024,16 @@
       <c r="AD314" s="12" t="n"/>
       <c r="AE314" s="12" t="n"/>
       <c r="AF314" s="12" t="n"/>
+      <c r="AG314" s="12" t="n"/>
+      <c r="AH314" s="12" t="n"/>
+      <c r="AI314" s="12" t="n"/>
+      <c r="AJ314" s="12" t="n"/>
+      <c r="AK314" s="12" t="n"/>
+      <c r="AL314" s="12" t="n"/>
+      <c r="AM314" s="12" t="n"/>
+      <c r="AN314" s="12" t="n"/>
+      <c r="AO314" s="12" t="n"/>
+      <c r="AP314" s="12" t="n"/>
     </row>
     <row r="315" ht="22" customHeight="1">
       <c r="A315" s="9" t="n"/>
@@ -14888,6 +18068,16 @@
       <c r="AD315" s="10" t="n"/>
       <c r="AE315" s="10" t="n"/>
       <c r="AF315" s="10" t="n"/>
+      <c r="AG315" s="10" t="n"/>
+      <c r="AH315" s="10" t="n"/>
+      <c r="AI315" s="10" t="n"/>
+      <c r="AJ315" s="10" t="n"/>
+      <c r="AK315" s="10" t="n"/>
+      <c r="AL315" s="10" t="n"/>
+      <c r="AM315" s="10" t="n"/>
+      <c r="AN315" s="10" t="n"/>
+      <c r="AO315" s="10" t="n"/>
+      <c r="AP315" s="10" t="n"/>
     </row>
     <row r="316" ht="22" customHeight="1">
       <c r="A316" s="11" t="n"/>
@@ -14922,6 +18112,16 @@
       <c r="AD316" s="12" t="n"/>
       <c r="AE316" s="12" t="n"/>
       <c r="AF316" s="12" t="n"/>
+      <c r="AG316" s="12" t="n"/>
+      <c r="AH316" s="12" t="n"/>
+      <c r="AI316" s="12" t="n"/>
+      <c r="AJ316" s="12" t="n"/>
+      <c r="AK316" s="12" t="n"/>
+      <c r="AL316" s="12" t="n"/>
+      <c r="AM316" s="12" t="n"/>
+      <c r="AN316" s="12" t="n"/>
+      <c r="AO316" s="12" t="n"/>
+      <c r="AP316" s="12" t="n"/>
     </row>
     <row r="317" ht="22" customHeight="1">
       <c r="A317" s="9" t="n"/>
@@ -14956,6 +18156,16 @@
       <c r="AD317" s="10" t="n"/>
       <c r="AE317" s="10" t="n"/>
       <c r="AF317" s="10" t="n"/>
+      <c r="AG317" s="10" t="n"/>
+      <c r="AH317" s="10" t="n"/>
+      <c r="AI317" s="10" t="n"/>
+      <c r="AJ317" s="10" t="n"/>
+      <c r="AK317" s="10" t="n"/>
+      <c r="AL317" s="10" t="n"/>
+      <c r="AM317" s="10" t="n"/>
+      <c r="AN317" s="10" t="n"/>
+      <c r="AO317" s="10" t="n"/>
+      <c r="AP317" s="10" t="n"/>
     </row>
     <row r="318" ht="22" customHeight="1">
       <c r="A318" s="11" t="n"/>
@@ -14990,6 +18200,16 @@
       <c r="AD318" s="12" t="n"/>
       <c r="AE318" s="12" t="n"/>
       <c r="AF318" s="12" t="n"/>
+      <c r="AG318" s="12" t="n"/>
+      <c r="AH318" s="12" t="n"/>
+      <c r="AI318" s="12" t="n"/>
+      <c r="AJ318" s="12" t="n"/>
+      <c r="AK318" s="12" t="n"/>
+      <c r="AL318" s="12" t="n"/>
+      <c r="AM318" s="12" t="n"/>
+      <c r="AN318" s="12" t="n"/>
+      <c r="AO318" s="12" t="n"/>
+      <c r="AP318" s="12" t="n"/>
     </row>
     <row r="319" ht="22" customHeight="1">
       <c r="A319" s="9" t="n"/>
@@ -15024,6 +18244,16 @@
       <c r="AD319" s="10" t="n"/>
       <c r="AE319" s="10" t="n"/>
       <c r="AF319" s="10" t="n"/>
+      <c r="AG319" s="10" t="n"/>
+      <c r="AH319" s="10" t="n"/>
+      <c r="AI319" s="10" t="n"/>
+      <c r="AJ319" s="10" t="n"/>
+      <c r="AK319" s="10" t="n"/>
+      <c r="AL319" s="10" t="n"/>
+      <c r="AM319" s="10" t="n"/>
+      <c r="AN319" s="10" t="n"/>
+      <c r="AO319" s="10" t="n"/>
+      <c r="AP319" s="10" t="n"/>
     </row>
     <row r="320" ht="22" customHeight="1">
       <c r="A320" s="11" t="n"/>
@@ -15058,6 +18288,16 @@
       <c r="AD320" s="12" t="n"/>
       <c r="AE320" s="12" t="n"/>
       <c r="AF320" s="12" t="n"/>
+      <c r="AG320" s="12" t="n"/>
+      <c r="AH320" s="12" t="n"/>
+      <c r="AI320" s="12" t="n"/>
+      <c r="AJ320" s="12" t="n"/>
+      <c r="AK320" s="12" t="n"/>
+      <c r="AL320" s="12" t="n"/>
+      <c r="AM320" s="12" t="n"/>
+      <c r="AN320" s="12" t="n"/>
+      <c r="AO320" s="12" t="n"/>
+      <c r="AP320" s="12" t="n"/>
     </row>
     <row r="321" ht="22" customHeight="1">
       <c r="A321" s="9" t="n"/>
@@ -15092,6 +18332,16 @@
       <c r="AD321" s="10" t="n"/>
       <c r="AE321" s="10" t="n"/>
       <c r="AF321" s="10" t="n"/>
+      <c r="AG321" s="10" t="n"/>
+      <c r="AH321" s="10" t="n"/>
+      <c r="AI321" s="10" t="n"/>
+      <c r="AJ321" s="10" t="n"/>
+      <c r="AK321" s="10" t="n"/>
+      <c r="AL321" s="10" t="n"/>
+      <c r="AM321" s="10" t="n"/>
+      <c r="AN321" s="10" t="n"/>
+      <c r="AO321" s="10" t="n"/>
+      <c r="AP321" s="10" t="n"/>
     </row>
     <row r="322" ht="22" customHeight="1">
       <c r="A322" s="11" t="n"/>
@@ -15126,6 +18376,16 @@
       <c r="AD322" s="12" t="n"/>
       <c r="AE322" s="12" t="n"/>
       <c r="AF322" s="12" t="n"/>
+      <c r="AG322" s="12" t="n"/>
+      <c r="AH322" s="12" t="n"/>
+      <c r="AI322" s="12" t="n"/>
+      <c r="AJ322" s="12" t="n"/>
+      <c r="AK322" s="12" t="n"/>
+      <c r="AL322" s="12" t="n"/>
+      <c r="AM322" s="12" t="n"/>
+      <c r="AN322" s="12" t="n"/>
+      <c r="AO322" s="12" t="n"/>
+      <c r="AP322" s="12" t="n"/>
     </row>
     <row r="323" ht="22" customHeight="1">
       <c r="A323" s="9" t="n"/>
@@ -15160,6 +18420,16 @@
       <c r="AD323" s="10" t="n"/>
       <c r="AE323" s="10" t="n"/>
       <c r="AF323" s="10" t="n"/>
+      <c r="AG323" s="10" t="n"/>
+      <c r="AH323" s="10" t="n"/>
+      <c r="AI323" s="10" t="n"/>
+      <c r="AJ323" s="10" t="n"/>
+      <c r="AK323" s="10" t="n"/>
+      <c r="AL323" s="10" t="n"/>
+      <c r="AM323" s="10" t="n"/>
+      <c r="AN323" s="10" t="n"/>
+      <c r="AO323" s="10" t="n"/>
+      <c r="AP323" s="10" t="n"/>
     </row>
     <row r="324" ht="22" customHeight="1">
       <c r="A324" s="11" t="n"/>
@@ -15194,6 +18464,16 @@
       <c r="AD324" s="12" t="n"/>
       <c r="AE324" s="12" t="n"/>
       <c r="AF324" s="12" t="n"/>
+      <c r="AG324" s="12" t="n"/>
+      <c r="AH324" s="12" t="n"/>
+      <c r="AI324" s="12" t="n"/>
+      <c r="AJ324" s="12" t="n"/>
+      <c r="AK324" s="12" t="n"/>
+      <c r="AL324" s="12" t="n"/>
+      <c r="AM324" s="12" t="n"/>
+      <c r="AN324" s="12" t="n"/>
+      <c r="AO324" s="12" t="n"/>
+      <c r="AP324" s="12" t="n"/>
     </row>
     <row r="325" ht="22" customHeight="1">
       <c r="A325" s="9" t="n"/>
@@ -15228,6 +18508,16 @@
       <c r="AD325" s="10" t="n"/>
       <c r="AE325" s="10" t="n"/>
       <c r="AF325" s="10" t="n"/>
+      <c r="AG325" s="10" t="n"/>
+      <c r="AH325" s="10" t="n"/>
+      <c r="AI325" s="10" t="n"/>
+      <c r="AJ325" s="10" t="n"/>
+      <c r="AK325" s="10" t="n"/>
+      <c r="AL325" s="10" t="n"/>
+      <c r="AM325" s="10" t="n"/>
+      <c r="AN325" s="10" t="n"/>
+      <c r="AO325" s="10" t="n"/>
+      <c r="AP325" s="10" t="n"/>
     </row>
     <row r="326" ht="22" customHeight="1">
       <c r="A326" s="11" t="n"/>
@@ -15262,6 +18552,16 @@
       <c r="AD326" s="12" t="n"/>
       <c r="AE326" s="12" t="n"/>
       <c r="AF326" s="12" t="n"/>
+      <c r="AG326" s="12" t="n"/>
+      <c r="AH326" s="12" t="n"/>
+      <c r="AI326" s="12" t="n"/>
+      <c r="AJ326" s="12" t="n"/>
+      <c r="AK326" s="12" t="n"/>
+      <c r="AL326" s="12" t="n"/>
+      <c r="AM326" s="12" t="n"/>
+      <c r="AN326" s="12" t="n"/>
+      <c r="AO326" s="12" t="n"/>
+      <c r="AP326" s="12" t="n"/>
     </row>
     <row r="327" ht="22" customHeight="1">
       <c r="A327" s="9" t="n"/>
@@ -15296,6 +18596,16 @@
       <c r="AD327" s="10" t="n"/>
       <c r="AE327" s="10" t="n"/>
       <c r="AF327" s="10" t="n"/>
+      <c r="AG327" s="10" t="n"/>
+      <c r="AH327" s="10" t="n"/>
+      <c r="AI327" s="10" t="n"/>
+      <c r="AJ327" s="10" t="n"/>
+      <c r="AK327" s="10" t="n"/>
+      <c r="AL327" s="10" t="n"/>
+      <c r="AM327" s="10" t="n"/>
+      <c r="AN327" s="10" t="n"/>
+      <c r="AO327" s="10" t="n"/>
+      <c r="AP327" s="10" t="n"/>
     </row>
     <row r="328" ht="22" customHeight="1">
       <c r="A328" s="11" t="n"/>
@@ -15330,6 +18640,16 @@
       <c r="AD328" s="12" t="n"/>
       <c r="AE328" s="12" t="n"/>
       <c r="AF328" s="12" t="n"/>
+      <c r="AG328" s="12" t="n"/>
+      <c r="AH328" s="12" t="n"/>
+      <c r="AI328" s="12" t="n"/>
+      <c r="AJ328" s="12" t="n"/>
+      <c r="AK328" s="12" t="n"/>
+      <c r="AL328" s="12" t="n"/>
+      <c r="AM328" s="12" t="n"/>
+      <c r="AN328" s="12" t="n"/>
+      <c r="AO328" s="12" t="n"/>
+      <c r="AP328" s="12" t="n"/>
     </row>
     <row r="329" ht="22" customHeight="1">
       <c r="A329" s="9" t="n"/>
@@ -15364,6 +18684,16 @@
       <c r="AD329" s="10" t="n"/>
       <c r="AE329" s="10" t="n"/>
       <c r="AF329" s="10" t="n"/>
+      <c r="AG329" s="10" t="n"/>
+      <c r="AH329" s="10" t="n"/>
+      <c r="AI329" s="10" t="n"/>
+      <c r="AJ329" s="10" t="n"/>
+      <c r="AK329" s="10" t="n"/>
+      <c r="AL329" s="10" t="n"/>
+      <c r="AM329" s="10" t="n"/>
+      <c r="AN329" s="10" t="n"/>
+      <c r="AO329" s="10" t="n"/>
+      <c r="AP329" s="10" t="n"/>
     </row>
     <row r="330" ht="22" customHeight="1">
       <c r="A330" s="11" t="n"/>
@@ -15398,6 +18728,16 @@
       <c r="AD330" s="12" t="n"/>
       <c r="AE330" s="12" t="n"/>
       <c r="AF330" s="12" t="n"/>
+      <c r="AG330" s="12" t="n"/>
+      <c r="AH330" s="12" t="n"/>
+      <c r="AI330" s="12" t="n"/>
+      <c r="AJ330" s="12" t="n"/>
+      <c r="AK330" s="12" t="n"/>
+      <c r="AL330" s="12" t="n"/>
+      <c r="AM330" s="12" t="n"/>
+      <c r="AN330" s="12" t="n"/>
+      <c r="AO330" s="12" t="n"/>
+      <c r="AP330" s="12" t="n"/>
     </row>
     <row r="331" ht="22" customHeight="1">
       <c r="A331" s="9" t="n"/>
@@ -15432,6 +18772,16 @@
       <c r="AD331" s="10" t="n"/>
       <c r="AE331" s="10" t="n"/>
       <c r="AF331" s="10" t="n"/>
+      <c r="AG331" s="10" t="n"/>
+      <c r="AH331" s="10" t="n"/>
+      <c r="AI331" s="10" t="n"/>
+      <c r="AJ331" s="10" t="n"/>
+      <c r="AK331" s="10" t="n"/>
+      <c r="AL331" s="10" t="n"/>
+      <c r="AM331" s="10" t="n"/>
+      <c r="AN331" s="10" t="n"/>
+      <c r="AO331" s="10" t="n"/>
+      <c r="AP331" s="10" t="n"/>
     </row>
     <row r="332" ht="22" customHeight="1">
       <c r="A332" s="11" t="n"/>
@@ -15466,6 +18816,16 @@
       <c r="AD332" s="12" t="n"/>
       <c r="AE332" s="12" t="n"/>
       <c r="AF332" s="12" t="n"/>
+      <c r="AG332" s="12" t="n"/>
+      <c r="AH332" s="12" t="n"/>
+      <c r="AI332" s="12" t="n"/>
+      <c r="AJ332" s="12" t="n"/>
+      <c r="AK332" s="12" t="n"/>
+      <c r="AL332" s="12" t="n"/>
+      <c r="AM332" s="12" t="n"/>
+      <c r="AN332" s="12" t="n"/>
+      <c r="AO332" s="12" t="n"/>
+      <c r="AP332" s="12" t="n"/>
     </row>
     <row r="333" ht="22" customHeight="1">
       <c r="A333" s="9" t="n"/>
@@ -15500,6 +18860,16 @@
       <c r="AD333" s="10" t="n"/>
       <c r="AE333" s="10" t="n"/>
       <c r="AF333" s="10" t="n"/>
+      <c r="AG333" s="10" t="n"/>
+      <c r="AH333" s="10" t="n"/>
+      <c r="AI333" s="10" t="n"/>
+      <c r="AJ333" s="10" t="n"/>
+      <c r="AK333" s="10" t="n"/>
+      <c r="AL333" s="10" t="n"/>
+      <c r="AM333" s="10" t="n"/>
+      <c r="AN333" s="10" t="n"/>
+      <c r="AO333" s="10" t="n"/>
+      <c r="AP333" s="10" t="n"/>
     </row>
     <row r="334" ht="22" customHeight="1">
       <c r="A334" s="11" t="n"/>
@@ -15534,6 +18904,16 @@
       <c r="AD334" s="12" t="n"/>
       <c r="AE334" s="12" t="n"/>
       <c r="AF334" s="12" t="n"/>
+      <c r="AG334" s="12" t="n"/>
+      <c r="AH334" s="12" t="n"/>
+      <c r="AI334" s="12" t="n"/>
+      <c r="AJ334" s="12" t="n"/>
+      <c r="AK334" s="12" t="n"/>
+      <c r="AL334" s="12" t="n"/>
+      <c r="AM334" s="12" t="n"/>
+      <c r="AN334" s="12" t="n"/>
+      <c r="AO334" s="12" t="n"/>
+      <c r="AP334" s="12" t="n"/>
     </row>
     <row r="335" ht="22" customHeight="1">
       <c r="A335" s="9" t="n"/>
@@ -15568,6 +18948,16 @@
       <c r="AD335" s="10" t="n"/>
       <c r="AE335" s="10" t="n"/>
       <c r="AF335" s="10" t="n"/>
+      <c r="AG335" s="10" t="n"/>
+      <c r="AH335" s="10" t="n"/>
+      <c r="AI335" s="10" t="n"/>
+      <c r="AJ335" s="10" t="n"/>
+      <c r="AK335" s="10" t="n"/>
+      <c r="AL335" s="10" t="n"/>
+      <c r="AM335" s="10" t="n"/>
+      <c r="AN335" s="10" t="n"/>
+      <c r="AO335" s="10" t="n"/>
+      <c r="AP335" s="10" t="n"/>
     </row>
     <row r="336" ht="22" customHeight="1">
       <c r="A336" s="11" t="n"/>
@@ -15602,6 +18992,16 @@
       <c r="AD336" s="12" t="n"/>
       <c r="AE336" s="12" t="n"/>
       <c r="AF336" s="12" t="n"/>
+      <c r="AG336" s="12" t="n"/>
+      <c r="AH336" s="12" t="n"/>
+      <c r="AI336" s="12" t="n"/>
+      <c r="AJ336" s="12" t="n"/>
+      <c r="AK336" s="12" t="n"/>
+      <c r="AL336" s="12" t="n"/>
+      <c r="AM336" s="12" t="n"/>
+      <c r="AN336" s="12" t="n"/>
+      <c r="AO336" s="12" t="n"/>
+      <c r="AP336" s="12" t="n"/>
     </row>
     <row r="337" ht="22" customHeight="1">
       <c r="A337" s="9" t="n"/>
@@ -15636,6 +19036,16 @@
       <c r="AD337" s="10" t="n"/>
       <c r="AE337" s="10" t="n"/>
       <c r="AF337" s="10" t="n"/>
+      <c r="AG337" s="10" t="n"/>
+      <c r="AH337" s="10" t="n"/>
+      <c r="AI337" s="10" t="n"/>
+      <c r="AJ337" s="10" t="n"/>
+      <c r="AK337" s="10" t="n"/>
+      <c r="AL337" s="10" t="n"/>
+      <c r="AM337" s="10" t="n"/>
+      <c r="AN337" s="10" t="n"/>
+      <c r="AO337" s="10" t="n"/>
+      <c r="AP337" s="10" t="n"/>
     </row>
     <row r="338" ht="22" customHeight="1">
       <c r="A338" s="11" t="n"/>
@@ -15670,6 +19080,16 @@
       <c r="AD338" s="12" t="n"/>
       <c r="AE338" s="12" t="n"/>
       <c r="AF338" s="12" t="n"/>
+      <c r="AG338" s="12" t="n"/>
+      <c r="AH338" s="12" t="n"/>
+      <c r="AI338" s="12" t="n"/>
+      <c r="AJ338" s="12" t="n"/>
+      <c r="AK338" s="12" t="n"/>
+      <c r="AL338" s="12" t="n"/>
+      <c r="AM338" s="12" t="n"/>
+      <c r="AN338" s="12" t="n"/>
+      <c r="AO338" s="12" t="n"/>
+      <c r="AP338" s="12" t="n"/>
     </row>
     <row r="339" ht="22" customHeight="1">
       <c r="A339" s="9" t="n"/>
@@ -15704,6 +19124,16 @@
       <c r="AD339" s="10" t="n"/>
       <c r="AE339" s="10" t="n"/>
       <c r="AF339" s="10" t="n"/>
+      <c r="AG339" s="10" t="n"/>
+      <c r="AH339" s="10" t="n"/>
+      <c r="AI339" s="10" t="n"/>
+      <c r="AJ339" s="10" t="n"/>
+      <c r="AK339" s="10" t="n"/>
+      <c r="AL339" s="10" t="n"/>
+      <c r="AM339" s="10" t="n"/>
+      <c r="AN339" s="10" t="n"/>
+      <c r="AO339" s="10" t="n"/>
+      <c r="AP339" s="10" t="n"/>
     </row>
     <row r="340" ht="22" customHeight="1">
       <c r="A340" s="11" t="n"/>
@@ -15738,6 +19168,16 @@
       <c r="AD340" s="12" t="n"/>
       <c r="AE340" s="12" t="n"/>
       <c r="AF340" s="12" t="n"/>
+      <c r="AG340" s="12" t="n"/>
+      <c r="AH340" s="12" t="n"/>
+      <c r="AI340" s="12" t="n"/>
+      <c r="AJ340" s="12" t="n"/>
+      <c r="AK340" s="12" t="n"/>
+      <c r="AL340" s="12" t="n"/>
+      <c r="AM340" s="12" t="n"/>
+      <c r="AN340" s="12" t="n"/>
+      <c r="AO340" s="12" t="n"/>
+      <c r="AP340" s="12" t="n"/>
     </row>
     <row r="341" ht="22" customHeight="1">
       <c r="A341" s="9" t="n"/>
@@ -15772,6 +19212,16 @@
       <c r="AD341" s="10" t="n"/>
       <c r="AE341" s="10" t="n"/>
       <c r="AF341" s="10" t="n"/>
+      <c r="AG341" s="10" t="n"/>
+      <c r="AH341" s="10" t="n"/>
+      <c r="AI341" s="10" t="n"/>
+      <c r="AJ341" s="10" t="n"/>
+      <c r="AK341" s="10" t="n"/>
+      <c r="AL341" s="10" t="n"/>
+      <c r="AM341" s="10" t="n"/>
+      <c r="AN341" s="10" t="n"/>
+      <c r="AO341" s="10" t="n"/>
+      <c r="AP341" s="10" t="n"/>
     </row>
     <row r="342" ht="22" customHeight="1">
       <c r="A342" s="11" t="n"/>
@@ -15806,6 +19256,16 @@
       <c r="AD342" s="12" t="n"/>
       <c r="AE342" s="12" t="n"/>
       <c r="AF342" s="12" t="n"/>
+      <c r="AG342" s="12" t="n"/>
+      <c r="AH342" s="12" t="n"/>
+      <c r="AI342" s="12" t="n"/>
+      <c r="AJ342" s="12" t="n"/>
+      <c r="AK342" s="12" t="n"/>
+      <c r="AL342" s="12" t="n"/>
+      <c r="AM342" s="12" t="n"/>
+      <c r="AN342" s="12" t="n"/>
+      <c r="AO342" s="12" t="n"/>
+      <c r="AP342" s="12" t="n"/>
     </row>
     <row r="343" ht="22" customHeight="1">
       <c r="A343" s="9" t="n"/>
@@ -15840,6 +19300,16 @@
       <c r="AD343" s="10" t="n"/>
       <c r="AE343" s="10" t="n"/>
       <c r="AF343" s="10" t="n"/>
+      <c r="AG343" s="10" t="n"/>
+      <c r="AH343" s="10" t="n"/>
+      <c r="AI343" s="10" t="n"/>
+      <c r="AJ343" s="10" t="n"/>
+      <c r="AK343" s="10" t="n"/>
+      <c r="AL343" s="10" t="n"/>
+      <c r="AM343" s="10" t="n"/>
+      <c r="AN343" s="10" t="n"/>
+      <c r="AO343" s="10" t="n"/>
+      <c r="AP343" s="10" t="n"/>
     </row>
     <row r="344" ht="22" customHeight="1">
       <c r="A344" s="11" t="n"/>
@@ -15874,6 +19344,16 @@
       <c r="AD344" s="12" t="n"/>
       <c r="AE344" s="12" t="n"/>
       <c r="AF344" s="12" t="n"/>
+      <c r="AG344" s="12" t="n"/>
+      <c r="AH344" s="12" t="n"/>
+      <c r="AI344" s="12" t="n"/>
+      <c r="AJ344" s="12" t="n"/>
+      <c r="AK344" s="12" t="n"/>
+      <c r="AL344" s="12" t="n"/>
+      <c r="AM344" s="12" t="n"/>
+      <c r="AN344" s="12" t="n"/>
+      <c r="AO344" s="12" t="n"/>
+      <c r="AP344" s="12" t="n"/>
     </row>
     <row r="345" ht="22" customHeight="1">
       <c r="A345" s="9" t="n"/>
@@ -15908,6 +19388,16 @@
       <c r="AD345" s="10" t="n"/>
       <c r="AE345" s="10" t="n"/>
       <c r="AF345" s="10" t="n"/>
+      <c r="AG345" s="10" t="n"/>
+      <c r="AH345" s="10" t="n"/>
+      <c r="AI345" s="10" t="n"/>
+      <c r="AJ345" s="10" t="n"/>
+      <c r="AK345" s="10" t="n"/>
+      <c r="AL345" s="10" t="n"/>
+      <c r="AM345" s="10" t="n"/>
+      <c r="AN345" s="10" t="n"/>
+      <c r="AO345" s="10" t="n"/>
+      <c r="AP345" s="10" t="n"/>
     </row>
     <row r="346" ht="22" customHeight="1">
       <c r="A346" s="11" t="n"/>
@@ -15942,6 +19432,16 @@
       <c r="AD346" s="12" t="n"/>
       <c r="AE346" s="12" t="n"/>
       <c r="AF346" s="12" t="n"/>
+      <c r="AG346" s="12" t="n"/>
+      <c r="AH346" s="12" t="n"/>
+      <c r="AI346" s="12" t="n"/>
+      <c r="AJ346" s="12" t="n"/>
+      <c r="AK346" s="12" t="n"/>
+      <c r="AL346" s="12" t="n"/>
+      <c r="AM346" s="12" t="n"/>
+      <c r="AN346" s="12" t="n"/>
+      <c r="AO346" s="12" t="n"/>
+      <c r="AP346" s="12" t="n"/>
     </row>
     <row r="347" ht="22" customHeight="1">
       <c r="A347" s="9" t="n"/>
@@ -15976,6 +19476,16 @@
       <c r="AD347" s="10" t="n"/>
       <c r="AE347" s="10" t="n"/>
       <c r="AF347" s="10" t="n"/>
+      <c r="AG347" s="10" t="n"/>
+      <c r="AH347" s="10" t="n"/>
+      <c r="AI347" s="10" t="n"/>
+      <c r="AJ347" s="10" t="n"/>
+      <c r="AK347" s="10" t="n"/>
+      <c r="AL347" s="10" t="n"/>
+      <c r="AM347" s="10" t="n"/>
+      <c r="AN347" s="10" t="n"/>
+      <c r="AO347" s="10" t="n"/>
+      <c r="AP347" s="10" t="n"/>
     </row>
     <row r="348" ht="22" customHeight="1">
       <c r="A348" s="11" t="n"/>
@@ -16010,6 +19520,16 @@
       <c r="AD348" s="12" t="n"/>
       <c r="AE348" s="12" t="n"/>
       <c r="AF348" s="12" t="n"/>
+      <c r="AG348" s="12" t="n"/>
+      <c r="AH348" s="12" t="n"/>
+      <c r="AI348" s="12" t="n"/>
+      <c r="AJ348" s="12" t="n"/>
+      <c r="AK348" s="12" t="n"/>
+      <c r="AL348" s="12" t="n"/>
+      <c r="AM348" s="12" t="n"/>
+      <c r="AN348" s="12" t="n"/>
+      <c r="AO348" s="12" t="n"/>
+      <c r="AP348" s="12" t="n"/>
     </row>
     <row r="349" ht="22" customHeight="1">
       <c r="A349" s="9" t="n"/>
@@ -16044,6 +19564,16 @@
       <c r="AD349" s="10" t="n"/>
       <c r="AE349" s="10" t="n"/>
       <c r="AF349" s="10" t="n"/>
+      <c r="AG349" s="10" t="n"/>
+      <c r="AH349" s="10" t="n"/>
+      <c r="AI349" s="10" t="n"/>
+      <c r="AJ349" s="10" t="n"/>
+      <c r="AK349" s="10" t="n"/>
+      <c r="AL349" s="10" t="n"/>
+      <c r="AM349" s="10" t="n"/>
+      <c r="AN349" s="10" t="n"/>
+      <c r="AO349" s="10" t="n"/>
+      <c r="AP349" s="10" t="n"/>
     </row>
     <row r="350" ht="22" customHeight="1">
       <c r="A350" s="11" t="n"/>
@@ -16078,6 +19608,16 @@
       <c r="AD350" s="12" t="n"/>
       <c r="AE350" s="12" t="n"/>
       <c r="AF350" s="12" t="n"/>
+      <c r="AG350" s="12" t="n"/>
+      <c r="AH350" s="12" t="n"/>
+      <c r="AI350" s="12" t="n"/>
+      <c r="AJ350" s="12" t="n"/>
+      <c r="AK350" s="12" t="n"/>
+      <c r="AL350" s="12" t="n"/>
+      <c r="AM350" s="12" t="n"/>
+      <c r="AN350" s="12" t="n"/>
+      <c r="AO350" s="12" t="n"/>
+      <c r="AP350" s="12" t="n"/>
     </row>
     <row r="351" ht="22" customHeight="1">
       <c r="A351" s="9" t="n"/>
@@ -16112,6 +19652,16 @@
       <c r="AD351" s="10" t="n"/>
       <c r="AE351" s="10" t="n"/>
       <c r="AF351" s="10" t="n"/>
+      <c r="AG351" s="10" t="n"/>
+      <c r="AH351" s="10" t="n"/>
+      <c r="AI351" s="10" t="n"/>
+      <c r="AJ351" s="10" t="n"/>
+      <c r="AK351" s="10" t="n"/>
+      <c r="AL351" s="10" t="n"/>
+      <c r="AM351" s="10" t="n"/>
+      <c r="AN351" s="10" t="n"/>
+      <c r="AO351" s="10" t="n"/>
+      <c r="AP351" s="10" t="n"/>
     </row>
     <row r="352" ht="22" customHeight="1">
       <c r="A352" s="11" t="n"/>
@@ -16146,6 +19696,16 @@
       <c r="AD352" s="12" t="n"/>
       <c r="AE352" s="12" t="n"/>
       <c r="AF352" s="12" t="n"/>
+      <c r="AG352" s="12" t="n"/>
+      <c r="AH352" s="12" t="n"/>
+      <c r="AI352" s="12" t="n"/>
+      <c r="AJ352" s="12" t="n"/>
+      <c r="AK352" s="12" t="n"/>
+      <c r="AL352" s="12" t="n"/>
+      <c r="AM352" s="12" t="n"/>
+      <c r="AN352" s="12" t="n"/>
+      <c r="AO352" s="12" t="n"/>
+      <c r="AP352" s="12" t="n"/>
     </row>
     <row r="353" ht="22" customHeight="1">
       <c r="A353" s="9" t="n"/>
@@ -16180,6 +19740,16 @@
       <c r="AD353" s="10" t="n"/>
       <c r="AE353" s="10" t="n"/>
       <c r="AF353" s="10" t="n"/>
+      <c r="AG353" s="10" t="n"/>
+      <c r="AH353" s="10" t="n"/>
+      <c r="AI353" s="10" t="n"/>
+      <c r="AJ353" s="10" t="n"/>
+      <c r="AK353" s="10" t="n"/>
+      <c r="AL353" s="10" t="n"/>
+      <c r="AM353" s="10" t="n"/>
+      <c r="AN353" s="10" t="n"/>
+      <c r="AO353" s="10" t="n"/>
+      <c r="AP353" s="10" t="n"/>
     </row>
     <row r="354" ht="22" customHeight="1">
       <c r="A354" s="11" t="n"/>
@@ -16214,6 +19784,16 @@
       <c r="AD354" s="12" t="n"/>
       <c r="AE354" s="12" t="n"/>
       <c r="AF354" s="12" t="n"/>
+      <c r="AG354" s="12" t="n"/>
+      <c r="AH354" s="12" t="n"/>
+      <c r="AI354" s="12" t="n"/>
+      <c r="AJ354" s="12" t="n"/>
+      <c r="AK354" s="12" t="n"/>
+      <c r="AL354" s="12" t="n"/>
+      <c r="AM354" s="12" t="n"/>
+      <c r="AN354" s="12" t="n"/>
+      <c r="AO354" s="12" t="n"/>
+      <c r="AP354" s="12" t="n"/>
     </row>
     <row r="355" ht="22" customHeight="1">
       <c r="A355" s="9" t="n"/>
@@ -16248,6 +19828,16 @@
       <c r="AD355" s="10" t="n"/>
       <c r="AE355" s="10" t="n"/>
       <c r="AF355" s="10" t="n"/>
+      <c r="AG355" s="10" t="n"/>
+      <c r="AH355" s="10" t="n"/>
+      <c r="AI355" s="10" t="n"/>
+      <c r="AJ355" s="10" t="n"/>
+      <c r="AK355" s="10" t="n"/>
+      <c r="AL355" s="10" t="n"/>
+      <c r="AM355" s="10" t="n"/>
+      <c r="AN355" s="10" t="n"/>
+      <c r="AO355" s="10" t="n"/>
+      <c r="AP355" s="10" t="n"/>
     </row>
     <row r="356" ht="22" customHeight="1">
       <c r="A356" s="11" t="n"/>
@@ -16282,6 +19872,16 @@
       <c r="AD356" s="12" t="n"/>
       <c r="AE356" s="12" t="n"/>
       <c r="AF356" s="12" t="n"/>
+      <c r="AG356" s="12" t="n"/>
+      <c r="AH356" s="12" t="n"/>
+      <c r="AI356" s="12" t="n"/>
+      <c r="AJ356" s="12" t="n"/>
+      <c r="AK356" s="12" t="n"/>
+      <c r="AL356" s="12" t="n"/>
+      <c r="AM356" s="12" t="n"/>
+      <c r="AN356" s="12" t="n"/>
+      <c r="AO356" s="12" t="n"/>
+      <c r="AP356" s="12" t="n"/>
     </row>
     <row r="357" ht="22" customHeight="1">
       <c r="A357" s="9" t="n"/>
@@ -16316,6 +19916,16 @@
       <c r="AD357" s="10" t="n"/>
       <c r="AE357" s="10" t="n"/>
       <c r="AF357" s="10" t="n"/>
+      <c r="AG357" s="10" t="n"/>
+      <c r="AH357" s="10" t="n"/>
+      <c r="AI357" s="10" t="n"/>
+      <c r="AJ357" s="10" t="n"/>
+      <c r="AK357" s="10" t="n"/>
+      <c r="AL357" s="10" t="n"/>
+      <c r="AM357" s="10" t="n"/>
+      <c r="AN357" s="10" t="n"/>
+      <c r="AO357" s="10" t="n"/>
+      <c r="AP357" s="10" t="n"/>
     </row>
     <row r="358" ht="22" customHeight="1">
       <c r="A358" s="11" t="n"/>
@@ -16350,6 +19960,16 @@
       <c r="AD358" s="12" t="n"/>
       <c r="AE358" s="12" t="n"/>
       <c r="AF358" s="12" t="n"/>
+      <c r="AG358" s="12" t="n"/>
+      <c r="AH358" s="12" t="n"/>
+      <c r="AI358" s="12" t="n"/>
+      <c r="AJ358" s="12" t="n"/>
+      <c r="AK358" s="12" t="n"/>
+      <c r="AL358" s="12" t="n"/>
+      <c r="AM358" s="12" t="n"/>
+      <c r="AN358" s="12" t="n"/>
+      <c r="AO358" s="12" t="n"/>
+      <c r="AP358" s="12" t="n"/>
     </row>
     <row r="359" ht="22" customHeight="1">
       <c r="A359" s="9" t="n"/>
@@ -16384,6 +20004,16 @@
       <c r="AD359" s="10" t="n"/>
       <c r="AE359" s="10" t="n"/>
       <c r="AF359" s="10" t="n"/>
+      <c r="AG359" s="10" t="n"/>
+      <c r="AH359" s="10" t="n"/>
+      <c r="AI359" s="10" t="n"/>
+      <c r="AJ359" s="10" t="n"/>
+      <c r="AK359" s="10" t="n"/>
+      <c r="AL359" s="10" t="n"/>
+      <c r="AM359" s="10" t="n"/>
+      <c r="AN359" s="10" t="n"/>
+      <c r="AO359" s="10" t="n"/>
+      <c r="AP359" s="10" t="n"/>
     </row>
     <row r="360" ht="22" customHeight="1">
       <c r="A360" s="11" t="n"/>
@@ -16418,6 +20048,16 @@
       <c r="AD360" s="12" t="n"/>
       <c r="AE360" s="12" t="n"/>
       <c r="AF360" s="12" t="n"/>
+      <c r="AG360" s="12" t="n"/>
+      <c r="AH360" s="12" t="n"/>
+      <c r="AI360" s="12" t="n"/>
+      <c r="AJ360" s="12" t="n"/>
+      <c r="AK360" s="12" t="n"/>
+      <c r="AL360" s="12" t="n"/>
+      <c r="AM360" s="12" t="n"/>
+      <c r="AN360" s="12" t="n"/>
+      <c r="AO360" s="12" t="n"/>
+      <c r="AP360" s="12" t="n"/>
     </row>
     <row r="361" ht="22" customHeight="1">
       <c r="A361" s="9" t="n"/>
@@ -16452,6 +20092,16 @@
       <c r="AD361" s="10" t="n"/>
       <c r="AE361" s="10" t="n"/>
       <c r="AF361" s="10" t="n"/>
+      <c r="AG361" s="10" t="n"/>
+      <c r="AH361" s="10" t="n"/>
+      <c r="AI361" s="10" t="n"/>
+      <c r="AJ361" s="10" t="n"/>
+      <c r="AK361" s="10" t="n"/>
+      <c r="AL361" s="10" t="n"/>
+      <c r="AM361" s="10" t="n"/>
+      <c r="AN361" s="10" t="n"/>
+      <c r="AO361" s="10" t="n"/>
+      <c r="AP361" s="10" t="n"/>
     </row>
     <row r="362" ht="22" customHeight="1">
       <c r="A362" s="11" t="n"/>
@@ -16486,6 +20136,16 @@
       <c r="AD362" s="12" t="n"/>
       <c r="AE362" s="12" t="n"/>
       <c r="AF362" s="12" t="n"/>
+      <c r="AG362" s="12" t="n"/>
+      <c r="AH362" s="12" t="n"/>
+      <c r="AI362" s="12" t="n"/>
+      <c r="AJ362" s="12" t="n"/>
+      <c r="AK362" s="12" t="n"/>
+      <c r="AL362" s="12" t="n"/>
+      <c r="AM362" s="12" t="n"/>
+      <c r="AN362" s="12" t="n"/>
+      <c r="AO362" s="12" t="n"/>
+      <c r="AP362" s="12" t="n"/>
     </row>
     <row r="363" ht="22" customHeight="1">
       <c r="A363" s="9" t="n"/>
@@ -16520,6 +20180,16 @@
       <c r="AD363" s="10" t="n"/>
       <c r="AE363" s="10" t="n"/>
       <c r="AF363" s="10" t="n"/>
+      <c r="AG363" s="10" t="n"/>
+      <c r="AH363" s="10" t="n"/>
+      <c r="AI363" s="10" t="n"/>
+      <c r="AJ363" s="10" t="n"/>
+      <c r="AK363" s="10" t="n"/>
+      <c r="AL363" s="10" t="n"/>
+      <c r="AM363" s="10" t="n"/>
+      <c r="AN363" s="10" t="n"/>
+      <c r="AO363" s="10" t="n"/>
+      <c r="AP363" s="10" t="n"/>
     </row>
     <row r="364" ht="22" customHeight="1">
       <c r="A364" s="11" t="n"/>
@@ -16554,6 +20224,16 @@
       <c r="AD364" s="12" t="n"/>
       <c r="AE364" s="12" t="n"/>
       <c r="AF364" s="12" t="n"/>
+      <c r="AG364" s="12" t="n"/>
+      <c r="AH364" s="12" t="n"/>
+      <c r="AI364" s="12" t="n"/>
+      <c r="AJ364" s="12" t="n"/>
+      <c r="AK364" s="12" t="n"/>
+      <c r="AL364" s="12" t="n"/>
+      <c r="AM364" s="12" t="n"/>
+      <c r="AN364" s="12" t="n"/>
+      <c r="AO364" s="12" t="n"/>
+      <c r="AP364" s="12" t="n"/>
     </row>
     <row r="365" ht="22" customHeight="1">
       <c r="A365" s="9" t="n"/>
@@ -16588,6 +20268,16 @@
       <c r="AD365" s="10" t="n"/>
       <c r="AE365" s="10" t="n"/>
       <c r="AF365" s="10" t="n"/>
+      <c r="AG365" s="10" t="n"/>
+      <c r="AH365" s="10" t="n"/>
+      <c r="AI365" s="10" t="n"/>
+      <c r="AJ365" s="10" t="n"/>
+      <c r="AK365" s="10" t="n"/>
+      <c r="AL365" s="10" t="n"/>
+      <c r="AM365" s="10" t="n"/>
+      <c r="AN365" s="10" t="n"/>
+      <c r="AO365" s="10" t="n"/>
+      <c r="AP365" s="10" t="n"/>
     </row>
     <row r="366" ht="22" customHeight="1">
       <c r="A366" s="11" t="n"/>
@@ -16622,6 +20312,16 @@
       <c r="AD366" s="12" t="n"/>
       <c r="AE366" s="12" t="n"/>
       <c r="AF366" s="12" t="n"/>
+      <c r="AG366" s="12" t="n"/>
+      <c r="AH366" s="12" t="n"/>
+      <c r="AI366" s="12" t="n"/>
+      <c r="AJ366" s="12" t="n"/>
+      <c r="AK366" s="12" t="n"/>
+      <c r="AL366" s="12" t="n"/>
+      <c r="AM366" s="12" t="n"/>
+      <c r="AN366" s="12" t="n"/>
+      <c r="AO366" s="12" t="n"/>
+      <c r="AP366" s="12" t="n"/>
     </row>
     <row r="367" ht="22" customHeight="1">
       <c r="A367" s="9" t="n"/>
@@ -16656,6 +20356,16 @@
       <c r="AD367" s="10" t="n"/>
       <c r="AE367" s="10" t="n"/>
       <c r="AF367" s="10" t="n"/>
+      <c r="AG367" s="10" t="n"/>
+      <c r="AH367" s="10" t="n"/>
+      <c r="AI367" s="10" t="n"/>
+      <c r="AJ367" s="10" t="n"/>
+      <c r="AK367" s="10" t="n"/>
+      <c r="AL367" s="10" t="n"/>
+      <c r="AM367" s="10" t="n"/>
+      <c r="AN367" s="10" t="n"/>
+      <c r="AO367" s="10" t="n"/>
+      <c r="AP367" s="10" t="n"/>
     </row>
     <row r="368" ht="22" customHeight="1">
       <c r="A368" s="11" t="n"/>
@@ -16690,6 +20400,16 @@
       <c r="AD368" s="12" t="n"/>
       <c r="AE368" s="12" t="n"/>
       <c r="AF368" s="12" t="n"/>
+      <c r="AG368" s="12" t="n"/>
+      <c r="AH368" s="12" t="n"/>
+      <c r="AI368" s="12" t="n"/>
+      <c r="AJ368" s="12" t="n"/>
+      <c r="AK368" s="12" t="n"/>
+      <c r="AL368" s="12" t="n"/>
+      <c r="AM368" s="12" t="n"/>
+      <c r="AN368" s="12" t="n"/>
+      <c r="AO368" s="12" t="n"/>
+      <c r="AP368" s="12" t="n"/>
     </row>
     <row r="369" ht="22" customHeight="1">
       <c r="A369" s="9" t="n"/>
@@ -16724,6 +20444,16 @@
       <c r="AD369" s="10" t="n"/>
       <c r="AE369" s="10" t="n"/>
       <c r="AF369" s="10" t="n"/>
+      <c r="AG369" s="10" t="n"/>
+      <c r="AH369" s="10" t="n"/>
+      <c r="AI369" s="10" t="n"/>
+      <c r="AJ369" s="10" t="n"/>
+      <c r="AK369" s="10" t="n"/>
+      <c r="AL369" s="10" t="n"/>
+      <c r="AM369" s="10" t="n"/>
+      <c r="AN369" s="10" t="n"/>
+      <c r="AO369" s="10" t="n"/>
+      <c r="AP369" s="10" t="n"/>
     </row>
     <row r="370" ht="22" customHeight="1">
       <c r="A370" s="11" t="n"/>
@@ -16758,6 +20488,16 @@
       <c r="AD370" s="12" t="n"/>
       <c r="AE370" s="12" t="n"/>
       <c r="AF370" s="12" t="n"/>
+      <c r="AG370" s="12" t="n"/>
+      <c r="AH370" s="12" t="n"/>
+      <c r="AI370" s="12" t="n"/>
+      <c r="AJ370" s="12" t="n"/>
+      <c r="AK370" s="12" t="n"/>
+      <c r="AL370" s="12" t="n"/>
+      <c r="AM370" s="12" t="n"/>
+      <c r="AN370" s="12" t="n"/>
+      <c r="AO370" s="12" t="n"/>
+      <c r="AP370" s="12" t="n"/>
     </row>
     <row r="371" ht="22" customHeight="1">
       <c r="A371" s="9" t="n"/>
@@ -16792,6 +20532,16 @@
       <c r="AD371" s="10" t="n"/>
       <c r="AE371" s="10" t="n"/>
       <c r="AF371" s="10" t="n"/>
+      <c r="AG371" s="10" t="n"/>
+      <c r="AH371" s="10" t="n"/>
+      <c r="AI371" s="10" t="n"/>
+      <c r="AJ371" s="10" t="n"/>
+      <c r="AK371" s="10" t="n"/>
+      <c r="AL371" s="10" t="n"/>
+      <c r="AM371" s="10" t="n"/>
+      <c r="AN371" s="10" t="n"/>
+      <c r="AO371" s="10" t="n"/>
+      <c r="AP371" s="10" t="n"/>
     </row>
     <row r="372" ht="22" customHeight="1">
       <c r="A372" s="11" t="n"/>
@@ -16826,6 +20576,16 @@
       <c r="AD372" s="12" t="n"/>
       <c r="AE372" s="12" t="n"/>
       <c r="AF372" s="12" t="n"/>
+      <c r="AG372" s="12" t="n"/>
+      <c r="AH372" s="12" t="n"/>
+      <c r="AI372" s="12" t="n"/>
+      <c r="AJ372" s="12" t="n"/>
+      <c r="AK372" s="12" t="n"/>
+      <c r="AL372" s="12" t="n"/>
+      <c r="AM372" s="12" t="n"/>
+      <c r="AN372" s="12" t="n"/>
+      <c r="AO372" s="12" t="n"/>
+      <c r="AP372" s="12" t="n"/>
     </row>
     <row r="373" ht="22" customHeight="1">
       <c r="A373" s="9" t="n"/>
@@ -16860,6 +20620,16 @@
       <c r="AD373" s="10" t="n"/>
       <c r="AE373" s="10" t="n"/>
       <c r="AF373" s="10" t="n"/>
+      <c r="AG373" s="10" t="n"/>
+      <c r="AH373" s="10" t="n"/>
+      <c r="AI373" s="10" t="n"/>
+      <c r="AJ373" s="10" t="n"/>
+      <c r="AK373" s="10" t="n"/>
+      <c r="AL373" s="10" t="n"/>
+      <c r="AM373" s="10" t="n"/>
+      <c r="AN373" s="10" t="n"/>
+      <c r="AO373" s="10" t="n"/>
+      <c r="AP373" s="10" t="n"/>
     </row>
     <row r="374" ht="22" customHeight="1">
       <c r="A374" s="11" t="n"/>
@@ -16894,6 +20664,16 @@
       <c r="AD374" s="12" t="n"/>
       <c r="AE374" s="12" t="n"/>
       <c r="AF374" s="12" t="n"/>
+      <c r="AG374" s="12" t="n"/>
+      <c r="AH374" s="12" t="n"/>
+      <c r="AI374" s="12" t="n"/>
+      <c r="AJ374" s="12" t="n"/>
+      <c r="AK374" s="12" t="n"/>
+      <c r="AL374" s="12" t="n"/>
+      <c r="AM374" s="12" t="n"/>
+      <c r="AN374" s="12" t="n"/>
+      <c r="AO374" s="12" t="n"/>
+      <c r="AP374" s="12" t="n"/>
     </row>
     <row r="375" ht="22" customHeight="1">
       <c r="A375" s="9" t="n"/>
@@ -16928,6 +20708,16 @@
       <c r="AD375" s="10" t="n"/>
       <c r="AE375" s="10" t="n"/>
       <c r="AF375" s="10" t="n"/>
+      <c r="AG375" s="10" t="n"/>
+      <c r="AH375" s="10" t="n"/>
+      <c r="AI375" s="10" t="n"/>
+      <c r="AJ375" s="10" t="n"/>
+      <c r="AK375" s="10" t="n"/>
+      <c r="AL375" s="10" t="n"/>
+      <c r="AM375" s="10" t="n"/>
+      <c r="AN375" s="10" t="n"/>
+      <c r="AO375" s="10" t="n"/>
+      <c r="AP375" s="10" t="n"/>
     </row>
     <row r="376" ht="22" customHeight="1">
       <c r="A376" s="11" t="n"/>
@@ -16962,6 +20752,16 @@
       <c r="AD376" s="12" t="n"/>
       <c r="AE376" s="12" t="n"/>
       <c r="AF376" s="12" t="n"/>
+      <c r="AG376" s="12" t="n"/>
+      <c r="AH376" s="12" t="n"/>
+      <c r="AI376" s="12" t="n"/>
+      <c r="AJ376" s="12" t="n"/>
+      <c r="AK376" s="12" t="n"/>
+      <c r="AL376" s="12" t="n"/>
+      <c r="AM376" s="12" t="n"/>
+      <c r="AN376" s="12" t="n"/>
+      <c r="AO376" s="12" t="n"/>
+      <c r="AP376" s="12" t="n"/>
     </row>
     <row r="377" ht="22" customHeight="1">
       <c r="A377" s="9" t="n"/>
@@ -16996,6 +20796,16 @@
       <c r="AD377" s="10" t="n"/>
       <c r="AE377" s="10" t="n"/>
       <c r="AF377" s="10" t="n"/>
+      <c r="AG377" s="10" t="n"/>
+      <c r="AH377" s="10" t="n"/>
+      <c r="AI377" s="10" t="n"/>
+      <c r="AJ377" s="10" t="n"/>
+      <c r="AK377" s="10" t="n"/>
+      <c r="AL377" s="10" t="n"/>
+      <c r="AM377" s="10" t="n"/>
+      <c r="AN377" s="10" t="n"/>
+      <c r="AO377" s="10" t="n"/>
+      <c r="AP377" s="10" t="n"/>
     </row>
     <row r="378" ht="22" customHeight="1">
       <c r="A378" s="11" t="n"/>
@@ -17030,6 +20840,16 @@
       <c r="AD378" s="12" t="n"/>
       <c r="AE378" s="12" t="n"/>
       <c r="AF378" s="12" t="n"/>
+      <c r="AG378" s="12" t="n"/>
+      <c r="AH378" s="12" t="n"/>
+      <c r="AI378" s="12" t="n"/>
+      <c r="AJ378" s="12" t="n"/>
+      <c r="AK378" s="12" t="n"/>
+      <c r="AL378" s="12" t="n"/>
+      <c r="AM378" s="12" t="n"/>
+      <c r="AN378" s="12" t="n"/>
+      <c r="AO378" s="12" t="n"/>
+      <c r="AP378" s="12" t="n"/>
     </row>
     <row r="379" ht="22" customHeight="1">
       <c r="A379" s="9" t="n"/>
@@ -17064,6 +20884,16 @@
       <c r="AD379" s="10" t="n"/>
       <c r="AE379" s="10" t="n"/>
       <c r="AF379" s="10" t="n"/>
+      <c r="AG379" s="10" t="n"/>
+      <c r="AH379" s="10" t="n"/>
+      <c r="AI379" s="10" t="n"/>
+      <c r="AJ379" s="10" t="n"/>
+      <c r="AK379" s="10" t="n"/>
+      <c r="AL379" s="10" t="n"/>
+      <c r="AM379" s="10" t="n"/>
+      <c r="AN379" s="10" t="n"/>
+      <c r="AO379" s="10" t="n"/>
+      <c r="AP379" s="10" t="n"/>
     </row>
     <row r="380" ht="22" customHeight="1">
       <c r="A380" s="11" t="n"/>
@@ -17098,6 +20928,16 @@
       <c r="AD380" s="12" t="n"/>
       <c r="AE380" s="12" t="n"/>
       <c r="AF380" s="12" t="n"/>
+      <c r="AG380" s="12" t="n"/>
+      <c r="AH380" s="12" t="n"/>
+      <c r="AI380" s="12" t="n"/>
+      <c r="AJ380" s="12" t="n"/>
+      <c r="AK380" s="12" t="n"/>
+      <c r="AL380" s="12" t="n"/>
+      <c r="AM380" s="12" t="n"/>
+      <c r="AN380" s="12" t="n"/>
+      <c r="AO380" s="12" t="n"/>
+      <c r="AP380" s="12" t="n"/>
     </row>
     <row r="381" ht="22" customHeight="1">
       <c r="A381" s="9" t="n"/>
@@ -17132,6 +20972,16 @@
       <c r="AD381" s="10" t="n"/>
       <c r="AE381" s="10" t="n"/>
       <c r="AF381" s="10" t="n"/>
+      <c r="AG381" s="10" t="n"/>
+      <c r="AH381" s="10" t="n"/>
+      <c r="AI381" s="10" t="n"/>
+      <c r="AJ381" s="10" t="n"/>
+      <c r="AK381" s="10" t="n"/>
+      <c r="AL381" s="10" t="n"/>
+      <c r="AM381" s="10" t="n"/>
+      <c r="AN381" s="10" t="n"/>
+      <c r="AO381" s="10" t="n"/>
+      <c r="AP381" s="10" t="n"/>
     </row>
     <row r="382" ht="22" customHeight="1">
       <c r="A382" s="11" t="n"/>
@@ -17166,6 +21016,16 @@
       <c r="AD382" s="12" t="n"/>
       <c r="AE382" s="12" t="n"/>
       <c r="AF382" s="12" t="n"/>
+      <c r="AG382" s="12" t="n"/>
+      <c r="AH382" s="12" t="n"/>
+      <c r="AI382" s="12" t="n"/>
+      <c r="AJ382" s="12" t="n"/>
+      <c r="AK382" s="12" t="n"/>
+      <c r="AL382" s="12" t="n"/>
+      <c r="AM382" s="12" t="n"/>
+      <c r="AN382" s="12" t="n"/>
+      <c r="AO382" s="12" t="n"/>
+      <c r="AP382" s="12" t="n"/>
     </row>
     <row r="383" ht="22" customHeight="1">
       <c r="A383" s="9" t="n"/>
@@ -17200,6 +21060,16 @@
       <c r="AD383" s="10" t="n"/>
       <c r="AE383" s="10" t="n"/>
       <c r="AF383" s="10" t="n"/>
+      <c r="AG383" s="10" t="n"/>
+      <c r="AH383" s="10" t="n"/>
+      <c r="AI383" s="10" t="n"/>
+      <c r="AJ383" s="10" t="n"/>
+      <c r="AK383" s="10" t="n"/>
+      <c r="AL383" s="10" t="n"/>
+      <c r="AM383" s="10" t="n"/>
+      <c r="AN383" s="10" t="n"/>
+      <c r="AO383" s="10" t="n"/>
+      <c r="AP383" s="10" t="n"/>
     </row>
     <row r="384" ht="22" customHeight="1">
       <c r="A384" s="11" t="n"/>
@@ -17234,6 +21104,16 @@
       <c r="AD384" s="12" t="n"/>
       <c r="AE384" s="12" t="n"/>
       <c r="AF384" s="12" t="n"/>
+      <c r="AG384" s="12" t="n"/>
+      <c r="AH384" s="12" t="n"/>
+      <c r="AI384" s="12" t="n"/>
+      <c r="AJ384" s="12" t="n"/>
+      <c r="AK384" s="12" t="n"/>
+      <c r="AL384" s="12" t="n"/>
+      <c r="AM384" s="12" t="n"/>
+      <c r="AN384" s="12" t="n"/>
+      <c r="AO384" s="12" t="n"/>
+      <c r="AP384" s="12" t="n"/>
     </row>
     <row r="385" ht="22" customHeight="1">
       <c r="A385" s="9" t="n"/>
@@ -17268,6 +21148,16 @@
       <c r="AD385" s="10" t="n"/>
       <c r="AE385" s="10" t="n"/>
       <c r="AF385" s="10" t="n"/>
+      <c r="AG385" s="10" t="n"/>
+      <c r="AH385" s="10" t="n"/>
+      <c r="AI385" s="10" t="n"/>
+      <c r="AJ385" s="10" t="n"/>
+      <c r="AK385" s="10" t="n"/>
+      <c r="AL385" s="10" t="n"/>
+      <c r="AM385" s="10" t="n"/>
+      <c r="AN385" s="10" t="n"/>
+      <c r="AO385" s="10" t="n"/>
+      <c r="AP385" s="10" t="n"/>
     </row>
     <row r="386" ht="22" customHeight="1">
       <c r="A386" s="11" t="n"/>
@@ -17302,6 +21192,16 @@
       <c r="AD386" s="12" t="n"/>
       <c r="AE386" s="12" t="n"/>
       <c r="AF386" s="12" t="n"/>
+      <c r="AG386" s="12" t="n"/>
+      <c r="AH386" s="12" t="n"/>
+      <c r="AI386" s="12" t="n"/>
+      <c r="AJ386" s="12" t="n"/>
+      <c r="AK386" s="12" t="n"/>
+      <c r="AL386" s="12" t="n"/>
+      <c r="AM386" s="12" t="n"/>
+      <c r="AN386" s="12" t="n"/>
+      <c r="AO386" s="12" t="n"/>
+      <c r="AP386" s="12" t="n"/>
     </row>
     <row r="387" ht="22" customHeight="1">
       <c r="A387" s="9" t="n"/>
@@ -17336,6 +21236,16 @@
       <c r="AD387" s="10" t="n"/>
       <c r="AE387" s="10" t="n"/>
       <c r="AF387" s="10" t="n"/>
+      <c r="AG387" s="10" t="n"/>
+      <c r="AH387" s="10" t="n"/>
+      <c r="AI387" s="10" t="n"/>
+      <c r="AJ387" s="10" t="n"/>
+      <c r="AK387" s="10" t="n"/>
+      <c r="AL387" s="10" t="n"/>
+      <c r="AM387" s="10" t="n"/>
+      <c r="AN387" s="10" t="n"/>
+      <c r="AO387" s="10" t="n"/>
+      <c r="AP387" s="10" t="n"/>
     </row>
     <row r="388" ht="22" customHeight="1">
       <c r="A388" s="11" t="n"/>
@@ -17370,6 +21280,16 @@
       <c r="AD388" s="12" t="n"/>
       <c r="AE388" s="12" t="n"/>
       <c r="AF388" s="12" t="n"/>
+      <c r="AG388" s="12" t="n"/>
+      <c r="AH388" s="12" t="n"/>
+      <c r="AI388" s="12" t="n"/>
+      <c r="AJ388" s="12" t="n"/>
+      <c r="AK388" s="12" t="n"/>
+      <c r="AL388" s="12" t="n"/>
+      <c r="AM388" s="12" t="n"/>
+      <c r="AN388" s="12" t="n"/>
+      <c r="AO388" s="12" t="n"/>
+      <c r="AP388" s="12" t="n"/>
     </row>
     <row r="389" ht="22" customHeight="1">
       <c r="A389" s="9" t="n"/>
@@ -17404,6 +21324,16 @@
       <c r="AD389" s="10" t="n"/>
       <c r="AE389" s="10" t="n"/>
       <c r="AF389" s="10" t="n"/>
+      <c r="AG389" s="10" t="n"/>
+      <c r="AH389" s="10" t="n"/>
+      <c r="AI389" s="10" t="n"/>
+      <c r="AJ389" s="10" t="n"/>
+      <c r="AK389" s="10" t="n"/>
+      <c r="AL389" s="10" t="n"/>
+      <c r="AM389" s="10" t="n"/>
+      <c r="AN389" s="10" t="n"/>
+      <c r="AO389" s="10" t="n"/>
+      <c r="AP389" s="10" t="n"/>
     </row>
     <row r="390" ht="22" customHeight="1">
       <c r="A390" s="11" t="n"/>
@@ -17438,6 +21368,16 @@
       <c r="AD390" s="12" t="n"/>
       <c r="AE390" s="12" t="n"/>
       <c r="AF390" s="12" t="n"/>
+      <c r="AG390" s="12" t="n"/>
+      <c r="AH390" s="12" t="n"/>
+      <c r="AI390" s="12" t="n"/>
+      <c r="AJ390" s="12" t="n"/>
+      <c r="AK390" s="12" t="n"/>
+      <c r="AL390" s="12" t="n"/>
+      <c r="AM390" s="12" t="n"/>
+      <c r="AN390" s="12" t="n"/>
+      <c r="AO390" s="12" t="n"/>
+      <c r="AP390" s="12" t="n"/>
     </row>
     <row r="391" ht="22" customHeight="1">
       <c r="A391" s="9" t="n"/>
@@ -17472,6 +21412,16 @@
       <c r="AD391" s="10" t="n"/>
       <c r="AE391" s="10" t="n"/>
       <c r="AF391" s="10" t="n"/>
+      <c r="AG391" s="10" t="n"/>
+      <c r="AH391" s="10" t="n"/>
+      <c r="AI391" s="10" t="n"/>
+      <c r="AJ391" s="10" t="n"/>
+      <c r="AK391" s="10" t="n"/>
+      <c r="AL391" s="10" t="n"/>
+      <c r="AM391" s="10" t="n"/>
+      <c r="AN391" s="10" t="n"/>
+      <c r="AO391" s="10" t="n"/>
+      <c r="AP391" s="10" t="n"/>
     </row>
     <row r="392" ht="22" customHeight="1">
       <c r="A392" s="11" t="n"/>
@@ -17506,6 +21456,16 @@
       <c r="AD392" s="12" t="n"/>
       <c r="AE392" s="12" t="n"/>
       <c r="AF392" s="12" t="n"/>
+      <c r="AG392" s="12" t="n"/>
+      <c r="AH392" s="12" t="n"/>
+      <c r="AI392" s="12" t="n"/>
+      <c r="AJ392" s="12" t="n"/>
+      <c r="AK392" s="12" t="n"/>
+      <c r="AL392" s="12" t="n"/>
+      <c r="AM392" s="12" t="n"/>
+      <c r="AN392" s="12" t="n"/>
+      <c r="AO392" s="12" t="n"/>
+      <c r="AP392" s="12" t="n"/>
     </row>
     <row r="393" ht="22" customHeight="1">
       <c r="A393" s="9" t="n"/>
@@ -17540,6 +21500,16 @@
       <c r="AD393" s="10" t="n"/>
       <c r="AE393" s="10" t="n"/>
       <c r="AF393" s="10" t="n"/>
+      <c r="AG393" s="10" t="n"/>
+      <c r="AH393" s="10" t="n"/>
+      <c r="AI393" s="10" t="n"/>
+      <c r="AJ393" s="10" t="n"/>
+      <c r="AK393" s="10" t="n"/>
+      <c r="AL393" s="10" t="n"/>
+      <c r="AM393" s="10" t="n"/>
+      <c r="AN393" s="10" t="n"/>
+      <c r="AO393" s="10" t="n"/>
+      <c r="AP393" s="10" t="n"/>
     </row>
     <row r="394" ht="22" customHeight="1">
       <c r="A394" s="11" t="n"/>
@@ -17574,6 +21544,16 @@
       <c r="AD394" s="12" t="n"/>
       <c r="AE394" s="12" t="n"/>
       <c r="AF394" s="12" t="n"/>
+      <c r="AG394" s="12" t="n"/>
+      <c r="AH394" s="12" t="n"/>
+      <c r="AI394" s="12" t="n"/>
+      <c r="AJ394" s="12" t="n"/>
+      <c r="AK394" s="12" t="n"/>
+      <c r="AL394" s="12" t="n"/>
+      <c r="AM394" s="12" t="n"/>
+      <c r="AN394" s="12" t="n"/>
+      <c r="AO394" s="12" t="n"/>
+      <c r="AP394" s="12" t="n"/>
     </row>
     <row r="395" ht="22" customHeight="1">
       <c r="A395" s="9" t="n"/>
@@ -17608,6 +21588,16 @@
       <c r="AD395" s="10" t="n"/>
       <c r="AE395" s="10" t="n"/>
       <c r="AF395" s="10" t="n"/>
+      <c r="AG395" s="10" t="n"/>
+      <c r="AH395" s="10" t="n"/>
+      <c r="AI395" s="10" t="n"/>
+      <c r="AJ395" s="10" t="n"/>
+      <c r="AK395" s="10" t="n"/>
+      <c r="AL395" s="10" t="n"/>
+      <c r="AM395" s="10" t="n"/>
+      <c r="AN395" s="10" t="n"/>
+      <c r="AO395" s="10" t="n"/>
+      <c r="AP395" s="10" t="n"/>
     </row>
     <row r="396" ht="22" customHeight="1">
       <c r="A396" s="11" t="n"/>
@@ -17642,6 +21632,16 @@
       <c r="AD396" s="12" t="n"/>
       <c r="AE396" s="12" t="n"/>
       <c r="AF396" s="12" t="n"/>
+      <c r="AG396" s="12" t="n"/>
+      <c r="AH396" s="12" t="n"/>
+      <c r="AI396" s="12" t="n"/>
+      <c r="AJ396" s="12" t="n"/>
+      <c r="AK396" s="12" t="n"/>
+      <c r="AL396" s="12" t="n"/>
+      <c r="AM396" s="12" t="n"/>
+      <c r="AN396" s="12" t="n"/>
+      <c r="AO396" s="12" t="n"/>
+      <c r="AP396" s="12" t="n"/>
     </row>
     <row r="397" ht="22" customHeight="1">
       <c r="A397" s="9" t="n"/>
@@ -17676,6 +21676,16 @@
       <c r="AD397" s="10" t="n"/>
       <c r="AE397" s="10" t="n"/>
       <c r="AF397" s="10" t="n"/>
+      <c r="AG397" s="10" t="n"/>
+      <c r="AH397" s="10" t="n"/>
+      <c r="AI397" s="10" t="n"/>
+      <c r="AJ397" s="10" t="n"/>
+      <c r="AK397" s="10" t="n"/>
+      <c r="AL397" s="10" t="n"/>
+      <c r="AM397" s="10" t="n"/>
+      <c r="AN397" s="10" t="n"/>
+      <c r="AO397" s="10" t="n"/>
+      <c r="AP397" s="10" t="n"/>
     </row>
     <row r="398" ht="22" customHeight="1">
       <c r="A398" s="11" t="n"/>
@@ -17710,6 +21720,16 @@
       <c r="AD398" s="12" t="n"/>
       <c r="AE398" s="12" t="n"/>
       <c r="AF398" s="12" t="n"/>
+      <c r="AG398" s="12" t="n"/>
+      <c r="AH398" s="12" t="n"/>
+      <c r="AI398" s="12" t="n"/>
+      <c r="AJ398" s="12" t="n"/>
+      <c r="AK398" s="12" t="n"/>
+      <c r="AL398" s="12" t="n"/>
+      <c r="AM398" s="12" t="n"/>
+      <c r="AN398" s="12" t="n"/>
+      <c r="AO398" s="12" t="n"/>
+      <c r="AP398" s="12" t="n"/>
     </row>
     <row r="399" ht="22" customHeight="1">
       <c r="A399" s="9" t="n"/>
@@ -17744,6 +21764,16 @@
       <c r="AD399" s="10" t="n"/>
       <c r="AE399" s="10" t="n"/>
       <c r="AF399" s="10" t="n"/>
+      <c r="AG399" s="10" t="n"/>
+      <c r="AH399" s="10" t="n"/>
+      <c r="AI399" s="10" t="n"/>
+      <c r="AJ399" s="10" t="n"/>
+      <c r="AK399" s="10" t="n"/>
+      <c r="AL399" s="10" t="n"/>
+      <c r="AM399" s="10" t="n"/>
+      <c r="AN399" s="10" t="n"/>
+      <c r="AO399" s="10" t="n"/>
+      <c r="AP399" s="10" t="n"/>
     </row>
     <row r="400" ht="22" customHeight="1">
       <c r="A400" s="11" t="n"/>
@@ -17778,6 +21808,16 @@
       <c r="AD400" s="12" t="n"/>
       <c r="AE400" s="12" t="n"/>
       <c r="AF400" s="12" t="n"/>
+      <c r="AG400" s="12" t="n"/>
+      <c r="AH400" s="12" t="n"/>
+      <c r="AI400" s="12" t="n"/>
+      <c r="AJ400" s="12" t="n"/>
+      <c r="AK400" s="12" t="n"/>
+      <c r="AL400" s="12" t="n"/>
+      <c r="AM400" s="12" t="n"/>
+      <c r="AN400" s="12" t="n"/>
+      <c r="AO400" s="12" t="n"/>
+      <c r="AP400" s="12" t="n"/>
     </row>
     <row r="401" ht="22" customHeight="1">
       <c r="A401" s="9" t="n"/>
@@ -17812,6 +21852,16 @@
       <c r="AD401" s="10" t="n"/>
       <c r="AE401" s="10" t="n"/>
       <c r="AF401" s="10" t="n"/>
+      <c r="AG401" s="10" t="n"/>
+      <c r="AH401" s="10" t="n"/>
+      <c r="AI401" s="10" t="n"/>
+      <c r="AJ401" s="10" t="n"/>
+      <c r="AK401" s="10" t="n"/>
+      <c r="AL401" s="10" t="n"/>
+      <c r="AM401" s="10" t="n"/>
+      <c r="AN401" s="10" t="n"/>
+      <c r="AO401" s="10" t="n"/>
+      <c r="AP401" s="10" t="n"/>
     </row>
     <row r="402" ht="22" customHeight="1">
       <c r="A402" s="11" t="n"/>
@@ -17846,6 +21896,16 @@
       <c r="AD402" s="12" t="n"/>
       <c r="AE402" s="12" t="n"/>
       <c r="AF402" s="12" t="n"/>
+      <c r="AG402" s="12" t="n"/>
+      <c r="AH402" s="12" t="n"/>
+      <c r="AI402" s="12" t="n"/>
+      <c r="AJ402" s="12" t="n"/>
+      <c r="AK402" s="12" t="n"/>
+      <c r="AL402" s="12" t="n"/>
+      <c r="AM402" s="12" t="n"/>
+      <c r="AN402" s="12" t="n"/>
+      <c r="AO402" s="12" t="n"/>
+      <c r="AP402" s="12" t="n"/>
     </row>
     <row r="403" ht="22" customHeight="1">
       <c r="A403" s="9" t="n"/>
@@ -17880,6 +21940,16 @@
       <c r="AD403" s="10" t="n"/>
       <c r="AE403" s="10" t="n"/>
       <c r="AF403" s="10" t="n"/>
+      <c r="AG403" s="10" t="n"/>
+      <c r="AH403" s="10" t="n"/>
+      <c r="AI403" s="10" t="n"/>
+      <c r="AJ403" s="10" t="n"/>
+      <c r="AK403" s="10" t="n"/>
+      <c r="AL403" s="10" t="n"/>
+      <c r="AM403" s="10" t="n"/>
+      <c r="AN403" s="10" t="n"/>
+      <c r="AO403" s="10" t="n"/>
+      <c r="AP403" s="10" t="n"/>
     </row>
     <row r="404" ht="22" customHeight="1">
       <c r="A404" s="11" t="n"/>
@@ -17914,6 +21984,16 @@
       <c r="AD404" s="12" t="n"/>
       <c r="AE404" s="12" t="n"/>
       <c r="AF404" s="12" t="n"/>
+      <c r="AG404" s="12" t="n"/>
+      <c r="AH404" s="12" t="n"/>
+      <c r="AI404" s="12" t="n"/>
+      <c r="AJ404" s="12" t="n"/>
+      <c r="AK404" s="12" t="n"/>
+      <c r="AL404" s="12" t="n"/>
+      <c r="AM404" s="12" t="n"/>
+      <c r="AN404" s="12" t="n"/>
+      <c r="AO404" s="12" t="n"/>
+      <c r="AP404" s="12" t="n"/>
     </row>
     <row r="405" ht="22" customHeight="1">
       <c r="A405" s="9" t="n"/>
@@ -17948,6 +22028,16 @@
       <c r="AD405" s="10" t="n"/>
       <c r="AE405" s="10" t="n"/>
       <c r="AF405" s="10" t="n"/>
+      <c r="AG405" s="10" t="n"/>
+      <c r="AH405" s="10" t="n"/>
+      <c r="AI405" s="10" t="n"/>
+      <c r="AJ405" s="10" t="n"/>
+      <c r="AK405" s="10" t="n"/>
+      <c r="AL405" s="10" t="n"/>
+      <c r="AM405" s="10" t="n"/>
+      <c r="AN405" s="10" t="n"/>
+      <c r="AO405" s="10" t="n"/>
+      <c r="AP405" s="10" t="n"/>
     </row>
     <row r="406" ht="22" customHeight="1">
       <c r="A406" s="11" t="n"/>
@@ -17982,6 +22072,16 @@
       <c r="AD406" s="12" t="n"/>
       <c r="AE406" s="12" t="n"/>
       <c r="AF406" s="12" t="n"/>
+      <c r="AG406" s="12" t="n"/>
+      <c r="AH406" s="12" t="n"/>
+      <c r="AI406" s="12" t="n"/>
+      <c r="AJ406" s="12" t="n"/>
+      <c r="AK406" s="12" t="n"/>
+      <c r="AL406" s="12" t="n"/>
+      <c r="AM406" s="12" t="n"/>
+      <c r="AN406" s="12" t="n"/>
+      <c r="AO406" s="12" t="n"/>
+      <c r="AP406" s="12" t="n"/>
     </row>
     <row r="407" ht="22" customHeight="1">
       <c r="A407" s="9" t="n"/>
@@ -18016,6 +22116,16 @@
       <c r="AD407" s="10" t="n"/>
       <c r="AE407" s="10" t="n"/>
       <c r="AF407" s="10" t="n"/>
+      <c r="AG407" s="10" t="n"/>
+      <c r="AH407" s="10" t="n"/>
+      <c r="AI407" s="10" t="n"/>
+      <c r="AJ407" s="10" t="n"/>
+      <c r="AK407" s="10" t="n"/>
+      <c r="AL407" s="10" t="n"/>
+      <c r="AM407" s="10" t="n"/>
+      <c r="AN407" s="10" t="n"/>
+      <c r="AO407" s="10" t="n"/>
+      <c r="AP407" s="10" t="n"/>
     </row>
     <row r="408" ht="22" customHeight="1">
       <c r="A408" s="11" t="n"/>
@@ -18050,6 +22160,16 @@
       <c r="AD408" s="12" t="n"/>
       <c r="AE408" s="12" t="n"/>
       <c r="AF408" s="12" t="n"/>
+      <c r="AG408" s="12" t="n"/>
+      <c r="AH408" s="12" t="n"/>
+      <c r="AI408" s="12" t="n"/>
+      <c r="AJ408" s="12" t="n"/>
+      <c r="AK408" s="12" t="n"/>
+      <c r="AL408" s="12" t="n"/>
+      <c r="AM408" s="12" t="n"/>
+      <c r="AN408" s="12" t="n"/>
+      <c r="AO408" s="12" t="n"/>
+      <c r="AP408" s="12" t="n"/>
     </row>
     <row r="409" ht="22" customHeight="1">
       <c r="A409" s="9" t="n"/>
@@ -18084,6 +22204,16 @@
       <c r="AD409" s="10" t="n"/>
       <c r="AE409" s="10" t="n"/>
       <c r="AF409" s="10" t="n"/>
+      <c r="AG409" s="10" t="n"/>
+      <c r="AH409" s="10" t="n"/>
+      <c r="AI409" s="10" t="n"/>
+      <c r="AJ409" s="10" t="n"/>
+      <c r="AK409" s="10" t="n"/>
+      <c r="AL409" s="10" t="n"/>
+      <c r="AM409" s="10" t="n"/>
+      <c r="AN409" s="10" t="n"/>
+      <c r="AO409" s="10" t="n"/>
+      <c r="AP409" s="10" t="n"/>
     </row>
     <row r="410" ht="22" customHeight="1">
       <c r="A410" s="11" t="n"/>
@@ -18118,6 +22248,16 @@
       <c r="AD410" s="12" t="n"/>
       <c r="AE410" s="12" t="n"/>
       <c r="AF410" s="12" t="n"/>
+      <c r="AG410" s="12" t="n"/>
+      <c r="AH410" s="12" t="n"/>
+      <c r="AI410" s="12" t="n"/>
+      <c r="AJ410" s="12" t="n"/>
+      <c r="AK410" s="12" t="n"/>
+      <c r="AL410" s="12" t="n"/>
+      <c r="AM410" s="12" t="n"/>
+      <c r="AN410" s="12" t="n"/>
+      <c r="AO410" s="12" t="n"/>
+      <c r="AP410" s="12" t="n"/>
     </row>
     <row r="411" ht="22" customHeight="1">
       <c r="A411" s="9" t="n"/>
@@ -18152,6 +22292,16 @@
       <c r="AD411" s="10" t="n"/>
       <c r="AE411" s="10" t="n"/>
       <c r="AF411" s="10" t="n"/>
+      <c r="AG411" s="10" t="n"/>
+      <c r="AH411" s="10" t="n"/>
+      <c r="AI411" s="10" t="n"/>
+      <c r="AJ411" s="10" t="n"/>
+      <c r="AK411" s="10" t="n"/>
+      <c r="AL411" s="10" t="n"/>
+      <c r="AM411" s="10" t="n"/>
+      <c r="AN411" s="10" t="n"/>
+      <c r="AO411" s="10" t="n"/>
+      <c r="AP411" s="10" t="n"/>
     </row>
     <row r="412" ht="22" customHeight="1">
       <c r="A412" s="11" t="n"/>
@@ -18186,6 +22336,16 @@
       <c r="AD412" s="12" t="n"/>
       <c r="AE412" s="12" t="n"/>
       <c r="AF412" s="12" t="n"/>
+      <c r="AG412" s="12" t="n"/>
+      <c r="AH412" s="12" t="n"/>
+      <c r="AI412" s="12" t="n"/>
+      <c r="AJ412" s="12" t="n"/>
+      <c r="AK412" s="12" t="n"/>
+      <c r="AL412" s="12" t="n"/>
+      <c r="AM412" s="12" t="n"/>
+      <c r="AN412" s="12" t="n"/>
+      <c r="AO412" s="12" t="n"/>
+      <c r="AP412" s="12" t="n"/>
     </row>
     <row r="413" ht="22" customHeight="1">
       <c r="A413" s="9" t="n"/>
@@ -18220,6 +22380,16 @@
       <c r="AD413" s="10" t="n"/>
       <c r="AE413" s="10" t="n"/>
       <c r="AF413" s="10" t="n"/>
+      <c r="AG413" s="10" t="n"/>
+      <c r="AH413" s="10" t="n"/>
+      <c r="AI413" s="10" t="n"/>
+      <c r="AJ413" s="10" t="n"/>
+      <c r="AK413" s="10" t="n"/>
+      <c r="AL413" s="10" t="n"/>
+      <c r="AM413" s="10" t="n"/>
+      <c r="AN413" s="10" t="n"/>
+      <c r="AO413" s="10" t="n"/>
+      <c r="AP413" s="10" t="n"/>
     </row>
     <row r="414" ht="22" customHeight="1">
       <c r="A414" s="11" t="n"/>
@@ -18254,6 +22424,16 @@
       <c r="AD414" s="12" t="n"/>
       <c r="AE414" s="12" t="n"/>
       <c r="AF414" s="12" t="n"/>
+      <c r="AG414" s="12" t="n"/>
+      <c r="AH414" s="12" t="n"/>
+      <c r="AI414" s="12" t="n"/>
+      <c r="AJ414" s="12" t="n"/>
+      <c r="AK414" s="12" t="n"/>
+      <c r="AL414" s="12" t="n"/>
+      <c r="AM414" s="12" t="n"/>
+      <c r="AN414" s="12" t="n"/>
+      <c r="AO414" s="12" t="n"/>
+      <c r="AP414" s="12" t="n"/>
     </row>
     <row r="415" ht="22" customHeight="1">
       <c r="A415" s="9" t="n"/>
@@ -18288,6 +22468,16 @@
       <c r="AD415" s="10" t="n"/>
       <c r="AE415" s="10" t="n"/>
       <c r="AF415" s="10" t="n"/>
+      <c r="AG415" s="10" t="n"/>
+      <c r="AH415" s="10" t="n"/>
+      <c r="AI415" s="10" t="n"/>
+      <c r="AJ415" s="10" t="n"/>
+      <c r="AK415" s="10" t="n"/>
+      <c r="AL415" s="10" t="n"/>
+      <c r="AM415" s="10" t="n"/>
+      <c r="AN415" s="10" t="n"/>
+      <c r="AO415" s="10" t="n"/>
+      <c r="AP415" s="10" t="n"/>
     </row>
     <row r="416" ht="22" customHeight="1">
       <c r="A416" s="11" t="n"/>
@@ -18322,6 +22512,16 @@
       <c r="AD416" s="12" t="n"/>
       <c r="AE416" s="12" t="n"/>
       <c r="AF416" s="12" t="n"/>
+      <c r="AG416" s="12" t="n"/>
+      <c r="AH416" s="12" t="n"/>
+      <c r="AI416" s="12" t="n"/>
+      <c r="AJ416" s="12" t="n"/>
+      <c r="AK416" s="12" t="n"/>
+      <c r="AL416" s="12" t="n"/>
+      <c r="AM416" s="12" t="n"/>
+      <c r="AN416" s="12" t="n"/>
+      <c r="AO416" s="12" t="n"/>
+      <c r="AP416" s="12" t="n"/>
     </row>
     <row r="417" ht="22" customHeight="1">
       <c r="A417" s="9" t="n"/>
@@ -18356,6 +22556,16 @@
       <c r="AD417" s="10" t="n"/>
       <c r="AE417" s="10" t="n"/>
       <c r="AF417" s="10" t="n"/>
+      <c r="AG417" s="10" t="n"/>
+      <c r="AH417" s="10" t="n"/>
+      <c r="AI417" s="10" t="n"/>
+      <c r="AJ417" s="10" t="n"/>
+      <c r="AK417" s="10" t="n"/>
+      <c r="AL417" s="10" t="n"/>
+      <c r="AM417" s="10" t="n"/>
+      <c r="AN417" s="10" t="n"/>
+      <c r="AO417" s="10" t="n"/>
+      <c r="AP417" s="10" t="n"/>
     </row>
     <row r="418" ht="22" customHeight="1">
       <c r="A418" s="11" t="n"/>
@@ -18390,6 +22600,16 @@
       <c r="AD418" s="12" t="n"/>
       <c r="AE418" s="12" t="n"/>
       <c r="AF418" s="12" t="n"/>
+      <c r="AG418" s="12" t="n"/>
+      <c r="AH418" s="12" t="n"/>
+      <c r="AI418" s="12" t="n"/>
+      <c r="AJ418" s="12" t="n"/>
+      <c r="AK418" s="12" t="n"/>
+      <c r="AL418" s="12" t="n"/>
+      <c r="AM418" s="12" t="n"/>
+      <c r="AN418" s="12" t="n"/>
+      <c r="AO418" s="12" t="n"/>
+      <c r="AP418" s="12" t="n"/>
     </row>
     <row r="419" ht="22" customHeight="1">
       <c r="A419" s="9" t="n"/>
@@ -18424,6 +22644,16 @@
       <c r="AD419" s="10" t="n"/>
       <c r="AE419" s="10" t="n"/>
       <c r="AF419" s="10" t="n"/>
+      <c r="AG419" s="10" t="n"/>
+      <c r="AH419" s="10" t="n"/>
+      <c r="AI419" s="10" t="n"/>
+      <c r="AJ419" s="10" t="n"/>
+      <c r="AK419" s="10" t="n"/>
+      <c r="AL419" s="10" t="n"/>
+      <c r="AM419" s="10" t="n"/>
+      <c r="AN419" s="10" t="n"/>
+      <c r="AO419" s="10" t="n"/>
+      <c r="AP419" s="10" t="n"/>
     </row>
     <row r="420" ht="22" customHeight="1">
       <c r="A420" s="11" t="n"/>
@@ -18458,6 +22688,16 @@
       <c r="AD420" s="12" t="n"/>
       <c r="AE420" s="12" t="n"/>
       <c r="AF420" s="12" t="n"/>
+      <c r="AG420" s="12" t="n"/>
+      <c r="AH420" s="12" t="n"/>
+      <c r="AI420" s="12" t="n"/>
+      <c r="AJ420" s="12" t="n"/>
+      <c r="AK420" s="12" t="n"/>
+      <c r="AL420" s="12" t="n"/>
+      <c r="AM420" s="12" t="n"/>
+      <c r="AN420" s="12" t="n"/>
+      <c r="AO420" s="12" t="n"/>
+      <c r="AP420" s="12" t="n"/>
     </row>
     <row r="421" ht="22" customHeight="1">
       <c r="A421" s="9" t="n"/>
@@ -18492,6 +22732,16 @@
       <c r="AD421" s="10" t="n"/>
       <c r="AE421" s="10" t="n"/>
       <c r="AF421" s="10" t="n"/>
+      <c r="AG421" s="10" t="n"/>
+      <c r="AH421" s="10" t="n"/>
+      <c r="AI421" s="10" t="n"/>
+      <c r="AJ421" s="10" t="n"/>
+      <c r="AK421" s="10" t="n"/>
+      <c r="AL421" s="10" t="n"/>
+      <c r="AM421" s="10" t="n"/>
+      <c r="AN421" s="10" t="n"/>
+      <c r="AO421" s="10" t="n"/>
+      <c r="AP421" s="10" t="n"/>
     </row>
     <row r="422" ht="22" customHeight="1">
       <c r="A422" s="11" t="n"/>
@@ -18526,6 +22776,16 @@
       <c r="AD422" s="12" t="n"/>
       <c r="AE422" s="12" t="n"/>
       <c r="AF422" s="12" t="n"/>
+      <c r="AG422" s="12" t="n"/>
+      <c r="AH422" s="12" t="n"/>
+      <c r="AI422" s="12" t="n"/>
+      <c r="AJ422" s="12" t="n"/>
+      <c r="AK422" s="12" t="n"/>
+      <c r="AL422" s="12" t="n"/>
+      <c r="AM422" s="12" t="n"/>
+      <c r="AN422" s="12" t="n"/>
+      <c r="AO422" s="12" t="n"/>
+      <c r="AP422" s="12" t="n"/>
     </row>
     <row r="423" ht="22" customHeight="1">
       <c r="A423" s="9" t="n"/>
@@ -18560,6 +22820,16 @@
       <c r="AD423" s="10" t="n"/>
       <c r="AE423" s="10" t="n"/>
       <c r="AF423" s="10" t="n"/>
+      <c r="AG423" s="10" t="n"/>
+      <c r="AH423" s="10" t="n"/>
+      <c r="AI423" s="10" t="n"/>
+      <c r="AJ423" s="10" t="n"/>
+      <c r="AK423" s="10" t="n"/>
+      <c r="AL423" s="10" t="n"/>
+      <c r="AM423" s="10" t="n"/>
+      <c r="AN423" s="10" t="n"/>
+      <c r="AO423" s="10" t="n"/>
+      <c r="AP423" s="10" t="n"/>
     </row>
     <row r="424" ht="22" customHeight="1">
       <c r="A424" s="11" t="n"/>
@@ -18594,6 +22864,16 @@
       <c r="AD424" s="12" t="n"/>
       <c r="AE424" s="12" t="n"/>
       <c r="AF424" s="12" t="n"/>
+      <c r="AG424" s="12" t="n"/>
+      <c r="AH424" s="12" t="n"/>
+      <c r="AI424" s="12" t="n"/>
+      <c r="AJ424" s="12" t="n"/>
+      <c r="AK424" s="12" t="n"/>
+      <c r="AL424" s="12" t="n"/>
+      <c r="AM424" s="12" t="n"/>
+      <c r="AN424" s="12" t="n"/>
+      <c r="AO424" s="12" t="n"/>
+      <c r="AP424" s="12" t="n"/>
     </row>
     <row r="425" ht="22" customHeight="1">
       <c r="A425" s="9" t="n"/>
@@ -18628,6 +22908,16 @@
       <c r="AD425" s="10" t="n"/>
       <c r="AE425" s="10" t="n"/>
       <c r="AF425" s="10" t="n"/>
+      <c r="AG425" s="10" t="n"/>
+      <c r="AH425" s="10" t="n"/>
+      <c r="AI425" s="10" t="n"/>
+      <c r="AJ425" s="10" t="n"/>
+      <c r="AK425" s="10" t="n"/>
+      <c r="AL425" s="10" t="n"/>
+      <c r="AM425" s="10" t="n"/>
+      <c r="AN425" s="10" t="n"/>
+      <c r="AO425" s="10" t="n"/>
+      <c r="AP425" s="10" t="n"/>
     </row>
     <row r="426" ht="22" customHeight="1">
       <c r="A426" s="11" t="n"/>
@@ -18662,6 +22952,16 @@
       <c r="AD426" s="12" t="n"/>
       <c r="AE426" s="12" t="n"/>
       <c r="AF426" s="12" t="n"/>
+      <c r="AG426" s="12" t="n"/>
+      <c r="AH426" s="12" t="n"/>
+      <c r="AI426" s="12" t="n"/>
+      <c r="AJ426" s="12" t="n"/>
+      <c r="AK426" s="12" t="n"/>
+      <c r="AL426" s="12" t="n"/>
+      <c r="AM426" s="12" t="n"/>
+      <c r="AN426" s="12" t="n"/>
+      <c r="AO426" s="12" t="n"/>
+      <c r="AP426" s="12" t="n"/>
     </row>
     <row r="427" ht="22" customHeight="1">
       <c r="A427" s="9" t="n"/>
@@ -18696,6 +22996,16 @@
       <c r="AD427" s="10" t="n"/>
       <c r="AE427" s="10" t="n"/>
       <c r="AF427" s="10" t="n"/>
+      <c r="AG427" s="10" t="n"/>
+      <c r="AH427" s="10" t="n"/>
+      <c r="AI427" s="10" t="n"/>
+      <c r="AJ427" s="10" t="n"/>
+      <c r="AK427" s="10" t="n"/>
+      <c r="AL427" s="10" t="n"/>
+      <c r="AM427" s="10" t="n"/>
+      <c r="AN427" s="10" t="n"/>
+      <c r="AO427" s="10" t="n"/>
+      <c r="AP427" s="10" t="n"/>
     </row>
     <row r="428" ht="22" customHeight="1">
       <c r="A428" s="11" t="n"/>
@@ -18730,6 +23040,16 @@
       <c r="AD428" s="12" t="n"/>
       <c r="AE428" s="12" t="n"/>
       <c r="AF428" s="12" t="n"/>
+      <c r="AG428" s="12" t="n"/>
+      <c r="AH428" s="12" t="n"/>
+      <c r="AI428" s="12" t="n"/>
+      <c r="AJ428" s="12" t="n"/>
+      <c r="AK428" s="12" t="n"/>
+      <c r="AL428" s="12" t="n"/>
+      <c r="AM428" s="12" t="n"/>
+      <c r="AN428" s="12" t="n"/>
+      <c r="AO428" s="12" t="n"/>
+      <c r="AP428" s="12" t="n"/>
     </row>
     <row r="429" ht="22" customHeight="1">
       <c r="A429" s="9" t="n"/>
@@ -18764,6 +23084,16 @@
       <c r="AD429" s="10" t="n"/>
       <c r="AE429" s="10" t="n"/>
       <c r="AF429" s="10" t="n"/>
+      <c r="AG429" s="10" t="n"/>
+      <c r="AH429" s="10" t="n"/>
+      <c r="AI429" s="10" t="n"/>
+      <c r="AJ429" s="10" t="n"/>
+      <c r="AK429" s="10" t="n"/>
+      <c r="AL429" s="10" t="n"/>
+      <c r="AM429" s="10" t="n"/>
+      <c r="AN429" s="10" t="n"/>
+      <c r="AO429" s="10" t="n"/>
+      <c r="AP429" s="10" t="n"/>
     </row>
     <row r="430" ht="22" customHeight="1">
       <c r="A430" s="11" t="n"/>
@@ -18798,6 +23128,16 @@
       <c r="AD430" s="12" t="n"/>
       <c r="AE430" s="12" t="n"/>
       <c r="AF430" s="12" t="n"/>
+      <c r="AG430" s="12" t="n"/>
+      <c r="AH430" s="12" t="n"/>
+      <c r="AI430" s="12" t="n"/>
+      <c r="AJ430" s="12" t="n"/>
+      <c r="AK430" s="12" t="n"/>
+      <c r="AL430" s="12" t="n"/>
+      <c r="AM430" s="12" t="n"/>
+      <c r="AN430" s="12" t="n"/>
+      <c r="AO430" s="12" t="n"/>
+      <c r="AP430" s="12" t="n"/>
     </row>
     <row r="431" ht="22" customHeight="1">
       <c r="A431" s="9" t="n"/>
@@ -18832,6 +23172,16 @@
       <c r="AD431" s="10" t="n"/>
       <c r="AE431" s="10" t="n"/>
       <c r="AF431" s="10" t="n"/>
+      <c r="AG431" s="10" t="n"/>
+      <c r="AH431" s="10" t="n"/>
+      <c r="AI431" s="10" t="n"/>
+      <c r="AJ431" s="10" t="n"/>
+      <c r="AK431" s="10" t="n"/>
+      <c r="AL431" s="10" t="n"/>
+      <c r="AM431" s="10" t="n"/>
+      <c r="AN431" s="10" t="n"/>
+      <c r="AO431" s="10" t="n"/>
+      <c r="AP431" s="10" t="n"/>
     </row>
     <row r="432" ht="22" customHeight="1">
       <c r="A432" s="11" t="n"/>
@@ -18866,6 +23216,16 @@
       <c r="AD432" s="12" t="n"/>
       <c r="AE432" s="12" t="n"/>
       <c r="AF432" s="12" t="n"/>
+      <c r="AG432" s="12" t="n"/>
+      <c r="AH432" s="12" t="n"/>
+      <c r="AI432" s="12" t="n"/>
+      <c r="AJ432" s="12" t="n"/>
+      <c r="AK432" s="12" t="n"/>
+      <c r="AL432" s="12" t="n"/>
+      <c r="AM432" s="12" t="n"/>
+      <c r="AN432" s="12" t="n"/>
+      <c r="AO432" s="12" t="n"/>
+      <c r="AP432" s="12" t="n"/>
     </row>
     <row r="433" ht="22" customHeight="1">
       <c r="A433" s="9" t="n"/>
@@ -18900,6 +23260,16 @@
       <c r="AD433" s="10" t="n"/>
       <c r="AE433" s="10" t="n"/>
       <c r="AF433" s="10" t="n"/>
+      <c r="AG433" s="10" t="n"/>
+      <c r="AH433" s="10" t="n"/>
+      <c r="AI433" s="10" t="n"/>
+      <c r="AJ433" s="10" t="n"/>
+      <c r="AK433" s="10" t="n"/>
+      <c r="AL433" s="10" t="n"/>
+      <c r="AM433" s="10" t="n"/>
+      <c r="AN433" s="10" t="n"/>
+      <c r="AO433" s="10" t="n"/>
+      <c r="AP433" s="10" t="n"/>
     </row>
     <row r="434" ht="22" customHeight="1">
       <c r="A434" s="11" t="n"/>
@@ -18934,6 +23304,16 @@
       <c r="AD434" s="12" t="n"/>
       <c r="AE434" s="12" t="n"/>
       <c r="AF434" s="12" t="n"/>
+      <c r="AG434" s="12" t="n"/>
+      <c r="AH434" s="12" t="n"/>
+      <c r="AI434" s="12" t="n"/>
+      <c r="AJ434" s="12" t="n"/>
+      <c r="AK434" s="12" t="n"/>
+      <c r="AL434" s="12" t="n"/>
+      <c r="AM434" s="12" t="n"/>
+      <c r="AN434" s="12" t="n"/>
+      <c r="AO434" s="12" t="n"/>
+      <c r="AP434" s="12" t="n"/>
     </row>
     <row r="435" ht="22" customHeight="1">
       <c r="A435" s="9" t="n"/>
@@ -18968,6 +23348,16 @@
       <c r="AD435" s="10" t="n"/>
       <c r="AE435" s="10" t="n"/>
       <c r="AF435" s="10" t="n"/>
+      <c r="AG435" s="10" t="n"/>
+      <c r="AH435" s="10" t="n"/>
+      <c r="AI435" s="10" t="n"/>
+      <c r="AJ435" s="10" t="n"/>
+      <c r="AK435" s="10" t="n"/>
+      <c r="AL435" s="10" t="n"/>
+      <c r="AM435" s="10" t="n"/>
+      <c r="AN435" s="10" t="n"/>
+      <c r="AO435" s="10" t="n"/>
+      <c r="AP435" s="10" t="n"/>
     </row>
     <row r="436" ht="22" customHeight="1">
       <c r="A436" s="11" t="n"/>
@@ -19002,6 +23392,16 @@
       <c r="AD436" s="12" t="n"/>
       <c r="AE436" s="12" t="n"/>
       <c r="AF436" s="12" t="n"/>
+      <c r="AG436" s="12" t="n"/>
+      <c r="AH436" s="12" t="n"/>
+      <c r="AI436" s="12" t="n"/>
+      <c r="AJ436" s="12" t="n"/>
+      <c r="AK436" s="12" t="n"/>
+      <c r="AL436" s="12" t="n"/>
+      <c r="AM436" s="12" t="n"/>
+      <c r="AN436" s="12" t="n"/>
+      <c r="AO436" s="12" t="n"/>
+      <c r="AP436" s="12" t="n"/>
     </row>
     <row r="437" ht="22" customHeight="1">
       <c r="A437" s="9" t="n"/>
@@ -19036,6 +23436,16 @@
       <c r="AD437" s="10" t="n"/>
       <c r="AE437" s="10" t="n"/>
       <c r="AF437" s="10" t="n"/>
+      <c r="AG437" s="10" t="n"/>
+      <c r="AH437" s="10" t="n"/>
+      <c r="AI437" s="10" t="n"/>
+      <c r="AJ437" s="10" t="n"/>
+      <c r="AK437" s="10" t="n"/>
+      <c r="AL437" s="10" t="n"/>
+      <c r="AM437" s="10" t="n"/>
+      <c r="AN437" s="10" t="n"/>
+      <c r="AO437" s="10" t="n"/>
+      <c r="AP437" s="10" t="n"/>
     </row>
     <row r="438" ht="22" customHeight="1">
       <c r="A438" s="11" t="n"/>
@@ -19070,6 +23480,16 @@
       <c r="AD438" s="12" t="n"/>
       <c r="AE438" s="12" t="n"/>
       <c r="AF438" s="12" t="n"/>
+      <c r="AG438" s="12" t="n"/>
+      <c r="AH438" s="12" t="n"/>
+      <c r="AI438" s="12" t="n"/>
+      <c r="AJ438" s="12" t="n"/>
+      <c r="AK438" s="12" t="n"/>
+      <c r="AL438" s="12" t="n"/>
+      <c r="AM438" s="12" t="n"/>
+      <c r="AN438" s="12" t="n"/>
+      <c r="AO438" s="12" t="n"/>
+      <c r="AP438" s="12" t="n"/>
     </row>
     <row r="439" ht="22" customHeight="1">
       <c r="A439" s="9" t="n"/>
@@ -19104,6 +23524,16 @@
       <c r="AD439" s="10" t="n"/>
       <c r="AE439" s="10" t="n"/>
       <c r="AF439" s="10" t="n"/>
+      <c r="AG439" s="10" t="n"/>
+      <c r="AH439" s="10" t="n"/>
+      <c r="AI439" s="10" t="n"/>
+      <c r="AJ439" s="10" t="n"/>
+      <c r="AK439" s="10" t="n"/>
+      <c r="AL439" s="10" t="n"/>
+      <c r="AM439" s="10" t="n"/>
+      <c r="AN439" s="10" t="n"/>
+      <c r="AO439" s="10" t="n"/>
+      <c r="AP439" s="10" t="n"/>
     </row>
     <row r="440" ht="22" customHeight="1">
       <c r="A440" s="11" t="n"/>
@@ -19138,6 +23568,16 @@
       <c r="AD440" s="12" t="n"/>
       <c r="AE440" s="12" t="n"/>
       <c r="AF440" s="12" t="n"/>
+      <c r="AG440" s="12" t="n"/>
+      <c r="AH440" s="12" t="n"/>
+      <c r="AI440" s="12" t="n"/>
+      <c r="AJ440" s="12" t="n"/>
+      <c r="AK440" s="12" t="n"/>
+      <c r="AL440" s="12" t="n"/>
+      <c r="AM440" s="12" t="n"/>
+      <c r="AN440" s="12" t="n"/>
+      <c r="AO440" s="12" t="n"/>
+      <c r="AP440" s="12" t="n"/>
     </row>
     <row r="441" ht="22" customHeight="1">
       <c r="A441" s="9" t="n"/>
@@ -19172,6 +23612,16 @@
       <c r="AD441" s="10" t="n"/>
       <c r="AE441" s="10" t="n"/>
       <c r="AF441" s="10" t="n"/>
+      <c r="AG441" s="10" t="n"/>
+      <c r="AH441" s="10" t="n"/>
+      <c r="AI441" s="10" t="n"/>
+      <c r="AJ441" s="10" t="n"/>
+      <c r="AK441" s="10" t="n"/>
+      <c r="AL441" s="10" t="n"/>
+      <c r="AM441" s="10" t="n"/>
+      <c r="AN441" s="10" t="n"/>
+      <c r="AO441" s="10" t="n"/>
+      <c r="AP441" s="10" t="n"/>
     </row>
     <row r="442" ht="22" customHeight="1">
       <c r="A442" s="11" t="n"/>
@@ -19206,6 +23656,16 @@
       <c r="AD442" s="12" t="n"/>
       <c r="AE442" s="12" t="n"/>
       <c r="AF442" s="12" t="n"/>
+      <c r="AG442" s="12" t="n"/>
+      <c r="AH442" s="12" t="n"/>
+      <c r="AI442" s="12" t="n"/>
+      <c r="AJ442" s="12" t="n"/>
+      <c r="AK442" s="12" t="n"/>
+      <c r="AL442" s="12" t="n"/>
+      <c r="AM442" s="12" t="n"/>
+      <c r="AN442" s="12" t="n"/>
+      <c r="AO442" s="12" t="n"/>
+      <c r="AP442" s="12" t="n"/>
     </row>
     <row r="443" ht="22" customHeight="1">
       <c r="A443" s="9" t="n"/>
@@ -19240,6 +23700,16 @@
       <c r="AD443" s="10" t="n"/>
       <c r="AE443" s="10" t="n"/>
       <c r="AF443" s="10" t="n"/>
+      <c r="AG443" s="10" t="n"/>
+      <c r="AH443" s="10" t="n"/>
+      <c r="AI443" s="10" t="n"/>
+      <c r="AJ443" s="10" t="n"/>
+      <c r="AK443" s="10" t="n"/>
+      <c r="AL443" s="10" t="n"/>
+      <c r="AM443" s="10" t="n"/>
+      <c r="AN443" s="10" t="n"/>
+      <c r="AO443" s="10" t="n"/>
+      <c r="AP443" s="10" t="n"/>
     </row>
     <row r="444" ht="22" customHeight="1">
       <c r="A444" s="11" t="n"/>
@@ -19274,6 +23744,16 @@
       <c r="AD444" s="12" t="n"/>
       <c r="AE444" s="12" t="n"/>
       <c r="AF444" s="12" t="n"/>
+      <c r="AG444" s="12" t="n"/>
+      <c r="AH444" s="12" t="n"/>
+      <c r="AI444" s="12" t="n"/>
+      <c r="AJ444" s="12" t="n"/>
+      <c r="AK444" s="12" t="n"/>
+      <c r="AL444" s="12" t="n"/>
+      <c r="AM444" s="12" t="n"/>
+      <c r="AN444" s="12" t="n"/>
+      <c r="AO444" s="12" t="n"/>
+      <c r="AP444" s="12" t="n"/>
     </row>
     <row r="445" ht="22" customHeight="1">
       <c r="A445" s="9" t="n"/>
@@ -19308,6 +23788,16 @@
       <c r="AD445" s="10" t="n"/>
       <c r="AE445" s="10" t="n"/>
       <c r="AF445" s="10" t="n"/>
+      <c r="AG445" s="10" t="n"/>
+      <c r="AH445" s="10" t="n"/>
+      <c r="AI445" s="10" t="n"/>
+      <c r="AJ445" s="10" t="n"/>
+      <c r="AK445" s="10" t="n"/>
+      <c r="AL445" s="10" t="n"/>
+      <c r="AM445" s="10" t="n"/>
+      <c r="AN445" s="10" t="n"/>
+      <c r="AO445" s="10" t="n"/>
+      <c r="AP445" s="10" t="n"/>
     </row>
     <row r="446" ht="22" customHeight="1">
       <c r="A446" s="11" t="n"/>
@@ -19342,6 +23832,16 @@
       <c r="AD446" s="12" t="n"/>
       <c r="AE446" s="12" t="n"/>
       <c r="AF446" s="12" t="n"/>
+      <c r="AG446" s="12" t="n"/>
+      <c r="AH446" s="12" t="n"/>
+      <c r="AI446" s="12" t="n"/>
+      <c r="AJ446" s="12" t="n"/>
+      <c r="AK446" s="12" t="n"/>
+      <c r="AL446" s="12" t="n"/>
+      <c r="AM446" s="12" t="n"/>
+      <c r="AN446" s="12" t="n"/>
+      <c r="AO446" s="12" t="n"/>
+      <c r="AP446" s="12" t="n"/>
     </row>
     <row r="447" ht="22" customHeight="1">
       <c r="A447" s="9" t="n"/>
@@ -19376,6 +23876,16 @@
       <c r="AD447" s="10" t="n"/>
       <c r="AE447" s="10" t="n"/>
       <c r="AF447" s="10" t="n"/>
+      <c r="AG447" s="10" t="n"/>
+      <c r="AH447" s="10" t="n"/>
+      <c r="AI447" s="10" t="n"/>
+      <c r="AJ447" s="10" t="n"/>
+      <c r="AK447" s="10" t="n"/>
+      <c r="AL447" s="10" t="n"/>
+      <c r="AM447" s="10" t="n"/>
+      <c r="AN447" s="10" t="n"/>
+      <c r="AO447" s="10" t="n"/>
+      <c r="AP447" s="10" t="n"/>
     </row>
     <row r="448" ht="22" customHeight="1">
       <c r="A448" s="11" t="n"/>
@@ -19410,6 +23920,16 @@
       <c r="AD448" s="12" t="n"/>
       <c r="AE448" s="12" t="n"/>
       <c r="AF448" s="12" t="n"/>
+      <c r="AG448" s="12" t="n"/>
+      <c r="AH448" s="12" t="n"/>
+      <c r="AI448" s="12" t="n"/>
+      <c r="AJ448" s="12" t="n"/>
+      <c r="AK448" s="12" t="n"/>
+      <c r="AL448" s="12" t="n"/>
+      <c r="AM448" s="12" t="n"/>
+      <c r="AN448" s="12" t="n"/>
+      <c r="AO448" s="12" t="n"/>
+      <c r="AP448" s="12" t="n"/>
     </row>
     <row r="449" ht="22" customHeight="1">
       <c r="A449" s="9" t="n"/>
@@ -19444,6 +23964,16 @@
       <c r="AD449" s="10" t="n"/>
       <c r="AE449" s="10" t="n"/>
       <c r="AF449" s="10" t="n"/>
+      <c r="AG449" s="10" t="n"/>
+      <c r="AH449" s="10" t="n"/>
+      <c r="AI449" s="10" t="n"/>
+      <c r="AJ449" s="10" t="n"/>
+      <c r="AK449" s="10" t="n"/>
+      <c r="AL449" s="10" t="n"/>
+      <c r="AM449" s="10" t="n"/>
+      <c r="AN449" s="10" t="n"/>
+      <c r="AO449" s="10" t="n"/>
+      <c r="AP449" s="10" t="n"/>
     </row>
     <row r="450" ht="22" customHeight="1">
       <c r="A450" s="11" t="n"/>
@@ -19478,6 +24008,16 @@
       <c r="AD450" s="12" t="n"/>
       <c r="AE450" s="12" t="n"/>
       <c r="AF450" s="12" t="n"/>
+      <c r="AG450" s="12" t="n"/>
+      <c r="AH450" s="12" t="n"/>
+      <c r="AI450" s="12" t="n"/>
+      <c r="AJ450" s="12" t="n"/>
+      <c r="AK450" s="12" t="n"/>
+      <c r="AL450" s="12" t="n"/>
+      <c r="AM450" s="12" t="n"/>
+      <c r="AN450" s="12" t="n"/>
+      <c r="AO450" s="12" t="n"/>
+      <c r="AP450" s="12" t="n"/>
     </row>
     <row r="451" ht="22" customHeight="1">
       <c r="A451" s="9" t="n"/>
@@ -19512,6 +24052,16 @@
       <c r="AD451" s="10" t="n"/>
       <c r="AE451" s="10" t="n"/>
       <c r="AF451" s="10" t="n"/>
+      <c r="AG451" s="10" t="n"/>
+      <c r="AH451" s="10" t="n"/>
+      <c r="AI451" s="10" t="n"/>
+      <c r="AJ451" s="10" t="n"/>
+      <c r="AK451" s="10" t="n"/>
+      <c r="AL451" s="10" t="n"/>
+      <c r="AM451" s="10" t="n"/>
+      <c r="AN451" s="10" t="n"/>
+      <c r="AO451" s="10" t="n"/>
+      <c r="AP451" s="10" t="n"/>
     </row>
     <row r="452" ht="22" customHeight="1">
       <c r="A452" s="11" t="n"/>
@@ -19546,6 +24096,16 @@
       <c r="AD452" s="12" t="n"/>
       <c r="AE452" s="12" t="n"/>
       <c r="AF452" s="12" t="n"/>
+      <c r="AG452" s="12" t="n"/>
+      <c r="AH452" s="12" t="n"/>
+      <c r="AI452" s="12" t="n"/>
+      <c r="AJ452" s="12" t="n"/>
+      <c r="AK452" s="12" t="n"/>
+      <c r="AL452" s="12" t="n"/>
+      <c r="AM452" s="12" t="n"/>
+      <c r="AN452" s="12" t="n"/>
+      <c r="AO452" s="12" t="n"/>
+      <c r="AP452" s="12" t="n"/>
     </row>
     <row r="453" ht="22" customHeight="1">
       <c r="A453" s="9" t="n"/>
@@ -19580,6 +24140,16 @@
       <c r="AD453" s="10" t="n"/>
       <c r="AE453" s="10" t="n"/>
       <c r="AF453" s="10" t="n"/>
+      <c r="AG453" s="10" t="n"/>
+      <c r="AH453" s="10" t="n"/>
+      <c r="AI453" s="10" t="n"/>
+      <c r="AJ453" s="10" t="n"/>
+      <c r="AK453" s="10" t="n"/>
+      <c r="AL453" s="10" t="n"/>
+      <c r="AM453" s="10" t="n"/>
+      <c r="AN453" s="10" t="n"/>
+      <c r="AO453" s="10" t="n"/>
+      <c r="AP453" s="10" t="n"/>
     </row>
     <row r="454" ht="22" customHeight="1">
       <c r="A454" s="11" t="n"/>
@@ -19614,6 +24184,16 @@
       <c r="AD454" s="12" t="n"/>
       <c r="AE454" s="12" t="n"/>
       <c r="AF454" s="12" t="n"/>
+      <c r="AG454" s="12" t="n"/>
+      <c r="AH454" s="12" t="n"/>
+      <c r="AI454" s="12" t="n"/>
+      <c r="AJ454" s="12" t="n"/>
+      <c r="AK454" s="12" t="n"/>
+      <c r="AL454" s="12" t="n"/>
+      <c r="AM454" s="12" t="n"/>
+      <c r="AN454" s="12" t="n"/>
+      <c r="AO454" s="12" t="n"/>
+      <c r="AP454" s="12" t="n"/>
     </row>
     <row r="455" ht="22" customHeight="1">
       <c r="A455" s="9" t="n"/>
@@ -19648,6 +24228,16 @@
       <c r="AD455" s="10" t="n"/>
       <c r="AE455" s="10" t="n"/>
       <c r="AF455" s="10" t="n"/>
+      <c r="AG455" s="10" t="n"/>
+      <c r="AH455" s="10" t="n"/>
+      <c r="AI455" s="10" t="n"/>
+      <c r="AJ455" s="10" t="n"/>
+      <c r="AK455" s="10" t="n"/>
+      <c r="AL455" s="10" t="n"/>
+      <c r="AM455" s="10" t="n"/>
+      <c r="AN455" s="10" t="n"/>
+      <c r="AO455" s="10" t="n"/>
+      <c r="AP455" s="10" t="n"/>
     </row>
     <row r="456" ht="22" customHeight="1">
       <c r="A456" s="11" t="n"/>
@@ -19682,6 +24272,16 @@
       <c r="AD456" s="12" t="n"/>
       <c r="AE456" s="12" t="n"/>
       <c r="AF456" s="12" t="n"/>
+      <c r="AG456" s="12" t="n"/>
+      <c r="AH456" s="12" t="n"/>
+      <c r="AI456" s="12" t="n"/>
+      <c r="AJ456" s="12" t="n"/>
+      <c r="AK456" s="12" t="n"/>
+      <c r="AL456" s="12" t="n"/>
+      <c r="AM456" s="12" t="n"/>
+      <c r="AN456" s="12" t="n"/>
+      <c r="AO456" s="12" t="n"/>
+      <c r="AP456" s="12" t="n"/>
     </row>
     <row r="457" ht="22" customHeight="1">
       <c r="A457" s="9" t="n"/>
@@ -19716,6 +24316,16 @@
       <c r="AD457" s="10" t="n"/>
       <c r="AE457" s="10" t="n"/>
       <c r="AF457" s="10" t="n"/>
+      <c r="AG457" s="10" t="n"/>
+      <c r="AH457" s="10" t="n"/>
+      <c r="AI457" s="10" t="n"/>
+      <c r="AJ457" s="10" t="n"/>
+      <c r="AK457" s="10" t="n"/>
+      <c r="AL457" s="10" t="n"/>
+      <c r="AM457" s="10" t="n"/>
+      <c r="AN457" s="10" t="n"/>
+      <c r="AO457" s="10" t="n"/>
+      <c r="AP457" s="10" t="n"/>
     </row>
     <row r="458" ht="22" customHeight="1">
       <c r="A458" s="11" t="n"/>
@@ -19750,6 +24360,16 @@
       <c r="AD458" s="12" t="n"/>
       <c r="AE458" s="12" t="n"/>
       <c r="AF458" s="12" t="n"/>
+      <c r="AG458" s="12" t="n"/>
+      <c r="AH458" s="12" t="n"/>
+      <c r="AI458" s="12" t="n"/>
+      <c r="AJ458" s="12" t="n"/>
+      <c r="AK458" s="12" t="n"/>
+      <c r="AL458" s="12" t="n"/>
+      <c r="AM458" s="12" t="n"/>
+      <c r="AN458" s="12" t="n"/>
+      <c r="AO458" s="12" t="n"/>
+      <c r="AP458" s="12" t="n"/>
     </row>
     <row r="459" ht="22" customHeight="1">
       <c r="A459" s="9" t="n"/>
@@ -19784,6 +24404,16 @@
       <c r="AD459" s="10" t="n"/>
       <c r="AE459" s="10" t="n"/>
       <c r="AF459" s="10" t="n"/>
+      <c r="AG459" s="10" t="n"/>
+      <c r="AH459" s="10" t="n"/>
+      <c r="AI459" s="10" t="n"/>
+      <c r="AJ459" s="10" t="n"/>
+      <c r="AK459" s="10" t="n"/>
+      <c r="AL459" s="10" t="n"/>
+      <c r="AM459" s="10" t="n"/>
+      <c r="AN459" s="10" t="n"/>
+      <c r="AO459" s="10" t="n"/>
+      <c r="AP459" s="10" t="n"/>
     </row>
     <row r="460" ht="22" customHeight="1">
       <c r="A460" s="11" t="n"/>
@@ -19818,6 +24448,16 @@
       <c r="AD460" s="12" t="n"/>
       <c r="AE460" s="12" t="n"/>
       <c r="AF460" s="12" t="n"/>
+      <c r="AG460" s="12" t="n"/>
+      <c r="AH460" s="12" t="n"/>
+      <c r="AI460" s="12" t="n"/>
+      <c r="AJ460" s="12" t="n"/>
+      <c r="AK460" s="12" t="n"/>
+      <c r="AL460" s="12" t="n"/>
+      <c r="AM460" s="12" t="n"/>
+      <c r="AN460" s="12" t="n"/>
+      <c r="AO460" s="12" t="n"/>
+      <c r="AP460" s="12" t="n"/>
     </row>
     <row r="461" ht="22" customHeight="1">
       <c r="A461" s="9" t="n"/>
@@ -19852,6 +24492,16 @@
       <c r="AD461" s="10" t="n"/>
       <c r="AE461" s="10" t="n"/>
       <c r="AF461" s="10" t="n"/>
+      <c r="AG461" s="10" t="n"/>
+      <c r="AH461" s="10" t="n"/>
+      <c r="AI461" s="10" t="n"/>
+      <c r="AJ461" s="10" t="n"/>
+      <c r="AK461" s="10" t="n"/>
+      <c r="AL461" s="10" t="n"/>
+      <c r="AM461" s="10" t="n"/>
+      <c r="AN461" s="10" t="n"/>
+      <c r="AO461" s="10" t="n"/>
+      <c r="AP461" s="10" t="n"/>
     </row>
     <row r="462" ht="22" customHeight="1">
       <c r="A462" s="11" t="n"/>
@@ -19886,6 +24536,16 @@
       <c r="AD462" s="12" t="n"/>
       <c r="AE462" s="12" t="n"/>
       <c r="AF462" s="12" t="n"/>
+      <c r="AG462" s="12" t="n"/>
+      <c r="AH462" s="12" t="n"/>
+      <c r="AI462" s="12" t="n"/>
+      <c r="AJ462" s="12" t="n"/>
+      <c r="AK462" s="12" t="n"/>
+      <c r="AL462" s="12" t="n"/>
+      <c r="AM462" s="12" t="n"/>
+      <c r="AN462" s="12" t="n"/>
+      <c r="AO462" s="12" t="n"/>
+      <c r="AP462" s="12" t="n"/>
     </row>
     <row r="463" ht="22" customHeight="1">
       <c r="A463" s="9" t="n"/>
@@ -19920,6 +24580,16 @@
       <c r="AD463" s="10" t="n"/>
       <c r="AE463" s="10" t="n"/>
       <c r="AF463" s="10" t="n"/>
+      <c r="AG463" s="10" t="n"/>
+      <c r="AH463" s="10" t="n"/>
+      <c r="AI463" s="10" t="n"/>
+      <c r="AJ463" s="10" t="n"/>
+      <c r="AK463" s="10" t="n"/>
+      <c r="AL463" s="10" t="n"/>
+      <c r="AM463" s="10" t="n"/>
+      <c r="AN463" s="10" t="n"/>
+      <c r="AO463" s="10" t="n"/>
+      <c r="AP463" s="10" t="n"/>
     </row>
     <row r="464" ht="22" customHeight="1">
       <c r="A464" s="11" t="n"/>
@@ -19954,6 +24624,16 @@
       <c r="AD464" s="12" t="n"/>
       <c r="AE464" s="12" t="n"/>
       <c r="AF464" s="12" t="n"/>
+      <c r="AG464" s="12" t="n"/>
+      <c r="AH464" s="12" t="n"/>
+      <c r="AI464" s="12" t="n"/>
+      <c r="AJ464" s="12" t="n"/>
+      <c r="AK464" s="12" t="n"/>
+      <c r="AL464" s="12" t="n"/>
+      <c r="AM464" s="12" t="n"/>
+      <c r="AN464" s="12" t="n"/>
+      <c r="AO464" s="12" t="n"/>
+      <c r="AP464" s="12" t="n"/>
     </row>
     <row r="465" ht="22" customHeight="1">
       <c r="A465" s="9" t="n"/>
@@ -19988,6 +24668,16 @@
       <c r="AD465" s="10" t="n"/>
       <c r="AE465" s="10" t="n"/>
       <c r="AF465" s="10" t="n"/>
+      <c r="AG465" s="10" t="n"/>
+      <c r="AH465" s="10" t="n"/>
+      <c r="AI465" s="10" t="n"/>
+      <c r="AJ465" s="10" t="n"/>
+      <c r="AK465" s="10" t="n"/>
+      <c r="AL465" s="10" t="n"/>
+      <c r="AM465" s="10" t="n"/>
+      <c r="AN465" s="10" t="n"/>
+      <c r="AO465" s="10" t="n"/>
+      <c r="AP465" s="10" t="n"/>
     </row>
     <row r="466" ht="22" customHeight="1">
       <c r="A466" s="11" t="n"/>
@@ -20022,6 +24712,16 @@
       <c r="AD466" s="12" t="n"/>
       <c r="AE466" s="12" t="n"/>
       <c r="AF466" s="12" t="n"/>
+      <c r="AG466" s="12" t="n"/>
+      <c r="AH466" s="12" t="n"/>
+      <c r="AI466" s="12" t="n"/>
+      <c r="AJ466" s="12" t="n"/>
+      <c r="AK466" s="12" t="n"/>
+      <c r="AL466" s="12" t="n"/>
+      <c r="AM466" s="12" t="n"/>
+      <c r="AN466" s="12" t="n"/>
+      <c r="AO466" s="12" t="n"/>
+      <c r="AP466" s="12" t="n"/>
     </row>
     <row r="467" ht="22" customHeight="1">
       <c r="A467" s="9" t="n"/>
@@ -20056,6 +24756,16 @@
       <c r="AD467" s="10" t="n"/>
       <c r="AE467" s="10" t="n"/>
       <c r="AF467" s="10" t="n"/>
+      <c r="AG467" s="10" t="n"/>
+      <c r="AH467" s="10" t="n"/>
+      <c r="AI467" s="10" t="n"/>
+      <c r="AJ467" s="10" t="n"/>
+      <c r="AK467" s="10" t="n"/>
+      <c r="AL467" s="10" t="n"/>
+      <c r="AM467" s="10" t="n"/>
+      <c r="AN467" s="10" t="n"/>
+      <c r="AO467" s="10" t="n"/>
+      <c r="AP467" s="10" t="n"/>
     </row>
     <row r="468" ht="22" customHeight="1">
       <c r="A468" s="11" t="n"/>
@@ -20090,6 +24800,16 @@
       <c r="AD468" s="12" t="n"/>
       <c r="AE468" s="12" t="n"/>
       <c r="AF468" s="12" t="n"/>
+      <c r="AG468" s="12" t="n"/>
+      <c r="AH468" s="12" t="n"/>
+      <c r="AI468" s="12" t="n"/>
+      <c r="AJ468" s="12" t="n"/>
+      <c r="AK468" s="12" t="n"/>
+      <c r="AL468" s="12" t="n"/>
+      <c r="AM468" s="12" t="n"/>
+      <c r="AN468" s="12" t="n"/>
+      <c r="AO468" s="12" t="n"/>
+      <c r="AP468" s="12" t="n"/>
     </row>
     <row r="469" ht="22" customHeight="1">
       <c r="A469" s="9" t="n"/>
@@ -20124,6 +24844,16 @@
       <c r="AD469" s="10" t="n"/>
       <c r="AE469" s="10" t="n"/>
       <c r="AF469" s="10" t="n"/>
+      <c r="AG469" s="10" t="n"/>
+      <c r="AH469" s="10" t="n"/>
+      <c r="AI469" s="10" t="n"/>
+      <c r="AJ469" s="10" t="n"/>
+      <c r="AK469" s="10" t="n"/>
+      <c r="AL469" s="10" t="n"/>
+      <c r="AM469" s="10" t="n"/>
+      <c r="AN469" s="10" t="n"/>
+      <c r="AO469" s="10" t="n"/>
+      <c r="AP469" s="10" t="n"/>
     </row>
     <row r="470" ht="22" customHeight="1">
       <c r="A470" s="11" t="n"/>
@@ -20158,6 +24888,16 @@
       <c r="AD470" s="12" t="n"/>
       <c r="AE470" s="12" t="n"/>
       <c r="AF470" s="12" t="n"/>
+      <c r="AG470" s="12" t="n"/>
+      <c r="AH470" s="12" t="n"/>
+      <c r="AI470" s="12" t="n"/>
+      <c r="AJ470" s="12" t="n"/>
+      <c r="AK470" s="12" t="n"/>
+      <c r="AL470" s="12" t="n"/>
+      <c r="AM470" s="12" t="n"/>
+      <c r="AN470" s="12" t="n"/>
+      <c r="AO470" s="12" t="n"/>
+      <c r="AP470" s="12" t="n"/>
     </row>
     <row r="471" ht="22" customHeight="1">
       <c r="A471" s="9" t="n"/>
@@ -20192,6 +24932,16 @@
       <c r="AD471" s="10" t="n"/>
       <c r="AE471" s="10" t="n"/>
       <c r="AF471" s="10" t="n"/>
+      <c r="AG471" s="10" t="n"/>
+      <c r="AH471" s="10" t="n"/>
+      <c r="AI471" s="10" t="n"/>
+      <c r="AJ471" s="10" t="n"/>
+      <c r="AK471" s="10" t="n"/>
+      <c r="AL471" s="10" t="n"/>
+      <c r="AM471" s="10" t="n"/>
+      <c r="AN471" s="10" t="n"/>
+      <c r="AO471" s="10" t="n"/>
+      <c r="AP471" s="10" t="n"/>
     </row>
     <row r="472" ht="22" customHeight="1">
       <c r="A472" s="11" t="n"/>
@@ -20226,6 +24976,16 @@
       <c r="AD472" s="12" t="n"/>
       <c r="AE472" s="12" t="n"/>
       <c r="AF472" s="12" t="n"/>
+      <c r="AG472" s="12" t="n"/>
+      <c r="AH472" s="12" t="n"/>
+      <c r="AI472" s="12" t="n"/>
+      <c r="AJ472" s="12" t="n"/>
+      <c r="AK472" s="12" t="n"/>
+      <c r="AL472" s="12" t="n"/>
+      <c r="AM472" s="12" t="n"/>
+      <c r="AN472" s="12" t="n"/>
+      <c r="AO472" s="12" t="n"/>
+      <c r="AP472" s="12" t="n"/>
     </row>
     <row r="473" ht="22" customHeight="1">
       <c r="A473" s="9" t="n"/>
@@ -20260,6 +25020,16 @@
       <c r="AD473" s="10" t="n"/>
       <c r="AE473" s="10" t="n"/>
       <c r="AF473" s="10" t="n"/>
+      <c r="AG473" s="10" t="n"/>
+      <c r="AH473" s="10" t="n"/>
+      <c r="AI473" s="10" t="n"/>
+      <c r="AJ473" s="10" t="n"/>
+      <c r="AK473" s="10" t="n"/>
+      <c r="AL473" s="10" t="n"/>
+      <c r="AM473" s="10" t="n"/>
+      <c r="AN473" s="10" t="n"/>
+      <c r="AO473" s="10" t="n"/>
+      <c r="AP473" s="10" t="n"/>
     </row>
     <row r="474" ht="22" customHeight="1">
       <c r="A474" s="11" t="n"/>
@@ -20294,6 +25064,16 @@
       <c r="AD474" s="12" t="n"/>
       <c r="AE474" s="12" t="n"/>
       <c r="AF474" s="12" t="n"/>
+      <c r="AG474" s="12" t="n"/>
+      <c r="AH474" s="12" t="n"/>
+      <c r="AI474" s="12" t="n"/>
+      <c r="AJ474" s="12" t="n"/>
+      <c r="AK474" s="12" t="n"/>
+      <c r="AL474" s="12" t="n"/>
+      <c r="AM474" s="12" t="n"/>
+      <c r="AN474" s="12" t="n"/>
+      <c r="AO474" s="12" t="n"/>
+      <c r="AP474" s="12" t="n"/>
     </row>
     <row r="475" ht="22" customHeight="1">
       <c r="A475" s="9" t="n"/>
@@ -20328,6 +25108,16 @@
       <c r="AD475" s="10" t="n"/>
       <c r="AE475" s="10" t="n"/>
       <c r="AF475" s="10" t="n"/>
+      <c r="AG475" s="10" t="n"/>
+      <c r="AH475" s="10" t="n"/>
+      <c r="AI475" s="10" t="n"/>
+      <c r="AJ475" s="10" t="n"/>
+      <c r="AK475" s="10" t="n"/>
+      <c r="AL475" s="10" t="n"/>
+      <c r="AM475" s="10" t="n"/>
+      <c r="AN475" s="10" t="n"/>
+      <c r="AO475" s="10" t="n"/>
+      <c r="AP475" s="10" t="n"/>
     </row>
     <row r="476" ht="22" customHeight="1">
       <c r="A476" s="11" t="n"/>
@@ -20362,6 +25152,16 @@
       <c r="AD476" s="12" t="n"/>
       <c r="AE476" s="12" t="n"/>
       <c r="AF476" s="12" t="n"/>
+      <c r="AG476" s="12" t="n"/>
+      <c r="AH476" s="12" t="n"/>
+      <c r="AI476" s="12" t="n"/>
+      <c r="AJ476" s="12" t="n"/>
+      <c r="AK476" s="12" t="n"/>
+      <c r="AL476" s="12" t="n"/>
+      <c r="AM476" s="12" t="n"/>
+      <c r="AN476" s="12" t="n"/>
+      <c r="AO476" s="12" t="n"/>
+      <c r="AP476" s="12" t="n"/>
     </row>
     <row r="477" ht="22" customHeight="1">
       <c r="A477" s="9" t="n"/>
@@ -20396,6 +25196,16 @@
       <c r="AD477" s="10" t="n"/>
       <c r="AE477" s="10" t="n"/>
       <c r="AF477" s="10" t="n"/>
+      <c r="AG477" s="10" t="n"/>
+      <c r="AH477" s="10" t="n"/>
+      <c r="AI477" s="10" t="n"/>
+      <c r="AJ477" s="10" t="n"/>
+      <c r="AK477" s="10" t="n"/>
+      <c r="AL477" s="10" t="n"/>
+      <c r="AM477" s="10" t="n"/>
+      <c r="AN477" s="10" t="n"/>
+      <c r="AO477" s="10" t="n"/>
+      <c r="AP477" s="10" t="n"/>
     </row>
     <row r="478" ht="22" customHeight="1">
       <c r="A478" s="11" t="n"/>
@@ -20430,6 +25240,16 @@
       <c r="AD478" s="12" t="n"/>
       <c r="AE478" s="12" t="n"/>
       <c r="AF478" s="12" t="n"/>
+      <c r="AG478" s="12" t="n"/>
+      <c r="AH478" s="12" t="n"/>
+      <c r="AI478" s="12" t="n"/>
+      <c r="AJ478" s="12" t="n"/>
+      <c r="AK478" s="12" t="n"/>
+      <c r="AL478" s="12" t="n"/>
+      <c r="AM478" s="12" t="n"/>
+      <c r="AN478" s="12" t="n"/>
+      <c r="AO478" s="12" t="n"/>
+      <c r="AP478" s="12" t="n"/>
     </row>
     <row r="479" ht="22" customHeight="1">
       <c r="A479" s="9" t="n"/>
@@ -20464,6 +25284,16 @@
       <c r="AD479" s="10" t="n"/>
       <c r="AE479" s="10" t="n"/>
       <c r="AF479" s="10" t="n"/>
+      <c r="AG479" s="10" t="n"/>
+      <c r="AH479" s="10" t="n"/>
+      <c r="AI479" s="10" t="n"/>
+      <c r="AJ479" s="10" t="n"/>
+      <c r="AK479" s="10" t="n"/>
+      <c r="AL479" s="10" t="n"/>
+      <c r="AM479" s="10" t="n"/>
+      <c r="AN479" s="10" t="n"/>
+      <c r="AO479" s="10" t="n"/>
+      <c r="AP479" s="10" t="n"/>
     </row>
     <row r="480" ht="22" customHeight="1">
       <c r="A480" s="11" t="n"/>
@@ -20498,6 +25328,16 @@
       <c r="AD480" s="12" t="n"/>
       <c r="AE480" s="12" t="n"/>
       <c r="AF480" s="12" t="n"/>
+      <c r="AG480" s="12" t="n"/>
+      <c r="AH480" s="12" t="n"/>
+      <c r="AI480" s="12" t="n"/>
+      <c r="AJ480" s="12" t="n"/>
+      <c r="AK480" s="12" t="n"/>
+      <c r="AL480" s="12" t="n"/>
+      <c r="AM480" s="12" t="n"/>
+      <c r="AN480" s="12" t="n"/>
+      <c r="AO480" s="12" t="n"/>
+      <c r="AP480" s="12" t="n"/>
     </row>
     <row r="481" ht="22" customHeight="1">
       <c r="A481" s="9" t="n"/>
@@ -20532,6 +25372,16 @@
       <c r="AD481" s="10" t="n"/>
       <c r="AE481" s="10" t="n"/>
       <c r="AF481" s="10" t="n"/>
+      <c r="AG481" s="10" t="n"/>
+      <c r="AH481" s="10" t="n"/>
+      <c r="AI481" s="10" t="n"/>
+      <c r="AJ481" s="10" t="n"/>
+      <c r="AK481" s="10" t="n"/>
+      <c r="AL481" s="10" t="n"/>
+      <c r="AM481" s="10" t="n"/>
+      <c r="AN481" s="10" t="n"/>
+      <c r="AO481" s="10" t="n"/>
+      <c r="AP481" s="10" t="n"/>
     </row>
     <row r="482" ht="22" customHeight="1">
       <c r="A482" s="11" t="n"/>
@@ -20566,6 +25416,16 @@
       <c r="AD482" s="12" t="n"/>
       <c r="AE482" s="12" t="n"/>
       <c r="AF482" s="12" t="n"/>
+      <c r="AG482" s="12" t="n"/>
+      <c r="AH482" s="12" t="n"/>
+      <c r="AI482" s="12" t="n"/>
+      <c r="AJ482" s="12" t="n"/>
+      <c r="AK482" s="12" t="n"/>
+      <c r="AL482" s="12" t="n"/>
+      <c r="AM482" s="12" t="n"/>
+      <c r="AN482" s="12" t="n"/>
+      <c r="AO482" s="12" t="n"/>
+      <c r="AP482" s="12" t="n"/>
     </row>
     <row r="483" ht="22" customHeight="1">
       <c r="A483" s="9" t="n"/>
@@ -20600,6 +25460,16 @@
       <c r="AD483" s="10" t="n"/>
       <c r="AE483" s="10" t="n"/>
       <c r="AF483" s="10" t="n"/>
+      <c r="AG483" s="10" t="n"/>
+      <c r="AH483" s="10" t="n"/>
+      <c r="AI483" s="10" t="n"/>
+      <c r="AJ483" s="10" t="n"/>
+      <c r="AK483" s="10" t="n"/>
+      <c r="AL483" s="10" t="n"/>
+      <c r="AM483" s="10" t="n"/>
+      <c r="AN483" s="10" t="n"/>
+      <c r="AO483" s="10" t="n"/>
+      <c r="AP483" s="10" t="n"/>
     </row>
     <row r="484" ht="22" customHeight="1">
       <c r="A484" s="11" t="n"/>
@@ -20634,6 +25504,16 @@
       <c r="AD484" s="12" t="n"/>
       <c r="AE484" s="12" t="n"/>
       <c r="AF484" s="12" t="n"/>
+      <c r="AG484" s="12" t="n"/>
+      <c r="AH484" s="12" t="n"/>
+      <c r="AI484" s="12" t="n"/>
+      <c r="AJ484" s="12" t="n"/>
+      <c r="AK484" s="12" t="n"/>
+      <c r="AL484" s="12" t="n"/>
+      <c r="AM484" s="12" t="n"/>
+      <c r="AN484" s="12" t="n"/>
+      <c r="AO484" s="12" t="n"/>
+      <c r="AP484" s="12" t="n"/>
     </row>
     <row r="485" ht="22" customHeight="1">
       <c r="A485" s="9" t="n"/>
@@ -20668,6 +25548,16 @@
       <c r="AD485" s="10" t="n"/>
       <c r="AE485" s="10" t="n"/>
       <c r="AF485" s="10" t="n"/>
+      <c r="AG485" s="10" t="n"/>
+      <c r="AH485" s="10" t="n"/>
+      <c r="AI485" s="10" t="n"/>
+      <c r="AJ485" s="10" t="n"/>
+      <c r="AK485" s="10" t="n"/>
+      <c r="AL485" s="10" t="n"/>
+      <c r="AM485" s="10" t="n"/>
+      <c r="AN485" s="10" t="n"/>
+      <c r="AO485" s="10" t="n"/>
+      <c r="AP485" s="10" t="n"/>
     </row>
     <row r="486" ht="22" customHeight="1">
       <c r="A486" s="11" t="n"/>
@@ -20702,6 +25592,16 @@
       <c r="AD486" s="12" t="n"/>
       <c r="AE486" s="12" t="n"/>
       <c r="AF486" s="12" t="n"/>
+      <c r="AG486" s="12" t="n"/>
+      <c r="AH486" s="12" t="n"/>
+      <c r="AI486" s="12" t="n"/>
+      <c r="AJ486" s="12" t="n"/>
+      <c r="AK486" s="12" t="n"/>
+      <c r="AL486" s="12" t="n"/>
+      <c r="AM486" s="12" t="n"/>
+      <c r="AN486" s="12" t="n"/>
+      <c r="AO486" s="12" t="n"/>
+      <c r="AP486" s="12" t="n"/>
     </row>
     <row r="487" ht="22" customHeight="1">
       <c r="A487" s="9" t="n"/>
@@ -20736,6 +25636,16 @@
       <c r="AD487" s="10" t="n"/>
       <c r="AE487" s="10" t="n"/>
       <c r="AF487" s="10" t="n"/>
+      <c r="AG487" s="10" t="n"/>
+      <c r="AH487" s="10" t="n"/>
+      <c r="AI487" s="10" t="n"/>
+      <c r="AJ487" s="10" t="n"/>
+      <c r="AK487" s="10" t="n"/>
+      <c r="AL487" s="10" t="n"/>
+      <c r="AM487" s="10" t="n"/>
+      <c r="AN487" s="10" t="n"/>
+      <c r="AO487" s="10" t="n"/>
+      <c r="AP487" s="10" t="n"/>
     </row>
     <row r="488" ht="22" customHeight="1">
       <c r="A488" s="11" t="n"/>
@@ -20770,6 +25680,16 @@
       <c r="AD488" s="12" t="n"/>
       <c r="AE488" s="12" t="n"/>
       <c r="AF488" s="12" t="n"/>
+      <c r="AG488" s="12" t="n"/>
+      <c r="AH488" s="12" t="n"/>
+      <c r="AI488" s="12" t="n"/>
+      <c r="AJ488" s="12" t="n"/>
+      <c r="AK488" s="12" t="n"/>
+      <c r="AL488" s="12" t="n"/>
+      <c r="AM488" s="12" t="n"/>
+      <c r="AN488" s="12" t="n"/>
+      <c r="AO488" s="12" t="n"/>
+      <c r="AP488" s="12" t="n"/>
     </row>
     <row r="489" ht="22" customHeight="1">
       <c r="A489" s="9" t="n"/>
@@ -20804,6 +25724,16 @@
       <c r="AD489" s="10" t="n"/>
       <c r="AE489" s="10" t="n"/>
       <c r="AF489" s="10" t="n"/>
+      <c r="AG489" s="10" t="n"/>
+      <c r="AH489" s="10" t="n"/>
+      <c r="AI489" s="10" t="n"/>
+      <c r="AJ489" s="10" t="n"/>
+      <c r="AK489" s="10" t="n"/>
+      <c r="AL489" s="10" t="n"/>
+      <c r="AM489" s="10" t="n"/>
+      <c r="AN489" s="10" t="n"/>
+      <c r="AO489" s="10" t="n"/>
+      <c r="AP489" s="10" t="n"/>
     </row>
     <row r="490" ht="22" customHeight="1">
       <c r="A490" s="11" t="n"/>
@@ -20838,6 +25768,16 @@
       <c r="AD490" s="12" t="n"/>
       <c r="AE490" s="12" t="n"/>
       <c r="AF490" s="12" t="n"/>
+      <c r="AG490" s="12" t="n"/>
+      <c r="AH490" s="12" t="n"/>
+      <c r="AI490" s="12" t="n"/>
+      <c r="AJ490" s="12" t="n"/>
+      <c r="AK490" s="12" t="n"/>
+      <c r="AL490" s="12" t="n"/>
+      <c r="AM490" s="12" t="n"/>
+      <c r="AN490" s="12" t="n"/>
+      <c r="AO490" s="12" t="n"/>
+      <c r="AP490" s="12" t="n"/>
     </row>
     <row r="491" ht="22" customHeight="1">
       <c r="A491" s="9" t="n"/>
@@ -20872,6 +25812,16 @@
       <c r="AD491" s="10" t="n"/>
       <c r="AE491" s="10" t="n"/>
       <c r="AF491" s="10" t="n"/>
+      <c r="AG491" s="10" t="n"/>
+      <c r="AH491" s="10" t="n"/>
+      <c r="AI491" s="10" t="n"/>
+      <c r="AJ491" s="10" t="n"/>
+      <c r="AK491" s="10" t="n"/>
+      <c r="AL491" s="10" t="n"/>
+      <c r="AM491" s="10" t="n"/>
+      <c r="AN491" s="10" t="n"/>
+      <c r="AO491" s="10" t="n"/>
+      <c r="AP491" s="10" t="n"/>
     </row>
     <row r="492" ht="22" customHeight="1">
       <c r="A492" s="11" t="n"/>
@@ -20906,6 +25856,16 @@
       <c r="AD492" s="12" t="n"/>
       <c r="AE492" s="12" t="n"/>
       <c r="AF492" s="12" t="n"/>
+      <c r="AG492" s="12" t="n"/>
+      <c r="AH492" s="12" t="n"/>
+      <c r="AI492" s="12" t="n"/>
+      <c r="AJ492" s="12" t="n"/>
+      <c r="AK492" s="12" t="n"/>
+      <c r="AL492" s="12" t="n"/>
+      <c r="AM492" s="12" t="n"/>
+      <c r="AN492" s="12" t="n"/>
+      <c r="AO492" s="12" t="n"/>
+      <c r="AP492" s="12" t="n"/>
     </row>
     <row r="493" ht="22" customHeight="1">
       <c r="A493" s="9" t="n"/>
@@ -20940,6 +25900,16 @@
       <c r="AD493" s="10" t="n"/>
       <c r="AE493" s="10" t="n"/>
       <c r="AF493" s="10" t="n"/>
+      <c r="AG493" s="10" t="n"/>
+      <c r="AH493" s="10" t="n"/>
+      <c r="AI493" s="10" t="n"/>
+      <c r="AJ493" s="10" t="n"/>
+      <c r="AK493" s="10" t="n"/>
+      <c r="AL493" s="10" t="n"/>
+      <c r="AM493" s="10" t="n"/>
+      <c r="AN493" s="10" t="n"/>
+      <c r="AO493" s="10" t="n"/>
+      <c r="AP493" s="10" t="n"/>
     </row>
     <row r="494" ht="22" customHeight="1">
       <c r="A494" s="11" t="n"/>
@@ -20974,6 +25944,16 @@
       <c r="AD494" s="12" t="n"/>
       <c r="AE494" s="12" t="n"/>
       <c r="AF494" s="12" t="n"/>
+      <c r="AG494" s="12" t="n"/>
+      <c r="AH494" s="12" t="n"/>
+      <c r="AI494" s="12" t="n"/>
+      <c r="AJ494" s="12" t="n"/>
+      <c r="AK494" s="12" t="n"/>
+      <c r="AL494" s="12" t="n"/>
+      <c r="AM494" s="12" t="n"/>
+      <c r="AN494" s="12" t="n"/>
+      <c r="AO494" s="12" t="n"/>
+      <c r="AP494" s="12" t="n"/>
     </row>
     <row r="495" ht="22" customHeight="1">
       <c r="A495" s="9" t="n"/>
@@ -21008,6 +25988,16 @@
       <c r="AD495" s="10" t="n"/>
       <c r="AE495" s="10" t="n"/>
       <c r="AF495" s="10" t="n"/>
+      <c r="AG495" s="10" t="n"/>
+      <c r="AH495" s="10" t="n"/>
+      <c r="AI495" s="10" t="n"/>
+      <c r="AJ495" s="10" t="n"/>
+      <c r="AK495" s="10" t="n"/>
+      <c r="AL495" s="10" t="n"/>
+      <c r="AM495" s="10" t="n"/>
+      <c r="AN495" s="10" t="n"/>
+      <c r="AO495" s="10" t="n"/>
+      <c r="AP495" s="10" t="n"/>
     </row>
     <row r="496" ht="22" customHeight="1">
       <c r="A496" s="11" t="n"/>
@@ -21042,6 +26032,16 @@
       <c r="AD496" s="12" t="n"/>
       <c r="AE496" s="12" t="n"/>
       <c r="AF496" s="12" t="n"/>
+      <c r="AG496" s="12" t="n"/>
+      <c r="AH496" s="12" t="n"/>
+      <c r="AI496" s="12" t="n"/>
+      <c r="AJ496" s="12" t="n"/>
+      <c r="AK496" s="12" t="n"/>
+      <c r="AL496" s="12" t="n"/>
+      <c r="AM496" s="12" t="n"/>
+      <c r="AN496" s="12" t="n"/>
+      <c r="AO496" s="12" t="n"/>
+      <c r="AP496" s="12" t="n"/>
     </row>
     <row r="497" ht="22" customHeight="1">
       <c r="A497" s="9" t="n"/>
@@ -21076,6 +26076,16 @@
       <c r="AD497" s="10" t="n"/>
       <c r="AE497" s="10" t="n"/>
       <c r="AF497" s="10" t="n"/>
+      <c r="AG497" s="10" t="n"/>
+      <c r="AH497" s="10" t="n"/>
+      <c r="AI497" s="10" t="n"/>
+      <c r="AJ497" s="10" t="n"/>
+      <c r="AK497" s="10" t="n"/>
+      <c r="AL497" s="10" t="n"/>
+      <c r="AM497" s="10" t="n"/>
+      <c r="AN497" s="10" t="n"/>
+      <c r="AO497" s="10" t="n"/>
+      <c r="AP497" s="10" t="n"/>
     </row>
     <row r="498" ht="22" customHeight="1">
       <c r="A498" s="11" t="n"/>
@@ -21110,6 +26120,16 @@
       <c r="AD498" s="12" t="n"/>
       <c r="AE498" s="12" t="n"/>
       <c r="AF498" s="12" t="n"/>
+      <c r="AG498" s="12" t="n"/>
+      <c r="AH498" s="12" t="n"/>
+      <c r="AI498" s="12" t="n"/>
+      <c r="AJ498" s="12" t="n"/>
+      <c r="AK498" s="12" t="n"/>
+      <c r="AL498" s="12" t="n"/>
+      <c r="AM498" s="12" t="n"/>
+      <c r="AN498" s="12" t="n"/>
+      <c r="AO498" s="12" t="n"/>
+      <c r="AP498" s="12" t="n"/>
     </row>
     <row r="499" ht="22" customHeight="1">
       <c r="A499" s="9" t="n"/>
@@ -21144,6 +26164,16 @@
       <c r="AD499" s="10" t="n"/>
       <c r="AE499" s="10" t="n"/>
       <c r="AF499" s="10" t="n"/>
+      <c r="AG499" s="10" t="n"/>
+      <c r="AH499" s="10" t="n"/>
+      <c r="AI499" s="10" t="n"/>
+      <c r="AJ499" s="10" t="n"/>
+      <c r="AK499" s="10" t="n"/>
+      <c r="AL499" s="10" t="n"/>
+      <c r="AM499" s="10" t="n"/>
+      <c r="AN499" s="10" t="n"/>
+      <c r="AO499" s="10" t="n"/>
+      <c r="AP499" s="10" t="n"/>
     </row>
     <row r="500" ht="22" customHeight="1">
       <c r="A500" s="11" t="n"/>
@@ -21178,12 +26208,22 @@
       <c r="AD500" s="12" t="n"/>
       <c r="AE500" s="12" t="n"/>
       <c r="AF500" s="12" t="n"/>
+      <c r="AG500" s="12" t="n"/>
+      <c r="AH500" s="12" t="n"/>
+      <c r="AI500" s="12" t="n"/>
+      <c r="AJ500" s="12" t="n"/>
+      <c r="AK500" s="12" t="n"/>
+      <c r="AL500" s="12" t="n"/>
+      <c r="AM500" s="12" t="n"/>
+      <c r="AN500" s="12" t="n"/>
+      <c r="AO500" s="12" t="n"/>
+      <c r="AP500" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AF500"/>
+  <autoFilter ref="A2:AP500"/>
   <dataValidations count="1">
     <dataValidation sqref="D3:D500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="结构形式无效" error="请使用模板支持的结构形式名称。" promptTitle="结构形式" prompt="请从下拉列表选择结构形式；不确定必填参数时查看后面的分类说明 sheet。" type="list">
-      <formula1>"明渠-梯形,明渠-复式梯形,明渠-矩形,明渠-圆形,明渠-U形,渡槽-U形,渡槽-矩形,隧洞-圆形,隧洞-平底圆形,隧洞-圆拱直墙型,隧洞-马蹄形Ⅰ型,隧洞-马蹄形Ⅱ型,暗涵-矩形,暗涵-圆拱直墙型,倒虹吸,有压管道,定向钻,顶管,分水闸,分水口,节制闸,泄水闸,退水闸"</formula1>
+      <formula1>"明渠-梯形,明渠-复式梯形,明渠-矩形,明渠-圆形,明渠-U形,渡槽-U形,渡槽-矩形,隧洞-圆形,隧洞-平底圆形,隧洞-圆拱直墙型,隧洞-马蹄形Ⅰ型,隧洞-马蹄形Ⅱ型,暗涵-矩形,暗涵-圆拱直墙型,倒虹吸,有压管道,定向钻,顶管,泄水渠与陡坡,分水闸,分水口,节制闸,泄水闸,退水闸"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21233,6 +26273,7 @@
       <c r="E2" s="14" t="n"/>
       <c r="F2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -21245,6 +26286,7 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -21333,7 +26375,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>从下拉列表选择：明渠、渡槽、隧洞、暗涵、倒虹吸、有压管道、闸类。</t>
+          <t>从下拉列表选择：明渠、渡槽、隧洞、暗涵、倒虹吸、有压管道、充水渠、闸类。泄水渠、泄水渠与陡坡导入时按充水渠处理。</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -21490,6 +26532,7 @@
       <c r="E2" s="14" t="n"/>
       <c r="F2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -21502,6 +26545,7 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -22001,6 +27045,7 @@
       <c r="E2" s="14" t="n"/>
       <c r="F2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -22013,6 +27058,7 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -22320,6 +27366,7 @@
       <c r="E2" s="14" t="n"/>
       <c r="F2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -22332,6 +27379,7 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -22607,6 +27655,7 @@
       <c r="E2" s="14" t="n"/>
       <c r="F2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -22619,6 +27668,7 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -22894,6 +27944,7 @@
       <c r="E2" s="14" t="n"/>
       <c r="F2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -22906,6 +27957,7 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -23146,7 +28198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23181,6 +28233,7 @@
       <c r="E2" s="14" t="n"/>
       <c r="F2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -23193,6 +28246,7 @@
       <c r="E4" s="14" t="n"/>
       <c r="F4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -23467,7 +28521,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>作为泄水建筑物节点占位，不是泄水渠与陡坡专项模块。</t>
+          <t>作为泄水建筑物节点占位，不是充水渠/泄水渠/泄水渠与陡坡专项模块。</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -23510,6 +28564,38 @@
       <c r="F15" s="4" t="inlineStr">
         <is>
           <t>不要填断面尺寸。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>逐行渠道段计算</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>必须/建议填：建筑物名称、流量段、X/Y、Q(m³/s)、糙率n、比降(1/)、底宽B(m)、边坡系数m、转弯半径(m)</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>作为表3正式结构类型，同名首行为进口、末行为出口；表3调用专项内核计算水面线。</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>表1/表2只做占位，不展开沿程采样点。</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>名称缺失或没有同名出口行会导致表3计算失败。</t>
         </is>
       </c>
     </row>
@@ -23529,7 +28615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -23566,6 +28652,7 @@
       <c r="F2" s="14" t="n"/>
       <c r="G2" s="15" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -23579,6 +28666,7 @@
       <c r="F4" s="14" t="n"/>
       <c r="G4" s="15" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -23691,39 +28779,39 @@
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>建筑物名称</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>必须填</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>建筑物或渠道段名称</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>文本</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>所有行</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>所有行；充水渠/泄水渠/泄水渠与陡坡按逐行渠道段处理</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>普通明渠可填 -</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>不同位置建筑物重名</t>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡允许名称留空，不判断进出口</t>
         </is>
       </c>
     </row>
@@ -23765,37 +28853,37 @@
       </c>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>必须填</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>平面坐标 X</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>工程坐标单位</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>后续水面线/平面成果</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>不要留空。</t>
         </is>
       </c>
-      <c r="G11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>X/Y 填反</t>
         </is>
@@ -23839,37 +28927,37 @@
       </c>
     </row>
     <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Q(m³/s)</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>必须填</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>设计流量</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>m³/s</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>明渠、渡槽、隧洞、暗涵；占位类建议填</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>参与断面计算不能空</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>明渠、渡槽、隧洞、暗涵、充水渠/泄水渠/泄水渠与陡坡；占位类建议填</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>参与断面计算或表3专项计算不能空</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>把加大流量填到本列</t>
         </is>
@@ -23898,12 +28986,12 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>明渠、渡槽、隧洞、暗涵</t>
+          <t>明渠、渡槽、隧洞、暗涵、充水渠/泄水渠/泄水渠与陡坡</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>参与断面计算不能空</t>
+          <t>参与断面计算或表3专项计算不能空</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
@@ -23913,37 +29001,37 @@
       </c>
     </row>
     <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>比降(1/)</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>必须填</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>坡降倒数</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>1/i</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>明渠、渡槽、隧洞、暗涵</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>明渠、渡槽、隧洞、暗涵、充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>如 1/3000 填 3000</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>误填 0.000333</t>
         </is>
@@ -23972,7 +29060,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>明渠-梯形；明渠-矩形可填 0</t>
+          <t>明渠-梯形、充水渠/泄水渠/泄水渠与陡坡；矩形可填 0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
@@ -23982,44 +29070,44 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>圆形、渡槽、隧洞误填</t>
+          <t>充水渠/泄水渠/泄水渠与陡坡 m=0 表示矩形断面</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>底宽B(m)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>可填/条件必填</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>底宽、槽宽、洞宽或平底宽</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>明渠梯形/矩形、渡槽矩形、隧洞平底圆形/圆拱直墙型、暗涵</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>多数类型可空自动搜索；平底圆形和暗涵固定 H/“H/B ”时必须填</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>不清楚结构时乱填导致固定尺寸</t>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>明渠梯形/矩形、渡槽矩形、隧洞平底圆形/圆拱直墙型、暗涵、充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>多数类型可空自动搜索；充水渠/泄水渠/泄水渠与陡坡必须填</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡缺底宽会导致表3计算失败</t>
         </is>
       </c>
     </row>
@@ -24061,37 +29149,37 @@
       </c>
     </row>
     <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>暗涵高度H(m)</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>条件必填</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>矩形暗涵内侧总高</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>暗涵-矩形</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>配合 B 使用；空白不固定高度</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>只填 H 不填 B，或与 H/B、β 同填</t>
         </is>
@@ -24135,37 +29223,37 @@
       </c>
     </row>
     <row r="21" ht="34" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>半径R(m)</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>可填/条件必填</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>圆弧半径或马蹄形基准半径</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>明渠-U形、渡槽-U形、隧洞-马蹄形Ⅰ/Ⅱ型</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>U形明渠需明确填写；渡槽U形和马蹄形可空自动搜索</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>圆形隧洞误填 R 而不是 D</t>
         </is>
@@ -24209,37 +29297,37 @@
       </c>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>矩形渡槽深宽比</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>可填</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>矩形渡槽 H/B</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>无</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>渡槽-矩形</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>空白默认 0.8</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>与明渠宽深比 β 混淆</t>
         </is>
@@ -24283,37 +29371,37 @@
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>倒角角度(°)</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>条件必填</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>矩形渡槽倒角角度；明渠-U形外倾角 α</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>度</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>渡槽-矩形、明渠-U形</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>渡槽倒角需与倒角底边同填；明渠-U形需填 α</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>只填倒角角度不填倒角底边</t>
         </is>
@@ -24357,37 +29445,37 @@
       </c>
     </row>
     <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>圆心角(°)</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>条件必填</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>圆拱或 U形圆弧角 θ</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>度</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>明渠-U形、隧洞-圆拱直墙型、暗涵-圆拱直墙型</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>圆拱直墙型空白默认 180；U形明渠需填</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>圆拱直墙型填到 90~180 以外</t>
         </is>
@@ -24431,37 +29519,37 @@
       </c>
     </row>
     <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>不淤流速</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>可填</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>最小允许流速</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>m/s</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>参与断面计算结构</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>空白按 0.1</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>大于不冲流速</t>
         </is>
@@ -24505,37 +29593,37 @@
       </c>
     </row>
     <row r="31" ht="34" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>转弯半径(m)</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>可填</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>平面转弯半径</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>后续推求水面线</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>空白或 0 表示不指定</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>误以为参与断面水力计算</t>
         </is>
@@ -24579,37 +29667,37 @@
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>左上坡m1</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>必须填</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>复式梯形左侧上部边坡</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>1:m</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>明渠-复式梯形</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>不能为负</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>漏填 6 个复式参数之一</t>
         </is>
@@ -24653,37 +29741,37 @@
       </c>
     </row>
     <row r="35" ht="34" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>左下坡m2</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>必须填</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>复式梯形左侧下部边坡</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>1:m</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>明渠-复式梯形</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>不能为负</t>
         </is>
       </c>
-      <c r="G35" s="4" t="inlineStr">
+      <c r="G35" s="5" t="inlineStr">
         <is>
           <t>与 m1 含义混淆</t>
         </is>
@@ -24727,37 +29815,37 @@
       </c>
     </row>
     <row r="37" ht="34" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>右坡m3</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>必须填</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>复式梯形右侧边坡</t>
         </is>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>1:m</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>明渠-复式梯形</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>不能为负</t>
         </is>
       </c>
-      <c r="G37" s="4" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>漏填右侧边坡</t>
         </is>
@@ -24800,8 +29888,432 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠入口宽度(m)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠进口堰宽</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>空白按 1.0</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>同名组多行填不同值</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠堰上总水头(m)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>进口堰上总水头</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>空白按 2.2</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>与表3入口水位混淆</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠入口连接形式</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>进口连接形式标签</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>空白按扭曲面连接</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>手输无法识别的连接形式</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠手动流量系数</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>手动入口流量系数</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>仅手动输入流量系数时填写</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>非手动连接形式仍强行填写</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠侧收缩系数</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>入口侧收缩修正系数</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>空白按 1.0</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>同名组多行冲突</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠动能修正系数</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>水面线动能修正系数</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>空白按 1.1</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>填成百分数</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠掺气系数</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>掺气侧墙计算系数</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>空白按 1.2</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>与糙率混淆</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠侧墙安全超高(m)</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>侧墙安全超高</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>空白按 0.4</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>填负数</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠池深系数</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>消能池深度系数</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>空白按 1.10</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>填成长度单位</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>泄水渠整流长度系数</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>可选</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>出口整流长度系数</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>充水渠/泄水渠/泄水渠与陡坡</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>空白按 10.0</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>填成出口长度</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n"/>
+      <c r="B49" s="5" t="n"/>
+      <c r="C49" s="5" t="n"/>
+      <c r="D49" s="5" t="n"/>
+      <c r="E49" s="5" t="n"/>
+      <c r="F49" s="5" t="n"/>
+      <c r="G49" s="5" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="n"/>
+      <c r="B50" s="5" t="n"/>
+      <c r="C50" s="5" t="n"/>
+      <c r="D50" s="5" t="n"/>
+      <c r="E50" s="5" t="n"/>
+      <c r="F50" s="5" t="n"/>
+      <c r="G50" s="5" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="n"/>
+      <c r="B52" s="5" t="n"/>
+      <c r="C52" s="5" t="n"/>
+      <c r="D52" s="5" t="n"/>
+      <c r="E52" s="5" t="n"/>
+      <c r="F52" s="5" t="n"/>
+      <c r="G52" s="5" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n"/>
+      <c r="B53" s="5" t="n"/>
+      <c r="C53" s="5" t="n"/>
+      <c r="D53" s="5" t="n"/>
+      <c r="E53" s="5" t="n"/>
+      <c r="F53" s="5" t="n"/>
+      <c r="G53" s="5" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="n"/>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A6:G38"/>
+  <autoFilter ref="A6:G48"/>
   <mergeCells count="3">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
